--- a/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
+++ b/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
@@ -236,14 +236,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -635,15 +635,15 @@
   <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1275,7 +1275,7 @@
     <mergeCell ref="D26:E26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="2"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1716,48 +1716,48 @@
       <c r="A6" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>Б.9</t>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>4.2.1</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Аудит проектной документации по чек-листам</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F6" s="26" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="G6" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="27" t="n">
+      <c r="H6" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="I6" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="J6" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K6" s="25" t="n">
-        <v>3</v>
+      <c r="K6" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="L6" s="21" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
@@ -1766,27 +1766,27 @@
       </c>
       <c r="N6" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Базовая линия и замер</t>
         </is>
       </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с HR срок оформления приказов по решениям волны 1</t>
+          <t>Провести пилотный аудит одного филиала и зафиксировать базовую линию</t>
         </is>
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr">
         <is>
-          <t>Оформление штата — исполнительный механизм всей первой волны: разделение блоков 1 и 2 и полномочия процессного офиса остаются предложением, пока HR не выпустит приказ (узкое место 8). Владелец процесса — HR, и он подтверждён; не хватает норматива срока, поэтому срок фиксируется вместе с самими решениями, а не после них.</t>
+          <t>Конкретное действие, с которого начинается вся программа. Единственный объект реестра, который запускается без единого согласования: чек-листы готовы, исполнитель определён, филиал выбирается решением директора. Идёт раньше регулярного аудита (4.2) и параллельно кадровым решениям волны — ничего не ждёт и никого не задерживает.</t>
         </is>
       </c>
       <c r="R6" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Назначение бизнес-владельца</t>
+          <t>Defect Rate; First Pass Yield</t>
         </is>
       </c>
     </row>
@@ -1794,48 +1794,48 @@
       <c r="A7" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>4.2</t>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Б.9</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Контроль качества и полноты проектных данных</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G7" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="20" t="n">
-        <v>2</v>
-      </c>
       <c r="J7" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="19" t="n">
-        <v>4</v>
+      <c r="K7" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L7" s="21" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M7" s="22" t="inlineStr">
         <is>
@@ -1844,27 +1844,27 @@
       </c>
       <c r="N7" s="12" t="inlineStr">
         <is>
-          <t>Базовая линия и замер</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>Возобновить аудит проектных данных по трём чек-листам методологии</t>
+          <t>Согласовать с HR срок оформления приказов по решениям волны 1</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
-          <t>Аудит остановлен после 2020 года, поэтому сегодня ни одно утверждение о состоянии процессов нельзя подтвердить цифрой. Это объект-фундамент: без базовой линии эффект любой последующей оптимизации останется предметом спора. Стоит недорого — чек-листы уже написаны.</t>
+          <t>Оформление штата — исполнительный механизм всей первой волны: разделение блоков 1 и 2 и полномочия процессного офиса остаются предложением, пока HR не выпустит приказ (узкое место 8). Владелец процесса — HR, и он подтверждён; не хватает норматива срока, поэтому срок фиксируется вместе с самими решениями, а не после них.</t>
         </is>
       </c>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>Defect Rate; First Pass Yield; Паспорт процесса и карта SIPOC</t>
+          <t>SLA Compliance %; On-Time %; Назначение бизнес-владельца</t>
         </is>
       </c>
     </row>
@@ -1874,17 +1874,17 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Аудит проектной документации по чек-листам</t>
+          <t>Контроль качества и полноты проектных данных</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       <c r="G8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H8" s="26" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="20" t="n">
@@ -1909,11 +1909,11 @@
       <c r="J8" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K8" s="28" t="n">
-        <v>5</v>
+      <c r="K8" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L8" s="21" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M8" s="22" t="inlineStr">
         <is>
@@ -1927,22 +1927,22 @@
       </c>
       <c r="O8" s="12" t="inlineStr">
         <is>
-          <t>Провести пилотный аудит одного филиала и зафиксировать базовую линию</t>
+          <t>Развернуть регулярный аудит проектных данных на весь портфель</t>
         </is>
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4, 4.2.1</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
-          <t>Конкретное действие, с которого начинается вся программа. Единственный объект реестра, который запускается без единого согласования: чек-листы готовы, исполнитель определён, филиал выбирается решением директора. Результат — первые достоверные цифры по качеству проектных данных.</t>
+          <t>Аудит остановлен после 2020 года, поэтому сегодня ни одно утверждение о состоянии процессов нельзя подтвердить цифрой. Это объект-фундамент: без базовой линии эффект любой последующей оптимизации останется предметом спора. В отличие от пилота, регулярный аудит требует последствий: пока право остановить проект по его результатам не закреплено приказом (объект 4), замер останется справкой.</t>
         </is>
       </c>
       <c r="R8" s="12" t="inlineStr">
         <is>
-          <t>Defect Rate; First Pass Yield</t>
+          <t>Defect Rate; First Pass Yield; Паспорт процесса и карта SIPOC</t>
         </is>
       </c>
     </row>
@@ -1975,10 +1975,10 @@
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G9" s="28" t="n">
+      <c r="G9" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="28" t="n">
+      <c r="H9" s="27" t="n">
         <v>5</v>
       </c>
       <c r="I9" s="25" t="n">
@@ -2053,7 +2053,7 @@
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G10" s="28" t="n">
+      <c r="G10" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H10" s="19" t="n">
@@ -2065,7 +2065,7 @@
       <c r="J10" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K10" s="28" t="n">
+      <c r="K10" s="27" t="n">
         <v>5</v>
       </c>
       <c r="L10" s="21" t="n">
@@ -2131,7 +2131,7 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G11" s="28" t="n">
+      <c r="G11" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H11" s="19" t="n">
@@ -2204,15 +2204,15 @@
           <t>ДРБ</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G12" s="28" t="n">
+      <c r="G12" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="28" t="n">
+      <c r="H12" s="27" t="n">
         <v>5</v>
       </c>
       <c r="I12" s="25" t="n">
@@ -2287,7 +2287,7 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G13" s="28" t="n">
+      <c r="G13" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H13" s="19" t="n">
@@ -2530,7 +2530,7 @@
       <c r="I16" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="J16" s="28" t="n">
+      <c r="J16" s="27" t="n">
         <v>5</v>
       </c>
       <c r="K16" s="25" t="n">
@@ -2611,7 +2611,7 @@
       <c r="J17" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K17" s="28" t="n">
+      <c r="K17" s="27" t="n">
         <v>5</v>
       </c>
       <c r="L17" s="21" t="n">
@@ -2672,7 +2672,7 @@
           <t>ДРБ</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -2833,7 +2833,7 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G20" s="28" t="n">
+      <c r="G20" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H20" s="19" t="n">
@@ -3307,13 +3307,13 @@
       <c r="H26" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="27" t="n">
+      <c r="I26" s="26" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K26" s="28" t="n">
+      <c r="K26" s="27" t="n">
         <v>5</v>
       </c>
       <c r="L26" s="21" t="n">
@@ -3385,13 +3385,13 @@
       <c r="H27" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="27" t="n">
+      <c r="I27" s="26" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K27" s="28" t="n">
+      <c r="K27" s="27" t="n">
         <v>5</v>
       </c>
       <c r="L27" s="21" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
-          <t>Процесс исполняется, но срок назначения нигде не нормирован, из-за чего проект какое-то время существует без ответственного на местах (узкое место 8). Вмешательство стоит одной строки в регламенте и опирается на матрицу «филиал → куратор», которая закрывается в волне 1.</t>
+          <t>Процесс исполняется, но срок назначения нигде не нормирован, из-за чего проект какое-то время существует без ответственного на местах (узкое место 8). Вмешательство стоит одной строки в регламенте и опирается на матрицу «филиал → куратор» (3.1), которая берётся в этой же волне раньше.</t>
         </is>
       </c>
       <c r="R27" s="12" t="inlineStr">
@@ -3460,16 +3460,16 @@
       <c r="G28" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="27" t="n">
+      <c r="H28" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="27" t="n">
+      <c r="I28" s="26" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="K28" s="28" t="n">
+      <c r="K28" s="27" t="n">
         <v>5</v>
       </c>
       <c r="L28" s="21" t="n">
@@ -3535,10 +3535,10 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G29" s="28" t="n">
+      <c r="G29" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="28" t="n">
+      <c r="H29" s="27" t="n">
         <v>5</v>
       </c>
       <c r="I29" s="19" t="n">
@@ -3613,10 +3613,10 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G30" s="28" t="n">
+      <c r="G30" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="28" t="n">
+      <c r="H30" s="27" t="n">
         <v>5</v>
       </c>
       <c r="I30" s="19" t="n">
@@ -3686,12 +3686,12 @@
           <t>ДРБ</t>
         </is>
       </c>
-      <c r="F31" s="26" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G31" s="28" t="n">
+      <c r="G31" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H31" s="19" t="n">
@@ -3700,7 +3700,7 @@
       <c r="I31" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="J31" s="28" t="n">
+      <c r="J31" s="27" t="n">
         <v>5</v>
       </c>
       <c r="K31" s="20" t="n">
@@ -3769,13 +3769,13 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G32" s="28" t="n">
+      <c r="G32" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H32" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I32" s="28" t="n">
+      <c r="I32" s="27" t="n">
         <v>5</v>
       </c>
       <c r="J32" s="19" t="n">
@@ -3847,13 +3847,13 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G33" s="28" t="n">
+      <c r="G33" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H33" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I33" s="28" t="n">
+      <c r="I33" s="27" t="n">
         <v>5</v>
       </c>
       <c r="J33" s="19" t="n">
@@ -3925,13 +3925,13 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G34" s="28" t="n">
+      <c r="G34" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H34" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I34" s="28" t="n">
+      <c r="I34" s="27" t="n">
         <v>5</v>
       </c>
       <c r="J34" s="19" t="n">
@@ -4076,7 +4076,7 @@
           <t>ДРБ</t>
         </is>
       </c>
-      <c r="F36" s="26" t="inlineStr">
+      <c r="F36" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -4159,7 +4159,7 @@
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G37" s="28" t="n">
+      <c r="G37" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H37" s="25" t="n">
@@ -4168,7 +4168,7 @@
       <c r="I37" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="J37" s="28" t="n">
+      <c r="J37" s="27" t="n">
         <v>5</v>
       </c>
       <c r="K37" s="25" t="n">
@@ -4310,7 +4310,7 @@
           <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="F39" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -4318,7 +4318,7 @@
       <c r="G39" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H39" s="28" t="n">
+      <c r="H39" s="27" t="n">
         <v>5</v>
       </c>
       <c r="I39" s="20" t="n">
@@ -4327,7 +4327,7 @@
       <c r="J39" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K39" s="27" t="n">
+      <c r="K39" s="26" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="21" t="n">
@@ -4388,12 +4388,12 @@
           <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
-      <c r="F40" s="26" t="inlineStr">
+      <c r="F40" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G40" s="28" t="n">
+      <c r="G40" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H40" s="19" t="n">
@@ -4466,7 +4466,7 @@
           <t>СТ</t>
         </is>
       </c>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="F41" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -4778,7 +4778,7 @@
           <t>Зерек</t>
         </is>
       </c>
-      <c r="F45" s="26" t="inlineStr">
+      <c r="F45" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -4856,7 +4856,7 @@
           <t>Юр блок</t>
         </is>
       </c>
-      <c r="F46" s="26" t="inlineStr">
+      <c r="F46" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -5012,7 +5012,7 @@
           <t>Юр блок</t>
         </is>
       </c>
-      <c r="F48" s="26" t="inlineStr">
+      <c r="F48" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -5090,7 +5090,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F49" s="26" t="inlineStr">
+      <c r="F49" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -5101,13 +5101,13 @@
       <c r="H49" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I49" s="27" t="n">
+      <c r="I49" s="26" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K49" s="27" t="n">
+      <c r="K49" s="26" t="n">
         <v>1</v>
       </c>
       <c r="L49" s="21" t="n">
@@ -5168,7 +5168,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F50" s="26" t="inlineStr">
+      <c r="F50" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -5185,7 +5185,7 @@
       <c r="J50" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K50" s="27" t="n">
+      <c r="K50" s="26" t="n">
         <v>1</v>
       </c>
       <c r="L50" s="21" t="n">
@@ -5257,7 +5257,7 @@
       <c r="H51" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I51" s="27" t="n">
+      <c r="I51" s="26" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="20" t="n">
@@ -5335,7 +5335,7 @@
       <c r="H52" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I52" s="28" t="n">
+      <c r="I52" s="27" t="n">
         <v>5</v>
       </c>
       <c r="J52" s="25" t="n">
@@ -5569,7 +5569,7 @@
       <c r="H55" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I55" s="27" t="n">
+      <c r="I55" s="26" t="n">
         <v>1</v>
       </c>
       <c r="J55" s="20" t="n">
@@ -5647,13 +5647,13 @@
       <c r="H56" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="27" t="n">
+      <c r="I56" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="27" t="n">
+      <c r="J56" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="K56" s="28" t="n">
+      <c r="K56" s="27" t="n">
         <v>5</v>
       </c>
       <c r="L56" s="21" t="n">
@@ -5878,7 +5878,7 @@
       <c r="G59" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H59" s="27" t="n">
+      <c r="H59" s="26" t="n">
         <v>1</v>
       </c>
       <c r="I59" s="20" t="n">
@@ -5948,7 +5948,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F60" s="26" t="inlineStr">
+      <c r="F60" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -5959,13 +5959,13 @@
       <c r="H60" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I60" s="27" t="n">
+      <c r="I60" s="26" t="n">
         <v>1</v>
       </c>
       <c r="J60" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="K60" s="27" t="n">
+      <c r="K60" s="26" t="n">
         <v>1</v>
       </c>
       <c r="L60" s="21" t="n">
@@ -6031,19 +6031,19 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G61" s="27" t="n">
+      <c r="G61" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H61" s="27" t="n">
+      <c r="H61" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I61" s="27" t="n">
+      <c r="I61" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J61" s="27" t="n">
+      <c r="J61" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="K61" s="27" t="n">
+      <c r="K61" s="26" t="n">
         <v>1</v>
       </c>
       <c r="L61" s="21" t="n">
@@ -6104,24 +6104,24 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F62" s="26" t="inlineStr">
+      <c r="F62" s="28" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G62" s="27" t="n">
+      <c r="G62" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H62" s="27" t="n">
+      <c r="H62" s="26" t="n">
         <v>1</v>
       </c>
       <c r="I62" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J62" s="27" t="n">
+      <c r="J62" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="K62" s="27" t="n">
+      <c r="K62" s="26" t="n">
         <v>1</v>
       </c>
       <c r="L62" s="21" t="n">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>2.0, 1, 2, 4, Б.9, 4.2, 4.2.1</t>
+          <t>2.0, 1, 2, 4, 4.2.1, Б.9, 4.2</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Пилотный аудит одного филиала по трём готовым чек-листам методологии (4.2.1) — единственное действие программы, которое не требует ни одного согласования</t>
+          <t>Чек-лист передачи «реализация → сопровождение» (2.0): без него приказ о разделении заместителей создаёт зависшие объекты. Параллельно и без единого согласования идёт пилотный аудит одного филиала по трём готовым чек-листам методологии (4.2.1)</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -6572,13 +6572,13 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Приказ о полномочиях ПМО (4) → аудит проектных данных (4.2, 4.2.1)</t>
+          <t>Приказ о полномочиях ПМО (4) → регулярный аудит проектных данных (4.2)</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Аудит по чек-листам методологии имеет смысл только тогда, когда его результат влечёт последствия. Пока право остановить проект по итогам аудита не закреплено приказом, замер превращается в справку.</t>
+          <t>Пилотный аудит (4.2.1) не ждёт ничего и даёт базовую линию. Регулярный аудит по всему портфелю имеет смысл только тогда, когда его результат влечёт последствия: пока право остановить проект по итогам аудита не закреплено приказом, замер превращается в справку.</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -6602,13 +6602,13 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Базовая линия → доказательство эффекта</t>
+          <t>Базовая линия (4.2.1) → доказательство эффекта</t>
         </is>
       </c>
       <c r="B16" s="12" t="n"/>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Пилотный аудит (4.2.1) даёт первые достоверные цифры. Без него любое утверждение об улучшении останется экспертной оценкой.</t>
+          <t>Пилотный аудит даёт первые достоверные цифры. Без него любое утверждение об улучшении останется экспертной оценкой (п. 176 Методики).</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>4.2.1, 4.2</t>
+          <t>4.2.1</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -7263,7 +7263,7 @@
       <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Заполнители — 15
-4.2, 4.2.1, 2.6, 3, 3.2, Б.5.1, 3.1, 1.3, 3.3, 2.8, 4.3, 1.4, 1.1.3, 1.6, Б.2.1</t>
+4.2.1, 4.2, 2.6, 3, 3.2, Б.5.1, 3.1, 1.3, 3.3, 2.8, 4.3, 1.4, 1.1.3, 1.6, Б.2.1</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>

--- a/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
+++ b/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
@@ -986,7 +986,7 @@
       <c r="B16" s="12" t="n"/>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Владельцы определены по критериям Таблицы 5 Методики, но четыре решения держатся на документах, которых пока нет: должности двух заместителей не введены, полномочия процессного офиса не закреплены приказом, точка передачи между блоками 1 и 2 не описана. По п. 33 Методики целевые значения метрик можно адресовать только существующей должности, поэтому такие объекты выходят в работу первыми независимо от балла.</t>
+          <t>Владельцы определены по критериям Таблицы 5 Методики, но четыре решения первой волны держатся на документах, которых пока нет: должности двух заместителей не введены, полномочия процессного офиса не закреплены приказом, точка передачи между блоками 1 и 2 не описана. По п. 33 Методики целевые значения метрик можно адресовать только существующей должности, поэтому такие объекты выходят в работу первыми независимо от балла.</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Владельцы определены по критериям Таблицы 5 Методики и зафиксированы в карте ролей. Но четыре решения держатся на документах, которых пока нет: должности двух заместителей не введены, полномочия процессного офиса не закреплены, точка передачи между блоками 1 и 2 не описана. По п. 33 Методики спрашивать за результат можно только с существующей должности, поэтому эти объекты идут первыми независимо от балла. Сюда же отнесён пилотный аудит: пока не снята базовая линия, эффект любой последующей оптимизации будет предметом спора, а не расчёта.</t>
+          <t>Владельцы определены по критериям Таблицы 5 Методики и зафиксированы в карте ролей. Но четыре решения этой волны держатся на документах, которых пока нет: должности двух заместителей не введены, полномочия процессного офиса не закреплены, точка передачи между блоками 1 и 2 не описана. По п. 33 Методики спрашивать за результат можно только с существующей должности, поэтому эти объекты идут первыми независимо от балла. Сюда же отнесён пилотный аудит: пока не снята базовая линия, эффект любой последующей оптимизации будет предметом спора, а не расчёта.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">

--- a/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
+++ b/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
@@ -986,7 +986,7 @@
       <c r="B16" s="12" t="n"/>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Владельцы определены по критериям Таблицы 5 Методики, но четыре решения первой волны держатся на документах, которых пока нет: должности двух заместителей не введены, полномочия процессного офиса не закреплены приказом, точка передачи между блоками 1 и 2 не описана. По п. 33 Методики целевые значения метрик можно адресовать только существующей должности, поэтому такие объекты выходят в работу первыми независимо от балла.</t>
+          <t>Владельцы определены по критериям Таблицы 5 Методики, но решения по объектам 1, 2, 2.0 и 4 держатся на документах, которых пока нет: должности двух заместителей не введены, полномочия процессного офиса не закреплены приказом, точка передачи между блоками 1 и 2 не описана. По п. 33 Методики целевые значения метрик можно адресовать только существующей должности, поэтому такие объекты выходят в работу первыми независимо от балла.</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Владельцы определены по критериям Таблицы 5 Методики и зафиксированы в карте ролей. Но четыре решения этой волны держатся на документах, которых пока нет: должности двух заместителей не введены, полномочия процессного офиса не закреплены, точка передачи между блоками 1 и 2 не описана. По п. 33 Методики спрашивать за результат можно только с существующей должности, поэтому эти объекты идут первыми независимо от балла. Сюда же отнесён пилотный аудит: пока не снята базовая линия, эффект любой последующей оптимизации будет предметом спора, а не расчёта.</t>
+          <t>Владельцы определены по критериям Таблицы 5 Методики и зафиксированы в карте ролей. Но решения по объектам 1, 2, 2.0 и 4 держатся на документах, которых пока нет: должности двух заместителей не введены, полномочия процессного офиса не закреплены, точка передачи между блоками 1 и 2 не описана. По п. 33 Методики спрашивать за результат можно только с существующей должности, поэтому эти объекты идут первыми независимо от балла. Сюда же отнесён пилотный аудит: пока не снята базовая линия, эффект любой последующей оптимизации будет предметом спора, а не расчёта.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">

--- a/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
+++ b/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
@@ -128,12 +128,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE3B3"/>
+        <fgColor rgb="00CFE0F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE0F7"/>
+        <fgColor rgb="00FFE3B3"/>
       </patternFill>
     </fill>
   </fills>
@@ -242,10 +242,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -980,13 +980,13 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Владение раньше метрик</t>
+          <t>Паспорт процесса раньше оптимизации его шагов</t>
         </is>
       </c>
       <c r="B16" s="12" t="n"/>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Владельцы определены по критериям Таблицы 5 Методики, но решения по объектам 1, 2, 2.0 и 4 держатся на документах, которых пока нет: должности двух заместителей не введены, полномочия процессного офиса не закреплены приказом, точка передачи между блоками 1 и 2 не описана. По п. 33 Методики целевые значения метрик можно адресовать только существующей должности, поэтому такие объекты выходят в работу первыми независимо от балла.</t>
+          <t>Владение закреплено по критериям Таблицы 5 Методики, стоп-факторов для старта нет. Но глава 8 и Приложение №2 делают паспорт процесса обязательным атрибутом: границы, вход, выход, владелец и показатели. Пока паспорта нет, улучшение отдельных шагов не с чем сверять — неизвестно, где процесс начинается и по какому показателю он стал лучше. Поэтому сквозные объекты верхнего уровня (1, 2, 4) и описание границы между ними (2.0) выходят в работу первыми независимо от балла.</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1080,11 +1080,11 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Довести решения о владении до приказа и снять базовую линию</t>
+          <t>Паспорта сквозных процессов и замер «до»</t>
         </is>
       </c>
       <c r="E24" s="12" t="n"/>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="M2" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="N2" s="12" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Q2" s="12" t="inlineStr">
         <is>
-          <t>Владелец точки передачи закреплён за передающей стороной — замом по строительству и реализации: принимающая сторона не может отвечать за полноту того, что ей не передали. Но самой процедуры не существует — момент, в который объект перестаёт быть стройкой и становится источником дохода, нигде не зафиксирован. Пока блоки 1 и 2 ведёт один человек, пробел не виден; в день разделения заместителей он превращается в зависшие объекты. Поэтому чек-лист проектируется раньше приказа о разделении, а не после него.</t>
+          <t>Владелец точки передачи закреплён за передающей стороной — замом по строительству и реализации: принимающая сторона не может отвечать за полноту того, что ей не передали. Но самой процедуры не существует — момент, в который объект перестаёт быть стройкой и становится источником дохода, нигде не зафиксирован. Этот момент одновременно является выходом процесса блока 1 и входом процесса блока 2, поэтому чек-лист проектируется раньше обоих паспортов: без него у двух сквозных процессов нет общей границы.</t>
         </is>
       </c>
       <c r="R2" s="12" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B3" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
-          <t>Реализация проекта</t>
+          <t>Постпроектное сопровождение</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
@@ -1510,8 +1510,8 @@
       <c r="G3" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="25" t="n">
-        <v>3</v>
+      <c r="H3" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="I3" s="25" t="n">
         <v>3</v>
@@ -1519,25 +1519,25 @@
       <c r="J3" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K3" s="20" t="n">
-        <v>2</v>
+      <c r="K3" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L3" s="21" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M3" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
-          <t>Закрепление владения приказом</t>
+          <t>Паспорт процесса и границы</t>
         </is>
       </c>
       <c r="O3" s="12" t="inlineStr">
         <is>
-          <t>Издать приказ о разделении заместителей и утвердить RACI v2</t>
+          <t>Утвердить паспорт процесса сопровождения: границы, вход, выход и три показателя</t>
         </is>
       </c>
       <c r="P3" s="12" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="Q3" s="12" t="inlineStr">
         <is>
-          <t>Владелец определён — зам. по строительству и реализации, но самой должности в штатном расписании пока нет: блоки 1 и 2 ведёт один человек, и срочное вытесняет доходное. По п. 33 Методики целевые значения по девяти подпроцессам блока 1 можно адресовать только существующей должности, поэтому приказ идёт раньше работы с самими процессами. Приказ выпускается после чек-листа передачи (2.0): разделение без описанной точки передачи создаёт зависшие объекты.</t>
+          <t>Фаза, в которой создаётся доход компании, описана хуже строительной: у блока 2 нет ни общих границ, ни показателей, ни регулярного учёта доходности объекта. Владелец — зам. по операционной деятельности — закреплён, но спрашивать с него не с чем: паспорта процесса нет, а по п. 176 Методики показатель без источника данных не учитывается. Вход процесса — принятый комплект объекта, поэтому паспорт идёт следом за чек-листом передачи (2.0).</t>
         </is>
       </c>
       <c r="R3" s="12" t="inlineStr">
         <is>
-          <t>Назначение бизнес-владельца; Паспорт процесса и карта SIPOC</t>
+          <t>Паспорт процесса и карта SIPOC; Budget Variance; Назначение бизнес-владельца</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>Постпроектное сопровождение</t>
+          <t>Реализация проекта</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
@@ -1591,31 +1591,31 @@
       <c r="H4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="25" t="n">
-        <v>3</v>
+      <c r="I4" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="J4" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K4" s="20" t="n">
-        <v>2</v>
+      <c r="K4" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L4" s="21" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>Закрепление владения приказом</t>
+          <t>Паспорт процесса и границы</t>
         </is>
       </c>
       <c r="O4" s="12" t="inlineStr">
         <is>
-          <t>Утвердить в оргсхеме отдельного заместителя по операционной деятельности</t>
+          <t>Утвердить паспорт процесса реализации: границы, вход, выход и три показателя</t>
         </is>
       </c>
       <c r="P4" s="12" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="Q4" s="12" t="inlineStr">
         <is>
-          <t>Вторая половина организационного решения. Пока блок 2 не имеет собственного заместителя, сопровождение проигрывает реализации конкуренцию за внимание: стройка срочная, эксплуатация — нет. При этом доход компании создаётся именно в этой фазе, поэтому владелец блока 2 назначается одновременно с владельцем блока 1.</t>
+          <t>Владелец закреплён — зам. по строительству и реализации, и это решение действует. Но девять подпроцессов блока не имеют общего описания: где фаза начинается, чем заканчивается и по каким показателям оценивается. Глава 8 и Приложение №2 Методики делают паспорт обязательным атрибутом процесса, поэтому он идёт раньше работы с отдельными подпроцессами. Выход процесса — момент передачи объекта в сопровождение, поэтому паспорт утверждается после чек-листа передачи (2.0), который этот выход описывает.</t>
         </is>
       </c>
       <c r="R4" s="12" t="inlineStr">
         <is>
-          <t>Назначение бизнес-владельца; Паспорт процесса и карта SIPOC</t>
+          <t>Паспорт процесса и карта SIPOC; On-Time %; Назначение бизнес-владельца</t>
         </is>
       </c>
     </row>
@@ -1675,25 +1675,25 @@
       <c r="J5" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="25" t="n">
-        <v>3</v>
+      <c r="K5" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L5" s="21" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M5" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="N5" s="12" t="inlineStr">
         <is>
-          <t>Закрепление владения приказом</t>
+          <t>Паспорт процесса и границы</t>
         </is>
       </c>
       <c r="O5" s="12" t="inlineStr">
         <is>
-          <t>Назначить главного менеджера проектов и закрепить за ним полномочия процессного офиса</t>
+          <t>Утвердить паспорт процесса методологии и положение о контроле качества проектных данных</t>
         </is>
       </c>
       <c r="P5" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="Q5" s="12" t="inlineStr">
         <is>
-          <t>Роль главного менеджера проектов — несущая конструкция всей трансформации: именно она ведёт паспорта процессов, аудит и портфельную отчётность. Пока роль не закреплена с полномочиями, у реинжиниринга нет исполнителя, и работа вернётся к заместителям, у которых на неё нет времени.</t>
+          <t>Роль главного менеджера проектов — несущая конструкция всей трансформации: именно она ведёт паспорта остальных процессов, аудит и портфельную отчётность. Владение и право остановить проект по результатам аудита закреплены, но собственного паспорта у процесса нет, а методолог без описанных границ своей работы не может требовать описания чужих. Объект никого не ждёт и идёт параллельно паспортам блоков 1 и 2.</t>
         </is>
       </c>
       <c r="R5" s="12" t="inlineStr">
         <is>
-          <t>Назначение бизнес-владельца; Паспорт процесса и карта SIPOC</t>
+          <t>Паспорт процесса и карта SIPOC; Defect Rate; Назначение бизнес-владельца</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="N6" s="12" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="Q6" s="12" t="inlineStr">
         <is>
-          <t>Конкретное действие, с которого начинается вся программа. Единственный объект реестра, который запускается без единого согласования: чек-листы готовы, исполнитель определён, филиал выбирается решением директора. Идёт раньше регулярного аудита (4.2) и параллельно кадровым решениям волны — ничего не ждёт и никого не задерживает.</t>
+          <t>Конкретное действие, с которого начинается вся программа. Единственный объект реестра, который запускается без единого согласования: чек-листы готовы, исполнитель определён, филиал выбирается решением директора. Идёт раньше регулярного аудита (4.2) и параллельно паспортам процессов — ничего не ждёт и никого не задерживает.</t>
         </is>
       </c>
       <c r="R6" s="12" t="inlineStr">
@@ -1794,77 +1794,77 @@
       <c r="A7" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>Б.9</t>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Контроль качества и полноты проектных данных</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F7" s="28" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="G7" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="26" t="n">
+      <c r="H7" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="I7" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="J7" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="25" t="n">
-        <v>3</v>
+      <c r="K7" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L7" s="21" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="N7" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Базовая линия и замер</t>
         </is>
       </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с HR срок оформления приказов по решениям волны 1</t>
+          <t>Развернуть регулярный аудит проектных данных на весь портфель</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4, 4.2.1</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
-          <t>Оформление штата — исполнительный механизм всей первой волны: разделение блоков 1 и 2 и полномочия процессного офиса остаются предложением, пока HR не выпустит приказ (узкое место 8). Владелец процесса — HR, и он подтверждён; не хватает норматива срока, поэтому срок фиксируется вместе с самими решениями, а не после них.</t>
+          <t>Аудит остановлен после 2020 года, поэтому сегодня ни одно утверждение о состоянии процессов нельзя подтвердить цифрой. Это объект-фундамент: без базовой линии эффект любой последующей оптимизации останется предметом спора. В отличие от пилота, регулярный аудит требует последствий: право остановить проект по его результатам принадлежит владельцу методологии, и оно фиксируется вместе с паспортом его процесса (объект 4) — иначе замер останется справкой.</t>
         </is>
       </c>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Назначение бизнес-владельца</t>
+          <t>Defect Rate; First Pass Yield; Паспорт процесса и карта SIPOC</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Контроль качества и полноты проектных данных</t>
+          <t>Приём и валидация пакета документов от ДРБ</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
+          <t>ДУП и ДРБ</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1897,14 +1897,14 @@
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G8" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <v>2</v>
+      <c r="G8" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="J8" s="19" t="n">
         <v>4</v>
@@ -1913,36 +1913,36 @@
         <v>4</v>
       </c>
       <c r="L8" s="21" t="n">
-        <v>54</v>
-      </c>
-      <c r="M8" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+        <v>86</v>
+      </c>
+      <c r="M8" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="N8" s="12" t="inlineStr">
         <is>
-          <t>Базовая линия и замер</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr">
         <is>
-          <t>Развернуть регулярный аудит проектных данных на весь портфель</t>
+          <t>Утвердить чек-лист минимального пакета и правило возврата неполного комплекта</t>
         </is>
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>4, 4.2.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
-          <t>Аудит остановлен после 2020 года, поэтому сегодня ни одно утверждение о состоянии процессов нельзя подтвердить цифрой. Это объект-фундамент: без базовой линии эффект любой последующей оптимизации останется предметом спора. В отличие от пилота, регулярный аудит требует последствий: пока право остановить проект по его результатам не закреплено приказом (объект 4), замер останется справкой.</t>
+          <t>Первый объект цепочки: дефект пакета на входе проявляется на всех последующих подпроцессах — от ФЭМ до закупок и приёмки. Минимальный состав пакета не зафиксирован письменно (узкие места 1 и 4), поэтому старт проекта растягивается на доуточнения. Исправляется одним чек-листом и одним письмом в ДРБ — это лучшее соотношение эффекта к усилию во всём реестре.</t>
         </is>
       </c>
       <c r="R8" s="12" t="inlineStr">
         <is>
-          <t>Defect Rate; First Pass Yield; Паспорт процесса и карта SIPOC</t>
+          <t>Cycle Time; On-Time %; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -1952,22 +1952,22 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Приём и валидация пакета документов от ДРБ</t>
+          <t>Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>ДУП и ДРБ</t>
+          <t>ДУП</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -1978,22 +1978,22 @@
       <c r="G9" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" s="19" t="n">
-        <v>4</v>
-      </c>
       <c r="L9" s="21" t="n">
-        <v>86</v>
-      </c>
-      <c r="M9" s="29" t="inlineStr">
+        <v>85</v>
+      </c>
+      <c r="M9" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -2005,22 +2005,22 @@
       </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>Утвердить чек-лист минимального пакета и правило возврата неполного комплекта</t>
+          <t>Ввести обязательную проверку по чек-листу до регистрации проекта в портфеле</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
-          <t>Первый объект цепочки: дефект пакета на входе проявляется на всех последующих подпроцессах — от ФЭМ до закупок и приёмки. Минимальный состав пакета не зафиксирован письменно (узкие места 1 и 4), поэтому старт проекта растягивается на доуточнения. Исправляется одним чек-листом и одним письмом в ДРБ — это лучшее соотношение эффекта к усилию во всём реестре.</t>
+          <t>Самый дешёвый контроль во всей цепочке: проверка по чек-листу занимает часы и отсекает дефект до того, как он превратится в неверный ФЭМ и неверную спецификацию закупки. Процессом владеет ДУП, поэтому внешних согласований не требуется вовсе.</t>
         </is>
       </c>
       <c r="R9" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; On-Time %; Defect Rate</t>
+          <t>Defect Rate; First Pass Yield; Rework Rate</t>
         </is>
       </c>
     </row>
@@ -2030,27 +2030,27 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
+          <t>Формирование реестра платежей и приоритизация</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F10" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="G10" s="27" t="n">
@@ -2059,19 +2059,19 @@
       <c r="H10" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="25" t="n">
-        <v>3</v>
+      <c r="I10" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="J10" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K10" s="27" t="n">
-        <v>5</v>
+      <c r="K10" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L10" s="21" t="n">
-        <v>85</v>
-      </c>
-      <c r="M10" s="29" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="M10" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>Ввести обязательную проверку по чек-листу до регистрации проекта в портфеле</t>
+          <t>Утвердить инструкцию по трём потокам платежей и единую форму реестра</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr">
         <is>
-          <t>Самый дешёвый контроль во всей цепочке: проверка по чек-листу занимает часы и отсекает дефект до того, как он превратится в неверный ФЭМ и неверную спецификацию закупки. Процессом владеет ДУП, поэтому внешних согласований не требуется вовсе.</t>
+          <t>Три потока платежей (ВУ / КИЗ / КОЗ) не формализованы, единой инструкции нет (узкие места 6 и 7). Задержка оплаты останавливает монтаж, то есть деньги и срок здесь связаны напрямую. Инструкция пишется внутри ДУП, от Финблока нужен только календарь приёма реестра — поэтому объект попадает в волну быстрых побед.</t>
         </is>
       </c>
       <c r="R10" s="12" t="inlineStr">
         <is>
-          <t>Defect Rate; First Pass Yield; Rework Rate</t>
+          <t>On-Time %; Cycle Time; COPQ</t>
         </is>
       </c>
     </row>
@@ -2106,39 +2106,39 @@
       <c r="A11" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>1.9</t>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Б.6</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Формирование реестра платежей и приоритизация</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>Передача проекта от ДРБ в ДУП</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>ДРБ</t>
         </is>
       </c>
       <c r="F11" s="30" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G11" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H11" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>4</v>
+      <c r="H11" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="J11" s="19" t="n">
         <v>4</v>
@@ -2149,34 +2149,34 @@
       <c r="L11" s="21" t="n">
         <v>83</v>
       </c>
-      <c r="M11" s="29" t="inlineStr">
+      <c r="M11" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
-          <t>Регламент и чек-лист</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>Утвердить инструкцию по трём потокам платежей и единую форму реестра</t>
+          <t>Направить в ДРБ письмо директора с минимальным составом пакета и сроком передачи</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>Три потока платежей (ВУ / КИЗ / КОЗ) не формализованы, единой инструкции нет (узкие места 6 и 7). Задержка оплаты останавливает монтаж, то есть деньги и срок здесь связаны напрямую. Инструкция пишется внутри ДУП, от Финблока нужен только календарь приёма реестра — поэтому объект попадает в волну быстрых побед.</t>
+          <t>Тот же предмет, что и объект 1.1, со стороны процесса ДРБ. Чек-лист внутри ДУП без встречного обязательства ДРБ работает только как основание для отказа; письмо директора превращает его в согласованный норматив. Оба действия выполняются в одной волне и одним пакетом.</t>
         </is>
       </c>
       <c r="R11" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Cycle Time; COPQ</t>
+          <t>SLA Compliance %; On-Time %; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -2184,36 +2184,36 @@
       <c r="A12" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>Б.6</t>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>Передача проекта от ДРБ в ДУП</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="F12" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="G12" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="27" t="n">
-        <v>5</v>
+      <c r="H12" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="I12" s="25" t="n">
         <v>3</v>
@@ -2221,25 +2221,25 @@
       <c r="J12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K12" s="25" t="n">
-        <v>3</v>
+      <c r="K12" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L12" s="21" t="n">
-        <v>83</v>
-      </c>
-      <c r="M12" s="29" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="M12" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="N12" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
-          <t>Направить в ДРБ письмо директора с минимальным составом пакета и сроком передачи</t>
+          <t>Ввести форму заявки и правило: тех. карты СТ собираются до подачи заявки</t>
         </is>
       </c>
       <c r="P12" s="12" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
-          <t>Тот же предмет, что и объект 1.1, со стороны процесса ДРБ. Чек-лист внутри ДУП без встречного обязательства ДРБ работает только как основание для отказа; письмо директора превращает его в согласованный норматив. Оба действия выполняются в одной волне и одним пакетом.</t>
+          <t>Этот шаг целиком внутри ДУП: полнота заявки и наличие тех. карт определяют, сколько раз процедура вернётся на доработку. Его можно исправить, не дожидаясь договорённостей с Закупщиками, поэтому он выносится в волну 2 отдельно от остальной части объекта 1.7.</t>
         </is>
       </c>
       <c r="R12" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Defect Rate</t>
+          <t>First Pass Yield; Rework Rate; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -2264,48 +2264,48 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
+          <t>Прогноз поступлений / расходов и контроль бюджета</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="F13" s="30" t="inlineStr">
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G13" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="25" t="n">
-        <v>3</v>
+      <c r="G13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="J13" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K13" s="19" t="n">
-        <v>4</v>
+      <c r="K13" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L13" s="21" t="n">
-        <v>82</v>
-      </c>
-      <c r="M13" s="29" t="inlineStr">
+        <v>73</v>
+      </c>
+      <c r="M13" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -2317,22 +2317,22 @@
       </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>Ввести форму заявки и правило: тех. карты СТ собираются до подачи заявки</t>
+          <t>Завести единый реестр прогноза и календарь его обновления</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr">
         <is>
-          <t>Этот шаг целиком внутри ДУП: полнота заявки и наличие тех. карт определяют, сколько раз процедура вернётся на доработку. Его можно исправить, не дожидаясь договорённостей с Закупщиками, поэтому он выносится в волну 2 отдельно от остальной части объекта 1.7.</t>
+          <t>Прогноз ведётся в чатах и ad-hoc (узкие места 6 и 7), из-за чего компания узнаёт о разрыве поступлений позже, чем могла бы. Реестр и календарь — инструменты внутри ДУП: от Финблока нужна только форма выгрузки. Это делает объект исполнимым в волне 2, тогда как процесс целиком (Б.3) остаётся в волне 3.</t>
         </is>
       </c>
       <c r="R13" s="12" t="inlineStr">
         <is>
-          <t>First Pass Yield; Rework Rate; Defect Rate</t>
+          <t>On-Time %; Budget Variance; Cycle Time</t>
         </is>
       </c>
     </row>
@@ -2342,75 +2342,75 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
+          <t>2.3.1</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Сбор данных и подтверждений по проектам</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F14" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="M14" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        </is>
+      </c>
+      <c r="N14" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>Утвердить форму и срок подачи данных филиалами в реестр прогноза</t>
+        </is>
+      </c>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Прогноз поступлений / расходов и контроль бюджета</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F14" s="30" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" s="21" t="n">
-        <v>73</v>
-      </c>
-      <c r="M14" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N14" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>Завести единый реестр прогноза и календарь его обновления</t>
-        </is>
-      </c>
-      <c r="P14" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="Q14" s="12" t="inlineStr">
         <is>
-          <t>Прогноз ведётся в чатах и ad-hoc (узкие места 6 и 7), из-за чего компания узнаёт о разрыве поступлений позже, чем могла бы. Реестр и календарь — инструменты внутри ДУП: от Финблока нужна только форма выгрузки. Это делает объект исполнимым в волне 2, тогда как процесс целиком (Б.3) остаётся в волне 3.</t>
+          <t>Шаг, который ДУП выполняет сам и который определяет достоверность всего прогноза. Отсутствие формы и срока — причина того, что данные приходят разрозненно и требуют ручной сверки.</t>
         </is>
       </c>
       <c r="R14" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Budget Variance; Cycle Time</t>
+          <t>On-Time %; First Pass Yield; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -2420,48 +2420,48 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Сбор данных и подтверждений по проектам</t>
+          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F15" s="30" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="G15" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>4</v>
+      <c r="H15" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L15" s="21" t="n">
         <v>72</v>
       </c>
-      <c r="M15" s="29" t="inlineStr">
+      <c r="M15" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -2473,22 +2473,22 @@
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>Утвердить форму и срок подачи данных филиалами в реестр прогноза</t>
+          <t>Утвердить форму фиксации дефекта и маршрут «эксплуатация → владелец ТЗ → закупки»</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr">
         <is>
-          <t>Шаг, который ДУП выполняет сам и который определяет достоверность всего прогноза. Отсутствие формы и срока — причина того, что данные приходят разрозненно и требуют ручной сверки.</t>
+          <t>Ущерб уже реализовался: кейс с хомутами показал, что сведения о дефекте компонента из эксплуатации не доходят до владельца технического задания и повторяются в следующей закупке (узкое место 9). Владелец закреплён за замом по операционной деятельности — тем, кто дефект обнаруживает и несёт потери от его повторения. Осталось описать маршрут: фиксация дефекта делается внутри ДУП, встречный срок реакции СТ фиксируется в волне 3 через объект Б.7.</t>
         </is>
       </c>
       <c r="R15" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; First Pass Yield; Defect Rate</t>
+          <t>COPQ; Defect Rate; Rework Rate</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
+          <t>Управление сроками и бюджетом проекта (статус-встречи)</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -2524,22 +2524,22 @@
       <c r="G16" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H16" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="27" t="n">
+      <c r="H16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="K16" s="25" t="n">
-        <v>3</v>
-      </c>
       <c r="L16" s="21" t="n">
-        <v>72</v>
-      </c>
-      <c r="M16" s="29" t="inlineStr">
+        <v>71</v>
+      </c>
+      <c r="M16" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -2551,22 +2551,22 @@
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
-          <t>Утвердить форму фиксации дефекта и маршрут «эксплуатация → владелец ТЗ → закупки»</t>
+          <t>Утвердить регламент статус-встреч: частота, повестка, протокол, адресат решений</t>
         </is>
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr">
         <is>
-          <t>Ущерб уже реализовался: кейс с хомутами показал, что сведения о дефекте компонента из эксплуатации не доходят до владельца технического задания и повторяются в следующей закупке (узкое место 9). Владелец закреплён за замом по операционной деятельности — тем, кто дефект обнаруживает и несёт потери от его повторения. Осталось описать маршрут: фиксация дефекта делается внутри ДУП, встречный срок реакции СТ фиксируется в волне 3 через объект Б.7.</t>
+          <t>Регламента нет, обязанности менеджера центрального аппарата исполняются примерно на одну шестую (узкое место 8). Объект ДУП меняет в одиночку: частота, повестка и форма протокола утверждаются внутри департамента, без единого внешнего согласования. Самое дешёвое восстановление управляемости портфеля из всего реестра.</t>
         </is>
       </c>
       <c r="R16" s="12" t="inlineStr">
         <is>
-          <t>COPQ; Defect Rate; Rework Rate</t>
+          <t>On-Time %; Time-to-Complete; CSAT internal</t>
         </is>
       </c>
     </row>
@@ -2576,75 +2576,75 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Управление сроками и бюджетом проекта (статус-встречи)</t>
+          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="F17" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G17" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H17" s="25" t="n">
-        <v>3</v>
+      <c r="H17" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="I17" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>5</v>
+      <c r="J17" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L17" s="21" t="n">
-        <v>71</v>
-      </c>
-      <c r="M17" s="29" t="inlineStr">
+        <v>69</v>
+      </c>
+      <c r="M17" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
-          <t>Регламент и чек-лист</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>Утвердить регламент статус-встреч: частота, повестка, протокол, адресат решений</t>
+          <t>Зафиксировать в письме ДРБ норматив срока передачи пакета и форму карточки проекта</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr">
         <is>
-          <t>Регламента нет, обязанности менеджера центрального аппарата исполняются примерно на одну шестую (узкое место 8). Объект ДУП меняет в одиночку: частота, повестка и форма протокола утверждаются внутри департамента, без единого внешнего согласования. Самое дешёвое восстановление управляемости портфеля из всего реестра.</t>
+          <t>Точка входа, которой ДУП не управляет: пакет формирует ДРБ. Берётся в одном пакете работ с 1.1, потому что норматив срока без чек-листа состава не имеет смысла — быстро переданный неполный пакет хуже, чем переданный вовремя полный.</t>
         </is>
       </c>
       <c r="R17" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Time-to-Complete; CSAT internal</t>
+          <t>On-Time %; SLA Compliance %</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>1.1.1</t>
+          <t>1.9.1</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -2664,17 +2664,17 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
+          <t>Агрегация заявок и данных филиалов</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="F18" s="28" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F18" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="G18" s="19" t="n">
@@ -2695,34 +2695,34 @@
       <c r="L18" s="21" t="n">
         <v>69</v>
       </c>
-      <c r="M18" s="29" t="inlineStr">
+      <c r="M18" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>Зафиксировать в письме ДРБ норматив срока передачи пакета и форму карточки проекта</t>
+          <t>Ввести единую форму заявки филиала и срок её подачи до даты формирования реестра</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
-          <t>Точка входа, которой ДУП не управляет: пакет формирует ДРБ. Берётся в одном пакете работ с 1.1, потому что норматив срока без чек-листа состава не имеет смысла — быстро переданный неполный пакет хуже, чем переданный вовремя полный.</t>
+          <t>Сбор заявок в разных форматах и без общего срока — причина того, что реестр собирается в авральном режиме. Унификация формы даёт эффект сразу и не требует ничего, кроме распоряжения по филиалам.</t>
         </is>
       </c>
       <c r="R18" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; SLA Compliance %</t>
+          <t>On-Time %; First Pass Yield</t>
         </is>
       </c>
     </row>
@@ -2732,75 +2732,75 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
+          <t>1.9.2</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F19" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>86</v>
+      </c>
+      <c r="M19" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>Описать правило очерёдности: какой платёж попадает в начало реестра и почему</t>
+        </is>
+      </c>
+      <c r="P19" s="12" t="inlineStr">
+        <is>
           <t>1.9.1</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Агрегация заявок и данных филиалов</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F19" s="30" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" s="21" t="n">
-        <v>69</v>
-      </c>
-      <c r="M19" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N19" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O19" s="12" t="inlineStr">
-        <is>
-          <t>Ввести единую форму заявки филиала и срок её подачи до даты формирования реестра</t>
-        </is>
-      </c>
-      <c r="P19" s="12" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>Сбор заявок в разных форматах и без общего срока — причина того, что реестр собирается в авральном режиме. Унификация формы даёт эффект сразу и не требует ничего, кроме распоряжения по филиалам.</t>
+          <t>Ядро узких мест 6 и 7: правила, по которому платёж попадает в начало или в конец реестра, не существует, поэтому очередность определяется телефонным звонком. Формализация умещается на одну страницу, а эффект измеряется днями просрочки перед подрядчиками.</t>
         </is>
       </c>
       <c r="R19" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; First Pass Yield</t>
+          <t>On-Time %; Wait Time %; COPQ</t>
         </is>
       </c>
     </row>
@@ -2810,34 +2810,34 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>1.9.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
+          <t>Обработка запросов на перенос оборудования</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F20" s="30" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" s="19" t="n">
-        <v>4</v>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="I20" s="19" t="n">
         <v>4</v>
@@ -2849,9 +2849,9 @@
         <v>4</v>
       </c>
       <c r="L20" s="21" t="n">
-        <v>86</v>
-      </c>
-      <c r="M20" s="29" t="inlineStr">
+        <v>66</v>
+      </c>
+      <c r="M20" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -2863,22 +2863,22 @@
       </c>
       <c r="O20" s="12" t="inlineStr">
         <is>
-          <t>Описать правило очерёдности: какой платёж попадает в начало реестра и почему</t>
+          <t>Завести реестр переносов с сопоставлением «факт против ФЭМ»</t>
         </is>
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>1.9.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>Ядро узких мест 6 и 7: правила, по которому платёж попадает в начало или в конец реестра, не существует, поэтому очередность определяется телефонным звонком. Формализация умещается на одну страницу, а эффект измеряется днями просрочки перед подрядчиками.</t>
+          <t>Переносы выполняются, но нигде не сопоставляются с количеством, заложенным в модель (узкое место 12), поэтому перерасход обнаруживается в конце года. Реестр заводится одной таблицей и решает вторую задачу: даёт фактические данные для ревизии нормативов ФЭМ в волне 3. Без него пересмотр норм снова будет экспертной оценкой.</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Wait Time %; COPQ</t>
+          <t>Budget Variance; COPQ; Пропускная способность</t>
         </is>
       </c>
     </row>
@@ -2888,75 +2888,75 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Выявление нехватки бюджета и вынесение на ОСУ</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>ДУП и ОСУ</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="M21" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>Зафиксировать порог и срок вынесения вопроса о нехватке бюджета на ОСУ</t>
+        </is>
+      </c>
+      <c r="P21" s="12" t="inlineStr">
+        <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Обработка запросов на перенос оборудования</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G21" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" s="21" t="n">
-        <v>66</v>
-      </c>
-      <c r="M21" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N21" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O21" s="12" t="inlineStr">
-        <is>
-          <t>Завести реестр переносов с сопоставлением «факт против ФЭМ»</t>
-        </is>
-      </c>
-      <c r="P21" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
-          <t>Переносы выполняются, но нигде не сопоставляются с количеством, заложенным в модель (узкое место 12), поэтому перерасход обнаруживается в конце года. Реестр заводится одной таблицей и решает вторую задачу: даёт фактические данные для ревизии нормативов ФЭМ в волне 3. Без него пересмотр норм снова будет экспертной оценкой.</t>
+          <t>Объект исполняется, но порог и срок вынесения не формализованы, поэтому вопрос попадает на утверждающий орган тогда, когда деньги уже потрачены. Формализация критерия — одна строка регламента, а эффект — возможность принять решение, пока оно ещё что-то меняет.</t>
         </is>
       </c>
       <c r="R21" s="12" t="inlineStr">
         <is>
-          <t>Budget Variance; COPQ; Пропускная способность</t>
+          <t>On-Time %; Budget Variance</t>
         </is>
       </c>
     </row>
@@ -2964,24 +2964,24 @@
       <c r="A22" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>2.6</t>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Выявление нехватки бюджета и вынесение на ОСУ</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>Управление филиальной сетью</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>ДУП и ОСУ</t>
+          <t>ДУП</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2995,8 +2995,8 @@
       <c r="H22" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="25" t="n">
-        <v>3</v>
+      <c r="I22" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="J22" s="25" t="n">
         <v>3</v>
@@ -3005,9 +3005,9 @@
         <v>4</v>
       </c>
       <c r="L22" s="21" t="n">
-        <v>59</v>
-      </c>
-      <c r="M22" s="29" t="inlineStr">
+        <v>55</v>
+      </c>
+      <c r="M22" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -3019,22 +3019,22 @@
       </c>
       <c r="O22" s="12" t="inlineStr">
         <is>
-          <t>Зафиксировать порог и срок вынесения вопроса о нехватке бюджета на ОСУ</t>
+          <t>Утвердить паспорт процесса филиальной сети и развести подпроцессы 3.1–3.3 по владельцам</t>
         </is>
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1, 2</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
-          <t>Объект исполняется, но порог и срок вынесения не формализованы, поэтому вопрос попадает на утверждающий орган тогда, когда деньги уже потрачены. Формализация критерия — одна строка регламента, а эффект — возможность принять решение, пока оно ещё что-то меняет.</t>
+          <t>Владение больше не размыто: сквозной процесс закреплён за директором ДУП как за курирующим руководителем (Таблица 4 Методики), подпроцессы разведены между директором и замом по операционной деятельности. Предмет работы сместился с вопроса «кто отвечает» на вопрос «по какому порядку»: паспорта процесса нет, поэтому любой регламент по филиальной сети исполняется на усмотрение исполнителя.</t>
         </is>
       </c>
       <c r="R22" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Budget Variance</t>
+          <t>Паспорт процесса и карта SIPOC; Cycle Time; On-Time %</t>
         </is>
       </c>
     </row>
@@ -3042,77 +3042,77 @@
       <c r="A23" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Участие ДУП в открытии нового филиала</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="M23" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        </is>
+      </c>
+      <c r="N23" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>Описать участок ДУП в открытии филиала: обоснование потребности, приём площадки, закрепление куратора</t>
+        </is>
+      </c>
+      <c r="P23" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>Управление филиальной сетью</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G23" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" s="21" t="n">
-        <v>55</v>
-      </c>
-      <c r="M23" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N23" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O23" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить паспорт процесса филиальной сети и развести подпроцессы 3.1–3.3 по владельцам</t>
-        </is>
-      </c>
-      <c r="P23" s="12" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
       <c r="Q23" s="12" t="inlineStr">
         <is>
-          <t>Владение больше не размыто: сквозной процесс закреплён за директором ДУП как за курирующим руководителем (Таблица 4 Методики), подпроцессы разведены между директором и замом по операционной деятельности. Предмет работы сместился с вопроса «кто отвечает» на вопрос «по какому порядку»: паспорта процесса нет, поэтому любой регламент по филиальной сети исполняется на усмотрение исполнителя.</t>
+          <t>Владелец участка закреплён за замом по операционной деятельности: он несёт потери от задержки открытия и принимает работающую площадку. Процедуры по-прежнему нет — куратор ведёт открытие по памяти, и при следующем филиале объём работ будет восстанавливаться заново. Своя часть описывается внутри ДУП и идёт раньше сквозного маршрута (Б.5), который требует согласия трёх подразделений.</t>
         </is>
       </c>
       <c r="R23" s="12" t="inlineStr">
         <is>
-          <t>Паспорт процесса и карта SIPOC; Cycle Time; On-Time %</t>
+          <t>Cycle Time; On-Time %; Паспорт процесса и карта SIPOC</t>
         </is>
       </c>
     </row>
@@ -3122,75 +3122,75 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
+          <t>Б.5.1</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Инициирование, участие в сборе данных</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="M24" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        </is>
+      </c>
+      <c r="N24" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>Утвердить критерий инициации открытия филиала и форму обоснования потребности</t>
+        </is>
+      </c>
+      <c r="P24" s="12" t="inlineStr">
+        <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Участие ДУП в открытии нового филиала</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G24" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" s="21" t="n">
-        <v>62</v>
-      </c>
-      <c r="M24" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N24" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O24" s="12" t="inlineStr">
-        <is>
-          <t>Описать участок ДУП в открытии филиала: обоснование потребности, приём площадки, закрепление куратора</t>
-        </is>
-      </c>
-      <c r="P24" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="Q24" s="12" t="inlineStr">
         <is>
-          <t>Владелец участка закреплён за замом по операционной деятельности: он несёт потери от задержки открытия и принимает работающую площадку. Процедуры по-прежнему нет — куратор ведёт открытие по памяти, и при следующем филиале объём работ будет восстанавливаться заново. Своя часть описывается внутри ДУП и идёт раньше сквозного маршрута (Б.5), который требует согласия трёх подразделений.</t>
+          <t>Вход в процесс: решение об открытии сегодня рождается по факту появления проекта в регионе без филиала, то есть поздно и авралом. Этап целиком в границах операционного контура ДУП, поэтому критерий и форма обоснования утверждаются внутренним документом, не дожидаясь сквозного маршрута.</t>
         </is>
       </c>
       <c r="R24" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; On-Time %; Паспорт процесса и карта SIPOC</t>
+          <t>On-Time %; Cycle Time</t>
         </is>
       </c>
     </row>
@@ -3200,17 +3200,17 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Б.5.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Инициирование, участие в сборе данных</t>
+          <t>Назначение куратора на филиал / проект</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -3226,22 +3226,22 @@
       <c r="G25" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" s="20" t="n">
-        <v>2</v>
+      <c r="H25" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K25" s="19" t="n">
-        <v>4</v>
+      <c r="K25" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="L25" s="21" t="n">
-        <v>59</v>
-      </c>
-      <c r="M25" s="29" t="inlineStr">
+        <v>54</v>
+      </c>
+      <c r="M25" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -3253,22 +3253,22 @@
       </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>Утвердить критерий инициации открытия филиала и форму обоснования потребности</t>
+          <t>Утвердить матрицу «филиал → куратор» приказом</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr">
         <is>
-          <t>Вход в процесс: решение об открытии сегодня рождается по факту появления проекта в регионе без филиала, то есть поздно и авралом. Этап целиком в границах операционного контура ДУП, поэтому критерий и форма обоснования утверждаются внутренним документом, не дожидаясь сквозного маршрута.</t>
+          <t>Самый дешёвый объект блока 3: матрица оформляется одной таблицей и приказом. Она же вход для назначения ответственных по проектам (1.3) и для всей региональной отчётности, поэтому внутри волны берётся раньше остальных объектов филиальной сети.</t>
         </is>
       </c>
       <c r="R25" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Cycle Time</t>
+          <t>Назначение бизнес-владельца; On-Time %</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Назначение куратора на филиал / проект</t>
+          <t>Назначение ответственного (куратор / филиал)</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -3319,7 +3319,7 @@
       <c r="L26" s="21" t="n">
         <v>54</v>
       </c>
-      <c r="M26" s="29" t="inlineStr">
+      <c r="M26" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -3331,22 +3331,22 @@
       </c>
       <c r="O26" s="12" t="inlineStr">
         <is>
-          <t>Утвердить матрицу «филиал → куратор» приказом</t>
+          <t>Ввести правило: куратор и филиал назначаются приказом в срок от даты регистрации проекта</t>
         </is>
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr">
         <is>
-          <t>Самый дешёвый объект блока 3: матрица оформляется одной таблицей и приказом. Она же вход для назначения ответственных по проектам (1.3) и для всей региональной отчётности, поэтому внутри волны берётся раньше остальных объектов филиальной сети.</t>
+          <t>Процесс исполняется, но срок назначения нигде не нормирован, из-за чего проект какое-то время существует без ответственного на местах (узкое место 8). Вмешательство стоит одной строки в регламенте и опирается на матрицу «филиал → куратор» (3.1), которая берётся в этой же волне раньше.</t>
         </is>
       </c>
       <c r="R26" s="12" t="inlineStr">
         <is>
-          <t>Назначение бизнес-владельца; On-Time %</t>
+          <t>On-Time %; Назначение бизнес-владельца</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Назначение ответственного (куратор / филиал)</t>
+          <t>Общие отношения с филиалом (вне привязки к проекту)</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -3379,25 +3379,25 @@
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G27" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" s="20" t="n">
-        <v>2</v>
+      <c r="G27" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="I27" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="25" t="n">
-        <v>3</v>
+      <c r="J27" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="K27" s="27" t="n">
         <v>5</v>
       </c>
       <c r="L27" s="21" t="n">
-        <v>54</v>
-      </c>
-      <c r="M27" s="29" t="inlineStr">
+        <v>41</v>
+      </c>
+      <c r="M27" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -3409,22 +3409,22 @@
       </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
-          <t>Ввести правило: куратор и филиал назначаются приказом в срок от даты регистрации проекта</t>
+          <t>Утвердить порядок обращений филиала вне проектной рамки: кто принимает и в какой срок</t>
         </is>
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
-          <t>Процесс исполняется, но срок назначения нигде не нормирован, из-за чего проект какое-то время существует без ответственного на местах (узкое место 8). Вмешательство стоит одной строки в регламенте и опирается на матрицу «филиал → куратор» (3.1), которая берётся в этой же волне раньше.</t>
+          <t>Владелец закреплён за замом по операционной деятельности — обращения филиалов касаются работающих объектов, а не строящихся. Собственной ценности объект почти не создаёт, но закрывается одной страницей регламента, поэтому идёт попутно с остальными объектами блока 3.</t>
         </is>
       </c>
       <c r="R27" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Назначение бизнес-владельца</t>
+          <t>On-Time %; CSAT internal</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -3444,65 +3444,65 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Общие отношения с филиалом (вне привязки к проекту)</t>
+          <t>Инициация и контроль закупок</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" s="27" t="n">
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="F28" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G28" s="27" t="n">
         <v>5</v>
       </c>
+      <c r="H28" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="L28" s="21" t="n">
-        <v>41</v>
-      </c>
-      <c r="M28" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        <v>84</v>
+      </c>
+      <c r="M28" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N28" s="12" t="inlineStr">
         <is>
-          <t>Регламент и чек-лист</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
-          <t>Утвердить порядок обращений филиала вне проектной рамки: кто принимает и в какой срок</t>
+          <t>Согласовать с Закупщиками нормативы сроков по шагам процедуры и правило эскалации</t>
         </is>
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr">
         <is>
-          <t>Владелец закреплён за замом по операционной деятельности — обращения филиалов касаются работающих объектов, а не строящихся. Собственной ценности объект почти не создаёт, но закрывается одной страницей регламента, поэтому идёт попутно с остальными объектами блока 3.</t>
+          <t>Закупки — главный источник срыва сроков реализации (узкое место 13): нормативов по шагам процедуры нет, и задержка обнаруживается постфактум, когда сдвинуть уже нечего. Это единственный внешний процесс, где ДУП стоит и на входе, и на выходе, то есть рычаг есть с обеих сторон. В волне 3, потому что нормативы устанавливаются совместно с владельцем процедуры.</t>
         </is>
       </c>
       <c r="R28" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; CSAT internal</t>
+          <t>Cycle Time; SLA Compliance %; Wait Time %</t>
         </is>
       </c>
     </row>
@@ -3510,19 +3510,19 @@
       <c r="A29" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>1.7</t>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Б.4</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Инициация и контроль закупок</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>Закупки выше упрощённого порога</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -3530,7 +3530,7 @@
           <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
-      <c r="F29" s="30" t="inlineStr">
+      <c r="F29" s="29" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с Закупщиками нормативы сроков по шагам процедуры и правило эскалации</t>
+          <t>Подписать с Закупщиками нормативы сроков по шагам процедуры и регламент эскалации</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
@@ -3575,12 +3575,12 @@
       </c>
       <c r="Q29" s="12" t="inlineStr">
         <is>
-          <t>Закупки — главный источник срыва сроков реализации (узкое место 13): нормативов по шагам процедуры нет, и задержка обнаруживается постфактум, когда сдвинуть уже нечего. Это единственный внешний процесс, где ДУП стоит и на входе, и на выходе, то есть рычаг есть с обеих сторон. В волне 3, потому что нормативы устанавливаются совместно с владельцем процедуры.</t>
+          <t>Тот же предмет, что и объект 1.7, со стороны владельца процедуры. Именно здесь расположено узкое место всей фазы реализации: по п. 140 Методики до его устранения ускорение соседних шагов не сократит общее время. Поэтому объект берётся несмотря на минимальную лёгкость реализации.</t>
         </is>
       </c>
       <c r="R29" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; SLA Compliance %; Wait Time %</t>
+          <t>SLA Compliance %; Cycle Time; Bottleneck Index</t>
         </is>
       </c>
     </row>
@@ -3588,48 +3588,48 @@
       <c r="A30" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>Б.4</t>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>Закупки выше упрощённого порога</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Подтверждение готовности продукта (пилот)</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
+          <t>ДРБ</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G30" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="27" t="n">
+      <c r="H30" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I30" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>4</v>
-      </c>
       <c r="K30" s="20" t="n">
         <v>2</v>
       </c>
       <c r="L30" s="21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M30" s="31" t="inlineStr">
         <is>
@@ -3638,27 +3638,27 @@
       </c>
       <c r="N30" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Проектирование TO-BE</t>
         </is>
       </c>
       <c r="O30" s="12" t="inlineStr">
         <is>
-          <t>Подписать с Закупщиками нормативы сроков по шагам процедуры и регламент эскалации</t>
+          <t>Разработать регламент gate «пилот → промышленная реализация» совместно с ДРБ</t>
         </is>
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr">
         <is>
-          <t>Тот же предмет, что и объект 1.7, со стороны владельца процедуры. Именно здесь расположено узкое место всей фазы реализации: по п. 140 Методики до его устранения ускорение соседних шагов не сократит общее время. Поэтому объект берётся несмотря на минимальную лёгкость реализации.</t>
+          <t>Один из двух подлинных пробелов: процедуры не существует. Решение о готовности продукта принимает ДРБ, а последствия незрелого продукта несёт ДУП уже на объектах, где переделка стоит дороже всего. Берётся в волне 3, потому что здесь нужно не восстановить процедуру, а спроектировать её с нуля и согласовать с внешним владельцем.</t>
         </is>
       </c>
       <c r="R30" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; Cycle Time; Bottleneck Index</t>
+          <t>First Pass Yield; COPQ; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -3678,36 +3678,36 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Подтверждение готовности продукта (пилот)</t>
+          <t>Формирование и согласование бюджета (ФЭМ)</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="F31" s="28" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F31" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="G31" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I31" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J31" s="27" t="n">
+      <c r="H31" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" s="27" t="n">
         <v>5</v>
       </c>
+      <c r="J31" s="19" t="n">
+        <v>4</v>
+      </c>
       <c r="K31" s="20" t="n">
         <v>2</v>
       </c>
       <c r="L31" s="21" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M31" s="31" t="inlineStr">
         <is>
@@ -3716,27 +3716,27 @@
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>Проектирование TO-BE</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>Разработать регламент gate «пилот → промышленная реализация» совместно с ДРБ</t>
+          <t>Провести ревизию нормативов ФЭМ и согласовать с Финблоком срок рассмотрения модели</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr">
         <is>
-          <t>Один из двух подлинных пробелов: процедуры не существует. Решение о готовности продукта принимает ДРБ, а последствия незрелого продукта несёт ДУП уже на объектах, где переделка стоит дороже всего. Берётся в волне 3, потому что здесь нужно не восстановить процедуру, а спроектировать её с нуля и согласовать с внешним владельцем.</t>
+          <t>Нормативы ФЭМ устарели (узкое место 11): бюджет проекта считается по ценам и нормам, не отражающим ни текущую стоимость поверки, ни фактическую частоту переносов. Ошибка здесь дороже любой другой — она тиражируется на весь срок проекта и возвращается перерасходом в блоке 2. Идёт в волне 3, потому что процессом целиком владеет Финблок, а данные для пересмотра норм даёт реестр переносов из волны 2.</t>
         </is>
       </c>
       <c r="R31" s="12" t="inlineStr">
         <is>
-          <t>First Pass Yield; COPQ; Defect Rate</t>
+          <t>Budget Variance; Стоимость объекта; SLA Compliance %</t>
         </is>
       </c>
     </row>
@@ -3746,17 +3746,17 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Формирование и согласование бюджета (ФЭМ)</t>
+          <t>Формирование ФЭМ по шаблону</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -3764,7 +3764,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F32" s="30" t="inlineStr">
+      <c r="F32" s="29" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -3781,11 +3781,11 @@
       <c r="J32" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K32" s="20" t="n">
-        <v>2</v>
+      <c r="K32" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L32" s="21" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M32" s="31" t="inlineStr">
         <is>
@@ -3794,27 +3794,27 @@
       </c>
       <c r="N32" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Пересмотр экономики</t>
         </is>
       </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
-          <t>Провести ревизию нормативов ФЭМ и согласовать с Финблоком срок рассмотрения модели</t>
+          <t>Пересчитать нормы поверки, переносов и логистики по фактическим данным за два года</t>
         </is>
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr">
         <is>
-          <t>Нормативы ФЭМ устарели (узкое место 11): бюджет проекта считается по ценам и нормам, не отражающим ни текущую стоимость поверки, ни фактическую частоту переносов. Ошибка здесь дороже любой другой — она тиражируется на весь срок проекта и возвращается перерасходом в блоке 2. Идёт в волне 3, потому что процессом целиком владеет Финблок, а данные для пересмотра норм даёт реестр переносов из волны 2.</t>
+          <t>Единственный шаг процесса ФЭМ, который выполняет ДУП, и именно в нём применяются устаревшие нормы. Самая дешёвая правка с наибольшим денежным следом: меняются не шаги процесса, а числа в модели.</t>
         </is>
       </c>
       <c r="R32" s="12" t="inlineStr">
         <is>
-          <t>Budget Variance; Стоимость объекта; SLA Compliance %</t>
+          <t>Budget Variance; Стоимость объекта</t>
         </is>
       </c>
     </row>
@@ -3822,19 +3822,19 @@
       <c r="A33" s="18" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>1.5.1</t>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Б.1</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Формирование ФЭМ по шаблону</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>Согласование бюджета проекта / ФЭМ</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -3842,7 +3842,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F33" s="30" t="inlineStr">
+      <c r="F33" s="29" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -3859,11 +3859,11 @@
       <c r="J33" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K33" s="25" t="n">
-        <v>3</v>
+      <c r="K33" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="L33" s="21" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M33" s="31" t="inlineStr">
         <is>
@@ -3872,27 +3872,27 @@
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
-          <t>Пересмотр экономики</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>Пересчитать нормы поверки, переносов и логистики по фактическим данным за два года</t>
+          <t>Подписать с Финблоком SLA: срок рассмотрения ФЭМ и порядок замечаний</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr">
         <is>
-          <t>Единственный шаг процесса ФЭМ, который выполняет ДУП, и именно в нём применяются устаревшие нормы. Самая дешёвая правка с наибольшим денежным следом: меняются не шаги процесса, а числа в модели.</t>
+          <t>Тот же предмет работы, что и объект 1.5, но со стороны процесса Финблока. Ведётся одним пакетом: ревизия нормативов — внутри ДУП, норматив срока согласования — в SLA с владельцем процесса. Разделять их нельзя: актуальная модель, согласуемая месяцами, не решает задачу.</t>
         </is>
       </c>
       <c r="R33" s="12" t="inlineStr">
         <is>
-          <t>Budget Variance; Стоимость объекта</t>
+          <t>SLA Compliance %; Cycle Time; Budget Variance</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>Б.1</t>
+          <t>Б.3</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>Согласование бюджета проекта / ФЭМ</t>
+          <t>Прогноз поступлений и расходов</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -3920,19 +3920,19 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F34" s="30" t="inlineStr">
+      <c r="F34" s="29" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G34" s="27" t="n">
-        <v>5</v>
+      <c r="G34" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="H34" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I34" s="27" t="n">
-        <v>5</v>
+      <c r="I34" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="J34" s="19" t="n">
         <v>4</v>
@@ -3941,7 +3941,7 @@
         <v>2</v>
       </c>
       <c r="L34" s="21" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M34" s="31" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
-          <t>Подписать с Финблоком SLA: срок рассмотрения ФЭМ и порядок замечаний</t>
+          <t>Подписать с Финблоком регламент прогноза: состав данных, календарь, ответственные с обеих сторон</t>
         </is>
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr">
         <is>
-          <t>Тот же предмет работы, что и объект 1.5, но со стороны процесса Финблока. Ведётся одним пакетом: ревизия нормативов — внутри ДУП, норматив срока согласования — в SLA с владельцем процесса. Разделять их нельзя: актуальная модель, согласуемая месяцами, не решает задачу.</t>
+          <t>Процесс целиком принадлежит Финблоку, тогда как объект 2.3 — только часть внутри ДУП. Реестр и календарь волны 2 дают порядок со стороны ДУП, но без встречных обязательств владельца процесса прогноз останется не связанным с решениями о финансировании.</t>
         </is>
       </c>
       <c r="R34" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; Cycle Time; Budget Variance</t>
+          <t>SLA Compliance %; On-Time %; Budget Variance</t>
         </is>
       </c>
     </row>
@@ -3978,29 +3978,29 @@
       <c r="A35" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Б.3</t>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>Прогноз поступлений и расходов</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Проверка завершения пилота / тестовой эксплуатации</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>ДРБ</t>
         </is>
       </c>
       <c r="F35" s="30" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G35" s="19" t="n">
@@ -4009,17 +4009,17 @@
       <c r="H35" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I35" s="19" t="n">
-        <v>4</v>
+      <c r="I35" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="J35" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="20" t="n">
-        <v>2</v>
+      <c r="K35" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L35" s="21" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M35" s="31" t="inlineStr">
         <is>
@@ -4028,27 +4028,27 @@
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Проектирование TO-BE</t>
         </is>
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>Подписать с Финблоком регламент прогноза: состав данных, календарь, ответственные с обеих сторон</t>
+          <t>Определить измеримые критерии завершения пилота и форму подтверждения от ДРБ</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr">
         <is>
-          <t>Процесс целиком принадлежит Финблоку, тогда как объект 2.3 — только часть внутри ДУП. Реестр и календарь волны 2 дают порядок со стороны ДУП, но без встречных обязательств владельца процесса прогноз останется не связанным с решениями о финансировании.</t>
+          <t>Без измеримых критериев готовности подпись под gate превращается в формальность. Это содержательная часть нового регламента: сначала критерии, затем процедура подписания.</t>
         </is>
       </c>
       <c r="R35" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Budget Variance</t>
+          <t>First Pass Yield; CSAT internal</t>
         </is>
       </c>
     </row>
@@ -4058,75 +4058,75 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
+          <t>1.2.2</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Подписание gate «продукт готов к реализации»</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" s="21" t="n">
+        <v>82</v>
+      </c>
+      <c r="M36" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        </is>
+      </c>
+      <c r="N36" s="12" t="inlineStr">
+        <is>
+          <t>Проектирование TO-BE</t>
+        </is>
+      </c>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>Закрепить право директора ДУП блокировать старт реализации при неподписанном gate</t>
+        </is>
+      </c>
+      <c r="P36" s="12" t="inlineStr">
+        <is>
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>Проверка завершения пилота / тестовой эксплуатации</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="F36" s="28" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G36" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H36" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I36" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K36" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" s="21" t="n">
-        <v>69</v>
-      </c>
-      <c r="M36" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N36" s="12" t="inlineStr">
-        <is>
-          <t>Проектирование TO-BE</t>
-        </is>
-      </c>
-      <c r="O36" s="12" t="inlineStr">
-        <is>
-          <t>Определить измеримые критерии завершения пилота и форму подтверждения от ДРБ</t>
-        </is>
-      </c>
-      <c r="P36" s="12" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="Q36" s="12" t="inlineStr">
         <is>
-          <t>Без измеримых критериев готовности подпись под gate превращается в формальность. Это содержательная часть нового регламента: сначала критерии, затем процедура подписания.</t>
+          <t>Ядро нового регламента: право подписи и право остановить старт. Без формально закреплённой блокировки gate превращается в уведомление и поведение сторон не меняет — именно поэтому объект оценён выше родительского.</t>
         </is>
       </c>
       <c r="R36" s="12" t="inlineStr">
         <is>
-          <t>First Pass Yield; CSAT internal</t>
+          <t>Назначение бизнес-владельца; COPQ</t>
         </is>
       </c>
     </row>
@@ -4136,46 +4136,46 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Подписание gate «продукт готов к реализации»</t>
+          <t>Инициация продления / модернизации контракта</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H37" s="25" t="n">
-        <v>3</v>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="F37" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="I37" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="J37" s="27" t="n">
-        <v>5</v>
+      <c r="J37" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="K37" s="25" t="n">
         <v>3</v>
       </c>
       <c r="L37" s="21" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="M37" s="31" t="inlineStr">
         <is>
@@ -4184,27 +4184,27 @@
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
-          <t>Проектирование TO-BE</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>Закрепить право директора ДУП блокировать старт реализации при неподписанном gate</t>
+          <t>Установить срок инициации продления до окончания договора и точку передачи в ДРБ</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr">
         <is>
-          <t>Ядро нового регламента: право подписи и право остановить старт. Без формально закреплённой блокировки gate превращается в уведомление и поведение сторон не меняет — именно поэтому объект оценён выше родительского.</t>
+          <t>Объект напрямую связан с доходом: пропущенный срок инициации означает паузу или потерю контракта, который уже работает. Сегодня срок отслеживается вручную, а коммерческое предложение готовится совместно с ДРБ — поэтому предметом работы является точка передачи между двумя департаментами, а не внутренняя процедура.</t>
         </is>
       </c>
       <c r="R37" s="12" t="inlineStr">
         <is>
-          <t>Назначение бизнес-владельца; COPQ</t>
+          <t>On-Time %; SLA Compliance %; Budget Variance</t>
         </is>
       </c>
     </row>
@@ -4214,46 +4214,46 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.7.2</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Инициация продления / модернизации контракта</t>
+          <t>Проведение процедуры закупки</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>ДРБ</t>
+          <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G38" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" s="19" t="n">
-        <v>4</v>
+      <c r="H38" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I38" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="J38" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K38" s="25" t="n">
-        <v>3</v>
+      <c r="K38" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="L38" s="21" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M38" s="31" t="inlineStr">
         <is>
@@ -4267,22 +4267,22 @@
       </c>
       <c r="O38" s="12" t="inlineStr">
         <is>
-          <t>Установить срок инициации продления до окончания договора и точку передачи в ДРБ</t>
+          <t>Внести шаги процедуры в общий трекер и установить точку эскалации при просрочке</t>
         </is>
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr">
         <is>
-          <t>Объект напрямую связан с доходом: пропущенный срок инициации означает паузу или потерю контракта, который уже работает. Сегодня срок отслеживается вручную, а коммерческое предложение готовится совместно с ДРБ — поэтому предметом работы является точка передачи между двумя департаментами, а не внутренняя процедура.</t>
+          <t>Самая длинная по времени часть цепочки реализации и при этом целиком вне периметра ДУП. По п. 140 Методики оптимизация соседних шагов не сократит общее время, пока не снято это ограничение, — поэтому объект берётся, хотя лёгкость реализации минимальная.</t>
         </is>
       </c>
       <c r="R38" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; SLA Compliance %; Budget Variance</t>
+          <t>Cycle Time; Bottleneck Index; SLA Compliance %</t>
         </is>
       </c>
     </row>
@@ -4292,75 +4292,75 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
+          <t>1.7.3</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Контроль сроков поставки и приёмка</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="F39" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="G39" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L39" s="21" t="n">
+        <v>83</v>
+      </c>
+      <c r="M39" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        </is>
+      </c>
+      <c r="N39" s="12" t="inlineStr">
+        <is>
+          <t>SLA на стык с ЦО</t>
+        </is>
+      </c>
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>Утвердить форму приёмки с фиксацией дефектов и маршрутом их передачи владельцу ТЗ</t>
+        </is>
+      </c>
+      <c r="P39" s="12" t="inlineStr">
+        <is>
           <t>1.7.2</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>Проведение процедуры закупки</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="F39" s="28" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H39" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="I39" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K39" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="21" t="n">
-        <v>67</v>
-      </c>
-      <c r="M39" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N39" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O39" s="12" t="inlineStr">
-        <is>
-          <t>Внести шаги процедуры в общий трекер и установить точку эскалации при просрочке</t>
-        </is>
-      </c>
-      <c r="P39" s="12" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
       <c r="Q39" s="12" t="inlineStr">
         <is>
-          <t>Самая длинная по времени часть цепочки реализации и при этом целиком вне периметра ДУП. По п. 140 Методики оптимизация соседних шагов не сократит общее время, пока не снято это ограничение, — поэтому объект берётся, хотя лёгкость реализации минимальная.</t>
+          <t>Точка, где ДУП принимает результат и где обнаруживаются дефекты компонентов. Связана с объектом 2.7: без маршрута обратной связи дефект принимается молча и повторяется в следующей закупке — так возник кейс с хомутами.</t>
         </is>
       </c>
       <c r="R39" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; Bottleneck Index; SLA Compliance %</t>
+          <t>Defect Rate; COPQ; On-Time %</t>
         </is>
       </c>
     </row>
@@ -4368,48 +4368,48 @@
       <c r="A40" s="18" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>1.7.3</t>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Б.7</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>Контроль сроков поставки и приёмка</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>Производство, монтаж и калибровка оборудования</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="F40" s="28" t="inlineStr">
+          <t>СТ</t>
+        </is>
+      </c>
+      <c r="F40" s="30" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G40" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H40" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I40" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K40" s="25" t="n">
-        <v>3</v>
+      <c r="G40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="L40" s="21" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="M40" s="31" t="inlineStr">
         <is>
@@ -4423,22 +4423,22 @@
       </c>
       <c r="O40" s="12" t="inlineStr">
         <is>
-          <t>Утвердить форму приёмки с фиксацией дефектов и маршрутом их передачи владельцу ТЗ</t>
+          <t>Зафиксировать со СТ срок выдачи тех. карт — до подачи заявки на закупку</t>
         </is>
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>1.7.2</t>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr">
         <is>
-          <t>Точка, где ДУП принимает результат и где обнаруживаются дефекты компонентов. Связана с объектом 2.7: без маршрута обратной связи дефект принимается молча и повторяется в следующей закупке — так возник кейс с хомутами.</t>
+          <t>Тех. карты нужны до закупки, но этот порядок нигде не закреплён, и спецификация иногда собирается параллельно с заявкой. Объект связан сразу с двумя другими: он питает инициацию закупки (1.7.1) и принимает обратную связь по дефектам (2.7).</t>
         </is>
       </c>
       <c r="R40" s="12" t="inlineStr">
         <is>
-          <t>Defect Rate; COPQ; On-Time %</t>
+          <t>SLA Compliance %; On-Time %; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -4446,29 +4446,29 @@
       <c r="A41" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>Б.7</t>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>2.8</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>Производство, монтаж и калибровка оборудования</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>Отчётность руководству и госпартнёру (операционный статус)</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>СТ</t>
-        </is>
-      </c>
-      <c r="F41" s="28" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="G41" s="25" t="n">
@@ -4477,17 +4477,17 @@
       <c r="H41" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" s="20" t="n">
-        <v>2</v>
+      <c r="I41" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L41" s="21" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M41" s="31" t="inlineStr">
         <is>
@@ -4496,27 +4496,27 @@
       </c>
       <c r="N41" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Устранение дублей и упрощение</t>
         </is>
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>Зафиксировать со СТ срок выдачи тех. карт — до подачи заявки на закупку</t>
+          <t>Развести проектный, операционный и портфельный уровень отчётности в матрице «кто, что, кому, когда»</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr">
         <is>
-          <t>Тех. карты нужны до закупки, но этот порядок нигде не закреплён, и спецификация иногда собирается параллельно с заявкой. Объект связан сразу с двумя другими: он питает инициацию закупки (1.7.1) и принимает обратную связь по дефектам (2.7).</t>
+          <t>Отчётность дублируется с объектами 1.8 и 4.3: три должностные инструкции описывают подготовку отчётов об одном и том же. Оптимизация здесь — не ускорение, а устранение повторной работы. Берётся после того, как регламент статус-встреч (1.8) определит проектный уровень, иначе разводить будет нечего.</t>
         </is>
       </c>
       <c r="R41" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Defect Rate</t>
+          <t>Трудоёмкость объекта; Rework Rate; CSAT external</t>
         </is>
       </c>
     </row>
@@ -4524,19 +4524,19 @@
       <c r="A42" s="18" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>2.8</t>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Б.5</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>Отчётность руководству и госпартнёру (операционный статус)</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>Открытие нового филиала</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
@@ -4558,11 +4558,11 @@
       <c r="I42" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" s="19" t="n">
-        <v>4</v>
+      <c r="J42" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K42" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="L42" s="21" t="n">
         <v>56</v>
@@ -4574,27 +4574,27 @@
       </c>
       <c r="N42" s="12" t="inlineStr">
         <is>
-          <t>Устранение дублей и упрощение</t>
+          <t>Проектирование TO-BE</t>
         </is>
       </c>
       <c r="O42" s="12" t="inlineStr">
         <is>
-          <t>Развести проектный, операционный и портфельный уровень отчётности в матрице «кто, что, кому, когда»</t>
+          <t>Утвердить на Операционном комитете сквозной маршрут Юр → HR → Финблок → ДУП и сроки по этапам</t>
         </is>
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr">
         <is>
-          <t>Отчётность дублируется с объектами 1.8 и 4.3: три должностные инструкции описывают подготовку отчётов об одном и том же. Оптимизация здесь — не ускорение, а устранение повторной работы. Берётся после того, как регламент статус-встреч (1.8) определит проектный уровень, иначе разводить будет нечего.</t>
+          <t>Тот же предмет, что и объект 3.2, но на уровне сквозного процесса. Владельцем по Таблице 4 Методики закреплён директор ДУП как курирующий руководитель кросс-функционального процесса: Юр блок отвечает только за регистрацию, HR — только за штат, за работающий филиал целиком не отвечает никто другой. Назначение владельца чужого сквозного процесса ДУП не утверждает в одностороннем порядке, поэтому объект идёт в волне 3: предметом работы является решение Операционного комитета, а не внутренний документ.</t>
         </is>
       </c>
       <c r="R42" s="12" t="inlineStr">
         <is>
-          <t>Трудоёмкость объекта; Rework Rate; CSAT external</t>
+          <t>Cycle Time; On-Time %; Паспорт процесса и карта SIPOC</t>
         </is>
       </c>
     </row>
@@ -4602,29 +4602,29 @@
       <c r="A43" s="18" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>Б.5</t>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
-        <is>
-          <t>Открытие нового филиала</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Проверка и согласование ФЭМ</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F43" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="G43" s="25" t="n">
@@ -4636,14 +4636,14 @@
       <c r="I43" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="19" t="n">
-        <v>4</v>
+      <c r="J43" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="K43" s="20" t="n">
         <v>2</v>
       </c>
       <c r="L43" s="21" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M43" s="31" t="inlineStr">
         <is>
@@ -4652,27 +4652,27 @@
       </c>
       <c r="N43" s="12" t="inlineStr">
         <is>
-          <t>Проектирование TO-BE</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>Утвердить на Операционном комитете сквозной маршрут Юр → HR → Финблок → ДУП и сроки по этапам</t>
+          <t>Зафиксировать в SLA срок рассмотрения ФЭМ Финблоком и состав замечаний</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr">
         <is>
-          <t>Тот же предмет, что и объект 3.2, но на уровне сквозного процесса. Владельцем по Таблице 4 Методики закреплён директор ДУП как курирующий руководитель кросс-функционального процесса: Юр блок отвечает только за регистрацию, HR — только за штат, за работающий филиал целиком не отвечает никто другой. Назначение владельца чужого сквозного процесса ДУП не утверждает в одностороннем порядке, поэтому объект идёт в волне 3: предметом работы является решение Операционного комитета, а не внутренний документ.</t>
+          <t>Шаг создаёт ожидание внутри цикла согласования бюджета, но целиком зависит от Финблока. Предметом работы является не порядок шагов, а норматив срока и требование давать замечания одним пакетом, а не итерациями.</t>
         </is>
       </c>
       <c r="R43" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; On-Time %; Паспорт процесса и карта SIPOC</t>
+          <t>Wait Time %; SLA Compliance %; Rework Rate</t>
         </is>
       </c>
     </row>
@@ -4680,29 +4680,29 @@
       <c r="A44" s="18" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>1.5.2</t>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Б.10</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>Проверка и согласование ФЭМ</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>Зерек</t>
         </is>
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Участник</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G44" s="25" t="n">
@@ -4735,22 +4735,22 @@
       </c>
       <c r="O44" s="12" t="inlineStr">
         <is>
-          <t>Зафиксировать в SLA срок рассмотрения ФЭМ Финблоком и состав замечаний</t>
+          <t>Включить интерфейс с Зерек в карту процессов и согласовать срок монтажа ИТ-инфраструктуры</t>
         </is>
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr">
         <is>
-          <t>Шаг создаёт ожидание внутри цикла согласования бюджета, но целиком зависит от Финблока. Предметом работы является не порядок шагов, а норматив срока и требование давать замечания одним пакетом, а не итерациями.</t>
+          <t>Стык существует, а договорённостей по нему нет: интерфейс не был отражён в дереве процессов до версии 3. Монтаж ИТ-инфраструктуры расположен на критическом пути ввода объекта в эксплуатацию, поэтому норматив срока нужен наравне с закупками. Входом служит та же техническая спецификация, что и для объекта Б.7, поэтому срок согласуется после того, как её состав зафиксирован (1.7.1).</t>
         </is>
       </c>
       <c r="R44" s="12" t="inlineStr">
         <is>
-          <t>Wait Time %; SLA Compliance %; Rework Rate</t>
+          <t>SLA Compliance %; On-Time %; Cycle Time</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>Б.10</t>
+          <t>Б.8</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -4770,15 +4770,15 @@
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
+          <t>Юридическое сопровождение договоров с контрагентами</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Зерек</t>
-        </is>
-      </c>
-      <c r="F45" s="28" t="inlineStr">
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="F45" s="30" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -4792,11 +4792,11 @@
       <c r="I45" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K45" s="20" t="n">
-        <v>2</v>
+      <c r="J45" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L45" s="21" t="n">
         <v>53</v>
@@ -4813,22 +4813,22 @@
       </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>Включить интерфейс с Зерек в карту процессов и согласовать срок монтажа ИТ-инфраструктуры</t>
+          <t>Согласовать с Юр блоком срок рассмотрения договора и типовые условия по проектам</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr">
         <is>
-          <t>Стык существует, а договорённостей по нему нет: интерфейс не был отражён в дереве процессов до версии 3. Монтаж ИТ-инфраструктуры расположен на критическом пути ввода объекта в эксплуатацию, поэтому норматив срока нужен наравне с закупками. Входом служит та же техническая спецификация, что и для объекта Б.7, поэтому срок согласуется после того, как её состав зафиксирован (1.7.1).</t>
+          <t>Объект исполняется, острых узких мест нет, но согласование договоров расположено на критическом пути запуска проекта. Типовые условия снимают повторное обсуждение одних и тех же пунктов по каждому проекту.</t>
         </is>
       </c>
       <c r="R45" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Cycle Time</t>
+          <t>SLA Compliance %; Cycle Time; Rework Rate</t>
         </is>
       </c>
     </row>
@@ -4836,36 +4836,36 @@
       <c r="A46" s="18" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="23" t="inlineStr">
-        <is>
-          <t>Б.8</t>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="inlineStr">
-        <is>
-          <t>Юридическое сопровождение договоров с контрагентами</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Портфельная отчётность руководству и заказчикам</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="F46" s="28" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="G46" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H46" s="25" t="n">
-        <v>3</v>
+      <c r="H46" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="I46" s="20" t="n">
         <v>2</v>
@@ -4873,11 +4873,11 @@
       <c r="J46" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="K46" s="25" t="n">
-        <v>3</v>
+      <c r="K46" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L46" s="21" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M46" s="31" t="inlineStr">
         <is>
@@ -4886,27 +4886,27 @@
       </c>
       <c r="N46" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Устранение дублей и упрощение</t>
         </is>
       </c>
       <c r="O46" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с Юр блоком срок рассмотрения договора и типовые условия по проектам</t>
+          <t>Отделить портфельный уровень отчётности от проектного и операционного</t>
         </is>
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr">
         <is>
-          <t>Объект исполняется, острых узких мест нет, но согласование договоров расположено на критическом пути запуска проекта. Типовые условия снимают повторное обсуждение одних и тех же пунктов по каждому проекту.</t>
+          <t>Третий участник дублирования отчётности вместе с 1.8 и 2.8. Разводится одним решением вместе с ними: сначала определяется проектный уровень, затем операционный, портфельный собирается из них без повторного сбора данных.</t>
         </is>
       </c>
       <c r="R46" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; Cycle Time; Rework Rate</t>
+          <t>Трудоёмкость объекта; Rework Rate</t>
         </is>
       </c>
     </row>
@@ -4916,27 +4916,27 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>Б.5.3</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Портфельная отчётность руководству и заказчикам</t>
+          <t>Регистрация и запуск филиала</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="F47" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G47" s="25" t="n">
@@ -4948,11 +4948,11 @@
       <c r="I47" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J47" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" s="19" t="n">
-        <v>4</v>
+      <c r="J47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L47" s="21" t="n">
         <v>52</v>
@@ -4964,27 +4964,27 @@
       </c>
       <c r="N47" s="12" t="inlineStr">
         <is>
-          <t>Устранение дублей и упрощение</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>Отделить портфельный уровень отчётности от проектного и операционного</t>
+          <t>Согласовать с Юр блоком срок регистрации филиала и чек-лист приёма его в работу</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>Б.5</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr">
         <is>
-          <t>Третий участник дублирования отчётности вместе с 1.8 и 2.8. Разводится одним решением вместе с ними: сначала определяется проектный уровень, затем операционный, портфельный собирается из них без повторного сбора данных.</t>
+          <t>Регистрация целиком выполняется Юр блоком, ДУП здесь клиент: он передаёт данные и принимает зарегистрированный филиал. Предметом работы является не порядок шагов, а норматив срока и момент, с которого филиал считается принятым в управление, — зеркало объекта 2.0 на границе двух подразделений.</t>
         </is>
       </c>
       <c r="R47" s="12" t="inlineStr">
         <is>
-          <t>Трудоёмкость объекта; Rework Rate</t>
+          <t>SLA Compliance %; On-Time %; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -4992,27 +4992,27 @@
       <c r="A48" s="18" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>Б.5.3</t>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>Б.9</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>Регистрация и запуск филиала</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="F48" s="28" t="inlineStr">
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="F48" s="30" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -5020,11 +5020,11 @@
       <c r="G48" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I48" s="20" t="n">
-        <v>2</v>
+      <c r="H48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="J48" s="25" t="n">
         <v>3</v>
@@ -5047,22 +5047,22 @@
       </c>
       <c r="O48" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с Юр блоком срок регистрации филиала и чек-лист приёма его в работу</t>
+          <t>Согласовать с HR срок оформления штата и кадровых приказов по филиалу</t>
         </is>
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>Б.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr">
         <is>
-          <t>Регистрация целиком выполняется Юр блоком, ДУП здесь клиент: он передаёт данные и принимает зарегистрированный филиал. Предметом работы является не порядок шагов, а норматив срока и момент, с которого филиал считается принятым в управление, — зеркало объекта 2.0 на границе двух подразделений.</t>
+          <t>Оформление штата и кадровых приказов — процесс HR, владелец подтверждён. ДУП здесь клиент: формирует потребность и принимает результат, поэтому предметом договорённости является не порядок шагов, а срок (узкое место 8). Норматив согласуется в общем пакете SLA со смежными подразделениями — вместе с Юр блоком, Финблоком и Закупщиками, одним заходом на Операционный комитет.</t>
         </is>
       </c>
       <c r="R48" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Defect Rate</t>
+          <t>SLA Compliance %; On-Time %</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F49" s="28" t="inlineStr">
+      <c r="F49" s="30" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -5168,7 +5168,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F50" s="28" t="inlineStr">
+      <c r="F50" s="30" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -5246,7 +5246,7 @@
           <t>Юр блок</t>
         </is>
       </c>
-      <c r="F51" s="30" t="inlineStr">
+      <c r="F51" s="29" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -5714,7 +5714,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F57" s="30" t="inlineStr">
+      <c r="F57" s="29" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -5792,7 +5792,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F58" s="30" t="inlineStr">
+      <c r="F58" s="29" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -5948,7 +5948,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F60" s="28" t="inlineStr">
+      <c r="F60" s="30" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -6026,7 +6026,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F61" s="30" t="inlineStr">
+      <c r="F61" s="29" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
@@ -6104,7 +6104,7 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F62" s="28" t="inlineStr">
+      <c r="F62" s="30" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
@@ -6263,7 +6263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -6286,7 +6286,7 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Волна — это ответ на вопрос «когда начинаем», а не «насколько объект важен». Состав волны определяется зависимостями: нельзя спрашивать за результат с должности, которой ещё нет в штатном расписании, и нельзя доказать эффект, пока не снята базовая линия. Внутри волны объекты идут по убыванию балла, но не раньше своих предшественников.</t>
+          <t>Волна — это ответ на вопрос «когда начинаем», а не «насколько объект важен». Состав волны определяется зависимостями: нельзя улучшать процесс, границы и показатели которого не описаны, и нельзя доказать эффект, пока не снята базовая линия. Внутри волны объекты идут по убыванию балла, но не раньше своих предшественников.</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
@@ -6345,30 +6345,30 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Довести решения о владении до приказа и снять базовую линию</t>
+          <t>Паспорта сквозных процессов и замер «до»</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>2.0, 1, 2, 4, 4.2.1, Б.9, 4.2</t>
+          <t>2.0, 2, 1, 4, 4.2.1, 4.2</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Чек-лист передачи «реализация → сопровождение» (2.0): без него приказ о разделении заместителей создаёт зависшие объекты. Параллельно и без единого согласования идёт пилотный аудит одного филиала по трём готовым чек-листам методологии (4.2.1)</t>
+          <t>Чек-лист передачи «реализация → сопровождение» (2.0): он описывает границу, общую для блоков 1 и 2, поэтому оба паспорта опираются на него. Параллельно и без единого согласования идёт пилотный аудит одного филиала по трём готовым чек-листам методологии (4.2.1)</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Владельцы определены по критериям Таблицы 5 Методики и зафиксированы в карте ролей. Но решения по объектам 1, 2, 2.0 и 4 держатся на документах, которых пока нет: должности двух заместителей не введены, полномочия процессного офиса не закреплены, точка передачи между блоками 1 и 2 не описана. По п. 33 Методики спрашивать за результат можно только с существующей должности, поэтому эти объекты идут первыми независимо от балла. Сюда же отнесён пилотный аудит: пока не снята базовая линия, эффект любой последующей оптимизации будет предметом спора, а не расчёта.</t>
+          <t>Владение закреплено: у каждого объекта реестра есть должность, отвечающая за результат, поэтому стоп-факторов для старта нет. Волна занята тем, без чего оптимизация не имеет точки отсчёта. Глава 8 и Приложение №2 Методики делают паспорт процесса обязательным атрибутом — границы, вход, выход, владелец и показатели; пока паспорта нет, улучшение отдельных шагов не с чем сверять, а по п. 176 показатель без источника данных не учитывается вовсе. Поэтому первыми идут три сквозных процесса, которыми ДУП владеет целиком, описание границы между ними и оба аудита проектных данных. Баллы здесь не решают: объекты волны создают линейку, которой измеряются все остальные.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Изданы приказ о разделении заместителей и приказ о полномочиях ПМО; утверждены чек-лист передачи и RACI v2; базовая линия по пилотному филиалу зафиксирована документом</t>
+          <t>Утверждены паспорта процессов блоков 1, 2 и 4 и чек-лист передачи между блоками; базовая линия по пилотному филиалу зафиксирована документом, регулярный аудит проектных данных развёрнут на весь портфель</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6429,11 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>1.7, Б.4, 1.2, 1.5, 1.5.1, Б.1, Б.3, 1.2.1, 1.2.2, 2.4, 1.7.2, 1.7.3, Б.7, 2.8, Б.5, 1.5.2, Б.10, Б.8, 4.3, Б.5.3, 1.9.3, 2.3.2, Б.5.2</t>
+          <t>1.7, Б.4, 1.2, 1.5, 1.5.1, Б.1, Б.3, 1.2.1, 1.2.2, 2.4, 1.7.2, 1.7.3, Б.7, 2.8, Б.5, 1.5.2, Б.10, Б.8, 4.3, Б.5.3, Б.9, 1.9.3, 2.3.2, Б.5.2</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -6557,13 +6557,13 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Чек-лист передачи (2.0) → приказ о разделении заместителей (1, 2)</t>
+          <t>Чек-лист передачи (2.0) → паспорта процессов блоков 1 и 2</t>
         </is>
       </c>
       <c r="B13" s="12" t="n"/>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Разделение блоков 1 и 2 без описанной точки передачи создаёт зависшие объекты: стройка закончилась, сопровождение не началось. Поэтому единственный объект первой волны, который никого не ждёт, — сам чек-лист передачи.</t>
+          <t>Выход процесса реализации и вход процесса сопровождения — один и тот же момент: передача объекта. Пока он не описан, у двух сквозных процессов нет общей границы и оба паспорта пришлось бы переписывать. Поэтому первый объект очереди — сам чек-лист передачи.</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -6572,13 +6572,13 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Приказ о полномочиях ПМО (4) → регулярный аудит проектных данных (4.2)</t>
+          <t>Паспорт процесса методологии (4) → регулярный аудит проектных данных (4.2)</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Пилотный аудит (4.2.1) не ждёт ничего и даёт базовую линию. Регулярный аудит по всему портфелю имеет смысл только тогда, когда его результат влечёт последствия: пока право остановить проект по итогам аудита не закреплено приказом, замер превращается в справку.</t>
+          <t>Пилотный аудит (4.2.1) не ждёт ничего и даёт базовую линию. Регулярный аудит по всему портфелю имеет смысл только тогда, когда его результат влечёт последствия: право остановить проект по итогам аудита фиксируется в положении о контроле качества вместе с паспортом процесса методологии.</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -6587,13 +6587,13 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>SLA с HR (Б.9) → исполнение решений волны 1</t>
+          <t>Базовая линия (4.2.1) → доказательство эффекта</t>
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Все кадровые решения первой волны становятся действующими в день приказа HR. Без норматива срока оформления волна 1 растягивается на неопределённое время, поэтому срок фиксируется вместе с самими решениями.</t>
+          <t>Пилотный аудит даёт первые достоверные цифры. Без него любое утверждение об улучшении останется экспертной оценкой (п. 176 Методики).</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -6602,13 +6602,13 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Базовая линия (4.2.1) → доказательство эффекта</t>
+          <t>Реестр переносов (2.5) → ревизия нормативов ФЭМ (1.5)</t>
         </is>
       </c>
       <c r="B16" s="12" t="n"/>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Пилотный аудит даёт первые достоверные цифры. Без него любое утверждение об улучшении останется экспертной оценкой (п. 176 Методики).</t>
+          <t>Пересмотр норм в модели требует фактических данных по переносам. Поэтому реестр заводится в волне 2, а ревизия нормативов идёт в волне 3.</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -6617,13 +6617,13 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Реестр переносов (2.5) → ревизия нормативов ФЭМ (1.5)</t>
+          <t>Регламент статус-встреч (1.8) → разведение отчётности (2.8, 4.3)</t>
         </is>
       </c>
       <c r="B17" s="12" t="n"/>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Пересмотр норм в модели требует фактических данных по переносам. Поэтому реестр заводится в волне 2, а ревизия нормативов идёт в волне 3.</t>
+          <t>Сначала определяется проектный уровень отчётности, затем операционный и портфельный собираются из него без повторного сбора данных.</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -6632,13 +6632,13 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Регламент статус-встреч (1.8) → разведение отчётности (2.8, 4.3)</t>
+          <t>Чек-лист приёмки (1.1) → письмо в ДРБ (Б.6)</t>
         </is>
       </c>
       <c r="B18" s="12" t="n"/>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Сначала определяется проектный уровень отчётности, затем операционный и портфельный собираются из него без повторного сбора данных.</t>
+          <t>Требовать норматив срока от смежного подразделения имеет смысл тогда, когда собственная процедура приёмки уже описана и исполняется.</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -6647,13 +6647,13 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Чек-лист приёмки (1.1) → письмо в ДРБ (Б.6)</t>
+          <t>Своя часть (3.2) → сквозной маршрут открытия филиала (Б.5)</t>
         </is>
       </c>
       <c r="B19" s="12" t="n"/>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Требовать норматив срока от смежного подразделения имеет смысл тогда, когда собственная процедура приёмки уже описана и исполняется.</t>
+          <t>Участок ДУП описывается внутренним документом и идёт в волне 2. Сквозной маршрут затрагивает Юр блок, HR и Финблок и утверждается Операционным комитетом, поэтому выносится в волну 3.</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -6662,44 +6662,27 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Своя часть (3.2) → сквозной маршрут открытия филиала (Б.5)</t>
+          <t>Работающие процессы → автоматизация</t>
         </is>
       </c>
       <c r="B20" s="12" t="n"/>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Участок ДУП описывается внутренним документом и идёт в волне 2. Сквозной маршрут затрагивает Юр блок, HR и Финблок и утверждается Операционным комитетом, поэтому выносится в волну 3.</t>
+          <t>Единая карточка проекта и уведомления имеют смысл, когда данные, которые они переносят, уже собираются по регламенту.</t>
         </is>
       </c>
       <c r="D20" s="12" t="n"/>
       <c r="E20" s="12" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Работающие процессы → автоматизация</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Единая карточка проекта и уведомления имеют смысл, когда данные, которые они переносят, уже собираются по регламенту.</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="19">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C21:E21"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A21:B21"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C18:E18"/>
@@ -6746,7 +6729,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Действий, с которых начинается работа, — 11. Шаги 1–5 доводят решения о владении до приказа и снимают базовую линию, шаги 6–11 восстанавливают исполнение там, где ДУП принимает решение самостоятельно. Ни один из них не требует ИТ-разработки и бюджета — это сознательный выбор: первая волна должна показать результат до того, как начнутся переговоры со смежными подразделениями.</t>
+          <t>Действий, с которых начинается работа, — 11. Шаги 1–5 задают точку отсчёта: паспорта сквозных процессов и базовая линия, шаги 6–11 восстанавливают исполнение там, где ДУП принимает решение самостоятельно. Ни один из них не требует ИТ-разработки и бюджета — это сознательный выбор: первая волна должна показать результат до того, как начнутся переговоры со смежными подразделениями.</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6836,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Владелец точки передачи закреплён, самой процедуры нет. Разделение заместителей без описанной точки передачи создаёт зависшие объекты, поэтому чек-лист идёт раньше приказа, а не после него.</t>
+          <t>Владелец точки передачи закреплён, самой процедуры нет. Этот момент — выход процесса блока 1 и вход процесса блока 2, поэтому он описывается раньше обоих паспортов: без него у двух сквозных процессов нет общей границы.</t>
         </is>
       </c>
     </row>
@@ -6863,17 +6846,17 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Приказ о разделении заместителей и матрица RACI v2</t>
+          <t>Паспорт процесса реализации (блок 1)</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>1, 2, 2.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Директор ДУП</t>
+          <t>Зам. по реализации, директор ДУП</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -6883,12 +6866,12 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Приказ, целевая оргсхема и RACI v2</t>
+          <t>Паспорт процесса: границы, вход, выход, владелец и три показателя</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Владельцы блоков 1 и 2 определены, но должностей в штатном расписании пока нет: обе фазы ведёт один человек, и срочная стройка вытесняет доходную эксплуатацию. Целевые значения метрик по 23 подпроцессам можно адресовать только существующей должности.</t>
+          <t>Девять подпроцессов блока работают без общего описания: где фаза начинается, чем заканчивается и по каким показателям оценивается. Глава 8 и Приложение №2 Методики делают паспорт обязательным атрибутом процесса — до него улучшать отдельные шаги не с чем сверять.</t>
         </is>
       </c>
     </row>
@@ -6898,17 +6881,17 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Приказ о полномочиях процессного офиса</t>
+          <t>Паспорт процесса сопровождения (блок 2)</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>4, 4.1, 4.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Директор ДУП</t>
+          <t>Зам. по операционной деятельности, директор ДУП</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -6918,12 +6901,12 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Приказ о полномочиях ПМО и должностная инструкция</t>
+          <t>Паспорт процесса: границы, вход, выход, владелец и три показателя</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Владелец методологии и аудита закреплён за главным менеджером проектов, но права остановить проект по результатам аудита у роли нет. Без этого полномочия аудит превращается в справку, а работа возвращается к заместителям.</t>
+          <t>Фаза, в которой создаётся доход компании, описана хуже строительной: ни общих границ, ни показателей, ни регулярного учёта доходности объекта. Владелец закреплён, но спрашивать с него пока не с чем.</t>
         </is>
       </c>
     </row>
@@ -6933,17 +6916,17 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Норматив срока оформления кадровых приказов с HR</t>
+          <t>Паспорт методологии и положение о контроле качества данных</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Б.9</t>
+          <t>4, 4.2</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Директор ДУП</t>
+          <t>Главный менеджер проектов, директор ДУП</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -6953,12 +6936,12 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Соглашение с HR о сроке оформления приказов по филиалу и проекту</t>
+          <t>Положение о контроле качества и паспорт процесса 4</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Кадровые решения первой волны вступают в силу в день приказа HR (узкое место 8). Без норматива срока волна 1 растягивается, поэтому срок фиксируется вместе с самими решениями.</t>
+          <t>Один документ закрывает две задачи: описывает процесс методологии и фиксирует право остановить проект по результатам аудита. Без этого права аудит превращается в справку, а паспорта остальных процессов некому требовать.</t>
         </is>
       </c>
     </row>
@@ -7237,18 +7220,18 @@
         </is>
       </c>
       <c r="B6" s="12" t="n"/>
-      <c r="C6" s="29" t="inlineStr">
-        <is>
-          <t>Быстрые победы — 10
-2.0, 1.1, 1.1.2, 1.7.1, 2.3.1, 1.8, 1.1.1, 1.9.1, 1.9.2, 2.5</t>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы — 13
+2.0, 2, 1, 4, 1.1, 1.1.2, 1.7.1, 2.3.1, 1.8, 1.1.1, 1.9.1, 1.9.2, 2.5</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="12" t="n"/>
       <c r="F6" s="31" t="inlineStr">
         <is>
-          <t>Крупные проекты — 21
-1, 2, 4, 1.9, Б.6, 2.3, 2.7, 1.7, Б.4, 1.2, 1.5, 1.5.1, Б.1, Б.3, 1.2.1, 1.2.2, 2.4, 1.7.2, 1.7.3, Б.7, 2.1</t>
+          <t>Крупные проекты — 18
+1.9, Б.6, 2.3, 2.7, 1.7, Б.4, 1.2, 1.5, 1.5.1, Б.1, Б.3, 1.2.1, 1.2.2, 2.4, 1.7.2, 1.7.3, Б.7, 2.1</t>
         </is>
       </c>
       <c r="G6" s="12" t="n"/>
@@ -7271,7 +7254,7 @@
       <c r="F7" s="33" t="inlineStr">
         <is>
           <t>Отложить — 15
-Б.9, Б.5, 1.5.2, Б.10, Б.8, Б.5.3, 1.9.3, 2.3.2, Б.5.2, 4.1, Б.2, 2.2, 1.5.3, Б.2.2, Б.2.3</t>
+Б.5, 1.5.2, Б.10, Б.8, Б.5.3, Б.9, 1.9.3, 2.3.2, Б.5.2, 4.1, Б.2, 2.2, 1.5.3, Б.2.2, Б.2.3</t>
         </is>
       </c>
       <c r="G7" s="12" t="n"/>
@@ -7305,7 +7288,7 @@
       <c r="G10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
@@ -7542,12 +7525,12 @@
       <c r="D21" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F21" s="29" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -7573,12 +7556,12 @@
       <c r="D22" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="29" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F22" s="29" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -7609,7 +7592,7 @@
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F23" s="29" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -7640,7 +7623,7 @@
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -7821,12 +7804,12 @@
       <c r="D30" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F30" s="29" t="inlineStr">
+      <c r="F30" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -7852,12 +7835,12 @@
       <c r="D31" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="29" t="inlineStr">
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F31" s="29" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -7888,7 +7871,7 @@
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F32" s="29" t="inlineStr">
+      <c r="F32" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -7981,7 +7964,7 @@
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F35" s="29" t="inlineStr">
+      <c r="F35" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -8007,12 +7990,12 @@
       <c r="D36" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E36" s="29" t="inlineStr">
+      <c r="E36" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F36" s="29" t="inlineStr">
+      <c r="F36" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -8086,43 +8069,43 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Реализация проекта</t>
+          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>70.59999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
-        </is>
-      </c>
-      <c r="F39" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+        <v>4</v>
+      </c>
+      <c r="E39" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы</t>
+        </is>
+      </c>
+      <c r="F39" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G39" s="11" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>1.1.1</t>
+          <t>1.9.1</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
+          <t>Агрегация заявок и данных филиалов</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
@@ -8131,12 +8114,12 @@
       <c r="D40" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E40" s="29" t="inlineStr">
+      <c r="E40" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F40" s="29" t="inlineStr">
+      <c r="F40" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -8148,78 +8131,78 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>1.9.1</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Агрегация заявок и данных филиалов</t>
+          <t>Управление сроками и бюджетом проекта (статус-встречи)</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>67.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="29" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E41" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F41" s="29" t="inlineStr">
+      <c r="F41" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G41" s="11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Управление сроками и бюджетом проекта (статус-встречи)</t>
+          <t>Постпроектное сопровождение</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
         <v>65.90000000000001</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E42" s="29" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E42" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F42" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="G42" s="11" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Постпроектное сопровождение</t>
+          <t>Организация поверки оборудования</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>65.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>2</v>
@@ -8229,86 +8212,86 @@
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F43" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+      <c r="F43" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G43" s="11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Организация поверки оборудования</t>
+          <t>Обработка запросов на перенос оборудования</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>64.7</v>
+        <v>63.5</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
-        </is>
-      </c>
-      <c r="F44" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+        <v>4</v>
+      </c>
+      <c r="E44" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы</t>
+        </is>
+      </c>
+      <c r="F44" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G44" s="11" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Обработка запросов на перенос оборудования</t>
+          <t>Передача проекта «реализация → сопровождение»</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>63.5</v>
+        <v>61.2</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E45" s="29" t="inlineStr">
+      <c r="E45" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F45" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="G45" s="11" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Передача проекта «реализация → сопровождение»</t>
+          <t>Реализация проекта</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
@@ -8317,14 +8300,14 @@
       <c r="D46" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E46" s="29" t="inlineStr">
+      <c r="E46" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="G46" s="11" t="n">
@@ -8346,20 +8329,20 @@
         <v>61.2</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
+        <v>4</v>
+      </c>
+      <c r="E47" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы</t>
         </is>
       </c>
       <c r="F47" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="G47" s="11" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48">
@@ -8415,7 +8398,7 @@
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F49" s="29" t="inlineStr">
+      <c r="F49" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -8477,7 +8460,7 @@
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F51" s="29" t="inlineStr">
+      <c r="F51" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -8508,7 +8491,7 @@
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F52" s="29" t="inlineStr">
+      <c r="F52" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -8582,54 +8565,54 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Б.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
+          <t>Отчётность руководству и госпартнёру (операционный статус)</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>54.1</v>
+        <v>51.8</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F55" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+        <v>4</v>
+      </c>
+      <c r="E55" s="36" t="inlineStr">
+        <is>
+          <t>Заполнители</t>
+        </is>
+      </c>
+      <c r="F55" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G55" s="11" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>Б.8</t>
         </is>
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>Отчётность руководству и госпартнёру (операционный статус)</t>
+          <t>Юридическое сопровождение договоров с контрагентами</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
         <v>51.8</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E56" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
+        <v>3</v>
+      </c>
+      <c r="E56" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
         </is>
       </c>
       <c r="F56" s="31" t="inlineStr">
@@ -8638,80 +8621,80 @@
         </is>
       </c>
       <c r="G56" s="11" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>Б.8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Юридическое сопровождение договоров с контрагентами</t>
+          <t>Управление филиальной сетью</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>51.8</v>
+        <v>50.6</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E57" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F57" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>4</v>
+      </c>
+      <c r="E57" s="36" t="inlineStr">
+        <is>
+          <t>Заполнители</t>
+        </is>
+      </c>
+      <c r="F57" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G57" s="11" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Б.5.3</t>
         </is>
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>Управление филиальной сетью</t>
+          <t>Регистрация и запуск филиала</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
         <v>50.6</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E58" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F58" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        <v>3</v>
+      </c>
+      <c r="E58" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="F58" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G58" s="11" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Б.5.3</t>
+          <t>Б.9</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Регистрация и запуск филиала</t>
+          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
@@ -8851,7 +8834,7 @@
       </c>
       <c r="F63" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="G63" s="11" t="n">
@@ -8882,7 +8865,7 @@
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Закрепление владения и базовая линия</t>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="G64" s="11" t="n">
@@ -8973,7 +8956,7 @@
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F67" s="29" t="inlineStr">
+      <c r="F67" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -9004,7 +8987,7 @@
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F68" s="29" t="inlineStr">
+      <c r="F68" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
@@ -9252,7 +9235,7 @@
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F76" s="29" t="inlineStr">
+      <c r="F76" s="28" t="inlineStr">
         <is>
           <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>

--- a/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
+++ b/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как читать" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приоритеты" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Порядок работ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Первые 11 шагов" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица ценность — лёгкость" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Как читать" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Приоритеты" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Порядок работ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Первые 11 шагов" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Матрица ценность — лёгкость" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приоритеты'!$A$1:$R$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приоритеты'!$A$1:$R$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Приоритеты'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Порядок работ'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Первые 11 шагов'!$4:$4</definedName>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Аудит проектной документации по чек-листам</t>
+          <t>Контроль качества и полноты проектных данных</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
-          <t>Провести пилотный аудит одного филиала и зафиксировать базовую линию</t>
+          <t>Провести пилотный аудит одного филиала и развернуть его на весь портфель</t>
         </is>
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr">
         <is>
-          <t>Конкретное действие, с которого начинается вся программа. Единственный объект реестра, который запускается без единого согласования: чек-листы готовы, исполнитель определён, филиал выбирается решением директора. Идёт раньше регулярного аудита (4.2) и параллельно паспортам процессов — ничего не ждёт и никого не задерживает.</t>
+          <t>Аудит остановлен после 2020 года, поэтому ни одно утверждение о состоянии процессов нельзя подтвердить цифрой. Пилот одного филиала не ждёт согласований: чек-листы готовы, филиал выбирает директор. Регулярный аудит на портфель имеет смысл, когда его результат влечёт последствия: право остановить проект зафиксировано за владельцем методологии вместе с паспортом процесса 4.</t>
         </is>
       </c>
       <c r="R6" s="12" t="inlineStr">
         <is>
-          <t>Defect Rate; First Pass Yield</t>
+          <t>Defect Rate; First Pass Yield; Паспорт процесса и карта SIPOC</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Контроль качества и полноты проектных данных</t>
+          <t>Приём и валидация пакета документов от ДРБ</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
+          <t>ДУП и ДРБ</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -1819,14 +1819,14 @@
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G7" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="20" t="n">
-        <v>2</v>
+      <c r="G7" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="J7" s="19" t="n">
         <v>4</v>
@@ -1835,36 +1835,36 @@
         <v>4</v>
       </c>
       <c r="L7" s="21" t="n">
-        <v>54</v>
-      </c>
-      <c r="M7" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+        <v>86</v>
+      </c>
+      <c r="M7" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="N7" s="12" t="inlineStr">
         <is>
-          <t>Базовая линия и замер</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>Развернуть регулярный аудит проектных данных на весь портфель</t>
+          <t>Утвердить чек-лист минимального пакета и правило возврата неполного комплекта</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>4, 4.2.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
-          <t>Аудит остановлен после 2020 года, поэтому сегодня ни одно утверждение о состоянии процессов нельзя подтвердить цифрой. Это объект-фундамент: без базовой линии эффект любой последующей оптимизации останется предметом спора. В отличие от пилота, регулярный аудит требует последствий: право остановить проект по его результатам принадлежит владельцу методологии, и оно фиксируется вместе с паспортом его процесса (объект 4) — иначе замер останется справкой.</t>
+          <t>Первый объект цепочки: дефект пакета на входе проявляется на всех последующих подпроцессах — от ФЭМ до закупок и приёмки. Минимальный состав пакета не зафиксирован письменно (узкие места 1 и 4), поэтому старт проекта растягивается на доуточнения. Исправляется одним чек-листом и одним письмом в ДРБ — это лучшее соотношение эффекта к усилию во всём реестре.</t>
         </is>
       </c>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>Defect Rate; First Pass Yield; Паспорт процесса и карта SIPOC</t>
+          <t>Cycle Time; On-Time %; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -1874,22 +1874,22 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Приём и валидация пакета документов от ДРБ</t>
+          <t>Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>ДУП и ДРБ</t>
+          <t>ДУП</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1900,20 +1900,20 @@
       <c r="G8" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" s="19" t="n">
-        <v>4</v>
-      </c>
       <c r="L8" s="21" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M8" s="28" t="inlineStr">
         <is>
@@ -1927,22 +1927,22 @@
       </c>
       <c r="O8" s="12" t="inlineStr">
         <is>
-          <t>Утвердить чек-лист минимального пакета и правило возврата неполного комплекта</t>
+          <t>Ввести обязательную проверку по чек-листу до регистрации проекта в портфеле</t>
         </is>
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
-          <t>Первый объект цепочки: дефект пакета на входе проявляется на всех последующих подпроцессах — от ФЭМ до закупок и приёмки. Минимальный состав пакета не зафиксирован письменно (узкие места 1 и 4), поэтому старт проекта растягивается на доуточнения. Исправляется одним чек-листом и одним письмом в ДРБ — это лучшее соотношение эффекта к усилию во всём реестре.</t>
+          <t>Самый дешёвый контроль во всей цепочке: проверка по чек-листу занимает часы и отсекает дефект до того, как он превратится в неверный ФЭМ и неверную спецификацию закупки. Процессом владеет ДУП, поэтому внешних согласований не требуется вовсе.</t>
         </is>
       </c>
       <c r="R8" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; On-Time %; Defect Rate</t>
+          <t>Defect Rate; First Pass Yield; Rework Rate</t>
         </is>
       </c>
     </row>
@@ -1952,27 +1952,27 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
+          <t>Формирование реестра платежей и приоритизация</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="G9" s="27" t="n">
@@ -1981,17 +1981,17 @@
       <c r="H9" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="25" t="n">
-        <v>3</v>
+      <c r="I9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="J9" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K9" s="27" t="n">
-        <v>5</v>
+      <c r="K9" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L9" s="21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M9" s="28" t="inlineStr">
         <is>
@@ -2005,22 +2005,22 @@
       </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>Ввести обязательную проверку по чек-листу до регистрации проекта в портфеле</t>
+          <t>Утвердить инструкцию по трём потокам платежей и единую форму реестра</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
-          <t>Самый дешёвый контроль во всей цепочке: проверка по чек-листу занимает часы и отсекает дефект до того, как он превратится в неверный ФЭМ и неверную спецификацию закупки. Процессом владеет ДУП, поэтому внешних согласований не требуется вовсе.</t>
+          <t>Три потока платежей (ВУ / КИЗ / КОЗ) не формализованы, единой инструкции нет (узкие места 6 и 7). Задержка оплаты останавливает монтаж, то есть деньги и срок здесь связаны напрямую. Инструкция пишется внутри ДУП, от Финблока нужен только календарь приёма реестра — поэтому объект попадает в волну быстрых побед.</t>
         </is>
       </c>
       <c r="R9" s="12" t="inlineStr">
         <is>
-          <t>Defect Rate; First Pass Yield; Rework Rate</t>
+          <t>On-Time %; Cycle Time; COPQ</t>
         </is>
       </c>
     </row>
@@ -2030,22 +2030,22 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Формирование реестра платежей и приоритизация</t>
+          <t>Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
       <c r="F10" s="29" t="inlineStr">
@@ -2059,17 +2059,17 @@
       <c r="H10" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="19" t="n">
-        <v>4</v>
+      <c r="I10" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="J10" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K10" s="25" t="n">
-        <v>3</v>
+      <c r="K10" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L10" s="21" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M10" s="28" t="inlineStr">
         <is>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>Утвердить инструкцию по трём потокам платежей и единую форму реестра</t>
+          <t>Ввести форму заявки и правило: тех. карты СТ собираются до подачи заявки</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr">
         <is>
-          <t>Три потока платежей (ВУ / КИЗ / КОЗ) не формализованы, единой инструкции нет (узкие места 6 и 7). Задержка оплаты останавливает монтаж, то есть деньги и срок здесь связаны напрямую. Инструкция пишется внутри ДУП, от Финблока нужен только календарь приёма реестра — поэтому объект попадает в волну быстрых побед.</t>
+          <t>Этот шаг целиком внутри ДУП: полнота заявки и наличие тех. карт определяют, сколько раз процедура вернётся на доработку. Его можно исправить, не дожидаясь договорённостей с Закупщиками, поэтому он выносится в волну 2 отдельно от остальной части объекта 1.7.</t>
         </is>
       </c>
       <c r="R10" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Cycle Time; COPQ</t>
+          <t>First Pass Yield; Rework Rate; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -2106,39 +2106,39 @@
       <c r="A11" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Б.6</t>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>Передача проекта от ДРБ в ДУП</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Прогноз поступлений / расходов и контроль бюджета</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="F11" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="25" t="n">
-        <v>3</v>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="J11" s="19" t="n">
         <v>4</v>
@@ -2147,7 +2147,7 @@
         <v>3</v>
       </c>
       <c r="L11" s="21" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="M11" s="28" t="inlineStr">
         <is>
@@ -2156,27 +2156,27 @@
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>Направить в ДРБ письмо директора с минимальным составом пакета и сроком передачи</t>
+          <t>Завести единый реестр прогноза и календарь его обновления</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>Тот же предмет, что и объект 1.1, со стороны процесса ДРБ. Чек-лист внутри ДУП без встречного обязательства ДРБ работает только как основание для отказа; письмо директора превращает его в согласованный норматив. Оба действия выполняются в одной волне и одним пакетом.</t>
+          <t>Прогноз ведётся в чатах и ad-hoc (узкие места 6 и 7), из-за чего компания узнаёт о разрыве поступлений позже, чем могла бы. Реестр и календарь — инструменты внутри ДУП: от Финблока нужна только форма выгрузки. Это делает объект исполнимым в волне 2. Встречный срок Финблока фиксируется отдельно, на этапе 2.3.2.</t>
         </is>
       </c>
       <c r="R11" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Defect Rate</t>
+          <t>On-Time %; Budget Variance; Cycle Time</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
+          <t>Сбор данных и подтверждений по проектам</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="F12" s="29" t="inlineStr">
@@ -2209,11 +2209,11 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G12" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>4</v>
+      <c r="G12" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="I12" s="25" t="n">
         <v>3</v>
@@ -2225,7 +2225,7 @@
         <v>4</v>
       </c>
       <c r="L12" s="21" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="M12" s="28" t="inlineStr">
         <is>
@@ -2239,22 +2239,22 @@
       </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
-          <t>Ввести форму заявки и правило: тех. карты СТ собираются до подачи заявки</t>
+          <t>Утвердить форму и срок подачи данных филиалами в реестр прогноза</t>
         </is>
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
-          <t>Этот шаг целиком внутри ДУП: полнота заявки и наличие тех. карт определяют, сколько раз процедура вернётся на доработку. Его можно исправить, не дожидаясь договорённостей с Закупщиками, поэтому он выносится в волну 2 отдельно от остальной части объекта 1.7.</t>
+          <t>Шаг, который ДУП выполняет сам и который определяет достоверность всего прогноза. Отсутствие формы и срока — причина того, что данные приходят разрозненно и требуют ручной сверки.</t>
         </is>
       </c>
       <c r="R12" s="12" t="inlineStr">
         <is>
-          <t>First Pass Yield; Rework Rate; Defect Rate</t>
+          <t>On-Time %; First Pass Yield; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -2274,36 +2274,36 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Прогноз поступлений / расходов и контроль бюджета</t>
+          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F13" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="G13" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="25" t="n">
-        <v>3</v>
+      <c r="H13" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="I13" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="J13" s="19" t="n">
-        <v>4</v>
+      <c r="J13" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="K13" s="25" t="n">
         <v>3</v>
       </c>
       <c r="L13" s="21" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M13" s="28" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>Завести единый реестр прогноза и календарь его обновления</t>
+          <t>Утвердить форму фиксации дефекта и маршрут «эксплуатация → владелец ТЗ → закупки»</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="Q13" s="12" t="inlineStr">
         <is>
-          <t>Прогноз ведётся в чатах и ad-hoc (узкие места 6 и 7), из-за чего компания узнаёт о разрыве поступлений позже, чем могла бы. Реестр и календарь — инструменты внутри ДУП: от Финблока нужна только форма выгрузки. Это делает объект исполнимым в волне 2, тогда как процесс целиком (Б.3) остаётся в волне 3.</t>
+          <t>Ущерб уже реализовался: кейс с хомутами показал, что сведения о дефекте компонента из эксплуатации не доходят до владельца технического задания и повторяются в следующей закупке (узкое место 9). Владелец закреплён за замом по операционной деятельности — тем, кто дефект обнаруживает и несёт потери от его повторения. Осталось описать маршрут: фиксация дефекта делается внутри ДУП, встречный срок реакции СТ фиксируется в волне 3 через объект Б.7.</t>
         </is>
       </c>
       <c r="R13" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Budget Variance; Cycle Time</t>
+          <t>COPQ; Defect Rate; Rework Rate</t>
         </is>
       </c>
     </row>
@@ -2342,27 +2342,27 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Сбор данных и подтверждений по проектам</t>
+          <t>Отчётность по проектам</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F14" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="G14" s="19" t="n">
@@ -2371,17 +2371,17 @@
       <c r="H14" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="25" t="n">
-        <v>3</v>
+      <c r="I14" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="J14" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K14" s="19" t="n">
-        <v>4</v>
+      <c r="K14" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="L14" s="21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M14" s="28" t="inlineStr">
         <is>
@@ -2395,22 +2395,22 @@
       </c>
       <c r="O14" s="12" t="inlineStr">
         <is>
-          <t>Утвердить форму и срок подачи данных филиалами в реестр прогноза</t>
+          <t>Утвердить один регламент отчётности: проект, операция, портфель</t>
         </is>
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr">
         <is>
-          <t>Шаг, который ДУП выполняет сам и который определяет достоверность всего прогноза. Отсутствие формы и срока — причина того, что данные приходят разрозненно и требуют ручной сверки.</t>
+          <t>Три отчёта собирались отдельно и описывали одни и те же данные. Один регламент внутри ДУП задаёт частоту, адресата и запрет повторного сбора. Самое дешёвое восстановление управляемости портфеля: внешних согласований нет.</t>
         </is>
       </c>
       <c r="R14" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; First Pass Yield; Defect Rate</t>
+          <t>On-Time %; Time-to-Complete; Трудоёмкость объекта</t>
         </is>
       </c>
     </row>
@@ -2420,17 +2420,17 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
+          <t>Статус-встречи по проекту</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -2446,20 +2446,20 @@
       <c r="G15" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="27" t="n">
+      <c r="H15" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="K15" s="25" t="n">
-        <v>3</v>
-      </c>
       <c r="L15" s="21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M15" s="28" t="inlineStr">
         <is>
@@ -2473,22 +2473,22 @@
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>Утвердить форму фиксации дефекта и маршрут «эксплуатация → владелец ТЗ → закупки»</t>
+          <t>Ввести статус-встречи: частота, повестка, протокол, адресат решений</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr">
         <is>
-          <t>Ущерб уже реализовался: кейс с хомутами показал, что сведения о дефекте компонента из эксплуатации не доходят до владельца технического задания и повторяются в следующей закупке (узкое место 9). Владелец закреплён за замом по операционной деятельности — тем, кто дефект обнаруживает и несёт потери от его повторения. Осталось описать маршрут: фиксация дефекта делается внутри ДУП, встречный срок реакции СТ фиксируется в волне 3 через объект Б.7.</t>
+          <t>Проектный уровень контура. Регламента нет, обязанности менеджера центрального аппарата исполняются примерно на одну шестую (узкое место 8). Идёт сразу за общим регламентом отчётности.</t>
         </is>
       </c>
       <c r="R15" s="12" t="inlineStr">
         <is>
-          <t>COPQ; Defect Rate; Rework Rate</t>
+          <t>On-Time %; Time-to-Complete; CSAT internal</t>
         </is>
       </c>
     </row>
@@ -2498,46 +2498,46 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Управление сроками и бюджетом проекта (статус-встречи)</t>
+          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G16" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H16" s="25" t="n">
-        <v>3</v>
+      <c r="H16" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="I16" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" s="27" t="n">
-        <v>5</v>
+      <c r="J16" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L16" s="21" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M16" s="28" t="inlineStr">
         <is>
@@ -2546,27 +2546,27 @@
       </c>
       <c r="N16" s="12" t="inlineStr">
         <is>
-          <t>Регламент и чек-лист</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
-          <t>Утвердить регламент статус-встреч: частота, повестка, протокол, адресат решений</t>
+          <t>Зафиксировать в письме ДРБ норматив срока передачи пакета и форму карточки проекта</t>
         </is>
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr">
         <is>
-          <t>Регламента нет, обязанности менеджера центрального аппарата исполняются примерно на одну шестую (узкое место 8). Объект ДУП меняет в одиночку: частота, повестка и форма протокола утверждаются внутри департамента, без единого внешнего согласования. Самое дешёвое восстановление управляемости портфеля из всего реестра.</t>
+          <t>Точка входа, которой ДУП не управляет: пакет формирует ДРБ. Берётся в одном пакете работ с 1.1, потому что норматив срока без чек-листа состава не имеет смысла — быстро переданный неполный пакет хуже, чем переданный вовремя полный.</t>
         </is>
       </c>
       <c r="R16" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Time-to-Complete; CSAT internal</t>
+          <t>On-Time %; SLA Compliance %</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>1.1.1</t>
+          <t>1.9.1</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
+          <t>Агрегация заявок и данных филиалов</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="F17" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F17" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="G17" s="19" t="n">
@@ -2624,27 +2624,27 @@
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>Зафиксировать в письме ДРБ норматив срока передачи пакета и форму карточки проекта</t>
+          <t>Ввести единую форму заявки филиала и срок её подачи до даты формирования реестра</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr">
         <is>
-          <t>Точка входа, которой ДУП не управляет: пакет формирует ДРБ. Берётся в одном пакете работ с 1.1, потому что норматив срока без чек-листа состава не имеет смысла — быстро переданный неполный пакет хуже, чем переданный вовремя полный.</t>
+          <t>Сбор заявок в разных форматах и без общего срока — причина того, что реестр собирается в авральном режиме. Унификация формы даёт эффект сразу и не требует ничего, кроме распоряжения по филиалам.</t>
         </is>
       </c>
       <c r="R17" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; SLA Compliance %</t>
+          <t>On-Time %; First Pass Yield</t>
         </is>
       </c>
     </row>
@@ -2654,75 +2654,75 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
+          <t>1.9.2</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F18" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="21" t="n">
+        <v>86</v>
+      </c>
+      <c r="M18" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>Описать правило очерёдности: какой платёж попадает в начало реестра и почему</t>
+        </is>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
           <t>1.9.1</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Агрегация заявок и данных филиалов</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F18" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H18" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" s="21" t="n">
-        <v>69</v>
-      </c>
-      <c r="M18" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N18" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O18" s="12" t="inlineStr">
-        <is>
-          <t>Ввести единую форму заявки филиала и срок её подачи до даты формирования реестра</t>
-        </is>
-      </c>
-      <c r="P18" s="12" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
-          <t>Сбор заявок в разных форматах и без общего срока — причина того, что реестр собирается в авральном режиме. Унификация формы даёт эффект сразу и не требует ничего, кроме распоряжения по филиалам.</t>
+          <t>Ядро узких мест 6 и 7: правила, по которому платёж попадает в начало или в конец реестра, не существует, поэтому очередность определяется телефонным звонком. Формализация умещается на одну страницу, а эффект измеряется днями просрочки перед подрядчиками.</t>
         </is>
       </c>
       <c r="R18" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; First Pass Yield</t>
+          <t>On-Time %; Wait Time %; COPQ</t>
         </is>
       </c>
     </row>
@@ -2732,34 +2732,34 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>1.9.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
+          <t>Обработка запросов на перенос оборудования</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F19" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>4</v>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="I19" s="19" t="n">
         <v>4</v>
@@ -2771,7 +2771,7 @@
         <v>4</v>
       </c>
       <c r="L19" s="21" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="M19" s="28" t="inlineStr">
         <is>
@@ -2785,22 +2785,22 @@
       </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>Описать правило очерёдности: какой платёж попадает в начало реестра и почему</t>
+          <t>Завести реестр переносов с сопоставлением «факт против ФЭМ»</t>
         </is>
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>1.9.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>Ядро узких мест 6 и 7: правила, по которому платёж попадает в начало или в конец реестра, не существует, поэтому очередность определяется телефонным звонком. Формализация умещается на одну страницу, а эффект измеряется днями просрочки перед подрядчиками.</t>
+          <t>Переносы выполняются, но нигде не сопоставляются с количеством, заложенным в модель (узкое место 12), поэтому перерасход обнаруживается в конце года. Реестр заводится одной таблицей и решает вторую задачу: даёт фактические данные для ревизии нормативов ФЭМ в волне 3. Без него пересмотр норм снова будет экспертной оценкой.</t>
         </is>
       </c>
       <c r="R19" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Wait Time %; COPQ</t>
+          <t>Budget Variance; COPQ; Пропускная способность</t>
         </is>
       </c>
     </row>
@@ -2810,75 +2810,75 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Выявление нехватки бюджета и вынесение на ОСУ</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>ДУП и ОСУ</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="M20" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        </is>
+      </c>
+      <c r="N20" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>Зафиксировать порог и срок вынесения вопроса о нехватке бюджета на ОСУ</t>
+        </is>
+      </c>
+      <c r="P20" s="12" t="inlineStr">
+        <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Обработка запросов на перенос оборудования</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" s="21" t="n">
-        <v>66</v>
-      </c>
-      <c r="M20" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N20" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O20" s="12" t="inlineStr">
-        <is>
-          <t>Завести реестр переносов с сопоставлением «факт против ФЭМ»</t>
-        </is>
-      </c>
-      <c r="P20" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>Переносы выполняются, но нигде не сопоставляются с количеством, заложенным в модель (узкое место 12), поэтому перерасход обнаруживается в конце года. Реестр заводится одной таблицей и решает вторую задачу: даёт фактические данные для ревизии нормативов ФЭМ в волне 3. Без него пересмотр норм снова будет экспертной оценкой.</t>
+          <t>Объект исполняется, но порог и срок вынесения не формализованы, поэтому вопрос попадает на утверждающий орган тогда, когда деньги уже потрачены. Формализация критерия — одна строка регламента, а эффект — возможность принять решение, пока оно ещё что-то меняет.</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
         <is>
-          <t>Budget Variance; COPQ; Пропускная способность</t>
+          <t>On-Time %; Budget Variance</t>
         </is>
       </c>
     </row>
@@ -2888,22 +2888,22 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Выявление нехватки бюджета и вынесение на ОСУ</t>
+          <t>Операционный статус руководству и госпартнёру</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>ДУП и ОСУ</t>
+          <t>ДУП</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -2914,20 +2914,20 @@
       <c r="G21" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H21" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="25" t="n">
-        <v>3</v>
+      <c r="H21" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="K21" s="19" t="n">
         <v>4</v>
       </c>
       <c r="L21" s="21" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M21" s="28" t="inlineStr">
         <is>
@@ -2936,27 +2936,27 @@
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Регламент и чек-лист</t>
+          <t>Устранение дублей и упрощение</t>
         </is>
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>Зафиксировать порог и срок вынесения вопроса о нехватке бюджета на ОСУ</t>
+          <t>Собирать операционный статус из протокола статус-встреч, без второго опроса</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
-          <t>Объект исполняется, но порог и срок вынесения не формализованы, поэтому вопрос попадает на утверждающий орган тогда, когда деньги уже потрачены. Формализация критерия — одна строка регламента, а эффект — возможность принять решение, пока оно ещё что-то меняет.</t>
+          <t>Операционный отчёт госпартнёру и руководству повторял данные проектного статуса. После того как статус-встречи задают проектный уровень, этот этап только выбирает из них нужный срез.</t>
         </is>
       </c>
       <c r="R21" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Budget Variance</t>
+          <t>Трудоёмкость объекта; Rework Rate; CSAT external</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="O22" s="12" t="inlineStr">
         <is>
-          <t>Утвердить паспорт процесса филиальной сети и развести подпроцессы 3.1–3.3 по владельцам</t>
+          <t>Утвердить паспорт процесса филиальной сети: отношения вне проекта и стык с открытием филиала</t>
         </is>
       </c>
       <c r="P22" s="12" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
-          <t>Владение больше не размыто: сквозной процесс закреплён за директором ДУП как за курирующим руководителем (Таблица 4 Методики), подпроцессы разведены между директором и замом по операционной деятельности. Предмет работы сместился с вопроса «кто отвечает» на вопрос «по какому порядку»: паспорта процесса нет, поэтому любой регламент по филиальной сети исполняется на усмотрение исполнителя.</t>
+          <t>Владение закреплено за директором ДУП. Назначение куратора вынесено в одну матрицу (1.3), открытие филиала — в сквозной маршрут (Б.5). У самого процесса паспорта нет, поэтому регламент по филиальной сети исполняется на усмотрение исполнителя.</t>
         </is>
       </c>
       <c r="R22" s="12" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>Б.5.1</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Участие ДУП в открытии нового филиала</t>
+          <t>Участие ДУП: потребность, данные по региону, приём площадки</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -3076,14 +3076,14 @@
       <c r="I23" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="19" t="n">
-        <v>4</v>
+      <c r="J23" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="K23" s="19" t="n">
         <v>4</v>
       </c>
       <c r="L23" s="21" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M23" s="28" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>Описать участок ДУП в открытии филиала: обоснование потребности, приём площадки, закрепление куратора</t>
+          <t>Утвердить критерий инициации открытия филиала и форму обоснования потребности</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="Q23" s="12" t="inlineStr">
         <is>
-          <t>Владелец участка закреплён за замом по операционной деятельности: он несёт потери от задержки открытия и принимает работающую площадку. Процедуры по-прежнему нет — куратор ведёт открытие по памяти, и при следующем филиале объём работ будет восстанавливаться заново. Своя часть описывается внутри ДУП и идёт раньше сквозного маршрута (Б.5), который требует согласия трёх подразделений.</t>
+          <t>Вход в процесс: решение об открытии сегодня рождается по факту появления проекта в регионе без филиала, то есть поздно и авралом. Этап целиком в границах операционного контура ДУП, поэтому критерий и форма обоснования утверждаются внутренним документом, не дожидаясь сквозного маршрута.</t>
         </is>
       </c>
       <c r="R23" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; On-Time %; Паспорт процесса и карта SIPOC</t>
+          <t>On-Time %; Cycle Time</t>
         </is>
       </c>
     </row>
@@ -3122,17 +3122,17 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Б.5.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Инициирование, участие в сборе данных</t>
+          <t>Назначение куратора (проект и филиал)</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -3148,20 +3148,20 @@
       <c r="G24" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" s="20" t="n">
-        <v>2</v>
+      <c r="H24" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="J24" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K24" s="19" t="n">
-        <v>4</v>
+      <c r="K24" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="L24" s="21" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M24" s="28" t="inlineStr">
         <is>
@@ -3175,22 +3175,22 @@
       </c>
       <c r="O24" s="12" t="inlineStr">
         <is>
-          <t>Утвердить критерий инициации открытия филиала и форму обоснования потребности</t>
+          <t>Утвердить одну матрицу «филиал → куратор» и срок назначения от даты регистрации проекта</t>
         </is>
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr">
         <is>
-          <t>Вход в процесс: решение об открытии сегодня рождается по факту появления проекта в регионе без филиала, то есть поздно и авралом. Этап целиком в границах операционного контура ДУП, поэтому критерий и форма обоснования утверждаются внутренним документом, не дожидаясь сквозного маршрута.</t>
+          <t>Куратор проекта и куратор филиала — одна запись. Процесс исполняется, но срок назначения не нормирован, и проект какое-то время живёт без ответственного на местах (узкое место 8). Закрывается одной матрицей и одной строкой в регламенте.</t>
         </is>
       </c>
       <c r="R24" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Cycle Time</t>
+          <t>On-Time %; Назначение бизнес-владельца</t>
         </is>
       </c>
     </row>
@@ -3200,17 +3200,17 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.3.3</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Назначение куратора на филиал / проект</t>
+          <t>Портфельная отчётность руководству и заказчикам</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -3229,17 +3229,17 @@
       <c r="H25" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" s="27" t="n">
-        <v>5</v>
+      <c r="I25" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L25" s="21" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M25" s="28" t="inlineStr">
         <is>
@@ -3248,27 +3248,27 @@
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Регламент и чек-лист</t>
+          <t>Устранение дублей и упрощение</t>
         </is>
       </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>Утвердить матрицу «филиал → куратор» приказом</t>
+          <t>Собирать портфельный отчёт из проектного и операционного статуса</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr">
         <is>
-          <t>Самый дешёвый объект блока 3: матрица оформляется одной таблицей и приказом. Она же вход для назначения ответственных по проектам (1.3) и для всей региональной отчётности, поэтому внутри волны берётся раньше остальных объектов филиальной сети.</t>
+          <t>Портфель — третий адресат того же контура. Отдельного сбора данных не требует: он складывается из двух предыдущих этапов.</t>
         </is>
       </c>
       <c r="R25" s="12" t="inlineStr">
         <is>
-          <t>Назначение бизнес-владельца; On-Time %</t>
+          <t>Трудоёмкость объекта; Rework Rate</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Назначение ответственного (куратор / филиал)</t>
+          <t>Общие отношения с филиалом (вне привязки к проекту)</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -3301,23 +3301,23 @@
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G26" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <v>2</v>
+      <c r="G26" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="I26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="25" t="n">
-        <v>3</v>
+      <c r="J26" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="K26" s="27" t="n">
         <v>5</v>
       </c>
       <c r="L26" s="21" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="M26" s="28" t="inlineStr">
         <is>
@@ -3331,22 +3331,22 @@
       </c>
       <c r="O26" s="12" t="inlineStr">
         <is>
-          <t>Ввести правило: куратор и филиал назначаются приказом в срок от даты регистрации проекта</t>
+          <t>Утвердить порядок обращений филиала вне проектной рамки: кто принимает и в какой срок</t>
         </is>
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr">
         <is>
-          <t>Процесс исполняется, но срок назначения нигде не нормирован, из-за чего проект какое-то время существует без ответственного на местах (узкое место 8). Вмешательство стоит одной строки в регламенте и опирается на матрицу «филиал → куратор» (3.1), которая берётся в этой же волне раньше.</t>
+          <t>Владелец закреплён за замом по операционной деятельности — обращения филиалов касаются работающих объектов, а не строящихся. Собственной ценности объект почти не создаёт, но закрывается одной страницей регламента, поэтому идёт попутно с остальными объектами блока 3.</t>
         </is>
       </c>
       <c r="R26" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Назначение бизнес-владельца</t>
+          <t>On-Time %; CSAT internal</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -3366,65 +3366,65 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Общие отношения с филиалом (вне привязки к проекту)</t>
+          <t>Инициация и контроль закупок</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" s="27" t="n">
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="F27" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G27" s="27" t="n">
         <v>5</v>
       </c>
+      <c r="H27" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="L27" s="21" t="n">
-        <v>41</v>
-      </c>
-      <c r="M27" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        <v>84</v>
+      </c>
+      <c r="M27" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
         <is>
-          <t>Регламент и чек-лист</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
-          <t>Утвердить порядок обращений филиала вне проектной рамки: кто принимает и в какой срок</t>
+          <t>Согласовать с Закупщиками нормативы сроков по шагам процедуры и правило эскалации</t>
         </is>
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
-          <t>Владелец закреплён за замом по операционной деятельности — обращения филиалов касаются работающих объектов, а не строящихся. Собственной ценности объект почти не создаёт, но закрывается одной страницей регламента, поэтому идёт попутно с остальными объектами блока 3.</t>
+          <t>Закупки — главный источник срыва сроков реализации (узкое место 13): нормативов по шагам процедуры нет, и задержка обнаруживается постфактум, когда сдвинуть уже нечего. Это единственный внешний процесс, где ДУП стоит и на входе, и на выходе, то есть рычаг есть с обеих сторон. В волне 3, потому что нормативы устанавливаются совместно с владельцем процедуры.</t>
         </is>
       </c>
       <c r="R27" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; CSAT internal</t>
+          <t>Cycle Time; SLA Compliance %; Wait Time %</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -3444,36 +3444,36 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Инициация и контроль закупок</t>
+          <t>Подтверждение готовности продукта (пилот)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="F28" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="F28" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G28" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="27" t="n">
+      <c r="H28" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I28" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="19" t="n">
-        <v>4</v>
-      </c>
       <c r="K28" s="20" t="n">
         <v>2</v>
       </c>
       <c r="L28" s="21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M28" s="31" t="inlineStr">
         <is>
@@ -3482,27 +3482,27 @@
       </c>
       <c r="N28" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Проектирование TO-BE</t>
         </is>
       </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с Закупщиками нормативы сроков по шагам процедуры и правило эскалации</t>
+          <t>Разработать регламент gate: критерии пилота, подпись директора ДУП и право блокировать старт</t>
         </is>
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr">
         <is>
-          <t>Закупки — главный источник срыва сроков реализации (узкое место 13): нормативов по шагам процедуры нет, и задержка обнаруживается постфактум, когда сдвинуть уже нечего. Это единственный внешний процесс, где ДУП стоит и на входе, и на выходе, то есть рычаг есть с обеих сторон. В волне 3, потому что нормативы устанавливаются совместно с владельцем процедуры.</t>
+          <t>Один из двух подлинных пробелов: процедуры не существует. Решение о готовности продукта принимает ДРБ, а последствия незрелого продукта несёт ДУП. Ядро регламента — право директора ДУП не пускать проект в реализацию без подписи: без блокировки gate остаётся уведомлением. Берётся в волне 3, потому что регламент проектируется с нуля и согласуется с внешним владельцем.</t>
         </is>
       </c>
       <c r="R28" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; SLA Compliance %; Wait Time %</t>
+          <t>First Pass Yield; COPQ; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -3510,24 +3510,24 @@
       <c r="A29" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>Б.4</t>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
-        <is>
-          <t>Закупки выше упрощённого порога</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Формирование и согласование бюджета (ФЭМ)</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="F29" s="29" t="inlineStr">
@@ -3538,12 +3538,12 @@
       <c r="G29" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="27" t="n">
+      <c r="H29" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="I29" s="19" t="n">
-        <v>4</v>
-      </c>
       <c r="J29" s="19" t="n">
         <v>4</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>2</v>
       </c>
       <c r="L29" s="21" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="M29" s="31" t="inlineStr">
         <is>
@@ -3565,22 +3565,22 @@
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>Подписать с Закупщиками нормативы сроков по шагам процедуры и регламент эскалации</t>
+          <t>Провести ревизию нормативов ФЭМ и согласовать с Финблоком срок рассмотрения модели</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr">
         <is>
-          <t>Тот же предмет, что и объект 1.7, со стороны владельца процедуры. Именно здесь расположено узкое место всей фазы реализации: по п. 140 Методики до его устранения ускорение соседних шагов не сократит общее время. Поэтому объект берётся несмотря на минимальную лёгкость реализации.</t>
+          <t>Нормативы ФЭМ устарели (узкое место 11): бюджет проекта считается по ценам и нормам, не отражающим ни текущую стоимость поверки, ни фактическую частоту переносов. Ошибка здесь дороже любой другой — она тиражируется на весь срок проекта и возвращается перерасходом в блоке 2. Идёт в волне 3, потому что процессом целиком владеет Финблок, а данные для пересмотра норм даёт реестр переносов из волны 2.</t>
         </is>
       </c>
       <c r="R29" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; Cycle Time; Bottleneck Index</t>
+          <t>Budget Variance; Стоимость объекта; SLA Compliance %</t>
         </is>
       </c>
     </row>
@@ -3590,43 +3590,43 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Подтверждение готовности продукта (пилот)</t>
+          <t>Формирование ФЭМ по шаблону</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="F30" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F30" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
         </is>
       </c>
       <c r="G30" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="27" t="n">
+      <c r="H30" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="K30" s="20" t="n">
-        <v>2</v>
+      <c r="J30" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L30" s="21" t="n">
         <v>83</v>
@@ -3638,27 +3638,27 @@
       </c>
       <c r="N30" s="12" t="inlineStr">
         <is>
-          <t>Проектирование TO-BE</t>
+          <t>Пересмотр экономики</t>
         </is>
       </c>
       <c r="O30" s="12" t="inlineStr">
         <is>
-          <t>Разработать регламент gate «пилот → промышленная реализация» совместно с ДРБ</t>
+          <t>Пересчитать нормы поверки, переносов и логистики по фактическим данным за два года</t>
         </is>
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr">
         <is>
-          <t>Один из двух подлинных пробелов: процедуры не существует. Решение о готовности продукта принимает ДРБ, а последствия незрелого продукта несёт ДУП уже на объектах, где переделка стоит дороже всего. Берётся в волне 3, потому что здесь нужно не восстановить процедуру, а спроектировать её с нуля и согласовать с внешним владельцем.</t>
+          <t>Единственный шаг процесса ФЭМ, который выполняет ДУП, и именно в нём применяются устаревшие нормы. Самая дешёвая правка с наибольшим денежным следом: меняются не шаги процесса, а числа в модели.</t>
         </is>
       </c>
       <c r="R30" s="12" t="inlineStr">
         <is>
-          <t>First Pass Yield; COPQ; Defect Rate</t>
+          <t>Budget Variance; Стоимость объекта</t>
         </is>
       </c>
     </row>
@@ -3668,46 +3668,46 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Формирование и согласование бюджета (ФЭМ)</t>
+          <t>Проверка завершения пилота / тестовой эксплуатации</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F31" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G31" s="27" t="n">
-        <v>5</v>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="F31" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="H31" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I31" s="27" t="n">
-        <v>5</v>
+      <c r="I31" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="J31" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K31" s="20" t="n">
-        <v>2</v>
+      <c r="K31" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L31" s="21" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M31" s="31" t="inlineStr">
         <is>
@@ -3716,27 +3716,27 @@
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Проектирование TO-BE</t>
         </is>
       </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>Провести ревизию нормативов ФЭМ и согласовать с Финблоком срок рассмотрения модели</t>
+          <t>Определить измеримые критерии завершения пилота и форму подтверждения от ДРБ</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr">
         <is>
-          <t>Нормативы ФЭМ устарели (узкое место 11): бюджет проекта считается по ценам и нормам, не отражающим ни текущую стоимость поверки, ни фактическую частоту переносов. Ошибка здесь дороже любой другой — она тиражируется на весь срок проекта и возвращается перерасходом в блоке 2. Идёт в волне 3, потому что процессом целиком владеет Финблок, а данные для пересмотра норм даёт реестр переносов из волны 2.</t>
+          <t>Без измеримых критериев готовности подпись под gate превращается в формальность. Это содержательная часть нового регламента: сначала критерии, затем процедура подписания.</t>
         </is>
       </c>
       <c r="R31" s="12" t="inlineStr">
         <is>
-          <t>Budget Variance; Стоимость объекта; SLA Compliance %</t>
+          <t>First Pass Yield; CSAT internal</t>
         </is>
       </c>
     </row>
@@ -3746,22 +3746,22 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Формирование ФЭМ по шаблону</t>
+          <t>Инициация продления / модернизации контракта</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>ДРБ</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
@@ -3769,14 +3769,14 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G32" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H32" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I32" s="27" t="n">
-        <v>5</v>
+      <c r="G32" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="J32" s="19" t="n">
         <v>4</v>
@@ -3785,7 +3785,7 @@
         <v>3</v>
       </c>
       <c r="L32" s="21" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="M32" s="31" t="inlineStr">
         <is>
@@ -3794,27 +3794,27 @@
       </c>
       <c r="N32" s="12" t="inlineStr">
         <is>
-          <t>Пересмотр экономики</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
-          <t>Пересчитать нормы поверки, переносов и логистики по фактическим данным за два года</t>
+          <t>Установить срок инициации продления до окончания договора и точку передачи в ДРБ</t>
         </is>
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr">
         <is>
-          <t>Единственный шаг процесса ФЭМ, который выполняет ДУП, и именно в нём применяются устаревшие нормы. Самая дешёвая правка с наибольшим денежным следом: меняются не шаги процесса, а числа в модели.</t>
+          <t>Объект напрямую связан с доходом: пропущенный срок инициации означает паузу или потерю контракта, который уже работает. Сегодня срок отслеживается вручную, а коммерческое предложение готовится совместно с ДРБ — поэтому предметом работы является точка передачи между двумя департаментами, а не внутренняя процедура.</t>
         </is>
       </c>
       <c r="R32" s="12" t="inlineStr">
         <is>
-          <t>Budget Variance; Стоимость объекта</t>
+          <t>On-Time %; SLA Compliance %; Budget Variance</t>
         </is>
       </c>
     </row>
@@ -3822,48 +3822,48 @@
       <c r="A33" s="18" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="23" t="inlineStr">
-        <is>
-          <t>Б.1</t>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>1.7.2</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D33" s="24" t="inlineStr">
-        <is>
-          <t>Согласование бюджета проекта / ФЭМ</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Проведение процедуры закупки</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F33" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G33" s="27" t="n">
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="F33" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H33" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>5</v>
+      <c r="I33" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="J33" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K33" s="20" t="n">
-        <v>2</v>
+      <c r="K33" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="L33" s="21" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="M33" s="31" t="inlineStr">
         <is>
@@ -3877,22 +3877,22 @@
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>Подписать с Финблоком SLA: срок рассмотрения ФЭМ и порядок замечаний</t>
+          <t>Внести шаги процедуры в общий трекер и установить точку эскалации при просрочке</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr">
         <is>
-          <t>Тот же предмет работы, что и объект 1.5, но со стороны процесса Финблока. Ведётся одним пакетом: ревизия нормативов — внутри ДУП, норматив срока согласования — в SLA с владельцем процесса. Разделять их нельзя: актуальная модель, согласуемая месяцами, не решает задачу.</t>
+          <t>Самая длинная по времени часть цепочки реализации и при этом целиком вне периметра ДУП. По п. 140 Методики оптимизация соседних шагов не сократит общее время, пока не снято это ограничение, — поэтому объект берётся, хотя лёгкость реализации минимальная.</t>
         </is>
       </c>
       <c r="R33" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; Cycle Time; Budget Variance</t>
+          <t>Cycle Time; Bottleneck Index; SLA Compliance %</t>
         </is>
       </c>
     </row>
@@ -3900,36 +3900,36 @@
       <c r="A34" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>Б.3</t>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>1.7.3</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr">
-        <is>
-          <t>Прогноз поступлений и расходов</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Контроль сроков поставки и приёмка</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F34" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G34" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H34" s="25" t="n">
-        <v>3</v>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="F34" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="I34" s="19" t="n">
         <v>4</v>
@@ -3937,11 +3937,11 @@
       <c r="J34" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K34" s="20" t="n">
-        <v>2</v>
+      <c r="K34" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L34" s="21" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="M34" s="31" t="inlineStr">
         <is>
@@ -3955,22 +3955,22 @@
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
-          <t>Подписать с Финблоком регламент прогноза: состав данных, календарь, ответственные с обеих сторон</t>
+          <t>Утвердить форму приёмки с фиксацией дефектов и маршрутом их передачи владельцу ТЗ</t>
         </is>
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>1.7.2</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr">
         <is>
-          <t>Процесс целиком принадлежит Финблоку, тогда как объект 2.3 — только часть внутри ДУП. Реестр и календарь волны 2 дают порядок со стороны ДУП, но без встречных обязательств владельца процесса прогноз останется не связанным с решениями о финансировании.</t>
+          <t>Точка, где ДУП принимает результат и где обнаруживаются дефекты компонентов. Связана с объектом 2.7: без маршрута обратной связи дефект принимается молча и повторяется в следующей закупке — так возник кейс с хомутами.</t>
         </is>
       </c>
       <c r="R34" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Budget Variance</t>
+          <t>Defect Rate; COPQ; On-Time %</t>
         </is>
       </c>
     </row>
@@ -3978,24 +3978,24 @@
       <c r="A35" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>1.2.1</t>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Б.7</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>Проверка завершения пилота / тестовой эксплуатации</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>Производство, монтаж и калибровка оборудования</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>ДРБ</t>
+          <t>СТ</t>
         </is>
       </c>
       <c r="F35" s="30" t="inlineStr">
@@ -4003,8 +4003,8 @@
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G35" s="19" t="n">
-        <v>4</v>
+      <c r="G35" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="H35" s="25" t="n">
         <v>3</v>
@@ -4012,14 +4012,14 @@
       <c r="I35" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J35" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K35" s="25" t="n">
-        <v>3</v>
+      <c r="J35" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="L35" s="21" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="M35" s="31" t="inlineStr">
         <is>
@@ -4028,27 +4028,27 @@
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
-          <t>Проектирование TO-BE</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>Определить измеримые критерии завершения пилота и форму подтверждения от ДРБ</t>
+          <t>Зафиксировать со СТ срок выдачи тех. карт — до подачи заявки на закупку</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr">
         <is>
-          <t>Без измеримых критериев готовности подпись под gate превращается в формальность. Это содержательная часть нового регламента: сначала критерии, затем процедура подписания.</t>
+          <t>Тех. карты нужны до закупки, но этот порядок нигде не закреплён, и спецификация иногда собирается параллельно с заявкой. Объект связан сразу с двумя другими: он питает инициацию закупки (1.7.1) и принимает обратную связь по дефектам (2.7).</t>
         </is>
       </c>
       <c r="R35" s="12" t="inlineStr">
         <is>
-          <t>First Pass Yield; CSAT internal</t>
+          <t>SLA Compliance %; On-Time %; Defect Rate</t>
         </is>
       </c>
     </row>
@@ -4056,19 +4056,19 @@
       <c r="A36" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>1.2.2</t>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Б.5</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>Подписание gate «продукт готов к реализации»</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>Открытие нового филиала</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -4081,23 +4081,23 @@
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G36" s="27" t="n">
-        <v>5</v>
+      <c r="G36" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="H36" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K36" s="25" t="n">
-        <v>3</v>
+      <c r="I36" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="L36" s="21" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="M36" s="31" t="inlineStr">
         <is>
@@ -4111,22 +4111,22 @@
       </c>
       <c r="O36" s="12" t="inlineStr">
         <is>
-          <t>Закрепить право директора ДУП блокировать старт реализации при неподписанном gate</t>
+          <t>Утвердить на Операционном комитете сквозной маршрут Юр → HR → Финблок → ДУП и сроки по этапам</t>
         </is>
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>Б.5.1</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr">
         <is>
-          <t>Ядро нового регламента: право подписи и право остановить старт. Без формально закреплённой блокировки gate превращается в уведомление и поведение сторон не меняет — именно поэтому объект оценён выше родительского.</t>
+          <t>Единственная строка открытия филиала. Участок ДУП — этап Б.5.1, он описывается раньше. Владельцем по Таблице 4 Методики закреплён директор ДУП как курирующий руководитель кросс-функционального процесса: Юр блок отвечает только за регистрацию, HR — только за штат, за работающий филиал целиком не отвечает никто другой. Назначение владельца чужого сквозного процесса ДУП не утверждает в одностороннем порядке, поэтому объект идёт в волне 3: предметом работы является решение Операционного комитета, а не внутренний документ.</t>
         </is>
       </c>
       <c r="R36" s="12" t="inlineStr">
         <is>
-          <t>Назначение бизнес-владельца; COPQ</t>
+          <t>Cycle Time; On-Time %; Паспорт процесса и карта SIPOC</t>
         </is>
       </c>
     </row>
@@ -4136,22 +4136,22 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Инициация продления / модернизации контракта</t>
+          <t>Проверка и согласование ФЭМ</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>ДРБ</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
@@ -4159,23 +4159,23 @@
           <t>Участник</t>
         </is>
       </c>
-      <c r="G37" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H37" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J37" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K37" s="25" t="n">
-        <v>3</v>
+      <c r="G37" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="L37" s="21" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="M37" s="31" t="inlineStr">
         <is>
@@ -4189,22 +4189,22 @@
       </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>Установить срок инициации продления до окончания договора и точку передачи в ДРБ</t>
+          <t>Зафиксировать в SLA срок рассмотрения ФЭМ Финблоком и состав замечаний</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr">
         <is>
-          <t>Объект напрямую связан с доходом: пропущенный срок инициации означает паузу или потерю контракта, который уже работает. Сегодня срок отслеживается вручную, а коммерческое предложение готовится совместно с ДРБ — поэтому предметом работы является точка передачи между двумя департаментами, а не внутренняя процедура.</t>
+          <t>Шаг создаёт ожидание внутри цикла согласования бюджета, но целиком зависит от Финблока. Предметом работы является не порядок шагов, а норматив срока и требование давать замечания одним пакетом, а не итерациями.</t>
         </is>
       </c>
       <c r="R37" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; SLA Compliance %; Budget Variance</t>
+          <t>Wait Time %; SLA Compliance %; Rework Rate</t>
         </is>
       </c>
     </row>
@@ -4212,24 +4212,24 @@
       <c r="A38" s="18" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>1.7.2</t>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Б.10</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>Проведение процедуры закупки</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
+          <t>Зерек</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
@@ -4237,23 +4237,23 @@
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G38" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" s="27" t="n">
-        <v>5</v>
+      <c r="G38" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="I38" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" s="26" t="n">
-        <v>1</v>
+      <c r="J38" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="L38" s="21" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="M38" s="31" t="inlineStr">
         <is>
@@ -4267,22 +4267,22 @@
       </c>
       <c r="O38" s="12" t="inlineStr">
         <is>
-          <t>Внести шаги процедуры в общий трекер и установить точку эскалации при просрочке</t>
+          <t>Включить интерфейс с Зерек в карту процессов и согласовать срок монтажа ИТ-инфраструктуры</t>
         </is>
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr">
         <is>
-          <t>Самая длинная по времени часть цепочки реализации и при этом целиком вне периметра ДУП. По п. 140 Методики оптимизация соседних шагов не сократит общее время, пока не снято это ограничение, — поэтому объект берётся, хотя лёгкость реализации минимальная.</t>
+          <t>Стык существует, а договорённостей по нему нет: интерфейс не был отражён в дереве процессов до версии 3. Монтаж ИТ-инфраструктуры расположен на критическом пути ввода объекта в эксплуатацию, поэтому норматив срока нужен наравне с закупками. Входом служит та же техническая спецификация, что и для объекта Б.7, поэтому срок согласуется после того, как её состав зафиксирован (1.7.1).</t>
         </is>
       </c>
       <c r="R38" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; Bottleneck Index; SLA Compliance %</t>
+          <t>SLA Compliance %; On-Time %; Cycle Time</t>
         </is>
       </c>
     </row>
@@ -4290,24 +4290,24 @@
       <c r="A39" s="18" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>1.7.3</t>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Б.8</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>Контроль сроков поставки и приёмка</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>Юридическое сопровождение договоров с контрагентами</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="F39" s="30" t="inlineStr">
@@ -4315,23 +4315,23 @@
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G39" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I39" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>4</v>
+      <c r="G39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="K39" s="25" t="n">
         <v>3</v>
       </c>
       <c r="L39" s="21" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="M39" s="31" t="inlineStr">
         <is>
@@ -4345,22 +4345,22 @@
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>Утвердить форму приёмки с фиксацией дефектов и маршрутом их передачи владельцу ТЗ</t>
+          <t>Согласовать с Юр блоком срок рассмотрения договора и типовые условия по проектам</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>1.7.2</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr">
         <is>
-          <t>Точка, где ДУП принимает результат и где обнаруживаются дефекты компонентов. Связана с объектом 2.7: без маршрута обратной связи дефект принимается молча и повторяется в следующей закупке — так возник кейс с хомутами.</t>
+          <t>Объект исполняется, острых узких мест нет, но согласование договоров расположено на критическом пути запуска проекта. Типовые условия снимают повторное обсуждение одних и тех же пунктов по каждому проекту.</t>
         </is>
       </c>
       <c r="R39" s="12" t="inlineStr">
         <is>
-          <t>Defect Rate; COPQ; On-Time %</t>
+          <t>SLA Compliance %; Cycle Time; Rework Rate</t>
         </is>
       </c>
     </row>
@@ -4368,24 +4368,24 @@
       <c r="A40" s="18" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="23" t="inlineStr">
-        <is>
-          <t>Б.7</t>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Б.5.3</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>Производство, монтаж и калибровка оборудования</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Регистрация и запуск филиала</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>СТ</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
@@ -4396,20 +4396,20 @@
       <c r="G40" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I40" s="25" t="n">
-        <v>3</v>
+      <c r="H40" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="J40" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K40" s="20" t="n">
-        <v>2</v>
+      <c r="K40" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L40" s="21" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M40" s="31" t="inlineStr">
         <is>
@@ -4423,17 +4423,17 @@
       </c>
       <c r="O40" s="12" t="inlineStr">
         <is>
-          <t>Зафиксировать со СТ срок выдачи тех. карт — до подачи заявки на закупку</t>
+          <t>Согласовать с Юр блоком срок регистрации филиала и чек-лист приёма его в работу</t>
         </is>
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>Б.5</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr">
         <is>
-          <t>Тех. карты нужны до закупки, но этот порядок нигде не закреплён, и спецификация иногда собирается параллельно с заявкой. Объект связан сразу с двумя другими: он питает инициацию закупки (1.7.1) и принимает обратную связь по дефектам (2.7).</t>
+          <t>Регистрация целиком выполняется Юр блоком, ДУП здесь клиент: он передаёт данные и принимает зарегистрированный филиал. Предметом работы является не порядок шагов, а норматив срока и момент, с которого филиал считается принятым в управление, — зеркало объекта 2.0 на границе двух подразделений.</t>
         </is>
       </c>
       <c r="R40" s="12" t="inlineStr">
@@ -4446,29 +4446,29 @@
       <c r="A41" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>2.8</t>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>Б.9</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>Отчётность руководству и госпартнёру (операционный статус)</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="F41" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G41" s="25" t="n">
@@ -4477,17 +4477,17 @@
       <c r="H41" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K41" s="19" t="n">
-        <v>4</v>
+      <c r="I41" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L41" s="21" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="M41" s="31" t="inlineStr">
         <is>
@@ -4496,27 +4496,27 @@
       </c>
       <c r="N41" s="12" t="inlineStr">
         <is>
-          <t>Устранение дублей и упрощение</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>Развести проектный, операционный и портфельный уровень отчётности в матрице «кто, что, кому, когда»</t>
+          <t>Согласовать с HR срок оформления штата и кадровых приказов по филиалу</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr">
         <is>
-          <t>Отчётность дублируется с объектами 1.8 и 4.3: три должностные инструкции описывают подготовку отчётов об одном и том же. Оптимизация здесь — не ускорение, а устранение повторной работы. Берётся после того, как регламент статус-встреч (1.8) определит проектный уровень, иначе разводить будет нечего.</t>
+          <t>Оформление штата и кадровых приказов — процесс HR, владелец подтверждён. ДУП здесь клиент: формирует потребность и принимает результат, поэтому предметом договорённости является не порядок шагов, а срок (узкое место 8). Норматив согласуется в общем пакете SLA со смежными подразделениями — вместе с Юр блоком, Финблоком и Закупщиками, одним заходом на Операционный комитет.</t>
         </is>
       </c>
       <c r="R41" s="12" t="inlineStr">
         <is>
-          <t>Трудоёмкость объекта; Rework Rate; CSAT external</t>
+          <t>SLA Compliance %; On-Time %</t>
         </is>
       </c>
     </row>
@@ -4524,29 +4524,29 @@
       <c r="A42" s="18" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>Б.5</t>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>1.9.3</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>Открытие нового филиала</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Решение об оплате и проведение платежа</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F42" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G42" s="25" t="n">
@@ -4555,17 +4555,17 @@
       <c r="H42" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I42" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K42" s="20" t="n">
-        <v>2</v>
+      <c r="I42" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="L42" s="21" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M42" s="31" t="inlineStr">
         <is>
@@ -4574,27 +4574,27 @@
       </c>
       <c r="N42" s="12" t="inlineStr">
         <is>
-          <t>Проектирование TO-BE</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="O42" s="12" t="inlineStr">
         <is>
-          <t>Утвердить на Операционном комитете сквозной маршрут Юр → HR → Финблок → ДУП и сроки по этапам</t>
+          <t>Согласовать с Финблоком норматив срока от передачи реестра до проведения платежа</t>
         </is>
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.9.2</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr">
         <is>
-          <t>Тот же предмет, что и объект 3.2, но на уровне сквозного процесса. Владельцем по Таблице 4 Методики закреплён директор ДУП как курирующий руководитель кросс-функционального процесса: Юр блок отвечает только за регистрацию, HR — только за штат, за работающий филиал целиком не отвечает никто другой. Назначение владельца чужого сквозного процесса ДУП не утверждает в одностороннем порядке, поэтому объект идёт в волне 3: предметом работы является решение Операционного комитета, а не внутренний документ.</t>
+          <t>Шаг выполняет Финблок, ДУП получает информацию о проведении платежа. Предметом договорённости является норматив срока: без него приоритизация реестра в волне 2 не доводится до результата.</t>
         </is>
       </c>
       <c r="R42" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; On-Time %; Паспорт процесса и карта SIPOC</t>
+          <t>SLA Compliance %; On-Time %</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>2.3.2</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Проверка и согласование ФЭМ</t>
+          <t>Планирование и решение по прогнозу</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
@@ -4622,16 +4622,16 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F43" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
+      <c r="F43" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="G43" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="25" t="n">
-        <v>3</v>
+      <c r="H43" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="I43" s="20" t="n">
         <v>2</v>
@@ -4639,11 +4639,11 @@
       <c r="J43" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K43" s="20" t="n">
-        <v>2</v>
+      <c r="K43" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="L43" s="21" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M43" s="31" t="inlineStr">
         <is>
@@ -4657,22 +4657,22 @@
       </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>Зафиксировать в SLA срок рассмотрения ФЭМ Финблоком и состав замечаний</t>
+          <t>Согласовать с Финблоком срок возврата утверждённого прогноза в ДУП</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr">
         <is>
-          <t>Шаг создаёт ожидание внутри цикла согласования бюджета, но целиком зависит от Финблока. Предметом работы является не порядок шагов, а норматив срока и требование давать замечания одним пакетом, а не итерациями.</t>
+          <t>Планирование и решение принимает Финблок. ДУП управляет здесь одним параметром — сроком получения утверждённого прогноза, без которого планирование работ на объектах ведётся вслепую.</t>
         </is>
       </c>
       <c r="R43" s="12" t="inlineStr">
         <is>
-          <t>Wait Time %; SLA Compliance %; Rework Rate</t>
+          <t>SLA Compliance %; Wait Time %</t>
         </is>
       </c>
     </row>
@@ -4680,48 +4680,48 @@
       <c r="A44" s="18" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="23" t="inlineStr">
-        <is>
-          <t>Б.10</t>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Б.5.2</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
-        <is>
-          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Подготовка пакета документов и доверенностей</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Зерек</t>
-        </is>
-      </c>
-      <c r="F44" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I44" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="25" t="n">
-        <v>3</v>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="F44" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="K44" s="20" t="n">
         <v>2</v>
       </c>
       <c r="L44" s="21" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="M44" s="31" t="inlineStr">
         <is>
@@ -4735,22 +4735,22 @@
       </c>
       <c r="O44" s="12" t="inlineStr">
         <is>
-          <t>Включить интерфейс с Зерек в карту процессов и согласовать срок монтажа ИТ-инфраструктуры</t>
+          <t>Согласовать с Юр блоком срок подготовки пакета документов и доверенностей</t>
         </is>
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>Б.5.1</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr">
         <is>
-          <t>Стык существует, а договорённостей по нему нет: интерфейс не был отражён в дереве процессов до версии 3. Монтаж ИТ-инфраструктуры расположен на критическом пути ввода объекта в эксплуатацию, поэтому норматив срока нужен наравне с закупками. Входом служит та же техническая спецификация, что и для объекта Б.7, поэтому срок согласуется после того, как её состав зафиксирован (1.7.1).</t>
+          <t>Шаг исполняется Юр блоком и проблем не вызывает. Включается в общий регламент открытия филиала только для того, чтобы у сквозного маршрута не осталось участка без норматива срока.</t>
         </is>
       </c>
       <c r="R44" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Cycle Time</t>
+          <t>SLA Compliance %; On-Time %</t>
         </is>
       </c>
     </row>
@@ -4758,77 +4758,77 @@
       <c r="A45" s="18" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>Б.8</t>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>Юридическое сопровождение договоров с контрагентами</t>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Организация поверки оборудования</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="F45" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="G45" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I45" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" s="25" t="n">
-        <v>3</v>
+      <c r="H45" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J45" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="L45" s="21" t="n">
-        <v>53</v>
-      </c>
-      <c r="M45" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>61</v>
+      </c>
+      <c r="M45" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N45" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Пересмотр экономики</t>
         </is>
       </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с Юр блоком срок рассмотрения договора и типовые условия по проектам</t>
+          <t>Рассчитать экономику собственной аккредитации против аутсорса поверки</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr">
         <is>
-          <t>Объект исполняется, острых узких мест нет, но согласование договоров расположено на критическом пути запуска проекта. Типовые условия снимают повторное обсуждение одних и тех же пунктов по каждому проекту.</t>
+          <t>Самый крупный денежный объект реестра: около 6 000 комплексов на поверке, методика устарела (узкое место 10), стоимость услуги растёт. Оптимизируется не порядок шагов, а модель оказания услуги, поэтому нужен расчёт и бюджетное решение. Берётся после того, как появится достоверная стоимость процесса по методу ABC — иначе сравнивать не с чем.</t>
         </is>
       </c>
       <c r="R45" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; Cycle Time; Rework Rate</t>
+          <t>Стоимость объекта; CPT; ROI автоматизации</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Портфельная отчётность руководству и заказчикам</t>
+          <t>Разработка проектной документации (устав, план, приказ)</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
@@ -4879,34 +4879,34 @@
       <c r="L46" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="M46" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M46" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N46" s="12" t="inlineStr">
         <is>
-          <t>Устранение дублей и упрощение</t>
+          <t>Шаблонизация</t>
         </is>
       </c>
       <c r="O46" s="12" t="inlineStr">
         <is>
-          <t>Отделить портфельный уровень отчётности от проектного и операционного</t>
+          <t>Утвердить типовой комплект: устав, план проекта, приказ</t>
         </is>
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr">
         <is>
-          <t>Третий участник дублирования отчётности вместе с 1.8 и 2.8. Разводится одним решением вместе с ними: сначала определяется проектный уровень, затем операционный, портфельный собирается из них без повторного сбора данных.</t>
+          <t>Объект исполняется, узких мест по нему не зафиксировано, поэтому в первых волнах он вытеснил бы более острые задачи. Берётся ради масштабируемости: типовой комплект сокращает подготовку документации и делает проекты сравнимыми между собой — без этого портфельная отчётность собирается вручную.</t>
         </is>
       </c>
       <c r="R46" s="12" t="inlineStr">
         <is>
-          <t>Трудоёмкость объекта; Rework Rate</t>
+          <t>Cycle Time; Трудоёмкость объекта</t>
         </is>
       </c>
     </row>
@@ -4916,27 +4916,27 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Б.5.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Регистрация и запуск филиала</t>
+          <t>Разработка и поддержка методологии, шаблонов, реестров</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="F47" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="G47" s="25" t="n">
@@ -4957,34 +4957,34 @@
       <c r="L47" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="M47" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M47" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N47" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Устранение дублей и упрощение</t>
         </is>
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с Юр блоком срок регистрации филиала и чек-лист приёма его в работу</t>
+          <t>Актуализировать методологию: роли вместо фамилий, глоссарий, архивация устаревшего</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>Б.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr">
         <is>
-          <t>Регистрация целиком выполняется Юр блоком, ДУП здесь клиент: он передаёт данные и принимает зарегистрированный филиал. Предметом работы является не порядок шагов, а норматив срока и момент, с которого филиал считается принятым в управление, — зеркало объекта 2.0 на границе двух подразделений.</t>
+          <t>В реестре методологии 434 документа, около 28% архива устарело, последняя правка — 2021 год. Задача не в переписывании, а в актуализации, и делать её имеет смысл тогда, когда новые регламенты волн 2 и 3 уже написаны — иначе методологию придётся актуализировать дважды.</t>
         </is>
       </c>
       <c r="R47" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Defect Rate</t>
+          <t>Паспорт процесса и карта SIPOC; CSAT internal</t>
         </is>
       </c>
     </row>
@@ -4992,77 +4992,77 @@
       <c r="A48" s="18" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="23" t="inlineStr">
-        <is>
-          <t>Б.9</t>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>1.1.3</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>Регистрация проекта в портфеле / системе</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F48" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
         </is>
       </c>
       <c r="G48" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="25" t="n">
-        <v>3</v>
+      <c r="H48" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="I48" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K48" s="25" t="n">
-        <v>3</v>
+      <c r="J48" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L48" s="21" t="n">
-        <v>52</v>
-      </c>
-      <c r="M48" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>48</v>
+      </c>
+      <c r="M48" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N48" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Автоматизация</t>
         </is>
       </c>
       <c r="O48" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с HR срок оформления штата и кадровых приказов по филиалу</t>
+          <t>Определить обязательные поля карточки проекта в SimBASE и запретить регистрацию без них</t>
         </is>
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr">
         <is>
-          <t>Оформление штата и кадровых приказов — процесс HR, владелец подтверждён. ДУП здесь клиент: формирует потребность и принимает результат, поэтому предметом договорённости является не порядок шагов, а срок (узкое место 8). Норматив согласуется в общем пакете SLA со смежными подразделениями — вместе с Юр блоком, Финблоком и Закупщиками, одним заходом на Операционный комитет.</t>
+          <t>Ручная регистрация сама по себе потерь почти не создаёт, поэтому балл низкий. Но именно она задаёт единый идентификатор проекта, без которого метрики по портфелю нельзя собрать автоматически. Объект берётся не ради экономии, а как обязательный элемент единой карточки проекта.</t>
         </is>
       </c>
       <c r="R48" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %</t>
+          <t>Уровень автоматизации; Cycle Time</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>1.9.3</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -5082,65 +5082,65 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Решение об оплате и проведение платежа</t>
+          <t>Оформление приказа на реализацию</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F49" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G49" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" s="25" t="n">
-        <v>3</v>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="I49" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K49" s="26" t="n">
+      <c r="J49" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="K49" s="27" t="n">
+        <v>5</v>
+      </c>
       <c r="L49" s="21" t="n">
-        <v>46</v>
-      </c>
-      <c r="M49" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>42</v>
+      </c>
+      <c r="M49" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N49" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Шаблонизация</t>
         </is>
       </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с Финблоком норматив срока от передачи реестра до проведения платежа</t>
+          <t>Свести устав и план в единую форму приказа на реализацию</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>1.9.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr">
         <is>
-          <t>Шаг выполняет Финблок, ДУП получает информацию о проведении платежа. Предметом договорённости является норматив срока: без него приоритизация реестра в волне 2 не доводится до результата.</t>
+          <t>Последний шаг комплекта 1.4, а не отдельный процесс. Исполняется, узких мест нет. Эффект — экономия времени на оформлении, поэтому шаг идёт вместе с типовым комплектом, а не раньше объектов с деньгами и сроками.</t>
         </is>
       </c>
       <c r="R49" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %</t>
+          <t>Cycle Time</t>
         </is>
       </c>
     </row>
@@ -5148,19 +5148,19 @@
       <c r="A50" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>2.3.2</t>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>Б.2</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>Планирование и решение по прогнозу</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>Финансовое закрытие проекта</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
@@ -5168,13 +5168,13 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F50" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G50" s="25" t="n">
-        <v>3</v>
+      <c r="F50" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="H50" s="20" t="n">
         <v>2</v>
@@ -5182,18 +5182,18 @@
       <c r="I50" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K50" s="26" t="n">
-        <v>1</v>
+      <c r="J50" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="L50" s="21" t="n">
-        <v>46</v>
-      </c>
-      <c r="M50" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>40</v>
+      </c>
+      <c r="M50" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N50" s="12" t="inlineStr">
@@ -5203,22 +5203,22 @@
       </c>
       <c r="O50" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с Финблоком срок возврата утверждённого прогноза в ДУП</t>
+          <t>Согласовать с Финблоком состав и срок пакета документов на закрытие проекта</t>
         </is>
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr">
         <is>
-          <t>Планирование и решение принимает Финблок. ДУП управляет здесь одним параметром — сроком получения утверждённого прогноза, без которого планирование работ на объектах ведётся вслепую.</t>
+          <t>Закрытие проекта выполняет Финблок, у ДУП здесь роль поставщика данных. Объект не создаёт ни срочности, ни денежного эффекта, поэтому берётся в конце: к этому моменту уже будет работать точка передачи 2.0, задающая, какие документы вообще накапливаются по проекту.</t>
         </is>
       </c>
       <c r="R50" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; Wait Time %</t>
+          <t>SLA Compliance %; On-Time %</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Б.5.2</t>
+          <t>Б.2.1</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Подготовка пакета документов и доверенностей</t>
+          <t>Служебная записка о необходимости закрытия</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Юр блок</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="F51" s="29" t="inlineStr">
@@ -5257,46 +5257,46 @@
       <c r="H51" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I51" s="26" t="n">
-        <v>1</v>
+      <c r="I51" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="J51" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="K51" s="20" t="n">
-        <v>2</v>
+      <c r="K51" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="L51" s="21" t="n">
-        <v>36</v>
-      </c>
-      <c r="M51" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>46</v>
+      </c>
+      <c r="M51" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N51" s="12" t="inlineStr">
         <is>
-          <t>SLA на стык с ЦО</t>
+          <t>Шаблонизация</t>
         </is>
       </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
-          <t>Согласовать с Юр блоком срок подготовки пакета документов и доверенностей</t>
+          <t>Ввести типовую форму служебной записки о закрытии проекта</t>
         </is>
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>Б.5.1</t>
+          <t>Б.2</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr">
         <is>
-          <t>Шаг исполняется Юр блоком и проблем не вызывает. Включается в общий регламент открытия филиала только для того, чтобы у сквозного маршрута не осталось участка без норматива срока.</t>
+          <t>Шаг выполняет ДУП, и он дёшев в исправлении, но повторяется несколько раз в год и ни на что не влияет до наступления самого закрытия. Типовая форма снимает переписку об уточнениях.</t>
         </is>
       </c>
       <c r="R51" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %</t>
+          <t>Cycle Time; First Pass Yield</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Организация поверки оборудования</t>
+          <t>Сопровождение канала связи</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
@@ -5329,23 +5329,23 @@
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G52" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="J52" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K52" s="20" t="n">
-        <v>2</v>
+      <c r="G52" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="L52" s="21" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="M52" s="32" t="inlineStr">
         <is>
@@ -5354,27 +5354,27 @@
       </c>
       <c r="N52" s="12" t="inlineStr">
         <is>
-          <t>Пересмотр экономики</t>
+          <t>Автоматизация</t>
         </is>
       </c>
       <c r="O52" s="12" t="inlineStr">
         <is>
-          <t>Рассчитать экономику собственной аккредитации против аутсорса поверки</t>
+          <t>Закрепить мониторинг канала связи в Zabbix и правило реакции на отказ</t>
         </is>
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1.1.3</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr">
         <is>
-          <t>Самый крупный денежный объект реестра: около 6 000 комплексов на поверке, методика устарела (узкое место 10), стоимость услуги растёт. Оптимизируется не порядок шагов, а модель оказания услуги, поэтому нужен расчёт и бюджетное решение. Берётся после того, как появится достоверная стоимость процесса по методу ABC — иначе сравнивать не с чем.</t>
+          <t>Объект исполняется, узких мест по нему не зафиксировано. Берётся в последней волне как часть ИТ-контура: дежурный мониторинг дешевле ручных проверок, но самостоятельной управленческой проблемы здесь нет.</t>
         </is>
       </c>
       <c r="R52" s="12" t="inlineStr">
         <is>
-          <t>Стоимость объекта; CPT; ROI автоматизации</t>
+          <t>Уровень автоматизации; Средний LOA; On-Time %</t>
         </is>
       </c>
     </row>
@@ -5384,75 +5384,75 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Разработка проектной документации (устав, план, приказ)</t>
+          <t>Утверждение бюджета, кредитование при необходимости</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F53" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G53" s="25" t="n">
-        <v>3</v>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F53" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="H53" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I53" s="20" t="n">
-        <v>2</v>
+      <c r="I53" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="J53" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="K53" s="19" t="n">
-        <v>4</v>
+      <c r="K53" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="L53" s="21" t="n">
-        <v>52</v>
-      </c>
-      <c r="M53" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+        <v>33</v>
+      </c>
+      <c r="M53" s="33" t="inlineStr">
+        <is>
+          <t>Вне очереди — наблюдение</t>
         </is>
       </c>
       <c r="N53" s="12" t="inlineStr">
         <is>
-          <t>Шаблонизация</t>
+          <t>Наблюдение — вмешательство не планируется</t>
         </is>
       </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>Утвердить типовой комплект: устав, план проекта, приказ</t>
+          <t>Отдельных действий не требуется — срок входит в SLA по объекту 1.5</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="Q53" s="12" t="inlineStr">
         <is>
-          <t>Объект исполняется, узких мест по нему не зафиксировано, поэтому в первых волнах он вытеснил бы более острые задачи. Берётся ради масштабируемости: типовой комплект сокращает подготовку документации и делает проекты сравнимыми между собой — без этого портфельная отчётность собирается вручную.</t>
+          <t>Решение принимает Финблок, ДУП только получает утверждённый бюджет. Оптимизировать нечего: единственный управляемый параметр — срок, и он фиксируется в SLA по родительскому объекту.</t>
         </is>
       </c>
       <c r="R53" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; Трудоёмкость объекта</t>
+          <t>On-Time %</t>
         </is>
       </c>
     </row>
@@ -5462,75 +5462,75 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>Б.2.2</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Разработка и поддержка методологии, шаблонов, реестров</t>
+          <t>Сбор актов сверок, уведомления о расторжении договоров</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F54" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G54" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K54" s="25" t="n">
-        <v>3</v>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F54" s="29" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G54" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="L54" s="21" t="n">
-        <v>52</v>
-      </c>
-      <c r="M54" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+        <v>20</v>
+      </c>
+      <c r="M54" s="33" t="inlineStr">
+        <is>
+          <t>Вне очереди — наблюдение</t>
         </is>
       </c>
       <c r="N54" s="12" t="inlineStr">
         <is>
-          <t>Устранение дублей и упрощение</t>
+          <t>Наблюдение — вмешательство не планируется</t>
         </is>
       </c>
       <c r="O54" s="12" t="inlineStr">
         <is>
-          <t>Актуализировать методологию: роли вместо фамилий, глоссарий, архивация устаревшего</t>
+          <t>Отдельных действий не требуется — данные предоставляются по запросу</t>
         </is>
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Б.2.1</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr">
         <is>
-          <t>В реестре методологии 434 документа, около 28% архива устарело, последняя правка — 2021 год. Задача не в переписывании, а в актуализации, и делать её имеет смысл тогда, когда новые регламенты волн 2 и 3 уже написаны — иначе методологию придётся актуализировать дважды.</t>
+          <t>Сбор актов сверок и уведомлений о расторжении ведут Финблок и Юр блок. ДУП предоставляет данные по запросу и ни срока, ни качества шага не определяет. Объект остаётся в реестре для полноты картины.</t>
         </is>
       </c>
       <c r="R54" s="12" t="inlineStr">
         <is>
-          <t>Паспорт процесса и карта SIPOC; CSAT internal</t>
+          <t>SLA Compliance %</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>1.1.3</t>
+          <t>Б.2.3</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -5550,708 +5550,162 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Регистрация проекта в портфеле / системе</t>
+          <t>Формирование бюджета на логистику / демонтаж, закрытие</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F55" s="30" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="G55" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="M55" s="33" t="inlineStr">
+        <is>
+          <t>Вне очереди — наблюдение</t>
+        </is>
+      </c>
+      <c r="N55" s="12" t="inlineStr">
+        <is>
+          <t>Наблюдение — вмешательство не планируется</t>
+        </is>
+      </c>
+      <c r="O55" s="12" t="inlineStr">
+        <is>
+          <t>Отдельных действий не требуется — подтверждение закрытия приходит из Финблока</t>
+        </is>
+      </c>
+      <c r="P55" s="12" t="inlineStr">
+        <is>
+          <t>Б.2.2</t>
+        </is>
+      </c>
+      <c r="Q55" s="12" t="inlineStr">
+        <is>
+          <t>Завершающий шаг целиком в периметре Финблока. Единственный интерес ДУП — получить подтверждение закрытия, чтобы снять проект с сопровождения; это обеспечивается точкой передачи, а не отдельной оптимизацией.</t>
+        </is>
+      </c>
+      <c r="R55" s="12" t="inlineStr">
+        <is>
+          <t>SLA Compliance %</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t>ДУП.0</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>Управление проектами (ГЧП / ГЗ)</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="F56" s="14" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G55" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I55" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K55" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L55" s="21" t="n">
-        <v>48</v>
-      </c>
-      <c r="M55" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="N55" s="12" t="inlineStr">
-        <is>
-          <t>Автоматизация</t>
-        </is>
-      </c>
-      <c r="O55" s="12" t="inlineStr">
-        <is>
-          <t>Определить обязательные поля карточки проекта в SimBASE и запретить регистрацию без них</t>
-        </is>
-      </c>
-      <c r="P55" s="12" t="inlineStr">
-        <is>
-          <t>1.1.2</t>
-        </is>
-      </c>
-      <c r="Q55" s="12" t="inlineStr">
-        <is>
-          <t>Ручная регистрация сама по себе потерь почти не создаёт, поэтому балл низкий. Но именно она задаёт единый идентификатор проекта, без которого метрики по портфелю нельзя собрать автоматически. Объект берётся не ради экономии, а как обязательный элемент единой карточки проекта.</t>
-        </is>
-      </c>
-      <c r="R55" s="12" t="inlineStr">
-        <is>
-          <t>Уровень автоматизации; Cycle Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="18" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>Оформление приказа на реализацию</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G56" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I56" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="L56" s="21" t="n">
-        <v>42</v>
-      </c>
-      <c r="M56" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K56" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L56" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="33" t="inlineStr">
+        <is>
+          <t>Не оценивается — агрегирующий уровень</t>
         </is>
       </c>
       <c r="N56" s="12" t="inlineStr">
         <is>
-          <t>Шаблонизация</t>
+          <t>Агрегирующий уровень</t>
         </is>
       </c>
       <c r="O56" s="12" t="inlineStr">
         <is>
-          <t>Свести документы проекта в единую форму приказа</t>
+          <t>Отдельных действий не требуется</t>
         </is>
       </c>
       <c r="P56" s="12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q56" s="12" t="inlineStr">
         <is>
-          <t>Объект исполняется, жалоб и узких мест по нему нет. Берётся последним из документарных задач: эффект ограничен экономией времени на оформлении, и браться за него раньше объектов с деньгами и сроками было бы неверно.</t>
+          <t>Корень дерева процессов: его результат складывается из блоков 1–4. Оптимизируется не сам по себе, а через входящие в него объекты, поэтому собственного места в очереди не занимает.</t>
         </is>
       </c>
       <c r="R56" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="18" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="23" t="inlineStr">
-        <is>
-          <t>Б.2</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="inlineStr">
-        <is>
-          <t>Финансовое закрытие проекта</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F57" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G57" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H57" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K57" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L57" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="M57" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="N57" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O57" s="12" t="inlineStr">
-        <is>
-          <t>Согласовать с Финблоком состав и срок пакета документов на закрытие проекта</t>
-        </is>
-      </c>
-      <c r="P57" s="12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="Q57" s="12" t="inlineStr">
-        <is>
-          <t>Закрытие проекта выполняет Финблок, у ДУП здесь роль поставщика данных. Объект не создаёт ни срочности, ни денежного эффекта, поэтому берётся в конце: к этому моменту уже будет работать точка передачи 2.0, задающая, какие документы вообще накапливаются по проекту.</t>
-        </is>
-      </c>
-      <c r="R57" s="12" t="inlineStr">
-        <is>
-          <t>SLA Compliance %; On-Time %</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="18" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>Б.2.1</t>
-        </is>
-      </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>Служебная записка о необходимости закрытия</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F58" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G58" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I58" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K58" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L58" s="21" t="n">
-        <v>46</v>
-      </c>
-      <c r="M58" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="N58" s="12" t="inlineStr">
-        <is>
-          <t>Шаблонизация</t>
-        </is>
-      </c>
-      <c r="O58" s="12" t="inlineStr">
-        <is>
-          <t>Ввести типовую форму служебной записки о закрытии проекта</t>
-        </is>
-      </c>
-      <c r="P58" s="12" t="inlineStr">
-        <is>
-          <t>Б.2</t>
-        </is>
-      </c>
-      <c r="Q58" s="12" t="inlineStr">
-        <is>
-          <t>Шаг выполняет ДУП, и он дёшев в исправлении, но повторяется несколько раз в год и ни на что не влияет до наступления самого закрытия. Типовая форма снимает переписку об уточнениях.</t>
-        </is>
-      </c>
-      <c r="R58" s="12" t="inlineStr">
-        <is>
-          <t>Cycle Time; First Pass Yield</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="18" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>Сопровождение канала связи</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G59" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K59" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L59" s="21" t="n">
-        <v>39</v>
-      </c>
-      <c r="M59" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="N59" s="12" t="inlineStr">
-        <is>
-          <t>Автоматизация</t>
-        </is>
-      </c>
-      <c r="O59" s="12" t="inlineStr">
-        <is>
-          <t>Закрепить мониторинг канала связи в Zabbix и правило реакции на отказ</t>
-        </is>
-      </c>
-      <c r="P59" s="12" t="inlineStr">
-        <is>
-          <t>1.1.3</t>
-        </is>
-      </c>
-      <c r="Q59" s="12" t="inlineStr">
-        <is>
-          <t>Объект исполняется, узких мест по нему не зафиксировано. Берётся в последней волне как часть ИТ-контура: дежурный мониторинг дешевле ручных проверок, но самостоятельной управленческой проблемы здесь нет.</t>
-        </is>
-      </c>
-      <c r="R59" s="12" t="inlineStr">
-        <is>
-          <t>Уровень автоматизации; Средний LOA; On-Time %</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="18" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>1.5.3</t>
-        </is>
-      </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>Утверждение бюджета, кредитование при необходимости</t>
-        </is>
-      </c>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F60" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G60" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H60" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I60" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K60" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" s="21" t="n">
-        <v>33</v>
-      </c>
-      <c r="M60" s="33" t="inlineStr">
-        <is>
-          <t>Вне очереди — наблюдение</t>
-        </is>
-      </c>
-      <c r="N60" s="12" t="inlineStr">
-        <is>
-          <t>Наблюдение — вмешательство не планируется</t>
-        </is>
-      </c>
-      <c r="O60" s="12" t="inlineStr">
-        <is>
-          <t>Отдельных действий не требуется — срок входит в SLA по объекту 1.5</t>
-        </is>
-      </c>
-      <c r="P60" s="12" t="inlineStr">
-        <is>
-          <t>1.5.2</t>
-        </is>
-      </c>
-      <c r="Q60" s="12" t="inlineStr">
-        <is>
-          <t>Решение принимает Финблок, ДУП только получает утверждённый бюджет. Оптимизировать нечего: единственный управляемый параметр — срок, и он фиксируется в SLA по родительскому объекту.</t>
-        </is>
-      </c>
-      <c r="R60" s="12" t="inlineStr">
-        <is>
-          <t>On-Time %</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="12" t="inlineStr">
-        <is>
-          <t>Б.2.2</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="inlineStr">
-        <is>
-          <t>Сбор актов сверок, уведомления о расторжении договоров</t>
-        </is>
-      </c>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F61" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G61" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I61" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="M61" s="33" t="inlineStr">
-        <is>
-          <t>Вне очереди — наблюдение</t>
-        </is>
-      </c>
-      <c r="N61" s="12" t="inlineStr">
-        <is>
-          <t>Наблюдение — вмешательство не планируется</t>
-        </is>
-      </c>
-      <c r="O61" s="12" t="inlineStr">
-        <is>
-          <t>Отдельных действий не требуется — данные предоставляются по запросу</t>
-        </is>
-      </c>
-      <c r="P61" s="12" t="inlineStr">
-        <is>
-          <t>Б.2.1</t>
-        </is>
-      </c>
-      <c r="Q61" s="12" t="inlineStr">
-        <is>
-          <t>Сбор актов сверок и уведомлений о расторжении ведут Финблок и Юр блок. ДУП предоставляет данные по запросу и ни срока, ни качества шага не определяет. Объект остаётся в реестре для полноты картины.</t>
-        </is>
-      </c>
-      <c r="R61" s="12" t="inlineStr">
-        <is>
-          <t>SLA Compliance %</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="18" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="12" t="inlineStr">
-        <is>
-          <t>Б.2.3</t>
-        </is>
-      </c>
-      <c r="C62" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
-        <is>
-          <t>Формирование бюджета на логистику / демонтаж, закрытие</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F62" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G62" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I62" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="21" t="n">
-        <v>24</v>
-      </c>
-      <c r="M62" s="33" t="inlineStr">
-        <is>
-          <t>Вне очереди — наблюдение</t>
-        </is>
-      </c>
-      <c r="N62" s="12" t="inlineStr">
-        <is>
-          <t>Наблюдение — вмешательство не планируется</t>
-        </is>
-      </c>
-      <c r="O62" s="12" t="inlineStr">
-        <is>
-          <t>Отдельных действий не требуется — подтверждение закрытия приходит из Финблока</t>
-        </is>
-      </c>
-      <c r="P62" s="12" t="inlineStr">
-        <is>
-          <t>Б.2.2</t>
-        </is>
-      </c>
-      <c r="Q62" s="12" t="inlineStr">
-        <is>
-          <t>Завершающий шаг целиком в периметре Финблока. Единственный интерес ДУП — получить подтверждение закрытия, чтобы снять проект с сопровождения; это обеспечивается точкой передачи, а не отдельной оптимизацией.</t>
-        </is>
-      </c>
-      <c r="R62" s="12" t="inlineStr">
-        <is>
-          <t>SLA Compliance %</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="18" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B63" s="23" t="inlineStr">
-        <is>
-          <t>ДУП.0</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D63" s="24" t="inlineStr">
-        <is>
-          <t>Управление проектами (ГЧП / ГЗ)</t>
-        </is>
-      </c>
-      <c r="E63" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F63" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G63" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J63" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K63" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L63" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M63" s="33" t="inlineStr">
-        <is>
-          <t>Не оценивается — агрегирующий уровень</t>
-        </is>
-      </c>
-      <c r="N63" s="12" t="inlineStr">
-        <is>
-          <t>Агрегирующий уровень</t>
-        </is>
-      </c>
-      <c r="O63" s="12" t="inlineStr">
-        <is>
-          <t>Отдельных действий не требуется</t>
-        </is>
-      </c>
-      <c r="P63" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q63" s="12" t="inlineStr">
-        <is>
-          <t>Корень дерева процессов: его результат складывается из блоков 1–4. Оптимизируется не сам по себе, а через входящие в него объекты, поэтому собственного места в очереди не занимает.</t>
-        </is>
-      </c>
-      <c r="R63" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R63"/>
+  <autoFilter ref="A1:R56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="2"/>
 </worksheet>
@@ -6349,16 +5803,16 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>2.0, 2, 1, 4, 4.2.1, 4.2</t>
+          <t>2.0, 2, 1, 4, 4.2</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Чек-лист передачи «реализация → сопровождение» (2.0): он описывает границу, общую для блоков 1 и 2, поэтому оба паспорта опираются на него. Параллельно и без единого согласования идёт пилотный аудит одного филиала по трём готовым чек-листам методологии (4.2.1)</t>
+          <t>Чек-лист передачи «реализация → сопровождение» (2.0): он описывает границу, общую для блоков 1 и 2, поэтому оба паспорта опираются на него. Параллельно и без единого согласования идёт пилотный аудит одного филиала по трём готовым чек-листам методологии — первый шаг объекта 4.2</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -6393,7 +5847,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>1.1, 1.1.2, 1.9, Б.6, 1.7.1, 2.3, 2.3.1, 2.7, 1.8, 1.1.1, 1.9.1, 1.9.2, 2.5, 2.6, 3, 3.2, Б.5.1, 3.1, 1.3, 3.3</t>
+          <t>1.1, 1.1.2, 1.9, 1.7.1, 2.3, 2.3.1, 2.7, 4.3, 4.3.1, 1.1.1, 1.9.1, 1.9.2, 2.5, 2.6, 4.3.2, 3, Б.5.1, 1.3, 4.3.3, 3.3</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -6429,11 +5883,11 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>1.7, Б.4, 1.2, 1.5, 1.5.1, Б.1, Б.3, 1.2.1, 1.2.2, 2.4, 1.7.2, 1.7.3, Б.7, 2.8, Б.5, 1.5.2, Б.10, Б.8, 4.3, Б.5.3, Б.9, 1.9.3, 2.3.2, Б.5.2</t>
+          <t>1.7, 1.2, 1.5, 1.5.1, 1.2.1, 2.4, 1.7.2, 1.7.3, Б.7, Б.5, 1.5.2, Б.10, Б.8, Б.5.3, Б.9, 1.9.3, 2.3.2, Б.5.2</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -6473,7 +5927,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>2.1, 1.4, 4.1, 1.1.3, 1.6, Б.2, Б.2.1, 2.2</t>
+          <t>2.1, 1.4, 4.1, 1.1.3, 1.4.1, Б.2, Б.2.1, 2.2</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -6572,13 +6026,13 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Паспорт процесса методологии (4) → регулярный аудит проектных данных (4.2)</t>
+          <t>Паспорт процесса методологии (4) → аудит проектных данных (4.2)</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Пилотный аудит (4.2.1) не ждёт ничего и даёт базовую линию. Регулярный аудит по всему портфелю имеет смысл только тогда, когда его результат влечёт последствия: право остановить проект по итогам аудита фиксируется в положении о контроле качества вместе с паспортом процесса методологии.</t>
+          <t>Пилот одного филиала и регулярный аудит — один объект. Пилот даёт базовую линию и не ждёт согласований. Развёртывание на портфель имеет смысл, когда результат аудита влечёт последствия: право остановить проект фиксируется в положении о контроле качества вместе с паспортом процесса методологии.</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -6587,7 +6041,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Базовая линия (4.2.1) → доказательство эффекта</t>
+          <t>Базовая линия (4.2) → доказательство эффекта</t>
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
@@ -6617,13 +6071,13 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Регламент статус-встреч (1.8) → разведение отчётности (2.8, 4.3)</t>
+          <t>Регламент отчётности (4.3) → этапы 4.3.1, 4.3.2, 4.3.3</t>
         </is>
       </c>
       <c r="B17" s="12" t="n"/>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Сначала определяется проектный уровень отчётности, затем операционный и портфельный собираются из него без повторного сбора данных.</t>
+          <t>Сначала один регламент, затем проектный статус, из него операционный, из обоих — портфель. Повторного сбора данных нет.</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -6632,13 +6086,13 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Чек-лист приёмки (1.1) → письмо в ДРБ (Б.6)</t>
+          <t>Чек-лист приёмки (1.1) → письмо в ДРБ</t>
         </is>
       </c>
       <c r="B18" s="12" t="n"/>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Требовать норматив срока от смежного подразделения имеет смысл тогда, когда собственная процедура приёмки уже описана и исполняется.</t>
+          <t>Письмо о сроке передачи — часть того же объекта 1.1, а не отдельный процесс. Требовать норматив от ДРБ имеет смысл, когда собственный чек-лист уже описан.</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -6647,7 +6101,7 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Своя часть (3.2) → сквозной маршрут открытия филиала (Б.5)</t>
+          <t>Участок ДУП (Б.5.1) → сквозной маршрут открытия филиала (Б.5)</t>
         </is>
       </c>
       <c r="B19" s="12" t="n"/>
@@ -6781,7 +6235,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -6956,7 +6410,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>3.1, 1.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -6991,7 +6445,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>1.1, 1.1.1, 1.1.2, Б.6</t>
+          <t>1.1, 1.1.1, 1.1.2</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -7061,7 +6515,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>4.3, 4.3.1</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -7170,7 +6624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7222,16 +6676,16 @@
       <c r="B6" s="12" t="n"/>
       <c r="C6" s="28" t="inlineStr">
         <is>
-          <t>Быстрые победы — 13
-2.0, 2, 1, 4, 1.1, 1.1.2, 1.7.1, 2.3.1, 1.8, 1.1.1, 1.9.1, 1.9.2, 2.5</t>
+          <t>Быстрые победы — 14
+2.0, 2, 1, 4, 1.1, 1.1.2, 1.7.1, 2.3.1, 4.3, 4.3.1, 1.1.1, 1.9.1, 1.9.2, 2.5</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="12" t="n"/>
       <c r="F6" s="31" t="inlineStr">
         <is>
-          <t>Крупные проекты — 18
-1.9, Б.6, 2.3, 2.7, 1.7, Б.4, 1.2, 1.5, 1.5.1, Б.1, Б.3, 1.2.1, 1.2.2, 2.4, 1.7.2, 1.7.3, Б.7, 2.1</t>
+          <t>Крупные проекты — 13
+1.9, 2.3, 2.7, 1.7, 1.2, 1.5, 1.5.1, 1.2.1, 2.4, 1.7.2, 1.7.3, Б.7, 2.1</t>
         </is>
       </c>
       <c r="G6" s="12" t="n"/>
@@ -7245,8 +6699,8 @@
       <c r="B7" s="12" t="n"/>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>Заполнители — 15
-4.2.1, 4.2, 2.6, 3, 3.2, Б.5.1, 3.1, 1.3, 3.3, 2.8, 4.3, 1.4, 1.1.3, 1.6, Б.2.1</t>
+          <t>Заполнители — 12
+4.2, 2.6, 4.3.2, 3, Б.5.1, 1.3, 4.3.3, 3.3, 1.4, 1.1.3, 1.4.1, Б.2.1</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -7449,16 +6903,16 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Б.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Закупки выше упрощённого порога</t>
+          <t>Подтверждение готовности продукта (пилот)</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>91.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>2</v>
@@ -7474,49 +6928,49 @@
         </is>
       </c>
       <c r="G19" s="11" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Подтверждение готовности продукта (пилот)</t>
+          <t>Приём и валидация пакета документов от ДРБ</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>90.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
-        </is>
-      </c>
-      <c r="F20" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>4</v>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G20" s="11" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.9.2</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Приём и валидация пакета документов от ДРБ</t>
+          <t>Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
@@ -7542,23 +6996,23 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>1.9.2</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
+          <t>Формирование реестра платежей и приоритизация</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
         <v>87.09999999999999</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="28" t="inlineStr">
-        <is>
-          <t>Быстрые победы</t>
+        <v>3</v>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>Крупные проекты</t>
         </is>
       </c>
       <c r="F22" s="28" t="inlineStr">
@@ -7567,18 +7021,18 @@
         </is>
       </c>
       <c r="G22" s="11" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Формирование реестра платежей и приоритизация</t>
+          <t>Формирование ФЭМ по шаблону</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
@@ -7592,9 +7046,9 @@
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G23" s="11" t="n">
@@ -7604,12 +7058,12 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Б.6</t>
+          <t>1.7.3</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Передача проекта от ДРБ в ДУП</t>
+          <t>Контроль сроков поставки и приёмка</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
@@ -7623,9 +7077,9 @@
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G24" s="11" t="n">
@@ -7635,19 +7089,19 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Формирование ФЭМ по шаблону</t>
+          <t>Формирование и согласование бюджета (ФЭМ)</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
         <v>87.09999999999999</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
@@ -7660,118 +7114,118 @@
         </is>
       </c>
       <c r="G25" s="11" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>1.7.3</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Контроль сроков поставки и приёмка</t>
+          <t>Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>87.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
-        </is>
-      </c>
-      <c r="F26" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>5</v>
+      </c>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы</t>
+        </is>
+      </c>
+      <c r="F26" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G26" s="11" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Формирование и согласование бюджета (ФЭМ)</t>
+          <t>Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>87.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
-        </is>
-      </c>
-      <c r="F27" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>4</v>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы</t>
+        </is>
+      </c>
+      <c r="F27" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G27" s="11" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Б.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Согласование бюджета проекта / ФЭМ</t>
+          <t>Прогноз поступлений / расходов и контроль бюджета</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>87.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F28" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F28" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G28" s="11" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.7.2</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Подписание gate «продукт готов к реализации»</t>
+          <t>Проведение процедуры закупки</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>85.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
@@ -7784,29 +7238,29 @@
         </is>
       </c>
       <c r="G29" s="11" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
+          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>82.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E30" s="28" t="inlineStr">
-        <is>
-          <t>Быстрые победы</t>
+        <v>3</v>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>Крупные проекты</t>
         </is>
       </c>
       <c r="F30" s="28" t="inlineStr">
@@ -7815,22 +7269,22 @@
         </is>
       </c>
       <c r="G30" s="11" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
+          <t>Сбор данных и подтверждений по проектам</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>82.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>4</v>
@@ -7846,22 +7300,22 @@
         </is>
       </c>
       <c r="G31" s="11" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Прогноз поступлений / расходов и контроль бюджета</t>
+          <t>Проверка завершения пилота / тестовой эксплуатации</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>75.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>3</v>
@@ -7871,31 +7325,31 @@
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F32" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G32" s="11" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Б.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Прогноз поступлений и расходов</t>
+          <t>Инициация продления / модернизации контракта</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>75.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="31" t="inlineStr">
         <is>
@@ -7908,60 +7362,60 @@
         </is>
       </c>
       <c r="G33" s="11" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>1.7.2</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Проведение процедуры закупки</t>
+          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>75.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
-        </is>
-      </c>
-      <c r="F34" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>4</v>
+      </c>
+      <c r="E34" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы</t>
+        </is>
+      </c>
+      <c r="F34" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G34" s="11" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>1.9.1</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
+          <t>Агрегация заявок и данных филиалов</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>74.09999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
+        <v>4</v>
+      </c>
+      <c r="E35" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы</t>
         </is>
       </c>
       <c r="F35" s="28" t="inlineStr">
@@ -7970,25 +7424,25 @@
         </is>
       </c>
       <c r="G35" s="11" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Сбор данных и подтверждений по проектам</t>
+          <t>Отчётность по проектам</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>70.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="28" t="inlineStr">
         <is>
@@ -8001,115 +7455,115 @@
         </is>
       </c>
       <c r="G36" s="11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Проверка завершения пилота / тестовой эксплуатации</t>
+          <t>Статус-встречи по проекту</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>70.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
-        </is>
-      </c>
-      <c r="F37" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>5</v>
+      </c>
+      <c r="E37" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы</t>
+        </is>
+      </c>
+      <c r="F37" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G37" s="11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Инициация продления / модернизации контракта</t>
+          <t>Постпроектное сопровождение</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>70.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
-        </is>
-      </c>
-      <c r="F38" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>4</v>
+      </c>
+      <c r="E38" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="G38" s="11" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>1.1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
+          <t>Организация поверки оборудования</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>67.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" s="28" t="inlineStr">
-        <is>
-          <t>Быстрые победы</t>
-        </is>
-      </c>
-      <c r="F39" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        <v>2</v>
+      </c>
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>Крупные проекты</t>
+        </is>
+      </c>
+      <c r="F39" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G39" s="11" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>1.9.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Агрегация заявок и данных филиалов</t>
+          <t>Обработка запросов на перенос оборудования</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>67.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>4</v>
@@ -8125,53 +7579,53 @@
         </is>
       </c>
       <c r="G40" s="11" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Управление сроками и бюджетом проекта (статус-встречи)</t>
+          <t>Передача проекта «реализация → сопровождение»</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>65.90000000000001</v>
+        <v>61.2</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" s="28" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F41" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="G41" s="11" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Постпроектное сопровождение</t>
+          <t>Реализация проекта</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>65.90000000000001</v>
+        <v>61.2</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>4</v>
@@ -8187,184 +7641,184 @@
         </is>
       </c>
       <c r="G42" s="11" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Организация поверки оборудования</t>
+          <t>Методология и контроль качества (ПМО)</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>64.7</v>
+        <v>61.2</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
-        </is>
-      </c>
-      <c r="F43" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+        <v>4</v>
+      </c>
+      <c r="E43" s="28" t="inlineStr">
+        <is>
+          <t>Быстрые победы</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="G43" s="11" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>Б.7</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Обработка запросов на перенос оборудования</t>
+          <t>Производство, монтаж и калибровка оборудования</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>63.5</v>
+        <v>60</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" s="28" t="inlineStr">
-        <is>
-          <t>Быстрые победы</t>
-        </is>
-      </c>
-      <c r="F44" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        <v>2</v>
+      </c>
+      <c r="E44" s="31" t="inlineStr">
+        <is>
+          <t>Крупные проекты</t>
+        </is>
+      </c>
+      <c r="F44" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G44" s="11" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Б.5</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Передача проекта «реализация → сопровождение»</t>
+          <t>Открытие нового филиала</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>61.2</v>
+        <v>58.8</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="28" t="inlineStr">
-        <is>
-          <t>Быстрые победы</t>
-        </is>
-      </c>
-      <c r="F45" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+        <v>2</v>
+      </c>
+      <c r="E45" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="F45" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G45" s="11" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Реализация проекта</t>
+          <t>Выявление нехватки бюджета и вынесение на ОСУ</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>61.2</v>
+        <v>55.3</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E46" s="28" t="inlineStr">
-        <is>
-          <t>Быстрые победы</t>
-        </is>
-      </c>
-      <c r="F46" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+      <c r="E46" s="36" t="inlineStr">
+        <is>
+          <t>Заполнители</t>
+        </is>
+      </c>
+      <c r="F46" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G46" s="11" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Б.5.1</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Методология и контроль качества (ПМО)</t>
+          <t>Участие ДУП: потребность, данные по региону, приём площадки</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>61.2</v>
+        <v>55.3</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E47" s="28" t="inlineStr">
-        <is>
-          <t>Быстрые победы</t>
-        </is>
-      </c>
-      <c r="F47" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+      <c r="E47" s="36" t="inlineStr">
+        <is>
+          <t>Заполнители</t>
+        </is>
+      </c>
+      <c r="F47" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G47" s="11" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Б.7</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Производство, монтаж и калибровка оборудования</t>
+          <t>Проверка и согласование ФЭМ</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>60</v>
+        <v>55.3</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="31" t="inlineStr">
-        <is>
-          <t>Крупные проекты</t>
+      <c r="E48" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
         </is>
       </c>
       <c r="F48" s="31" t="inlineStr">
@@ -8373,65 +7827,65 @@
         </is>
       </c>
       <c r="G48" s="11" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>Б.10</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Участие ДУП в открытии нового филиала</t>
+          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>58.8</v>
+        <v>55.3</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F49" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        <v>2</v>
+      </c>
+      <c r="E49" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="F49" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G49" s="11" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Б.5</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Открытие нового филиала</t>
+          <t>Операционный статус руководству и госпартнёру</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>58.8</v>
+        <v>51.8</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F50" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>4</v>
+      </c>
+      <c r="E50" s="36" t="inlineStr">
+        <is>
+          <t>Заполнители</t>
+        </is>
+      </c>
+      <c r="F50" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G50" s="11" t="n">
@@ -8441,47 +7895,47 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>Б.8</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Выявление нехватки бюджета и вынесение на ОСУ</t>
+          <t>Юридическое сопровождение договоров с контрагентами</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>55.3</v>
+        <v>51.8</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F51" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        <v>3</v>
+      </c>
+      <c r="E51" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="F51" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G51" s="11" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Б.5.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Инициирование, участие в сборе данных</t>
+          <t>Управление филиальной сетью</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>55.3</v>
+        <v>50.6</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>4</v>
@@ -8497,25 +7951,25 @@
         </is>
       </c>
       <c r="G52" s="11" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>Б.5.3</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Проверка и согласование ФЭМ</t>
+          <t>Регистрация и запуск филиала</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>55.3</v>
+        <v>50.6</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" s="33" t="inlineStr">
         <is>
@@ -8528,25 +7982,25 @@
         </is>
       </c>
       <c r="G53" s="11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>Б.10</t>
+          <t>Б.9</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
+          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>55.3</v>
+        <v>50.6</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" s="33" t="inlineStr">
         <is>
@@ -8559,56 +8013,56 @@
         </is>
       </c>
       <c r="G54" s="11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Отчётность руководству и госпартнёру (операционный статус)</t>
+          <t>Разработка и поддержка методологии, шаблонов, реестров</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>51.8</v>
+        <v>50.6</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E55" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F55" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>3</v>
+      </c>
+      <c r="E55" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="F55" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G55" s="11" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>Б.8</t>
+          <t>1.9.3</t>
         </is>
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>Юридическое сопровождение договоров с контрагентами</t>
+          <t>Решение об оплате и проведение платежа</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>51.8</v>
+        <v>50.6</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" s="33" t="inlineStr">
         <is>
@@ -8621,96 +8075,96 @@
         </is>
       </c>
       <c r="G56" s="11" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.3.2</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Управление филиальной сетью</t>
+          <t>Планирование и решение по прогнозу</t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
         <v>50.6</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F57" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        <v>1</v>
+      </c>
+      <c r="E57" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="F57" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G57" s="11" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>Б.5.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>Регистрация и запуск филиала</t>
+          <t>Контроль качества и полноты проектных данных</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>50.6</v>
+        <v>49.4</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E58" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F58" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>5</v>
+      </c>
+      <c r="E58" s="36" t="inlineStr">
+        <is>
+          <t>Заполнители</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Паспорта и базовая линия</t>
         </is>
       </c>
       <c r="G58" s="11" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Б.9</t>
+          <t>4.3.3</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
+          <t>Портфельная отчётность руководству и заказчикам</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>50.6</v>
+        <v>47.1</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E59" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F59" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>4</v>
+      </c>
+      <c r="E59" s="36" t="inlineStr">
+        <is>
+          <t>Заполнители</t>
+        </is>
+      </c>
+      <c r="F59" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G59" s="11" t="n">
@@ -8720,23 +8174,23 @@
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>Разработка и поддержка методологии, шаблонов, реестров</t>
+          <t>Разработка проектной документации (устав, план, приказ)</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>50.6</v>
+        <v>47.1</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E60" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
+        <v>4</v>
+      </c>
+      <c r="E60" s="36" t="inlineStr">
+        <is>
+          <t>Заполнители</t>
         </is>
       </c>
       <c r="F60" s="32" t="inlineStr">
@@ -8751,233 +8205,233 @@
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>1.9.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Решение об оплате и проведение платежа</t>
+          <t>Назначение куратора (проект и филиал)</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>50.6</v>
+        <v>45.9</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F61" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>5</v>
+      </c>
+      <c r="E61" s="36" t="inlineStr">
+        <is>
+          <t>Заполнители</t>
+        </is>
+      </c>
+      <c r="F61" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G61" s="11" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>1.1.3</t>
         </is>
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>Планирование и решение по прогнозу</t>
+          <t>Регистрация проекта в портфеле / системе</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
-        <v>50.6</v>
+        <v>42.4</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F62" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>4</v>
+      </c>
+      <c r="E62" s="36" t="inlineStr">
+        <is>
+          <t>Заполнители</t>
+        </is>
+      </c>
+      <c r="F62" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G62" s="11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>Б.2.1</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Аудит проектной документации по чек-листам</t>
+          <t>Служебная записка о необходимости закрытия</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>49.4</v>
+        <v>40</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E63" s="36" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F63" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+      <c r="F63" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G63" s="11" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>Б.2</t>
         </is>
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>Контроль качества и полноты проектных данных</t>
+          <t>Финансовое закрытие проекта</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>49.4</v>
+        <v>40</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E64" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F64" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+        <v>2</v>
+      </c>
+      <c r="E64" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="F64" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G64" s="11" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Портфельная отчётность руководству и заказчикам</t>
+          <t>Сопровождение канала связи</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>47.1</v>
+        <v>35.3</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F65" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+        <v>3</v>
+      </c>
+      <c r="E65" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="F65" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G65" s="11" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>Б.5.2</t>
         </is>
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>Разработка проектной документации (устав, план, приказ)</t>
+          <t>Подготовка пакета документов и доверенностей</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>47.1</v>
+        <v>35.3</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E66" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F66" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+        <v>2</v>
+      </c>
+      <c r="E66" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="F66" s="31" t="inlineStr">
+        <is>
+          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G66" s="11" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Назначение куратора на филиал / проект</t>
+          <t>Утверждение бюджета, кредитование при необходимости</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>45.9</v>
+        <v>35.3</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E67" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F67" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+        <v>1</v>
+      </c>
+      <c r="E67" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="F67" s="33" t="inlineStr">
+        <is>
+          <t>Вне очереди — наблюдение</t>
         </is>
       </c>
       <c r="G67" s="11" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>Назначение ответственного (куратор / филиал)</t>
+          <t>Оформление приказа на реализацию</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>45.9</v>
+        <v>31.8</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>5</v>
@@ -8987,322 +8441,105 @@
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F68" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>Волна 4. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G68" s="11" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>1.1.3</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Регистрация проекта в портфеле / системе</t>
+          <t>Общие отношения с филиалом (вне привязки к проекту)</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>42.4</v>
+        <v>30.6</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E69" s="36" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="F69" s="28" t="inlineStr">
+        <is>
+          <t>Волна 2. Быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="G69" s="11" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>Б.2.1</t>
+          <t>Б.2.3</t>
         </is>
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>Служебная записка о необходимости закрытия</t>
+          <t>Формирование бюджета на логистику / демонтаж, закрытие</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>40</v>
+        <v>24.7</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E70" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+        <v>1</v>
+      </c>
+      <c r="E70" s="33" t="inlineStr">
+        <is>
+          <t>Отложить</t>
+        </is>
+      </c>
+      <c r="F70" s="33" t="inlineStr">
+        <is>
+          <t>Вне очереди — наблюдение</t>
         </is>
       </c>
       <c r="G70" s="11" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>Б.2</t>
+          <t>Б.2.2</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Финансовое закрытие проекта</t>
+          <t>Сбор актов сверок, уведомления о расторжении договоров</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="33" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="F71" s="33" t="inlineStr">
+        <is>
+          <t>Вне очереди — наблюдение</t>
         </is>
       </c>
       <c r="G71" s="11" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="B72" s="12" t="inlineStr">
-        <is>
-          <t>Сопровождение канала связи</t>
-        </is>
-      </c>
-      <c r="C72" s="11" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="D72" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E72" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="G72" s="11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t>Б.5.2</t>
-        </is>
-      </c>
-      <c r="B73" s="12" t="inlineStr">
-        <is>
-          <t>Подготовка пакета документов и доверенностей</t>
-        </is>
-      </c>
-      <c r="C73" s="11" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="D73" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="G73" s="11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t>1.5.3</t>
-        </is>
-      </c>
-      <c r="B74" s="12" t="inlineStr">
-        <is>
-          <t>Утверждение бюджета, кредитование при необходимости</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="D74" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F74" s="33" t="inlineStr">
-        <is>
-          <t>Вне очереди — наблюдение</t>
-        </is>
-      </c>
-      <c r="G74" s="11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="12" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="B75" s="12" t="inlineStr">
-        <is>
-          <t>Оформление приказа на реализацию</t>
-        </is>
-      </c>
-      <c r="C75" s="11" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D75" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E75" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="G75" s="11" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>Общие отношения с филиалом (вне привязки к проекту)</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="D76" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E76" s="36" t="inlineStr">
-        <is>
-          <t>Заполнители</t>
-        </is>
-      </c>
-      <c r="F76" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="G76" s="11" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="12" t="inlineStr">
-        <is>
-          <t>Б.2.3</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>Формирование бюджета на логистику / демонтаж, закрытие</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="D77" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F77" s="33" t="inlineStr">
-        <is>
-          <t>Вне очереди — наблюдение</t>
-        </is>
-      </c>
-      <c r="G77" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="inlineStr">
-        <is>
-          <t>Б.2.2</t>
-        </is>
-      </c>
-      <c r="B78" s="12" t="inlineStr">
-        <is>
-          <t>Сбор актов сверок, уведомления о расторжении договоров</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="D78" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="33" t="inlineStr">
-        <is>
-          <t>Отложить</t>
-        </is>
-      </c>
-      <c r="F78" s="33" t="inlineStr">
-        <is>
-          <t>Вне очереди — наблюдение</t>
-        </is>
-      </c>
-      <c r="G78" s="11" t="n">
         <v>20</v>
       </c>
     </row>

--- a/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
+++ b/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
@@ -69,7 +69,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -108,11 +108,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
@@ -123,17 +118,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDF1F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00CFE0F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE3B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF1F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,67 +192,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -632,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -980,13 +969,13 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Паспорт процесса раньше оптимизации его шагов</t>
+          <t>Паспорт не держит очередь быстрых побед</t>
         </is>
       </c>
       <c r="B16" s="12" t="n"/>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Владение закреплено по критериям Таблицы 5 Методики, стоп-факторов для старта нет. Но глава 8 и Приложение №2 делают паспорт процесса обязательным атрибутом: границы, вход, выход, владелец и показатели. Пока паспорта нет, улучшение отдельных шагов не с чем сверять — неизвестно, где процесс начинается и по какому показателю он стал лучше. Поэтому сквозные объекты верхнего уровня (1, 2, 4) и описание границы между ними (2.0) выходят в работу первыми независимо от балла.</t>
+          <t>Владение закреплено по критериям Таблицы 5 Методики, стоп-факторов для старта нет. Глава 8 и Приложение №2 делают паспорт обязательным атрибутом: границы, вход, выход, владелец и показатели. Паспорт пишется в волне запуска, но отсутствие готового документа не блокирует чек-лист или регламент, который ДУП утверждает сам. Объекты 1, 2, 4 и 2.0 стоят в этой волне на месте, которое им даёт балл.</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -994,13 +983,13 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Базовая линия раньше улучшений</t>
+          <t>Базовая линия измеряет эффект и не держит старт</t>
         </is>
       </c>
       <c r="B17" s="12" t="n"/>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Аудит проектных данных имеет невысокий балл, но идёт в первой волне: пока не снят замер, эффект последующих вмешательств будет предметом спора, а не расчёта (п. 176 — показатели без источника данных не учитываются).</t>
+          <t>Аудит проектных данных остаётся в волне запуска: пока не снят замер, эффект вмешательств будет предметом спора, а не расчёта (п. 176 — показатель без источника данных не учитывается). Снимать его нужно, но остальные объекты волны не ждут отчёта пилота и занимают место по баллу.</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1080,20 +1069,20 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Фазы 0–1 дорожной карты</t>
+          <t>Старт программы</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Паспорта сквозных процессов и замер «до»</t>
+          <t>Паспорта, замер «до» и быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="E24" s="12" t="n"/>
@@ -1101,20 +1090,20 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Фаза 2 дорожной карты</t>
+          <t>Стыки с центральным офисом</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Восстановить исполнение там, где ДУП решает в одиночку</t>
+          <t>Договориться о стыках и спроектировать то, чего нет</t>
         </is>
       </c>
       <c r="E25" s="12" t="n"/>
@@ -1122,20 +1111,20 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Фаза 3 дорожной карты</t>
+          <t>Масштаб программы</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Договориться о стыках и спроектировать то, чего нет</t>
+          <t>Пересмотреть экономику и закрепить результат в системах</t>
         </is>
       </c>
       <c r="E26" s="12" t="n"/>
@@ -1143,110 +1132,89 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+          <t>Вне очереди — наблюдение</t>
         </is>
       </c>
       <c r="B27" s="11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Фаза 4 дорожной карты</t>
+          <t>Вне периметра работ</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Пересмотреть экономику и закрепить результат в системах</t>
+          <t>Держать под наблюдением, в очередь не ставить</t>
         </is>
       </c>
       <c r="E27" s="12" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Вне очереди — наблюдение</t>
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Не оценивается — агрегирующий уровень</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Вне периметра работ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Держать под наблюдением, в очередь не ставить</t>
+          <t>Корень дерева процессов</t>
         </is>
       </c>
       <c r="E28" s="12" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Не оценивается — агрегирующий уровень</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Корень дерева процессов</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Как пользоваться файлом</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>1. «Приоритеты» — основной лист. Строки уже стоят в порядке работ: сначала волна. Внутри волны 1 — строго по убыванию балла. В волнах 2 и 3 — по убыванию балла, но не раньше предшественников. Сортировка по колонке «Итоговый балл» даёт чистый рейтинг ценности без учёта волны.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1. «Приоритеты» — основной лист. Строки уже стоят в порядке работ: сначала волна, внутри волны — по убыванию балла, но не раньше предшественников. Сортировка по колонке «Итоговый балл» даёт чистый рейтинг ценности без учёта зависимостей.</t>
+          <t>2. «Порядок работ» — что делает каждая волна, с чего она начинается и по какому критерию считается завершённой.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2. «Порядок работ» — что делает каждая волна, с чего она начинается и по какому критерию считается завершённой.</t>
+          <t>3. «Первые 11 шагов» — конкретная программа старта: действие, объекты, ответственный, результат и причина, по которой шаг стоит именно на этом месте.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>3. «Первые 11 шагов» — конкретная программа старта: действие, объекты, ответственный, результат и причина, по которой шаг стоит именно на этом месте.</t>
+          <t>4. «Матрица ценность — лёгкость» — тот же реестр в координатах «что это даёт» и «чего это стоит»; помогает объяснить выбор на управляющем комитете.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>4. «Матрица ценность — лёгкость» — тот же реестр в координатах «что это даёт» и «чего это стоит»; помогает объяснить выбор на управляющем комитете.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
           <t>5. Колонка «Чем подтвердим эффект» называет метрики из файла «ДУП_метрики_процессов.xlsx» — по ним снимается замер до и после вмешательства.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="25">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C20:D20"/>
@@ -1260,6 +1228,7 @@
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A31:I31"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="C17:D17"/>
@@ -1267,8 +1236,6 @@
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A36:I36"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="C18:D18"/>
@@ -1401,1459 +1368,1459 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="17" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Приём и валидация пакета документов от ДРБ</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>ДУП и ДРБ</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" s="21" t="n">
+        <v>86</v>
+      </c>
+      <c r="M2" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O2" s="12" t="inlineStr">
+        <is>
+          <t>Утвердить чек-лист минимального пакета и правило возврата неполного комплекта</t>
+        </is>
+      </c>
+      <c r="P2" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q2" s="12" t="inlineStr">
+        <is>
+          <t>Первый объект цепочки: дефект пакета на входе проявляется на всех последующих подпроцессах — от ФЭМ до закупок и приёмки. Минимальный состав пакета не зафиксирован письменно (узкие места 1 и 4), поэтому старт проекта растягивается на доуточнения. Исправляется одним чек-листом и одним письмом в ДРБ — это лучшее соотношение эффекта к усилию во всём реестре.</t>
+        </is>
+      </c>
+      <c r="R2" s="12" t="inlineStr">
+        <is>
+          <t>Cycle Time; On-Time %; Defect Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>1.9.2</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" s="21" t="n">
+        <v>86</v>
+      </c>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>Описать правило очерёдности: какой платёж попадает в начало реестра и почему</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>1.9.1</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>Ядро узких мест 6 и 7: правила, по которому платёж попадает в начало или в конец реестра, не существует, поэтому очередность определяется телефонным звонком. Формализация умещается на одну страницу, а эффект измеряется днями просрочки перед подрядчиками.</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Wait Time %; COPQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>1.1.2</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="M4" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>Ввести обязательную проверку по чек-листу до регистрации проекта в портфеле</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>Самый дешёвый контроль во всей цепочке: проверка по чек-листу занимает часы и отсекает дефект до того, как он превратится в неверный ФЭМ и неверную спецификацию закупки. Процессом владеет ДУП, поэтому внешних согласований не требуется вовсе.</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>Defect Rate; First Pass Yield; Rework Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Формирование реестра платежей и приоритизация</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="21" t="n">
+        <v>83</v>
+      </c>
+      <c r="M5" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>Утвердить инструкцию по трём потокам платежей и единую форму реестра</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>Три потока платежей (ВУ / КИЗ / КОЗ) не формализованы, единой инструкции нет (узкие места 6 и 7). Задержка оплаты останавливает монтаж, то есть деньги и срок здесь связаны напрямую. Инструкция пишется внутри ДУП, от Финблока нужен только календарь приёма реестра — поэтому объект попадает в волну быстрых побед.</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Cycle Time; COPQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>1.7.1</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="21" t="n">
+        <v>82</v>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>Ввести форму заявки и правило: тех. карты СТ собираются до подачи заявки</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>1.1.2</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>Этот шаг целиком внутри ДУП: полнота заявки и наличие тех. карт определяют, сколько раз процедура вернётся на доработку. Его можно исправить, не дожидаясь договорённостей с Закупщиками, поэтому он остаётся в волне 1 отдельно от остальной части объекта 1.7.</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>First Pass Yield; Rework Rate; Defect Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Прогноз поступлений / расходов и контроль бюджета</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="21" t="n">
+        <v>73</v>
+      </c>
+      <c r="M7" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>Завести единый реестр прогноза и календарь его обновления</t>
+        </is>
+      </c>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q7" s="12" t="inlineStr">
+        <is>
+          <t>Прогноз ведётся в чатах и ad-hoc (узкие места 6 и 7), из-за чего компания узнаёт о разрыве поступлений позже, чем могла бы. Реестр и календарь — инструменты внутри ДУП: от Финблока нужна только форма выгрузки. Это делает объект исполнимым в волне 1. Встречный срок Финблока фиксируется отдельно, на этапе 2.3.2.</t>
+        </is>
+      </c>
+      <c r="R7" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Budget Variance; Cycle Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>2.3.1</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Сбор данных и подтверждений по проектам</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="M8" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>Утвердить форму и срок подачи данных филиалами в реестр прогноза</t>
+        </is>
+      </c>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="Q8" s="12" t="inlineStr">
+        <is>
+          <t>Шаг, который ДУП выполняет сам и который определяет достоверность всего прогноза. Отсутствие формы и срока — причина того, что данные приходят разрозненно и требуют ручной сверки.</t>
+        </is>
+      </c>
+      <c r="R8" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; First Pass Yield; Defect Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>Утвердить форму фиксации дефекта и маршрут «эксплуатация → владелец ТЗ → закупки»</t>
+        </is>
+      </c>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q9" s="12" t="inlineStr">
+        <is>
+          <t>Ущерб уже реализовался: кейс с хомутами показал, что сведения о дефекте компонента из эксплуатации не доходят до владельца технического задания и повторяются в следующей закупке (узкое место 9). Владелец закреплён за замом по операционной деятельности — тем, кто дефект обнаруживает и несёт потери от его повторения. Осталось описать маршрут: фиксация дефекта делается внутри ДУП, встречный срок реакции СТ фиксируется в волне 2 через объект Б.7.</t>
+        </is>
+      </c>
+      <c r="R9" s="12" t="inlineStr">
+        <is>
+          <t>COPQ; Defect Rate; Rework Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Отчётность по проектам</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="M10" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N10" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>Утвердить один регламент отчётности: проект, операция, портфель</t>
+        </is>
+      </c>
+      <c r="P10" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q10" s="12" t="inlineStr">
+        <is>
+          <t>Три отчёта собирались отдельно и описывали одни и те же данные. Один регламент внутри ДУП задаёт частоту, адресата и запрет повторного сбора. Самое дешёвое восстановление управляемости портфеля: внешних согласований нет.</t>
+        </is>
+      </c>
+      <c r="R10" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Time-to-Complete; Трудоёмкость объекта</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Статус-встречи по проекту</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="M11" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>Ввести статус-встречи: частота, повестка, протокол, адресат решений</t>
+        </is>
+      </c>
+      <c r="P11" s="12" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="Q11" s="12" t="inlineStr">
+        <is>
+          <t>Проектный уровень контура. Регламента нет, обязанности менеджера центрального аппарата исполняются примерно на одну шестую (узкое место 8). Идёт сразу за общим регламентом отчётности.</t>
+        </is>
+      </c>
+      <c r="R11" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Time-to-Complete; CSAT internal</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>1.1.1</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" s="21" t="n">
+        <v>69</v>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N12" s="12" t="inlineStr">
+        <is>
+          <t>SLA на стык с ЦО</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>Зафиксировать в письме ДРБ норматив срока передачи пакета и форму карточки проекта</t>
+        </is>
+      </c>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="Q12" s="12" t="inlineStr">
+        <is>
+          <t>Точка входа, которой ДУП не управляет: пакет формирует ДРБ. Берётся в одном пакете работ с 1.1, потому что норматив срока без чек-листа состава не имеет смысла — быстро переданный неполный пакет хуже, чем переданный вовремя полный.</t>
+        </is>
+      </c>
+      <c r="R12" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; SLA Compliance %</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>1.9.1</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Агрегация заявок и данных филиалов</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" s="21" t="n">
+        <v>69</v>
+      </c>
+      <c r="M13" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>Ввести единую форму заявки филиала и срок её подачи до даты формирования реестра</t>
+        </is>
+      </c>
+      <c r="P13" s="12" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="Q13" s="12" t="inlineStr">
+        <is>
+          <t>Сбор заявок в разных форматах и без общего срока — причина того, что реестр собирается в авральном режиме. Унификация формы даёт эффект сразу и не требует ничего, кроме распоряжения по филиалам.</t>
+        </is>
+      </c>
+      <c r="R13" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; First Pass Yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Постпроектное сопровождение</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="21" t="n">
+        <v>68</v>
+      </c>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N14" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса и границы</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>Утвердить паспорт процесса сопровождения: границы, вход, выход и три показателя</t>
+        </is>
+      </c>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="Q14" s="12" t="inlineStr">
+        <is>
+          <t>Фаза, в которой создаётся доход компании, описана хуже строительной: у блока 2 нет ни общих границ, ни показателей, ни регулярного учёта доходности объекта. Владелец — зам. по операционной деятельности — закреплён, но спрашивать с него не с чем: паспорта процесса нет, а по п. 176 Методики показатель без источника данных не учитывается. Вход процесса — принятый комплект объекта, его описывает чек-лист передачи (2.0). Оба документа входят в волну запуска и не держат очередь друг друга: место каждого задаёт балл.</t>
+        </is>
+      </c>
+      <c r="R14" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса и карта SIPOC; Budget Variance; Назначение бизнес-владельца</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Обработка запросов на перенос оборудования</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" s="21" t="n">
+        <v>66</v>
+      </c>
+      <c r="M15" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>Завести реестр переносов с сопоставлением «факт против ФЭМ»</t>
+        </is>
+      </c>
+      <c r="P15" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q15" s="12" t="inlineStr">
+        <is>
+          <t>Переносы выполняются, но нигде не сопоставляются с количеством, заложенным в модель (узкое место 12), поэтому перерасход обнаруживается в конце года. Реестр заводится одной таблицей и решает вторую задачу: даёт фактические данные для ревизии нормативов ФЭМ в волне 2. Без него пересмотр норм снова будет экспертной оценкой.</t>
+        </is>
+      </c>
+      <c r="R15" s="12" t="inlineStr">
+        <is>
+          <t>Budget Variance; COPQ; Пропускная способность</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Реализация проекта</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" s="21" t="n">
+        <v>64</v>
+      </c>
+      <c r="M16" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N16" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса и границы</t>
+        </is>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>Утвердить паспорт процесса реализации: границы, вход, выход и три показателя</t>
+        </is>
+      </c>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="Q16" s="12" t="inlineStr">
+        <is>
+          <t>Владелец закреплён — зам. по строительству и реализации, и это решение действует. Но девять подпроцессов блока не имеют общего описания: где фаза начинается, чем заканчивается и по каким показателям оценивается. Глава 8 и Приложение №2 Методики делают паспорт обязательным атрибутом процесса. Он пишется в волне запуска вместе с быстрыми победами и занимает место по баллу: чек-листы блока не ждут его утверждения. Общая граница с блоком 2 описана чек-листом передачи (2.0); оба документа делаются в одной волне.</t>
+        </is>
+      </c>
+      <c r="R16" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса и карта SIPOC; On-Time %; Назначение бизнес-владельца</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Передача проекта «реализация → сопровождение»</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G2" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" s="21" t="n">
+      <c r="G17" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" s="21" t="n">
         <v>64</v>
       </c>
-      <c r="M2" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
-        </is>
-      </c>
-      <c r="N2" s="12" t="inlineStr">
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N17" s="12" t="inlineStr">
         <is>
           <t>Проектирование TO-BE</t>
         </is>
       </c>
-      <c r="O2" s="12" t="inlineStr">
+      <c r="O17" s="12" t="inlineStr">
         <is>
           <t>Спроектировать чек-лист передачи и внести обязательную дату handover в карточку проекта</t>
         </is>
       </c>
-      <c r="P2" s="12" t="inlineStr">
+      <c r="P17" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q2" s="12" t="inlineStr">
-        <is>
-          <t>Владелец точки передачи закреплён за передающей стороной — замом по строительству и реализации: принимающая сторона не может отвечать за полноту того, что ей не передали. Но самой процедуры не существует — момент, в который объект перестаёт быть стройкой и становится источником дохода, нигде не зафиксирован. Этот момент одновременно является выходом процесса блока 1 и входом процесса блока 2, поэтому чек-лист проектируется раньше обоих паспортов: без него у двух сквозных процессов нет общей границы.</t>
-        </is>
-      </c>
-      <c r="R2" s="12" t="inlineStr">
+      <c r="Q17" s="12" t="inlineStr">
+        <is>
+          <t>Владелец точки передачи закреплён за передающей стороной — замом по строительству и реализации: принимающая сторона не может отвечать за полноту того, что ей не передали. Но самой процедуры не существует — момент, в который объект перестаёт быть стройкой и становится источником дохода, нигде не зафиксирован. Этот момент одновременно является выходом процесса блока 1 и входом процесса блока 2. Чек-лист описывает общую границу и делается в той же волне, что и оба паспорта; в очереди он стоит по своему баллу.</t>
+        </is>
+      </c>
+      <c r="R17" s="12" t="inlineStr">
         <is>
           <t>Назначение бизнес-владельца; Паспорт процесса и карта SIPOC</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t>Постпроектное сопровождение</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Методология и контроль качества (ПМО)</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G3" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" s="21" t="n">
-        <v>68</v>
-      </c>
-      <c r="M3" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
-        </is>
-      </c>
-      <c r="N3" s="12" t="inlineStr">
+      <c r="G18" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="21" t="n">
+        <v>64</v>
+      </c>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
         <is>
           <t>Паспорт процесса и границы</t>
         </is>
       </c>
-      <c r="O3" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить паспорт процесса сопровождения: границы, вход, выход и три показателя</t>
-        </is>
-      </c>
-      <c r="P3" s="12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="12" t="inlineStr">
-        <is>
-          <t>Фаза, в которой создаётся доход компании, описана хуже строительной: у блока 2 нет ни общих границ, ни показателей, ни регулярного учёта доходности объекта. Владелец — зам. по операционной деятельности — закреплён, но спрашивать с него не с чем: паспорта процесса нет, а по п. 176 Методики показатель без источника данных не учитывается. Вход процесса — принятый комплект объекта, поэтому паспорт идёт следом за чек-листом передачи (2.0).</t>
-        </is>
-      </c>
-      <c r="R3" s="12" t="inlineStr">
-        <is>
-          <t>Паспорт процесса и карта SIPOC; Budget Variance; Назначение бизнес-владельца</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>Реализация проекта</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>Утвердить паспорт процесса методологии и положение о контроле качества проектных данных</t>
+        </is>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q18" s="12" t="inlineStr">
+        <is>
+          <t>Роль главного менеджера проектов — несущая конструкция всей трансформации: именно она ведёт паспорта остальных процессов, аудит и портфельную отчётность. Владение и право остановить проект по результатам аудита закреплены, но собственного паспорта у процесса нет, а методолог без описанных границ своей работы не может требовать описания чужих. Объект никого не ждёт и идёт параллельно паспортам блоков 1 и 2.</t>
+        </is>
+      </c>
+      <c r="R18" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса и карта SIPOC; Defect Rate; Назначение бизнес-владельца</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Выявление нехватки бюджета и вынесение на ОСУ</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>ДУП и ОСУ</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>Зафиксировать порог и срок вынесения вопроса о нехватке бюджета на ОСУ</t>
+        </is>
+      </c>
+      <c r="P19" s="12" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q19" s="12" t="inlineStr">
+        <is>
+          <t>Объект исполняется, но порог и срок вынесения не формализованы, поэтому вопрос попадает на утверждающий орган тогда, когда деньги уже потрачены. Формализация критерия — одна строка регламента, а эффект — возможность принять решение, пока оно ещё что-то меняет.</t>
+        </is>
+      </c>
+      <c r="R19" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Budget Variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Б.5.1</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Участие ДУП: потребность, данные по региону, приём площадки</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G4" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" s="21" t="n">
-        <v>64</v>
-      </c>
-      <c r="M4" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
-        </is>
-      </c>
-      <c r="N4" s="12" t="inlineStr">
-        <is>
-          <t>Паспорт процесса и границы</t>
-        </is>
-      </c>
-      <c r="O4" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить паспорт процесса реализации: границы, вход, выход и три показателя</t>
-        </is>
-      </c>
-      <c r="P4" s="12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="Q4" s="12" t="inlineStr">
-        <is>
-          <t>Владелец закреплён — зам. по строительству и реализации, и это решение действует. Но девять подпроцессов блока не имеют общего описания: где фаза начинается, чем заканчивается и по каким показателям оценивается. Глава 8 и Приложение №2 Методики делают паспорт обязательным атрибутом процесса, поэтому он идёт раньше работы с отдельными подпроцессами. Выход процесса — момент передачи объекта в сопровождение, поэтому паспорт утверждается после чек-листа передачи (2.0), который этот выход описывает.</t>
-        </is>
-      </c>
-      <c r="R4" s="12" t="inlineStr">
-        <is>
-          <t>Паспорт процесса и карта SIPOC; On-Time %; Назначение бизнес-владельца</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>Методология и контроль качества (ПМО)</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="21" t="n">
-        <v>64</v>
-      </c>
-      <c r="M5" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="inlineStr">
-        <is>
-          <t>Паспорт процесса и границы</t>
-        </is>
-      </c>
-      <c r="O5" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить паспорт процесса методологии и положение о контроле качества проектных данных</t>
-        </is>
-      </c>
-      <c r="P5" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q5" s="12" t="inlineStr">
-        <is>
-          <t>Роль главного менеджера проектов — несущая конструкция всей трансформации: именно она ведёт паспорта остальных процессов, аудит и портфельную отчётность. Владение и право остановить проект по результатам аудита закреплены, но собственного паспорта у процесса нет, а методолог без описанных границ своей работы не может требовать описания чужих. Объект никого не ждёт и идёт параллельно паспортам блоков 1 и 2.</t>
-        </is>
-      </c>
-      <c r="R5" s="12" t="inlineStr">
-        <is>
-          <t>Паспорт процесса и карта SIPOC; Defect Rate; Назначение бизнес-владельца</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Контроль качества и полноты проектных данных</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" s="21" t="n">
-        <v>57</v>
-      </c>
-      <c r="M6" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
-        </is>
-      </c>
-      <c r="N6" s="12" t="inlineStr">
-        <is>
-          <t>Базовая линия и замер</t>
-        </is>
-      </c>
-      <c r="O6" s="12" t="inlineStr">
-        <is>
-          <t>Провести пилотный аудит одного филиала и развернуть его на весь портфель</t>
-        </is>
-      </c>
-      <c r="P6" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q6" s="12" t="inlineStr">
-        <is>
-          <t>Аудит остановлен после 2020 года, поэтому ни одно утверждение о состоянии процессов нельзя подтвердить цифрой. Пилот одного филиала не ждёт согласований: чек-листы готовы, филиал выбирает директор. Регулярный аудит на портфель имеет смысл, когда его результат влечёт последствия: право остановить проект зафиксировано за владельцем методологии вместе с паспортом процесса 4.</t>
-        </is>
-      </c>
-      <c r="R6" s="12" t="inlineStr">
-        <is>
-          <t>Defect Rate; First Pass Yield; Паспорт процесса и карта SIPOC</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Приём и валидация пакета документов от ДРБ</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>ДУП и ДРБ</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" s="21" t="n">
-        <v>86</v>
-      </c>
-      <c r="M7" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N7" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O7" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить чек-лист минимального пакета и правило возврата неполного комплекта</t>
-        </is>
-      </c>
-      <c r="P7" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q7" s="12" t="inlineStr">
-        <is>
-          <t>Первый объект цепочки: дефект пакета на входе проявляется на всех последующих подпроцессах — от ФЭМ до закупок и приёмки. Минимальный состав пакета не зафиксирован письменно (узкие места 1 и 4), поэтому старт проекта растягивается на доуточнения. Исправляется одним чек-листом и одним письмом в ДРБ — это лучшее соотношение эффекта к усилию во всём реестре.</t>
-        </is>
-      </c>
-      <c r="R7" s="12" t="inlineStr">
-        <is>
-          <t>Cycle Time; On-Time %; Defect Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>1.1.2</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" s="21" t="n">
-        <v>85</v>
-      </c>
-      <c r="M8" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N8" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>Ввести обязательную проверку по чек-листу до регистрации проекта в портфеле</t>
-        </is>
-      </c>
-      <c r="P8" s="12" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="Q8" s="12" t="inlineStr">
-        <is>
-          <t>Самый дешёвый контроль во всей цепочке: проверка по чек-листу занимает часы и отсекает дефект до того, как он превратится в неверный ФЭМ и неверную спецификацию закупки. Процессом владеет ДУП, поэтому внешних согласований не требуется вовсе.</t>
-        </is>
-      </c>
-      <c r="R8" s="12" t="inlineStr">
-        <is>
-          <t>Defect Rate; First Pass Yield; Rework Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Формирование реестра платежей и приоритизация</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F9" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="21" t="n">
-        <v>83</v>
-      </c>
-      <c r="M9" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N9" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить инструкцию по трём потокам платежей и единую форму реестра</t>
-        </is>
-      </c>
-      <c r="P9" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q9" s="12" t="inlineStr">
-        <is>
-          <t>Три потока платежей (ВУ / КИЗ / КОЗ) не формализованы, единой инструкции нет (узкие места 6 и 7). Задержка оплаты останавливает монтаж, то есть деньги и срок здесь связаны напрямую. Инструкция пишется внутри ДУП, от Финблока нужен только календарь приёма реестра — поэтому объект попадает в волну быстрых побед.</t>
-        </is>
-      </c>
-      <c r="R9" s="12" t="inlineStr">
-        <is>
-          <t>On-Time %; Cycle Time; COPQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>1.7.1</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="F10" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" s="21" t="n">
-        <v>82</v>
-      </c>
-      <c r="M10" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N10" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>Ввести форму заявки и правило: тех. карты СТ собираются до подачи заявки</t>
-        </is>
-      </c>
-      <c r="P10" s="12" t="inlineStr">
-        <is>
-          <t>1.1.2</t>
-        </is>
-      </c>
-      <c r="Q10" s="12" t="inlineStr">
-        <is>
-          <t>Этот шаг целиком внутри ДУП: полнота заявки и наличие тех. карт определяют, сколько раз процедура вернётся на доработку. Его можно исправить, не дожидаясь договорённостей с Закупщиками, поэтому он выносится в волну 2 отдельно от остальной части объекта 1.7.</t>
-        </is>
-      </c>
-      <c r="R10" s="12" t="inlineStr">
-        <is>
-          <t>First Pass Yield; Rework Rate; Defect Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Прогноз поступлений / расходов и контроль бюджета</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F11" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" s="21" t="n">
-        <v>73</v>
-      </c>
-      <c r="M11" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N11" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>Завести единый реестр прогноза и календарь его обновления</t>
-        </is>
-      </c>
-      <c r="P11" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q11" s="12" t="inlineStr">
-        <is>
-          <t>Прогноз ведётся в чатах и ad-hoc (узкие места 6 и 7), из-за чего компания узнаёт о разрыве поступлений позже, чем могла бы. Реестр и календарь — инструменты внутри ДУП: от Финблока нужна только форма выгрузки. Это делает объект исполнимым в волне 2. Встречный срок Финблока фиксируется отдельно, на этапе 2.3.2.</t>
-        </is>
-      </c>
-      <c r="R11" s="12" t="inlineStr">
-        <is>
-          <t>On-Time %; Budget Variance; Cycle Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>2.3.1</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Сбор данных и подтверждений по проектам</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F12" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" s="21" t="n">
-        <v>72</v>
-      </c>
-      <c r="M12" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N12" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить форму и срок подачи данных филиалами в реестр прогноза</t>
-        </is>
-      </c>
-      <c r="P12" s="12" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="Q12" s="12" t="inlineStr">
-        <is>
-          <t>Шаг, который ДУП выполняет сам и который определяет достоверность всего прогноза. Отсутствие формы и срока — причина того, что данные приходят разрозненно и требуют ручной сверки.</t>
-        </is>
-      </c>
-      <c r="R12" s="12" t="inlineStr">
-        <is>
-          <t>On-Time %; First Pass Yield; Defect Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" s="21" t="n">
-        <v>72</v>
-      </c>
-      <c r="M13" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить форму фиксации дефекта и маршрут «эксплуатация → владелец ТЗ → закупки»</t>
-        </is>
-      </c>
-      <c r="P13" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q13" s="12" t="inlineStr">
-        <is>
-          <t>Ущерб уже реализовался: кейс с хомутами показал, что сведения о дефекте компонента из эксплуатации не доходят до владельца технического задания и повторяются в следующей закупке (узкое место 9). Владелец закреплён за замом по операционной деятельности — тем, кто дефект обнаруживает и несёт потери от его повторения. Осталось описать маршрут: фиксация дефекта делается внутри ДУП, встречный срок реакции СТ фиксируется в волне 3 через объект Б.7.</t>
-        </is>
-      </c>
-      <c r="R13" s="12" t="inlineStr">
-        <is>
-          <t>COPQ; Defect Rate; Rework Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Отчётность по проектам</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="L14" s="21" t="n">
-        <v>71</v>
-      </c>
-      <c r="M14" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N14" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить один регламент отчётности: проект, операция, портфель</t>
-        </is>
-      </c>
-      <c r="P14" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q14" s="12" t="inlineStr">
-        <is>
-          <t>Три отчёта собирались отдельно и описывали одни и те же данные. Один регламент внутри ДУП задаёт частоту, адресата и запрет повторного сбора. Самое дешёвое восстановление управляемости портфеля: внешних согласований нет.</t>
-        </is>
-      </c>
-      <c r="R14" s="12" t="inlineStr">
-        <is>
-          <t>On-Time %; Time-to-Complete; Трудоёмкость объекта</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>4.3.1</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Статус-встречи по проекту</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" s="21" t="n">
-        <v>71</v>
-      </c>
-      <c r="M15" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N15" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O15" s="12" t="inlineStr">
-        <is>
-          <t>Ввести статус-встречи: частота, повестка, протокол, адресат решений</t>
-        </is>
-      </c>
-      <c r="P15" s="12" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="Q15" s="12" t="inlineStr">
-        <is>
-          <t>Проектный уровень контура. Регламента нет, обязанности менеджера центрального аппарата исполняются примерно на одну шестую (узкое место 8). Идёт сразу за общим регламентом отчётности.</t>
-        </is>
-      </c>
-      <c r="R15" s="12" t="inlineStr">
-        <is>
-          <t>On-Time %; Time-to-Complete; CSAT internal</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>1.1.1</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="F16" s="30" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" s="21" t="n">
-        <v>69</v>
-      </c>
-      <c r="M16" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N16" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O16" s="12" t="inlineStr">
-        <is>
-          <t>Зафиксировать в письме ДРБ норматив срока передачи пакета и форму карточки проекта</t>
-        </is>
-      </c>
-      <c r="P16" s="12" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="Q16" s="12" t="inlineStr">
-        <is>
-          <t>Точка входа, которой ДУП не управляет: пакет формирует ДРБ. Берётся в одном пакете работ с 1.1, потому что норматив срока без чек-листа состава не имеет смысла — быстро переданный неполный пакет хуже, чем переданный вовремя полный.</t>
-        </is>
-      </c>
-      <c r="R16" s="12" t="inlineStr">
-        <is>
-          <t>On-Time %; SLA Compliance %</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>1.9.1</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Агрегация заявок и данных филиалов</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F17" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" s="21" t="n">
-        <v>69</v>
-      </c>
-      <c r="M17" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N17" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O17" s="12" t="inlineStr">
-        <is>
-          <t>Ввести единую форму заявки филиала и срок её подачи до даты формирования реестра</t>
-        </is>
-      </c>
-      <c r="P17" s="12" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="Q17" s="12" t="inlineStr">
-        <is>
-          <t>Сбор заявок в разных форматах и без общего срока — причина того, что реестр собирается в авральном режиме. Унификация формы даёт эффект сразу и не требует ничего, кроме распоряжения по филиалам.</t>
-        </is>
-      </c>
-      <c r="R17" s="12" t="inlineStr">
-        <is>
-          <t>On-Time %; First Pass Yield</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>1.9.2</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F18" s="29" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="H18" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" s="21" t="n">
-        <v>86</v>
-      </c>
-      <c r="M18" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N18" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O18" s="12" t="inlineStr">
-        <is>
-          <t>Описать правило очерёдности: какой платёж попадает в начало реестра и почему</t>
-        </is>
-      </c>
-      <c r="P18" s="12" t="inlineStr">
-        <is>
-          <t>1.9.1</t>
-        </is>
-      </c>
-      <c r="Q18" s="12" t="inlineStr">
-        <is>
-          <t>Ядро узких мест 6 и 7: правила, по которому платёж попадает в начало или в конец реестра, не существует, поэтому очередность определяется телефонным звонком. Формализация умещается на одну страницу, а эффект измеряется днями просрочки перед подрядчиками.</t>
-        </is>
-      </c>
-      <c r="R18" s="12" t="inlineStr">
-        <is>
-          <t>On-Time %; Wait Time %; COPQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Обработка запросов на перенос оборудования</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J19" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" s="21" t="n">
-        <v>66</v>
-      </c>
-      <c r="M19" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N19" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O19" s="12" t="inlineStr">
-        <is>
-          <t>Завести реестр переносов с сопоставлением «факт против ФЭМ»</t>
-        </is>
-      </c>
-      <c r="P19" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q19" s="12" t="inlineStr">
-        <is>
-          <t>Переносы выполняются, но нигде не сопоставляются с количеством, заложенным в модель (узкое место 12), поэтому перерасход обнаруживается в конце года. Реестр заводится одной таблицей и решает вторую задачу: даёт фактические данные для ревизии нормативов ФЭМ в волне 3. Без него пересмотр норм снова будет экспертной оценкой.</t>
-        </is>
-      </c>
-      <c r="R19" s="12" t="inlineStr">
-        <is>
-          <t>Budget Variance; COPQ; Пропускная способность</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Выявление нехватки бюджета и вынесение на ОСУ</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>ДУП и ОСУ</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" s="19" t="n">
+      <c r="G20" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="20" t="n">
         <v>4</v>
       </c>
       <c r="L20" s="21" t="n">
         <v>59</v>
       </c>
-      <c r="M20" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="M20" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="N20" s="12" t="inlineStr">
@@ -2863,309 +2830,309 @@
       </c>
       <c r="O20" s="12" t="inlineStr">
         <is>
-          <t>Зафиксировать порог и срок вынесения вопроса о нехватке бюджета на ОСУ</t>
+          <t>Утвердить критерий инициации открытия филиала и форму обоснования потребности</t>
         </is>
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>Объект исполняется, но порог и срок вынесения не формализованы, поэтому вопрос попадает на утверждающий орган тогда, когда деньги уже потрачены. Формализация критерия — одна строка регламента, а эффект — возможность принять решение, пока оно ещё что-то меняет.</t>
+          <t>Вход в процесс: решение об открытии сегодня рождается по факту появления проекта в регионе без филиала, то есть поздно и авралом. Этап целиком в границах операционного контура ДУП, поэтому критерий и форма обоснования утверждаются внутренним документом, не дожидаясь сквозного маршрута.</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Budget Variance</t>
+          <t>On-Time %; Cycle Time</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="17" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Контроль качества и полноты проектных данных</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="M21" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr">
+        <is>
+          <t>Базовая линия и замер</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>Провести пилотный аудит одного филиала и развернуть его на весь портфель</t>
+        </is>
+      </c>
+      <c r="P21" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q21" s="12" t="inlineStr">
+        <is>
+          <t>Аудит остановлен после 2020 года, поэтому ни одно утверждение о состоянии процессов нельзя подтвердить цифрой. Пилот одного филиала не ждёт согласований: чек-листы готовы, филиал выбирает директор. Регулярный аудит на портфель имеет смысл, когда его результат влечёт последствия: право остановить проект зафиксировано за владельцем методологии вместе с паспортом процесса 4.</t>
+        </is>
+      </c>
+      <c r="R21" s="12" t="inlineStr">
+        <is>
+          <t>Defect Rate; First Pass Yield; Паспорт процесса и карта SIPOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
           <t>4.3.2</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Операционный статус руководству и госпартнёру</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G21" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" s="21" t="n">
+      <c r="G22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" s="21" t="n">
         <v>56</v>
       </c>
-      <c r="M21" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N21" s="12" t="inlineStr">
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N22" s="12" t="inlineStr">
         <is>
           <t>Устранение дублей и упрощение</t>
         </is>
       </c>
-      <c r="O21" s="12" t="inlineStr">
+      <c r="O22" s="12" t="inlineStr">
         <is>
           <t>Собирать операционный статус из протокола статус-встреч, без второго опроса</t>
         </is>
       </c>
-      <c r="P21" s="12" t="inlineStr">
+      <c r="P22" s="12" t="inlineStr">
         <is>
           <t>4.3.1</t>
         </is>
       </c>
-      <c r="Q21" s="12" t="inlineStr">
+      <c r="Q22" s="12" t="inlineStr">
         <is>
           <t>Операционный отчёт госпартнёру и руководству повторял данные проектного статуса. После того как статус-встречи задают проектный уровень, этот этап только выбирает из них нужный срез.</t>
         </is>
       </c>
-      <c r="R21" s="12" t="inlineStr">
+      <c r="R22" s="12" t="inlineStr">
         <is>
           <t>Трудоёмкость объекта; Rework Rate; CSAT external</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="18" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>Управление филиальной сетью</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G22" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" s="21" t="n">
+      <c r="G23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" s="21" t="n">
         <v>55</v>
       </c>
-      <c r="M22" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N22" s="12" t="inlineStr">
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="N23" s="12" t="inlineStr">
         <is>
           <t>Регламент и чек-лист</t>
         </is>
       </c>
-      <c r="O22" s="12" t="inlineStr">
+      <c r="O23" s="12" t="inlineStr">
         <is>
           <t>Утвердить паспорт процесса филиальной сети: отношения вне проекта и стык с открытием филиала</t>
         </is>
       </c>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="P23" s="12" t="inlineStr">
         <is>
           <t>1, 2</t>
         </is>
       </c>
-      <c r="Q22" s="12" t="inlineStr">
+      <c r="Q23" s="12" t="inlineStr">
         <is>
           <t>Владение закреплено за директором ДУП. Назначение куратора вынесено в одну матрицу (1.3), открытие филиала — в сквозной маршрут (Б.5). У самого процесса паспорта нет, поэтому регламент по филиальной сети исполняется на усмотрение исполнителя.</t>
         </is>
       </c>
-      <c r="R22" s="12" t="inlineStr">
+      <c r="R23" s="12" t="inlineStr">
         <is>
           <t>Паспорт процесса и карта SIPOC; Cycle Time; On-Time %</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="18" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Б.5.1</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Участие ДУП: потребность, данные по региону, приём площадки</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Назначение куратора (проект и филиал)</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G23" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" s="21" t="n">
-        <v>59</v>
-      </c>
-      <c r="M23" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
-        </is>
-      </c>
-      <c r="N23" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O23" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить критерий инициации открытия филиала и форму обоснования потребности</t>
-        </is>
-      </c>
-      <c r="P23" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q23" s="12" t="inlineStr">
-        <is>
-          <t>Вход в процесс: решение об открытии сегодня рождается по факту появления проекта в регионе без филиала, то есть поздно и авралом. Этап целиком в границах операционного контура ДУП, поэтому критерий и форма обоснования утверждаются внутренним документом, не дожидаясь сквозного маршрута.</t>
-        </is>
-      </c>
-      <c r="R23" s="12" t="inlineStr">
-        <is>
-          <t>On-Time %; Cycle Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Назначение куратора (проект и филиал)</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G24" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="26" t="n">
+      <c r="G24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="27" t="n">
+      <c r="J24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="18" t="n">
         <v>5</v>
       </c>
       <c r="L24" s="21" t="n">
         <v>54</v>
       </c>
-      <c r="M24" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="N24" s="12" t="inlineStr">
@@ -3195,7 +3162,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="17" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
@@ -3218,32 +3185,32 @@
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G25" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" s="19" t="n">
+      <c r="G25" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="20" t="n">
         <v>4</v>
       </c>
       <c r="L25" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="M25" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
@@ -3273,7 +3240,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="17" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -3296,32 +3263,32 @@
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G26" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="26" t="n">
+      <c r="G26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="26" t="n">
+      <c r="I26" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" s="27" t="n">
+      <c r="J26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="18" t="n">
         <v>5</v>
       </c>
       <c r="L26" s="21" t="n">
         <v>41</v>
       </c>
-      <c r="M26" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="N26" s="12" t="inlineStr">
@@ -3351,7 +3318,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="17" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
@@ -3374,32 +3341,32 @@
           <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
-      <c r="F27" s="29" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G27" s="27" t="n">
+      <c r="G27" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="27" t="n">
+      <c r="H27" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" s="20" t="n">
+      <c r="I27" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" s="24" t="n">
         <v>2</v>
       </c>
       <c r="L27" s="21" t="n">
         <v>84</v>
       </c>
-      <c r="M27" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M27" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N27" s="12" t="inlineStr">
@@ -3419,7 +3386,7 @@
       </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
-          <t>Закупки — главный источник срыва сроков реализации (узкое место 13): нормативов по шагам процедуры нет, и задержка обнаруживается постфактум, когда сдвинуть уже нечего. Это единственный внешний процесс, где ДУП стоит и на входе, и на выходе, то есть рычаг есть с обеих сторон. В волне 3, потому что нормативы устанавливаются совместно с владельцем процедуры.</t>
+          <t>Закупки — главный источник срыва сроков реализации (узкое место 13): нормативов по шагам процедуры нет, и задержка обнаруживается постфактум, когда сдвинуть уже нечего. Это единственный внешний процесс, где ДУП стоит и на входе, и на выходе, то есть рычаг есть с обеих сторон. В волне 2, потому что нормативы устанавливаются совместно с владельцем процедуры.</t>
         </is>
       </c>
       <c r="R27" s="12" t="inlineStr">
@@ -3429,7 +3396,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="17" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -3452,32 +3419,32 @@
           <t>ДРБ</t>
         </is>
       </c>
-      <c r="F28" s="30" t="inlineStr">
+      <c r="F28" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G28" s="27" t="n">
+      <c r="G28" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="27" t="n">
+      <c r="H28" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="K28" s="20" t="n">
+      <c r="K28" s="24" t="n">
         <v>2</v>
       </c>
       <c r="L28" s="21" t="n">
         <v>83</v>
       </c>
-      <c r="M28" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M28" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N28" s="12" t="inlineStr">
@@ -3497,7 +3464,7 @@
       </c>
       <c r="Q28" s="12" t="inlineStr">
         <is>
-          <t>Один из двух подлинных пробелов: процедуры не существует. Решение о готовности продукта принимает ДРБ, а последствия незрелого продукта несёт ДУП. Ядро регламента — право директора ДУП не пускать проект в реализацию без подписи: без блокировки gate остаётся уведомлением. Берётся в волне 3, потому что регламент проектируется с нуля и согласуется с внешним владельцем.</t>
+          <t>Один из двух подлинных пробелов: процедуры не существует. Решение о готовности продукта принимает ДРБ, а последствия незрелого продукта несёт ДУП. Ядро регламента — право директора ДУП не пускать проект в реализацию без подписи: без блокировки gate остаётся уведомлением. Берётся в волне 2, потому что регламент проектируется с нуля и согласуется с внешним владельцем.</t>
         </is>
       </c>
       <c r="R28" s="12" t="inlineStr">
@@ -3507,7 +3474,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="17" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
@@ -3530,32 +3497,32 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F29" s="29" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G29" s="27" t="n">
+      <c r="G29" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" s="27" t="n">
+      <c r="H29" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="J29" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K29" s="20" t="n">
+      <c r="J29" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="24" t="n">
         <v>2</v>
       </c>
       <c r="L29" s="21" t="n">
         <v>80</v>
       </c>
-      <c r="M29" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M29" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N29" s="12" t="inlineStr">
@@ -3575,7 +3542,7 @@
       </c>
       <c r="Q29" s="12" t="inlineStr">
         <is>
-          <t>Нормативы ФЭМ устарели (узкое место 11): бюджет проекта считается по ценам и нормам, не отражающим ни текущую стоимость поверки, ни фактическую частоту переносов. Ошибка здесь дороже любой другой — она тиражируется на весь срок проекта и возвращается перерасходом в блоке 2. Идёт в волне 3, потому что процессом целиком владеет Финблок, а данные для пересмотра норм даёт реестр переносов из волны 2.</t>
+          <t>Нормативы ФЭМ устарели (узкое место 11): бюджет проекта считается по ценам и нормам, не отражающим ни текущую стоимость поверки, ни фактическую частоту переносов. Ошибка здесь дороже любой другой — она тиражируется на весь срок проекта и возвращается перерасходом в блоке 2. Идёт в волне 2, потому что процессом целиком владеет Финблок, а данные для пересмотра норм даёт реестр переносов из волны 2.</t>
         </is>
       </c>
       <c r="R29" s="12" t="inlineStr">
@@ -3585,7 +3552,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="17" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="12" t="inlineStr">
@@ -3608,32 +3575,32 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F30" s="29" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G30" s="27" t="n">
+      <c r="G30" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" s="27" t="n">
+      <c r="H30" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="J30" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K30" s="25" t="n">
+      <c r="J30" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L30" s="21" t="n">
         <v>83</v>
       </c>
-      <c r="M30" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M30" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N30" s="12" t="inlineStr">
@@ -3663,7 +3630,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="17" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
@@ -3686,32 +3653,32 @@
           <t>ДРБ</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G31" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H31" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I31" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K31" s="25" t="n">
+      <c r="G31" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L31" s="21" t="n">
         <v>69</v>
       </c>
-      <c r="M31" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M31" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N31" s="12" t="inlineStr">
@@ -3741,7 +3708,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="17" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -3764,32 +3731,32 @@
           <t>ДРБ</t>
         </is>
       </c>
-      <c r="F32" s="29" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G32" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H32" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K32" s="25" t="n">
+      <c r="G32" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L32" s="21" t="n">
         <v>69</v>
       </c>
-      <c r="M32" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M32" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N32" s="12" t="inlineStr">
@@ -3819,7 +3786,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="17" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
@@ -3842,32 +3809,32 @@
           <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
-      <c r="F33" s="30" t="inlineStr">
+      <c r="F33" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G33" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H33" s="27" t="n">
+      <c r="G33" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="I33" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K33" s="26" t="n">
+      <c r="I33" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" s="28" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="21" t="n">
         <v>67</v>
       </c>
-      <c r="M33" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M33" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N33" s="12" t="inlineStr">
@@ -3897,7 +3864,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="17" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -3920,32 +3887,32 @@
           <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
-      <c r="F34" s="30" t="inlineStr">
+      <c r="F34" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G34" s="27" t="n">
+      <c r="G34" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H34" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J34" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K34" s="25" t="n">
+      <c r="H34" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L34" s="21" t="n">
         <v>83</v>
       </c>
-      <c r="M34" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M34" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N34" s="12" t="inlineStr">
@@ -3975,10 +3942,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="17" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>Б.7</t>
         </is>
@@ -3988,7 +3955,7 @@
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="27" t="inlineStr">
         <is>
           <t>Производство, монтаж и калибровка оборудования</t>
         </is>
@@ -3998,32 +3965,32 @@
           <t>СТ</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="F35" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G35" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I35" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" s="20" t="n">
+      <c r="G35" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="24" t="n">
         <v>2</v>
       </c>
       <c r="L35" s="21" t="n">
         <v>57</v>
       </c>
-      <c r="M35" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M35" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N35" s="12" t="inlineStr">
@@ -4053,10 +4020,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>Б.5</t>
         </is>
@@ -4066,7 +4033,7 @@
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>Открытие нового филиала</t>
         </is>
@@ -4076,32 +4043,32 @@
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G36" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I36" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="K36" s="20" t="n">
+      <c r="G36" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" s="24" t="n">
         <v>2</v>
       </c>
       <c r="L36" s="21" t="n">
         <v>56</v>
       </c>
-      <c r="M36" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M36" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N36" s="12" t="inlineStr">
@@ -4121,7 +4088,7 @@
       </c>
       <c r="Q36" s="12" t="inlineStr">
         <is>
-          <t>Единственная строка открытия филиала. Участок ДУП — этап Б.5.1, он описывается раньше. Владельцем по Таблице 4 Методики закреплён директор ДУП как курирующий руководитель кросс-функционального процесса: Юр блок отвечает только за регистрацию, HR — только за штат, за работающий филиал целиком не отвечает никто другой. Назначение владельца чужого сквозного процесса ДУП не утверждает в одностороннем порядке, поэтому объект идёт в волне 3: предметом работы является решение Операционного комитета, а не внутренний документ.</t>
+          <t>Единственная строка открытия филиала. Участок ДУП — этап Б.5.1, он описывается раньше. Владельцем по Таблице 4 Методики закреплён директор ДУП как курирующий руководитель кросс-функционального процесса: Юр блок отвечает только за регистрацию, HR — только за штат, за работающий филиал целиком не отвечает никто другой. Назначение владельца чужого сквозного процесса ДУП не утверждает в одностороннем порядке, поэтому объект идёт в волне 2: предметом работы является решение Операционного комитета, а не внутренний документ.</t>
         </is>
       </c>
       <c r="R36" s="12" t="inlineStr">
@@ -4131,7 +4098,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="17" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
@@ -4154,32 +4121,32 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F37" s="29" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G37" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H37" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I37" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K37" s="20" t="n">
+      <c r="G37" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" s="24" t="n">
         <v>2</v>
       </c>
       <c r="L37" s="21" t="n">
         <v>53</v>
       </c>
-      <c r="M37" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M37" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N37" s="12" t="inlineStr">
@@ -4209,10 +4176,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="17" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>Б.10</t>
         </is>
@@ -4222,7 +4189,7 @@
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="27" t="inlineStr">
         <is>
           <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
         </is>
@@ -4232,32 +4199,32 @@
           <t>Зерек</t>
         </is>
       </c>
-      <c r="F38" s="30" t="inlineStr">
+      <c r="F38" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G38" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H38" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I38" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K38" s="20" t="n">
+      <c r="G38" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="24" t="n">
         <v>2</v>
       </c>
       <c r="L38" s="21" t="n">
         <v>53</v>
       </c>
-      <c r="M38" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M38" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N38" s="12" t="inlineStr">
@@ -4287,10 +4254,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="17" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>Б.8</t>
         </is>
@@ -4300,7 +4267,7 @@
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
+      <c r="D39" s="27" t="inlineStr">
         <is>
           <t>Юридическое сопровождение договоров с контрагентами</t>
         </is>
@@ -4310,32 +4277,32 @@
           <t>Юр блок</t>
         </is>
       </c>
-      <c r="F39" s="30" t="inlineStr">
+      <c r="F39" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G39" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" s="25" t="n">
+      <c r="G39" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L39" s="21" t="n">
         <v>53</v>
       </c>
-      <c r="M39" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M39" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N39" s="12" t="inlineStr">
@@ -4365,7 +4332,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="17" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="12" t="inlineStr">
@@ -4388,32 +4355,32 @@
           <t>Юр блок</t>
         </is>
       </c>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="F40" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K40" s="25" t="n">
+      <c r="G40" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L40" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="M40" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M40" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N40" s="12" t="inlineStr">
@@ -4443,10 +4410,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>Б.9</t>
         </is>
@@ -4456,7 +4423,7 @@
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D41" s="24" t="inlineStr">
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
         </is>
@@ -4466,32 +4433,32 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F41" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" s="26" t="n">
+      <c r="G41" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" s="25" t="n">
+      <c r="J41" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L41" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="M41" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M41" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N41" s="12" t="inlineStr">
@@ -4521,7 +4488,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="17" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -4544,32 +4511,32 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F42" s="30" t="inlineStr">
+      <c r="F42" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I42" s="26" t="n">
+      <c r="G42" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K42" s="26" t="n">
+      <c r="J42" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" s="28" t="n">
         <v>1</v>
       </c>
       <c r="L42" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="M42" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M42" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N42" s="12" t="inlineStr">
@@ -4589,7 +4556,7 @@
       </c>
       <c r="Q42" s="12" t="inlineStr">
         <is>
-          <t>Шаг выполняет Финблок, ДУП получает информацию о проведении платежа. Предметом договорённости является норматив срока: без него приоритизация реестра в волне 2 не доводится до результата.</t>
+          <t>Шаг выполняет Финблок, ДУП получает информацию о проведении платежа. Предметом договорённости является норматив срока: без него приоритизация реестра в волне 1 не доводится до результата.</t>
         </is>
       </c>
       <c r="R42" s="12" t="inlineStr">
@@ -4599,7 +4566,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="17" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="12" t="inlineStr">
@@ -4622,32 +4589,32 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F43" s="30" t="inlineStr">
+      <c r="F43" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" s="26" t="n">
+      <c r="G43" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" s="28" t="n">
         <v>1</v>
       </c>
       <c r="L43" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="M43" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M43" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N43" s="12" t="inlineStr">
@@ -4677,7 +4644,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="17" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -4700,32 +4667,32 @@
           <t>Юр блок</t>
         </is>
       </c>
-      <c r="F44" s="29" t="inlineStr">
+      <c r="F44" s="23" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G44" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" s="26" t="n">
+      <c r="G44" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K44" s="20" t="n">
+      <c r="J44" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" s="24" t="n">
         <v>2</v>
       </c>
       <c r="L44" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="M44" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="M44" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="N44" s="12" t="inlineStr">
@@ -4755,7 +4722,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="17" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="12" t="inlineStr">
@@ -4778,32 +4745,32 @@
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="F45" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" s="27" t="n">
+      <c r="G45" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="J45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K45" s="20" t="n">
+      <c r="J45" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" s="24" t="n">
         <v>2</v>
       </c>
       <c r="L45" s="21" t="n">
         <v>61</v>
       </c>
-      <c r="M45" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="M45" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N45" s="12" t="inlineStr">
@@ -4833,7 +4800,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="17" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="12" t="inlineStr">
@@ -4856,32 +4823,32 @@
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H46" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" s="19" t="n">
+      <c r="G46" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" s="20" t="n">
         <v>4</v>
       </c>
       <c r="L46" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="M46" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="M46" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N46" s="12" t="inlineStr">
@@ -4911,7 +4878,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="17" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="12" t="inlineStr">
@@ -4934,32 +4901,32 @@
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="F47" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H47" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K47" s="25" t="n">
+      <c r="G47" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L47" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="M47" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="M47" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N47" s="12" t="inlineStr">
@@ -4979,7 +4946,7 @@
       </c>
       <c r="Q47" s="12" t="inlineStr">
         <is>
-          <t>В реестре методологии 434 документа, около 28% архива устарело, последняя правка — 2021 год. Задача не в переписывании, а в актуализации, и делать её имеет смысл тогда, когда новые регламенты волн 2 и 3 уже написаны — иначе методологию придётся актуализировать дважды.</t>
+          <t>В реестре методологии 434 документа, около 28% архива устарело, последняя правка — 2021 год. Задача не в переписывании, а в актуализации, и делать её имеет смысл тогда, когда новые регламенты волн 1 и 2 уже написаны — иначе методологию придётся актуализировать дважды.</t>
         </is>
       </c>
       <c r="R47" s="12" t="inlineStr">
@@ -4989,7 +4956,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="17" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="12" t="inlineStr">
@@ -5012,32 +4979,32 @@
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H48" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I48" s="26" t="n">
+      <c r="G48" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K48" s="19" t="n">
+      <c r="J48" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" s="20" t="n">
         <v>4</v>
       </c>
       <c r="L48" s="21" t="n">
         <v>48</v>
       </c>
-      <c r="M48" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="M48" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N48" s="12" t="inlineStr">
@@ -5067,7 +5034,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="17" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="12" t="inlineStr">
@@ -5090,32 +5057,32 @@
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="F49" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G49" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H49" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" s="26" t="n">
+      <c r="G49" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="26" t="n">
+      <c r="J49" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="K49" s="27" t="n">
+      <c r="K49" s="18" t="n">
         <v>5</v>
       </c>
       <c r="L49" s="21" t="n">
         <v>42</v>
       </c>
-      <c r="M49" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="M49" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N49" s="12" t="inlineStr">
@@ -5145,10 +5112,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="17" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>Б.2</t>
         </is>
@@ -5158,7 +5125,7 @@
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D50" s="24" t="inlineStr">
+      <c r="D50" s="27" t="inlineStr">
         <is>
           <t>Финансовое закрытие проекта</t>
         </is>
@@ -5168,32 +5135,32 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F50" s="29" t="inlineStr">
+      <c r="F50" s="23" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G50" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I50" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K50" s="20" t="n">
+      <c r="G50" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" s="24" t="n">
         <v>2</v>
       </c>
       <c r="L50" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="M50" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="M50" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N50" s="12" t="inlineStr">
@@ -5223,7 +5190,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="17" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="12" t="inlineStr">
@@ -5246,32 +5213,32 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F51" s="29" t="inlineStr">
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G51" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K51" s="19" t="n">
+      <c r="G51" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" s="20" t="n">
         <v>4</v>
       </c>
       <c r="L51" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="M51" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="M51" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N51" s="12" t="inlineStr">
@@ -5301,7 +5268,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="17" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="inlineStr">
@@ -5324,32 +5291,32 @@
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G52" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" s="26" t="n">
+      <c r="G52" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K52" s="25" t="n">
+      <c r="I52" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" s="19" t="n">
         <v>3</v>
       </c>
       <c r="L52" s="21" t="n">
         <v>39</v>
       </c>
-      <c r="M52" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="M52" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="N52" s="12" t="inlineStr">
@@ -5379,7 +5346,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="17" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="12" t="inlineStr">
@@ -5402,30 +5369,30 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F53" s="30" t="inlineStr">
+      <c r="F53" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G53" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" s="26" t="n">
+      <c r="G53" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K53" s="26" t="n">
+      <c r="J53" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" s="28" t="n">
         <v>1</v>
       </c>
       <c r="L53" s="21" t="n">
         <v>33</v>
       </c>
-      <c r="M53" s="33" t="inlineStr">
+      <c r="M53" s="31" t="inlineStr">
         <is>
           <t>Вне очереди — наблюдение</t>
         </is>
@@ -5457,7 +5424,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="17" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="12" t="inlineStr">
@@ -5480,30 +5447,30 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F54" s="29" t="inlineStr">
+      <c r="F54" s="23" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G54" s="26" t="n">
+      <c r="G54" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="26" t="n">
+      <c r="H54" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I54" s="26" t="n">
+      <c r="I54" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="26" t="n">
+      <c r="J54" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="K54" s="26" t="n">
+      <c r="K54" s="28" t="n">
         <v>1</v>
       </c>
       <c r="L54" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="M54" s="33" t="inlineStr">
+      <c r="M54" s="31" t="inlineStr">
         <is>
           <t>Вне очереди — наблюдение</t>
         </is>
@@ -5535,7 +5502,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="17" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="12" t="inlineStr">
@@ -5558,30 +5525,30 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F55" s="30" t="inlineStr">
+      <c r="F55" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G55" s="26" t="n">
+      <c r="G55" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="26" t="n">
+      <c r="H55" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I55" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" s="26" t="n">
+      <c r="I55" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="K55" s="26" t="n">
+      <c r="K55" s="28" t="n">
         <v>1</v>
       </c>
       <c r="L55" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="M55" s="33" t="inlineStr">
+      <c r="M55" s="31" t="inlineStr">
         <is>
           <t>Вне очереди — наблюдение</t>
         </is>
@@ -5613,12 +5580,12 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B56" s="23" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>ДУП.0</t>
         </is>
@@ -5628,7 +5595,7 @@
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D56" s="24" t="inlineStr">
+      <c r="D56" s="27" t="inlineStr">
         <is>
           <t>Управление проектами (ГЧП / ГЗ)</t>
         </is>
@@ -5638,32 +5605,32 @@
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F56" s="14" t="inlineStr">
+      <c r="F56" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G56" s="18" t="inlineStr">
+      <c r="G56" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H56" s="18" t="inlineStr">
+      <c r="H56" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I56" s="18" t="inlineStr">
+      <c r="I56" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J56" s="18" t="inlineStr">
+      <c r="J56" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K56" s="18" t="inlineStr">
+      <c r="K56" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5673,7 +5640,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M56" s="33" t="inlineStr">
+      <c r="M56" s="31" t="inlineStr">
         <is>
           <t>Не оценивается — агрегирующий уровень</t>
         </is>
@@ -5717,7 +5684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5731,16 +5698,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Порядок работ по волнам</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Волна — это ответ на вопрос «когда начинаем», а не «насколько объект важен». Состав волны определяется зависимостями: нельзя улучшать процесс, границы и показатели которого не описаны, и нельзя доказать эффект, пока не снята базовая линия. Внутри волны объекты идут по убыванию балла, но не раньше своих предшественников.</t>
+          <t>Волна — это ответ на вопрос «с кем договариваемся», а не «насколько объект важен». Волна 1 — всё, что ДУП начинает сам; внутри неё порядок строго по убыванию балла, паспорт и базовая линия очередь не держат. Волны 2 и 3 ждут договорённости с другим подразделением или работающего процесса на входе: там объект не встаёт раньше своего предшественника.</t>
         </is>
       </c>
     </row>
@@ -5789,235 +5756,210 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Фазы 0–1 дорожной карты</t>
+          <t>Старт программы</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Паспорта сквозных процессов и замер «до»</t>
+          <t>Паспорта, замер «до» и быстрые победы внутри ДУП</t>
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>2.0, 2, 1, 4, 4.2</t>
+          <t>1.1, 1.9.2, 1.1.2, 1.9, 1.7.1, 2.3, 2.3.1, 2.7, 4.3, 4.3.1, 1.1.1, 1.9.1, 2, 2.5, 1, 2.0, 4, 2.6, Б.5.1, 4.2, 4.3.2, 3, 1.3, 4.3.3, 3.3</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Чек-лист передачи «реализация → сопровождение» (2.0): он описывает границу, общую для блоков 1 и 2, поэтому оба паспорта опираются на него. Параллельно и без единого согласования идёт пилотный аудит одного филиала по трём готовым чек-листам методологии — первый шаг объекта 4.2</t>
+          <t>Чек-лист минимального пакета от ДРБ (1.1) и правило очерёдности платежей (1.9.2) — два объекта с высшим баллом. Паспорта блоков 1, 2 и 4 и пилотный аудит идут в той же волне, каждый на своём месте в рейтинге</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Владение закреплено: у каждого объекта реестра есть должность, отвечающая за результат, поэтому стоп-факторов для старта нет. Волна занята тем, без чего оптимизация не имеет точки отсчёта. Глава 8 и Приложение №2 Методики делают паспорт процесса обязательным атрибутом — границы, вход, выход, владелец и показатели; пока паспорта нет, улучшение отдельных шагов не с чем сверять, а по п. 176 показатель без источника данных не учитывается вовсе. Поэтому первыми идут три сквозных процесса, которыми ДУП владеет целиком, описание границы между ними и оба аудита проектных данных. Баллы здесь не решают: объекты волны создают линейку, которой измеряются все остальные.</t>
+          <t>Волна собрана из всего, что ДУП начинает без стоп-фактора и без переговоров с другим подразделением: паспорта сквозных процессов, пилотный аудит и объекты, где вмешательство умещается в регламент или чек-лист. Глава 8 и Приложение №2 по-прежнему требуют паспорт, а п. 176 — источник данных для показателя. И то и другое делается в этой же волне, а не перед ней: объект с более высоким баллом начинается сразу. Внутри волны очередь идёт строго по убыванию балла.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Утверждены паспорта процессов блоков 1, 2 и 4 и чек-лист передачи между блоками; базовая линия по пилотному филиалу зафиксирована документом, регулярный аудит проектных данных развёрнут на весь портфель</t>
+          <t>Не менее восьми объектов волны работают по регламенту два месяца подряд; утверждены паспорта процессов блоков 1, 2 и 4; базовая линия по пилотному филиалу зафиксирована документом</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Фаза 2 дорожной карты</t>
+          <t>Стыки с центральным офисом</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Восстановить исполнение там, где ДУП решает в одиночку</t>
+          <t>Договориться о стыках и спроектировать то, чего нет</t>
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>1.1, 1.1.2, 1.9, 1.7.1, 2.3, 2.3.1, 2.7, 4.3, 4.3.1, 1.1.1, 1.9.1, 1.9.2, 2.5, 2.6, 4.3.2, 3, Б.5.1, 1.3, 4.3.3, 3.3</t>
+          <t>1.7, 1.2, 1.5, 1.5.1, 1.2.1, 2.4, 1.7.2, 1.7.3, Б.7, Б.5, 1.5.2, Б.10, Б.8, Б.5.3, Б.9, 1.9.3, 2.3.2, Б.5.2</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Чек-лист минимального пакета от ДРБ (1.1) — первый объект цепочки, дефект на входе тиражируется на все последующие подпроцессы</t>
+          <t>Ревизия нормативов ФЭМ (1.5) — ошибка в модели тиражируется на весь срок проекта и возвращается перерасходом в блоке 2</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Объекты волны объединены одним признаком: ДУП — бизнес-владелец, вмешательство умещается в регламент или чек-лист, внешних согласований не требуется. Это даёт результат до того, как начнутся переговоры с центральным офисом, и создаёт переговорную позицию: требовать нормативов от смежников убедительнее, когда собственные нормативы уже исполняются.</t>
+          <t>Здесь собраны самые тяжёлые по согласованию объекты — ФЭМ, закупки, gate готовности продукта. Часть из них ценнее многих объектов волны 1, но предметом работы является договорённость с другим подразделением, а не внутреннее решение ДУП. Волна идёт второй по этой причине, а не потому, что объекты менее важны.</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Не менее восьми объектов волны работают по регламенту два месяца подряд; по каждому ведётся фактический замер On-Time % и Defect Rate</t>
+          <t>Подписаны SLA с Финблоком, Закупщиками, Юр блоком и ДРБ; утверждены регламент gate готовности продукта и сквозной маршрут открытия филиала</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Фаза 3 дорожной карты</t>
+          <t>Масштаб программы</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Договориться о стыках и спроектировать то, чего нет</t>
+          <t>Пересмотреть экономику и закрепить результат в системах</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>1.7, 1.2, 1.5, 1.5.1, 1.2.1, 2.4, 1.7.2, 1.7.3, Б.7, Б.5, 1.5.2, Б.10, Б.8, Б.5.3, Б.9, 1.9.3, 2.3.2, Б.5.2</t>
+          <t>2.1, 1.4, 4.1, 1.1.3, 1.4.1, Б.2, Б.2.1, 2.2</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Ревизия нормативов ФЭМ (1.5 / Б.1) — ошибка в модели тиражируется на весь срок проекта и возвращается перерасходом в блоке 2</t>
+          <t>Расчёт экономики собственной аккредитации для поверки (2.1) — около 6 000 комплексов и растущая стоимость услуги</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Здесь собраны самые ценные по баллу объекты — ФЭМ, закупки, gate готовности продукта — и одновременно самые тяжёлые: процессами владеют другие подразделения, а gate готовности продукта и сквозной маршрут открытия филиала нужно проектировать с нуля. Волна идёт третьей не потому, что объекты менее важны, а потому, что предметом работы является договорённость с другим подразделением, а не внутреннее решение ДУП.</t>
+          <t>Объекты волны требуют либо денег и расчёта (поверка), либо работающих процессов и достоверных данных на входе (автоматизация). Автоматизировать процесс, который не исполняется, — значит закрепить беспорядок в коде: Методика прямо связывает автоматизацию с этапом 2 цикла управления, следующим за проектированием.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Подписаны SLA с Финблоком, Закупщиками, Юр блоком и ДРБ; утверждены регламент gate готовности продукта и сквозной маршрут открытия филиала</t>
+          <t>Принято решение по модели поверки; единая карточка проекта работает в промышленной эксплуатации; уровень автоматизации измеряется</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+          <t>Вне очереди — наблюдение</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Фаза 4 дорожной карты</t>
+          <t>Вне периметра работ</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Пересмотреть экономику и закрепить результат в системах</t>
+          <t>Держать под наблюдением, в очередь не ставить</t>
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>2.1, 1.4, 4.1, 1.1.3, 1.4.1, Б.2, Б.2.1, 2.2</t>
+          <t>1.5.3, Б.2.2, Б.2.3</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Расчёт экономики собственной аккредитации для поверки (2.1) — около 6 000 комплексов и растущая стоимость услуги</t>
+          <t>Отдельных действий не требуется — срок контролируется через SLA по родительскому объекту</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Объекты волны требуют либо денег и расчёта (поверка), либо работающих процессов и достоверных данных на входе (автоматизация). Автоматизировать процесс, который не исполняется, — значит закрепить беспорядок в коде: Методика прямо связывает автоматизацию с этапом 2 цикла управления, следующим за проектированием.</t>
+          <t>Объекты целиком исполняются другим подразделением, ДУП получает только результат. Оптимизировать здесь нечего: предметом договорённости является не порядок шагов, а срок, и он фиксируется в SLA по родительскому объекту.</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Принято решение по модели поверки; единая карточка проекта работает в промышленной эксплуатации; уровень автоматизации измеряется</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Вне очереди — наблюдение</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Вне периметра работ</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Держать под наблюдением, в очередь не ставить</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>1.5.3, Б.2.2, Б.2.3</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Отдельных действий не требуется — срок контролируется через SLA по родительскому объекту</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>Объекты целиком исполняются другим подразделением, ДУП получает только результат. Оптимизировать здесь нечего: предметом договорённости является не порядок шагов, а срок, и он фиксируется в SLA по родительскому объекту.</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
           <t>Нарушение срока по объекту становится основанием пересмотреть SLA родительского объекта (п. 195.1)</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Зависимости, определившие порядок</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Зависимости, определившие порядок</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Зависимость</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Что она означает для очереди</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Зависимость</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Что она означает для очереди</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Чек-лист передачи (2.0) и паспорта процессов блоков 1 и 2</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Выход процесса реализации и вход процесса сопровождения — один и тот же момент: передача объекта. Чек-лист и оба паспорта описывают одну границу и делаются в волне 1. В очереди каждый стоит по своему баллу, никто из них не блокирует остальные объекты волны.</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Чек-лист передачи (2.0) → паспорта процессов блоков 1 и 2</t>
+          <t>Паспорт процесса методологии (4) и аудит проектных данных (4.2)</t>
         </is>
       </c>
       <c r="B13" s="12" t="n"/>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Выход процесса реализации и вход процесса сопровождения — один и тот же момент: передача объекта. Пока он не описан, у двух сквозных процессов нет общей границы и оба паспорта пришлось бы переписывать. Поэтому первый объект очереди — сам чек-лист передачи.</t>
+          <t>Пилот одного филиала и регулярный аудит — один объект. Пилот даёт базовую линию и не ждёт согласований. Право остановить проект фиксируется в положении о контроле качества вместе с паспортом процесса методологии. Оба стоят в волне 1 по своему баллу и не держат старт соседних работ.</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -6026,13 +5968,13 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Паспорт процесса методологии (4) → аудит проектных данных (4.2)</t>
+          <t>Базовая линия (4.2) доказывает эффект</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Пилот одного филиала и регулярный аудит — один объект. Пилот даёт базовую линию и не ждёт согласований. Развёртывание на портфель имеет смысл, когда результат аудита влечёт последствия: право остановить проект фиксируется в положении о контроле качества вместе с паспортом процесса методологии.</t>
+          <t>Пилотный аудит даёт первые достоверные цифры. Без него любое утверждение об улучшении останется экспертной оценкой (п. 176 Методики). Замер идёт параллельно с регламентами волны 1, а не перед ними.</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -6041,13 +5983,13 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Базовая линия (4.2) → доказательство эффекта</t>
+          <t>Реестр переносов (2.5) → ревизия нормативов ФЭМ (1.5)</t>
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Пилотный аудит даёт первые достоверные цифры. Без него любое утверждение об улучшении останется экспертной оценкой (п. 176 Методики).</t>
+          <t>Пересмотр норм в модели требует фактических данных по переносам. Поэтому реестр заводится в волне 1, а ревизия нормативов идёт в волне 2.</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -6056,13 +5998,13 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Реестр переносов (2.5) → ревизия нормативов ФЭМ (1.5)</t>
+          <t>Регламент отчётности (4.3) → этапы 4.3.1, 4.3.2, 4.3.3</t>
         </is>
       </c>
       <c r="B16" s="12" t="n"/>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Пересмотр норм в модели требует фактических данных по переносам. Поэтому реестр заводится в волне 2, а ревизия нормативов идёт в волне 3.</t>
+          <t>Сначала один регламент, затем проектный статус, из него операционный, из обоих — портфель. Повторного сбора данных нет.</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -6071,13 +6013,13 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Регламент отчётности (4.3) → этапы 4.3.1, 4.3.2, 4.3.3</t>
+          <t>Чек-лист приёмки (1.1) → письмо в ДРБ</t>
         </is>
       </c>
       <c r="B17" s="12" t="n"/>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Сначала один регламент, затем проектный статус, из него операционный, из обоих — портфель. Повторного сбора данных нет.</t>
+          <t>Письмо о сроке передачи — часть того же объекта 1.1, а не отдельный процесс. Требовать норматив от ДРБ имеет смысл, когда собственный чек-лист уже описан.</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -6086,13 +6028,13 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Чек-лист приёмки (1.1) → письмо в ДРБ</t>
+          <t>Участок ДУП (Б.5.1) → сквозной маршрут открытия филиала (Б.5)</t>
         </is>
       </c>
       <c r="B18" s="12" t="n"/>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Письмо о сроке передачи — часть того же объекта 1.1, а не отдельный процесс. Требовать норматив от ДРБ имеет смысл, когда собственный чек-лист уже описан.</t>
+          <t>Участок ДУП описывается внутренним документом и идёт в волне 1. Сквозной маршрут затрагивает Юр блок, HR и Финблок и утверждается Операционным комитетом, поэтому выносится в волну 2.</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -6101,38 +6043,25 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Участок ДУП (Б.5.1) → сквозной маршрут открытия филиала (Б.5)</t>
+          <t>Работающие процессы → автоматизация</t>
         </is>
       </c>
       <c r="B19" s="12" t="n"/>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Участок ДУП описывается внутренним документом и идёт в волне 2. Сквозной маршрут затрагивает Юр блок, HR и Финблок и утверждается Операционным комитетом, поэтому выносится в волну 3.</t>
+          <t>Единая карточка проекта и уведомления имеют смысл, когда данные, которые они переносят, уже собираются по регламенту.</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
       <c r="E19" s="12" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Работающие процессы → автоматизация</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Единая карточка проекта и уведомления имеют смысл, когда данные, которые они переносят, уже собираются по регламенту.</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C11:E11"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="A18:B18"/>
@@ -6143,12 +6072,10 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C15:E15"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C20:E20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -6174,7 +6101,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Первые 11 шагов: программа старта реинжиниринга</t>
         </is>
@@ -6183,7 +6110,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Действий, с которых начинается работа, — 11. Шаги 1–5 задают точку отсчёта: паспорта сквозных процессов и базовая линия, шаги 6–11 восстанавливают исполнение там, где ДУП принимает решение самостоятельно. Ни один из них не требует ИТ-разработки и бюджета — это сознательный выбор: первая волна должна показать результат до того, как начнутся переговоры со смежными подразделениями.</t>
+          <t>Действий, с которых начинается работа, — 11. Все они входят в волну 1 и стоят по убыванию балла ведущего объекта: сначала чек-лист приёмки и платежи, затем прогноз и статус-встречи, паспорта и пилотный аудит — на своём месте в рейтинге. Ни один шаг не требует ИТ-разработки и бюджета и не держит остальные: переговоры со смежными подразделениями начинаются в волне 2.</t>
         </is>
       </c>
     </row>
@@ -6225,387 +6152,387 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="n">
+      <c r="A5" s="33" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
+          <t>Чек-лист минимального пакета от ДРБ и письмо о сроке передачи</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>1.1, 1.1.1, 1.1.2</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Зам. по реализации, директор ДУП</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Волна 1</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Чек-лист приёмки и письмо в ДРБ</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Высший балл волны: дефект на входе тиражируется на ФЭМ, закупки и приёмку. Лучшее соотношение эффекта к усилию во всём реестре — один документ внутри и одно письмо вовне. Паспорта процессов этот шаг не держат.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Инструкция по трём потокам платежей ВУ / КИЗ / КОЗ</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>1.9, 1.9.1, 1.9.2</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Зам. по реализации</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Волна 1</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Инструкция по очерёдности и единая форма реестра</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Тот же высший балл. Узкие места 6 и 7: правила очерёдности платежей нет, приоритет определяется звонком. Задержка оплаты останавливает монтаж, а инструкция умещается на одну страницу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Единый реестр и календарь прогноза поступлений и расходов</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>2.3, 2.3.1</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Волна 1</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Реестр прогноза и календарь его обновления</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Прогноз ведётся в чатах (узкие места 6 и 7), поэтому разрыв поступлений выявляется поздно. Реестр — инструмент внутри ДУП, встречные обязательства Финблока фиксируются позже, в волне 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Регламент статус-встреч по проектам</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>4.3, 4.3.1</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Зам. по реализации</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Волна 1</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Регламент, шаблон повестки и протокола</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Обязанности менеджера центрального аппарата исполняются примерно на одну шестую (узкое место 8). Самое дешёвое восстановление управляемости портфеля: решение принимается внутри департамента без единого внешнего согласования.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Паспорт процесса сопровождения (блок 2)</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности, директор ДУП</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Волна 1</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса: границы, вход, выход, владелец и три показателя</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Фаза, в которой создаётся доход компании, описана хуже строительной: ни общих границ, ни показателей, ни регулярного учёта доходности объекта. Владелец закреплён. Паспорт пишется параллельно с регламентами блока и не держит их очередь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Реестр переносов оборудования «факт против ФЭМ»</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Волна 1</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Реестр переносов с сопоставлением по каждому проекту</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Решает сразу две задачи: закрывает узкое место 12 и даёт фактические данные для ревизии нормативов ФЭМ в волне 2. Без него пересмотр норм снова будет экспертной оценкой, а не расчётом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Паспорт процесса реализации (блок 1)</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Зам. по реализации, директор ДУП</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Волна 1</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса: границы, вход, выход, владелец и три показателя</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Девять подпроцессов блока работают без общего описания: где фаза начинается, чем заканчивается и по каким показателям оценивается. Глава 8 требует паспорт, но чек-листы блока начинаются по своему баллу и паспорта не ждут.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Чек-лист передачи «реализация → сопровождение»</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Зам. по строительству и реализации</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Волна 1</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Чек-лист передачи и обязательная дата handover в карточке проекта</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Владелец точки передачи закреплён, самой процедуры нет. Этот момент — выход процесса блока 1 и вход процесса блока 2. Чек-лист описывает общую границу и стоит в очереди по своему баллу, а не перед паспортами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Паспорт методологии и положение о контроле качества данных</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов, директор ДУП</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Волна 1</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Положение о контроле качества и паспорт процесса 4</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Один документ описывает процесс методологии и фиксирует право остановить проект по результатам аудита. Пишется в той же волне, что и пилотный аудит, и не блокирует регламенты с более высоким баллом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
           <t>Пилотный аудит одного филиала по трём чек-листам методологии</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Главный менеджер проектов</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Фаза 0</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Волна 1</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Отчёт аудита и зафиксированная базовая линия</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>Единственное действие программы, которое не требует ни одного согласования: чек-листы написаны, исполнитель определён. Даёт цифры, без которых эффект всех последующих шагов нечем подтвердить.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Чек-лист передачи «реализация → сопровождение»</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Зам. по строительству и реализации</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Фаза 1</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>Чек-лист передачи и обязательная дата handover в карточке проекта</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Владелец точки передачи закреплён, самой процедуры нет. Этот момент — выход процесса блока 1 и вход процесса блока 2, поэтому он описывается раньше обоих паспортов: без него у двух сквозных процессов нет общей границы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Паспорт процесса реализации (блок 1)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Зам. по реализации, директор ДУП</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Фаза 1</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Паспорт процесса: границы, вход, выход, владелец и три показателя</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>Девять подпроцессов блока работают без общего описания: где фаза начинается, чем заканчивается и по каким показателям оценивается. Глава 8 и Приложение №2 Методики делают паспорт обязательным атрибутом процесса — до него улучшать отдельные шаги не с чем сверять.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Паспорт процесса сопровождения (блок 2)</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Зам. по операционной деятельности, директор ДУП</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Фаза 1</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>Паспорт процесса: границы, вход, выход, владелец и три показателя</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Фаза, в которой создаётся доход компании, описана хуже строительной: ни общих границ, ни показателей, ни регулярного учёта доходности объекта. Владелец закреплён, но спрашивать с него пока не с чем.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Паспорт методологии и положение о контроле качества данных</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>4, 4.2</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Главный менеджер проектов, директор ДУП</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Фаза 1</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Положение о контроле качества и паспорт процесса 4</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>Один документ закрывает две задачи: описывает процесс методологии и фиксирует право остановить проект по результатам аудита. Без этого права аудит превращается в справку, а паспорта остальных процессов некому требовать.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Чек-листы написаны, исполнитель определён, согласований нет. Даёт цифры, которыми потом подтверждают эффект. Соседние шаги волны замер не ждут.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Утверждение матрицы «филиал → куратор»</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Директор ДУП</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Фаза 2</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Волна 1</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Утверждённая приказом матрица</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>Вход для назначения ответственных по проектам и для всей региональной отчётности. Оформляется одной таблицей, а закрывает часть узкого места 8.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Чек-лист минимального пакета от ДРБ и письмо о сроке передачи</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>1.1, 1.1.1, 1.1.2</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Зам. по реализации, директор ДУП</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Фаза 2</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Чек-лист приёмки и письмо в ДРБ</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>Первый объект цепочки: дефект на входе тиражируется на ФЭМ, закупки и приёмку. Лучшее соотношение эффекта к усилию во всём реестре — один документ внутри и одно письмо вовне.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Инструкция по трём потокам платежей ВУ / КИЗ / КОЗ</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>1.9, 1.9.1, 1.9.2</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Зам. по реализации</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>Фаза 2</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>Инструкция по очерёдности и единая форма реестра</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>Узкие места 6 и 7: правила очерёдности платежей не существует, поэтому приоритет определяется звонком. Задержка оплаты останавливает монтаж — здесь деньги и срок связаны напрямую, а инструкция умещается на одну страницу.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Регламент статус-встреч по проектам</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>4.3, 4.3.1</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Зам. по реализации</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>Фаза 2</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Регламент, шаблон повестки и протокола</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>Обязанности менеджера центрального аппарата исполняются примерно на одну шестую (узкое место 8). Самое дешёвое восстановление управляемости портфеля: решение принимается внутри департамента без единого внешнего согласования.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Единый реестр и календарь прогноза поступлений и расходов</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>2.3, 2.3.1</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Зам. по операционной деятельности</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>Фаза 2</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>Реестр прогноза и календарь его обновления</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>Прогноз ведётся в чатах (узкие места 6 и 7), поэтому разрыв поступлений выявляется поздно. Реестр — инструмент внутри ДУП, встречные обязательства Финблока фиксируются позже, в волне 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="35" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Реестр переносов оборудования «факт против ФЭМ»</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Зам. по операционной деятельности</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Фаза 2</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Реестр переносов с сопоставлением по каждому проекту</t>
-        </is>
-      </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Решает сразу две задачи: закрывает узкое место 12 и даёт фактические данные для ревизии нормативов ФЭМ в волне 3. Без него пересмотр норм снова будет экспертной оценкой, а не расчётом.</t>
+          <t>Вход для назначения ответственных по проектам и для всей региональной отчётности. Оформляется одной таблицей и закрывает часть узкого места 8. Балл ниже остальных шагов программы, поэтому матрица замыкает волну запуска.</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6564,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Матрица «ценность — лёгкость реализации»</t>
         </is>
@@ -6674,15 +6601,15 @@
         </is>
       </c>
       <c r="B6" s="12" t="n"/>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы — 14
-2.0, 2, 1, 4, 1.1, 1.1.2, 1.7.1, 2.3.1, 4.3, 4.3.1, 1.1.1, 1.9.1, 1.9.2, 2.5</t>
+1.1, 1.9.2, 1.1.2, 1.7.1, 2.3.1, 4.3, 4.3.1, 1.1.1, 1.9.1, 2, 2.5, 1, 2.0, 4</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="12" t="n"/>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты — 13
 1.9, 2.3, 2.7, 1.7, 1.2, 1.5, 1.5.1, 1.2.1, 2.4, 1.7.2, 1.7.3, Б.7, 2.1</t>
@@ -6697,15 +6624,15 @@
         </is>
       </c>
       <c r="B7" s="12" t="n"/>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>Заполнители — 12
-4.2, 2.6, 4.3.2, 3, Б.5.1, 1.3, 4.3.3, 3.3, 1.4, 1.1.3, 1.4.1, Б.2.1</t>
+2.6, Б.5.1, 4.2, 4.3.2, 3, 1.3, 4.3.3, 3.3, 1.4, 1.1.3, 1.4.1, Б.2.1</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="12" t="n"/>
-      <c r="F7" s="33" t="inlineStr">
+      <c r="F7" s="31" t="inlineStr">
         <is>
           <t>Отложить — 15
 Б.5, 1.5.2, Б.10, Б.8, Б.5.3, Б.9, 1.9.3, 2.3.2, Б.5.2, 4.1, Б.2, 2.2, 1.5.3, Б.2.2, Б.2.3</t>
@@ -6742,7 +6669,7 @@
       <c r="G10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
@@ -6763,7 +6690,7 @@
       <c r="G11" s="12" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
@@ -6784,7 +6711,7 @@
       <c r="G12" s="12" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
@@ -6805,7 +6732,7 @@
       <c r="G13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
@@ -6886,14 +6813,14 @@
       <c r="D18" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="31" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F18" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G18" s="11" t="n">
@@ -6917,14 +6844,14 @@
       <c r="D19" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="31" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F19" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G19" s="11" t="n">
@@ -6948,14 +6875,14 @@
       <c r="D20" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G20" s="11" t="n">
@@ -6979,14 +6906,14 @@
       <c r="D21" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G21" s="11" t="n">
@@ -7010,14 +6937,14 @@
       <c r="D22" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G22" s="11" t="n">
@@ -7041,14 +6968,14 @@
       <c r="D23" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="31" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F23" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F23" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G23" s="11" t="n">
@@ -7072,14 +6999,14 @@
       <c r="D24" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E24" s="31" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F24" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F24" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G24" s="11" t="n">
@@ -7103,14 +7030,14 @@
       <c r="D25" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F25" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F25" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G25" s="11" t="n">
@@ -7134,14 +7061,14 @@
       <c r="D26" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F26" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G26" s="11" t="n">
@@ -7165,14 +7092,14 @@
       <c r="D27" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F27" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G27" s="11" t="n">
@@ -7196,14 +7123,14 @@
       <c r="D28" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E28" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G28" s="11" t="n">
@@ -7227,14 +7154,14 @@
       <c r="D29" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F29" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F29" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G29" s="11" t="n">
@@ -7258,14 +7185,14 @@
       <c r="D30" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="31" t="inlineStr">
+      <c r="E30" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G30" s="11" t="n">
@@ -7289,14 +7216,14 @@
       <c r="D31" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G31" s="11" t="n">
@@ -7320,14 +7247,14 @@
       <c r="D32" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="31" t="inlineStr">
+      <c r="E32" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F32" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F32" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G32" s="11" t="n">
@@ -7351,14 +7278,14 @@
       <c r="D33" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="31" t="inlineStr">
+      <c r="E33" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F33" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F33" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G33" s="11" t="n">
@@ -7382,14 +7309,14 @@
       <c r="D34" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G34" s="11" t="n">
@@ -7413,14 +7340,14 @@
       <c r="D35" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F35" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G35" s="11" t="n">
@@ -7444,14 +7371,14 @@
       <c r="D36" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F36" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G36" s="11" t="n">
@@ -7475,14 +7402,14 @@
       <c r="D37" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F37" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G37" s="11" t="n">
@@ -7506,14 +7433,14 @@
       <c r="D38" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E38" s="28" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G38" s="11" t="n">
@@ -7537,14 +7464,14 @@
       <c r="D39" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="31" t="inlineStr">
+      <c r="E39" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F39" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="F39" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G39" s="11" t="n">
@@ -7568,14 +7495,14 @@
       <c r="D40" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E40" s="28" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
-      <c r="F40" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G40" s="11" t="n">
@@ -7585,12 +7512,12 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Передача проекта «реализация → сопровождение»</t>
+          <t>Реализация проекта</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
@@ -7599,14 +7526,14 @@
       <c r="D41" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E41" s="28" t="inlineStr">
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
       <c r="F41" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G41" s="11" t="n">
@@ -7616,12 +7543,12 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Реализация проекта</t>
+          <t>Передача проекта «реализация → сопровождение»</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
@@ -7630,14 +7557,14 @@
       <c r="D42" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E42" s="28" t="inlineStr">
+      <c r="E42" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G42" s="11" t="n">
@@ -7661,14 +7588,14 @@
       <c r="D43" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E43" s="28" t="inlineStr">
+      <c r="E43" s="22" t="inlineStr">
         <is>
           <t>Быстрые победы</t>
         </is>
       </c>
       <c r="F43" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G43" s="11" t="n">
@@ -7692,14 +7619,14 @@
       <c r="D44" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E44" s="31" t="inlineStr">
+      <c r="E44" s="29" t="inlineStr">
         <is>
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F44" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F44" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G44" s="11" t="n">
@@ -7723,14 +7650,14 @@
       <c r="D45" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="33" t="inlineStr">
+      <c r="E45" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F45" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F45" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G45" s="11" t="n">
@@ -7754,14 +7681,14 @@
       <c r="D46" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E46" s="36" t="inlineStr">
+      <c r="E46" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F46" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G46" s="11" t="n">
@@ -7785,14 +7712,14 @@
       <c r="D47" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E47" s="36" t="inlineStr">
+      <c r="E47" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F47" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G47" s="11" t="n">
@@ -7816,14 +7743,14 @@
       <c r="D48" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="33" t="inlineStr">
+      <c r="E48" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F48" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F48" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G48" s="11" t="n">
@@ -7847,14 +7774,14 @@
       <c r="D49" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="33" t="inlineStr">
+      <c r="E49" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F49" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F49" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G49" s="11" t="n">
@@ -7878,14 +7805,14 @@
       <c r="D50" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E50" s="36" t="inlineStr">
+      <c r="E50" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F50" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G50" s="11" t="n">
@@ -7909,14 +7836,14 @@
       <c r="D51" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E51" s="33" t="inlineStr">
+      <c r="E51" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F51" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F51" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G51" s="11" t="n">
@@ -7940,14 +7867,14 @@
       <c r="D52" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E52" s="36" t="inlineStr">
+      <c r="E52" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F52" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G52" s="11" t="n">
@@ -7971,14 +7898,14 @@
       <c r="D53" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E53" s="33" t="inlineStr">
+      <c r="E53" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F53" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F53" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G53" s="11" t="n">
@@ -8002,14 +7929,14 @@
       <c r="D54" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E54" s="33" t="inlineStr">
+      <c r="E54" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F54" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F54" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G54" s="11" t="n">
@@ -8033,14 +7960,14 @@
       <c r="D55" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E55" s="33" t="inlineStr">
+      <c r="E55" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F55" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="F55" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G55" s="11" t="n">
@@ -8064,14 +7991,14 @@
       <c r="D56" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="33" t="inlineStr">
+      <c r="E56" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F56" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F56" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G56" s="11" t="n">
@@ -8095,14 +8022,14 @@
       <c r="D57" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="33" t="inlineStr">
+      <c r="E57" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F57" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F57" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G57" s="11" t="n">
@@ -8126,14 +8053,14 @@
       <c r="D58" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E58" s="36" t="inlineStr">
+      <c r="E58" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t>Волна 1. Паспорта и базовая линия</t>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G58" s="11" t="n">
@@ -8157,14 +8084,14 @@
       <c r="D59" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E59" s="36" t="inlineStr">
+      <c r="E59" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F59" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G59" s="11" t="n">
@@ -8188,14 +8115,14 @@
       <c r="D60" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E60" s="36" t="inlineStr">
+      <c r="E60" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F60" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="F60" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G60" s="11" t="n">
@@ -8219,14 +8146,14 @@
       <c r="D61" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E61" s="36" t="inlineStr">
+      <c r="E61" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F61" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F61" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G61" s="11" t="n">
@@ -8250,14 +8177,14 @@
       <c r="D62" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E62" s="36" t="inlineStr">
+      <c r="E62" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F62" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="F62" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G62" s="11" t="n">
@@ -8281,14 +8208,14 @@
       <c r="D63" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E63" s="36" t="inlineStr">
+      <c r="E63" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F63" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="F63" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G63" s="11" t="n">
@@ -8312,14 +8239,14 @@
       <c r="D64" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E64" s="33" t="inlineStr">
+      <c r="E64" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F64" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="F64" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G64" s="11" t="n">
@@ -8343,14 +8270,14 @@
       <c r="D65" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E65" s="33" t="inlineStr">
+      <c r="E65" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F65" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="F65" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G65" s="11" t="n">
@@ -8374,14 +8301,14 @@
       <c r="D66" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E66" s="33" t="inlineStr">
+      <c r="E66" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F66" s="31" t="inlineStr">
-        <is>
-          <t>Волна 3. Стыки с ЦО и закрытие пробелов</t>
+      <c r="F66" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="G66" s="11" t="n">
@@ -8405,12 +8332,12 @@
       <c r="D67" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="33" t="inlineStr">
+      <c r="E67" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F67" s="33" t="inlineStr">
+      <c r="F67" s="31" t="inlineStr">
         <is>
           <t>Вне очереди — наблюдение</t>
         </is>
@@ -8436,14 +8363,14 @@
       <c r="D68" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E68" s="36" t="inlineStr">
+      <c r="E68" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>Волна 4. Масштаб, экономика и автоматизация</t>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="G68" s="11" t="n">
@@ -8467,14 +8394,14 @@
       <c r="D69" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E69" s="36" t="inlineStr">
+      <c r="E69" s="34" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F69" s="28" t="inlineStr">
-        <is>
-          <t>Волна 2. Быстрые победы внутри ДУП</t>
+      <c r="F69" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="G69" s="11" t="n">
@@ -8498,12 +8425,12 @@
       <c r="D70" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E70" s="33" t="inlineStr">
+      <c r="E70" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F70" s="33" t="inlineStr">
+      <c r="F70" s="31" t="inlineStr">
         <is>
           <t>Вне очереди — наблюдение</t>
         </is>
@@ -8529,12 +8456,12 @@
       <c r="D71" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E71" s="33" t="inlineStr">
+      <c r="E71" s="31" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F71" s="33" t="inlineStr">
+      <c r="F71" s="31" t="inlineStr">
         <is>
           <t>Вне очереди — наблюдение</t>
         </is>

--- a/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
+++ b/dup_project/01_Процессы/ДУП_приоритеты_реинжиниринга.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Как читать" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Приоритеты" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Порядок работ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Первые 11 шагов" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Матрица ценность — лёгкость" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как читать" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приоритеты" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Порядок работ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Первые 11 шагов" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица ценность — лёгкость" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приоритеты'!$A$1:$R$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приоритеты'!$A$1:$T$61</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Приоритеты'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Порядок работ'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Первые 11 шагов'!$4:$4</definedName>
@@ -118,7 +118,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE0F7"/>
+        <fgColor rgb="00EDF1F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -128,7 +128,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDF1F7"/>
+        <fgColor rgb="00CFE0F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -158,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -207,13 +207,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,31 +222,28 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1157,7 +1154,7 @@
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
@@ -1166,7 +1163,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Корень дерева процессов</t>
+          <t>Головной процесс без отдельной оценки: работа идёт по его подпроцессам</t>
         </is>
       </c>
       <c r="E28" s="12" t="n"/>
@@ -1181,7 +1178,7 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1. «Приоритеты» — основной лист. Строки уже стоят в порядке работ: сначала волна. Внутри волны 1 — строго по убыванию балла. В волнах 2 и 3 — по убыванию балла, но не раньше предшественников. Сортировка по колонке «Итоговый балл» даёт чистый рейтинг ценности без учёта волны.</t>
+          <t>1. «Приоритеты» — основной лист. Строки разложены деревом: головной процесс, под ним его подпроцессы и этапы. Номер в очереди — это порядок работ: волна 1 строго по убыванию балла, волны 2 и 3 — по баллу, но не раньше предшественников. Сортировка по колонке «Итоговый балл» даёт рейтинг ценности.</t>
         </is>
       </c>
     </row>
@@ -1252,27 +1249,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:T61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="70" customWidth="1" min="19" max="19"/>
+    <col width="28" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
@@ -1293,75 +1292,85 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Наименование объекта</t>
+          <t>Процесс</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>Бизнес-владелец</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Роль ДУП</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Влияние на результат</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Экономия времени</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Экономия денег</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Риск бездействия</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Лёгкость реализации</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Итоговый балл</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Волна</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Тип вмешательства</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Первый шаг</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Предшественники</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Обоснование — почему берёмся за объект именно здесь</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Чем подтвердим эффект</t>
         </is>
@@ -1369,323 +1378,363 @@
     </row>
     <row r="2">
       <c r="A2" s="17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>Приём и валидация пакета документов от ДРБ</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>Реализация проекта</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>ДУП и ДРБ</t>
-        </is>
-      </c>
-      <c r="F2" s="13" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G2" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" s="18" t="n">
-        <v>5</v>
-      </c>
       <c r="I2" s="19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K2" s="20" t="n">
+      <c r="M2" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L2" s="21" t="n">
-        <v>86</v>
-      </c>
-      <c r="M2" s="22" t="inlineStr">
+      <c r="N2" s="21" t="n">
+        <v>64</v>
+      </c>
+      <c r="O2" s="22" t="inlineStr">
         <is>
           <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
-      <c r="N2" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O2" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить чек-лист минимального пакета и правило возврата неполного комплекта</t>
-        </is>
-      </c>
       <c r="P2" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Паспорт процесса и границы</t>
         </is>
       </c>
       <c r="Q2" s="12" t="inlineStr">
         <is>
-          <t>Первый объект цепочки: дефект пакета на входе проявляется на всех последующих подпроцессах — от ФЭМ до закупок и приёмки. Минимальный состав пакета не зафиксирован письменно (узкие места 1 и 4), поэтому старт проекта растягивается на доуточнения. Исправляется одним чек-листом и одним письмом в ДРБ — это лучшее соотношение эффекта к усилию во всём реестре.</t>
+          <t>Утвердить паспорт процесса реализации: границы, вход, выход и три показателя</t>
         </is>
       </c>
       <c r="R2" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; On-Time %; Defect Rate</t>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="S2" s="12" t="inlineStr">
+        <is>
+          <t>Владелец закреплён — зам. по строительству и реализации, и это решение действует. Но приём пакета, назначение куратора и проектная документация не имеют общего описания: где фаза начинается, чем заканчивается и по каким показателям оценивается. Глава 8 и Приложение №2 Методики делают паспорт обязательным атрибутом процесса. Он пишется в волне запуска вместе с быстрыми победами и занимает место по баллу: чек-листы блока не ждут его утверждения. Общая граница с блоком 2 описана чек-листом передачи (2.0); оба документа делаются в одной волне.</t>
+        </is>
+      </c>
+      <c r="T2" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса и карта SIPOC; On-Time %; Назначение бизнес-владельца</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>1.9.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G3" s="18" t="n">
+          <t>Реализация проекта</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Приём и валидация пакета документов от ДРБ</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>ДУП и ДРБ</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I3" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="20" t="n">
+      <c r="J3" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I3" s="20" t="n">
+      <c r="M3" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="J3" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" s="21" t="n">
+      <c r="N3" s="21" t="n">
         <v>86</v>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
-      <c r="N3" s="12" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>Регламент и чек-лист</t>
         </is>
       </c>
-      <c r="O3" s="12" t="inlineStr">
-        <is>
-          <t>Описать правило очерёдности: какой платёж попадает в начало реестра и почему</t>
-        </is>
-      </c>
-      <c r="P3" s="12" t="inlineStr">
-        <is>
-          <t>1.9.1</t>
-        </is>
-      </c>
       <c r="Q3" s="12" t="inlineStr">
         <is>
-          <t>Ядро узких мест 6 и 7: правила, по которому платёж попадает в начало или в конец реестра, не существует, поэтому очередность определяется телефонным звонком. Формализация умещается на одну страницу, а эффект измеряется днями просрочки перед подрядчиками.</t>
+          <t>Утвердить чек-лист минимального пакета и правило возврата неполного комплекта</t>
         </is>
       </c>
       <c r="R3" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Wait Time %; COPQ</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>Первый объект цепочки: дефект пакета на входе проявляется на всех последующих подпроцессах — от ФЭМ до закупок и приёмки. Минимальный состав пакета не зафиксирован письменно (узкие места 1 и 4), поэтому старт проекта растягивается на доуточнения. Исправляется одним чек-листом и одним письмом в ДРБ — это лучшее соотношение эффекта к усилию во всём реестре.</t>
+        </is>
+      </c>
+      <c r="T3" s="12" t="inlineStr">
+        <is>
+          <t>Cycle Time; On-Time %; Defect Rate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>1.1.1</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Реализация проекта</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Приём и валидация пакета документов от ДРБ</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>1.1.2</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20" t="n">
+      <c r="M4" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I4" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L4" s="21" t="n">
-        <v>85</v>
-      </c>
-      <c r="M4" s="22" t="inlineStr">
+      <c r="N4" s="21" t="n">
+        <v>69</v>
+      </c>
+      <c r="O4" s="22" t="inlineStr">
         <is>
           <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
-      <c r="N4" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O4" s="12" t="inlineStr">
-        <is>
-          <t>Ввести обязательную проверку по чек-листу до регистрации проекта в портфеле</t>
-        </is>
-      </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
+          <t>SLA на стык с ЦО</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>Зафиксировать в письме ДРБ норматив срока передачи пакета и форму карточки проекта</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="Q4" s="12" t="inlineStr">
-        <is>
-          <t>Самый дешёвый контроль во всей цепочке: проверка по чек-листу занимает часы и отсекает дефект до того, как он превратится в неверный ФЭМ и неверную спецификацию закупки. Процессом владеет ДУП, поэтому внешних согласований не требуется вовсе.</t>
-        </is>
-      </c>
-      <c r="R4" s="12" t="inlineStr">
-        <is>
-          <t>Defect Rate; First Pass Yield; Rework Rate</t>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>Точка входа, которой ДУП не управляет: пакет формирует ДРБ. Берётся в одном пакете работ с 1.1, потому что норматив срока без чек-листа состава не имеет смысла — быстро переданный неполный пакет хуже, чем переданный вовремя полный.</t>
+        </is>
+      </c>
+      <c r="T4" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; SLA Compliance %</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>1.1.2</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Реализация проекта</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Приём и валидация пакета документов от ДРБ</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Проверка полноты пакета (договор, ФЭМ, ТЗ, адресная программа)</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Формирование реестра платежей и приоритизация</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G5" s="18" t="n">
+      <c r="K5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="21" t="n">
-        <v>83</v>
-      </c>
-      <c r="M5" s="22" t="inlineStr">
+      <c r="N5" s="21" t="n">
+        <v>85</v>
+      </c>
+      <c r="O5" s="22" t="inlineStr">
         <is>
           <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
-      <c r="N5" s="12" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>Регламент и чек-лист</t>
         </is>
       </c>
-      <c r="O5" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить инструкцию по трём потокам платежей и единую форму реестра</t>
-        </is>
-      </c>
-      <c r="P5" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q5" s="12" t="inlineStr">
         <is>
-          <t>Три потока платежей (ВУ / КИЗ / КОЗ) не формализованы, единой инструкции нет (узкие места 6 и 7). Задержка оплаты останавливает монтаж, то есть деньги и срок здесь связаны напрямую. Инструкция пишется внутри ДУП, от Финблока нужен только календарь приёма реестра — поэтому объект попадает в волну быстрых побед.</t>
+          <t>Ввести обязательную проверку по чек-листу до регистрации проекта в портфеле</t>
         </is>
       </c>
       <c r="R5" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Cycle Time; COPQ</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>Самый дешёвый контроль во всей цепочке: проверка по чек-листу занимает часы и отсекает дефект до того, как он превратится в неверный ФЭМ и неверную спецификацию закупки. Процессом владеет ДУП, поэтому внешних согласований не требуется вовсе.</t>
+        </is>
+      </c>
+      <c r="T5" s="12" t="inlineStr">
+        <is>
+          <t>Defect Rate; First Pass Yield; Rework Rate</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>1.1.3</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -1695,75 +1744,85 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
+          <t>Реализация проекта</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="20" t="n">
+          <t>Приём и валидация пакета документов от ДРБ</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Регистрация проекта в портфеле / системе</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" s="21" t="n">
-        <v>82</v>
-      </c>
-      <c r="M6" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N6" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O6" s="12" t="inlineStr">
-        <is>
-          <t>Ввести форму заявки и правило: тех. карты СТ собираются до подачи заявки</t>
+      <c r="N6" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="27" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
+          <t>Автоматизация</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>Определить обязательные поля карточки проекта в SimBASE и запретить регистрацию без них</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="Q6" s="12" t="inlineStr">
-        <is>
-          <t>Этот шаг целиком внутри ДУП: полнота заявки и наличие тех. карт определяют, сколько раз процедура вернётся на доработку. Его можно исправить, не дожидаясь договорённостей с Закупщиками, поэтому он остаётся в волне 1 отдельно от остальной части объекта 1.7.</t>
-        </is>
-      </c>
-      <c r="R6" s="12" t="inlineStr">
-        <is>
-          <t>First Pass Yield; Rework Rate; Defect Rate</t>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>Ручная регистрация сама по себе потерь почти не создаёт, поэтому балл низкий. Но именно она задаёт единый идентификатор проекта, без которого метрики по портфелю нельзя собрать автоматически. Объект берётся не ради экономии, а как обязательный элемент единой карточки проекта.</t>
+        </is>
+      </c>
+      <c r="T6" s="12" t="inlineStr">
+        <is>
+          <t>Уровень автоматизации; Cycle Time</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1773,387 +1832,451 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Прогноз поступлений / расходов и контроль бюджета</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="19" t="n">
+          <t>Реализация проекта</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Назначение куратора (проект и филиал)</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="20" t="n">
-        <v>4</v>
-      </c>
       <c r="J7" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="21" t="n">
-        <v>73</v>
-      </c>
-      <c r="M7" s="22" t="inlineStr">
+      <c r="M7" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
-      <c r="N7" s="12" t="inlineStr">
+      <c r="P7" s="12" t="inlineStr">
         <is>
           <t>Регламент и чек-лист</t>
         </is>
       </c>
-      <c r="O7" s="12" t="inlineStr">
-        <is>
-          <t>Завести единый реестр прогноза и календарь его обновления</t>
-        </is>
-      </c>
-      <c r="P7" s="12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
-          <t>Прогноз ведётся в чатах и ad-hoc (узкие места 6 и 7), из-за чего компания узнаёт о разрыве поступлений позже, чем могла бы. Реестр и календарь — инструменты внутри ДУП: от Финблока нужна только форма выгрузки. Это делает объект исполнимым в волне 1. Встречный срок Финблока фиксируется отдельно, на этапе 2.3.2.</t>
+          <t>Утвердить одну матрицу «филиал → куратор» и срок назначения от даты регистрации проекта</t>
         </is>
       </c>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Budget Variance; Cycle Time</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="inlineStr">
+        <is>
+          <t>Куратор проекта и куратор филиала — одна запись. Процесс исполняется, но срок назначения не нормирован, и проект какое-то время живёт без ответственного на местах (узкое место 8). Закрывается одной матрицей и одной строкой в регламенте.</t>
+        </is>
+      </c>
+      <c r="T7" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Назначение бизнес-владельца</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Сбор данных и подтверждений по проектам</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="n">
+          <t>Реализация проекта</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Разработка проектной документации (устав, план, приказ)</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" s="21" t="n">
-        <v>72</v>
-      </c>
-      <c r="M8" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N8" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить форму и срок подачи данных филиалами в реестр прогноза</t>
+      <c r="N8" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="O8" s="27" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>Шаблонизация</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
-          <t>Шаг, который ДУП выполняет сам и который определяет достоверность всего прогноза. Отсутствие формы и срока — причина того, что данные приходят разрозненно и требуют ручной сверки.</t>
+          <t>Утвердить типовой комплект: устав, план проекта, приказ</t>
         </is>
       </c>
       <c r="R8" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; First Pass Yield; Defect Rate</t>
+          <t>1.1.2</t>
+        </is>
+      </c>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>Объект исполняется, узких мест по нему не зафиксировано, поэтому в первых волнах он вытеснил бы более острые задачи. Берётся ради масштабируемости: типовой комплект сокращает подготовку документации и делает проекты сравнимыми между собой — без этого портфельная отчётность собирается вручную.</t>
+        </is>
+      </c>
+      <c r="T8" s="12" t="inlineStr">
+        <is>
+          <t>Cycle Time; Трудоёмкость объекта</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
+          <t>Реализация проекта</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
+          <t>Разработка проектной документации (устав, план, приказ)</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Оформление приказа на реализацию</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G9" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" s="24" t="n">
+      <c r="I9" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="K9" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="21" t="n">
-        <v>72</v>
-      </c>
-      <c r="M9" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N9" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить форму фиксации дефекта и маршрут «эксплуатация → владелец ТЗ → закупки»</t>
+      <c r="N9" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="O9" s="27" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Шаблонизация</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
-          <t>Ущерб уже реализовался: кейс с хомутами показал, что сведения о дефекте компонента из эксплуатации не доходят до владельца технического задания и повторяются в следующей закупке (узкое место 9). Владелец закреплён за замом по операционной деятельности — тем, кто дефект обнаруживает и несёт потери от его повторения. Осталось описать маршрут: фиксация дефекта делается внутри ДУП, встречный срок реакции СТ фиксируется в волне 2 через объект Б.7.</t>
+          <t>Свести устав и план в единую форму приказа на реализацию</t>
         </is>
       </c>
       <c r="R9" s="12" t="inlineStr">
         <is>
-          <t>COPQ; Defect Rate; Rework Rate</t>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>Последний шаг комплекта 1.4, а не отдельный процесс. Исполняется, узких мест нет. Эффект — экономия времени на оформлении, поэтому шаг идёт вместе с типовым комплектом, а не раньше объектов с деньгами и сроками.</t>
+        </is>
+      </c>
+      <c r="T9" s="12" t="inlineStr">
+        <is>
+          <t>Cycle Time</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>9</v>
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>ГП</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Отчётность по проектам</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Вывод продукта в реализацию</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" s="21" t="n">
-        <v>71</v>
-      </c>
-      <c r="M10" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N10" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить один регламент отчётности: проект, операция, портфель</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O10" s="28" t="inlineStr">
+        <is>
+          <t>Не оценивается — агрегирующий уровень</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Агрегирующий уровень</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr">
         <is>
-          <t>Три отчёта собирались отдельно и описывали одни и те же данные. Один регламент внутри ДУП задаёт частоту, адресата и запрет повторного сбора. Самое дешёвое восстановление управляемости портфеля: внешних согласований нет.</t>
+          <t>Отдельных действий не требуется — очередь ведётся по подпроцессу 1.2</t>
         </is>
       </c>
       <c r="R10" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Time-to-Complete; Трудоёмкость объекта</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>Головной процесс вывода продукта. Оценку и место в очереди получает подпроцесс подтверждения готовности и его этап, чтобы одна работа не считалась дважды.</t>
+        </is>
+      </c>
+      <c r="T10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>4.3.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Статус-встречи по проекту</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="n">
+          <t>Вывод продукта в реализацию</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Подтверждение готовности продукта (пилот)</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="24" t="n">
+      <c r="K11" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" s="21" t="n">
-        <v>71</v>
-      </c>
-      <c r="M11" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N11" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>Ввести статус-встречи: частота, повестка, протокол, адресат решений</t>
+      <c r="N11" s="21" t="n">
+        <v>83</v>
+      </c>
+      <c r="O11" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>Проектирование TO-BE</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>Проектный уровень контура. Регламента нет, обязанности менеджера центрального аппарата исполняются примерно на одну шестую (узкое место 8). Идёт сразу за общим регламентом отчётности.</t>
+          <t>Разработать регламент gate: критерии пилота, подпись директора ДУП и право блокировать старт</t>
         </is>
       </c>
       <c r="R11" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Time-to-Complete; CSAT internal</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>Один из двух подлинных пробелов: процедуры не существует. Решение о готовности продукта принимает ДРБ, а последствия незрелого продукта несёт ДУП. Ядро регламента — право директора ДУП не пускать проект в реализацию без подписи: без блокировки gate остаётся уведомлением. Берётся в волне 2, потому что регламент проектируется с нуля и согласуется с внешним владельцем.</t>
+        </is>
+      </c>
+      <c r="T11" s="12" t="inlineStr">
+        <is>
+          <t>First Pass Yield; COPQ; Defect Rate</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>1.1.1</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -2163,465 +2286,541 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Получение карточки проекта и комплекта документов от ДРБ</t>
+          <t>Вывод продукта в реализацию</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
+          <t>Подтверждение готовности продукта (пилот)</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Проверка завершения пилота / тестовой эксплуатации</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
           <t>ДРБ</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="H12" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="I12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="J12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="19" t="n">
+      <c r="M12" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" s="21" t="n">
+      <c r="N12" s="21" t="n">
         <v>69</v>
       </c>
-      <c r="M12" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N12" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>Зафиксировать в письме ДРБ норматив срока передачи пакета и форму карточки проекта</t>
+      <c r="O12" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>Проектирование TO-BE</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
-          <t>Точка входа, которой ДУП не управляет: пакет формирует ДРБ. Берётся в одном пакете работ с 1.1, потому что норматив срока без чек-листа состава не имеет смысла — быстро переданный неполный пакет хуже, чем переданный вовремя полный.</t>
+          <t>Определить измеримые критерии завершения пилота и форму подтверждения от ДРБ</t>
         </is>
       </c>
       <c r="R12" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; SLA Compliance %</t>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>Без измеримых критериев готовности подпись под gate превращается в формальность. Это содержательная часть нового регламента: сначала критерии, затем процедура подписания.</t>
+        </is>
+      </c>
+      <c r="T12" s="12" t="inlineStr">
+        <is>
+          <t>First Pass Yield; CSAT internal</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>12</v>
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>1.9.1</t>
+          <t>БЖ</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Агрегация заявок и данных филиалов</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Бюджетирование проекта</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="H13" s="30" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G13" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" s="21" t="n">
-        <v>69</v>
-      </c>
-      <c r="M13" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>Ввести единую форму заявки филиала и срок её подачи до даты формирования реестра</t>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O13" s="28" t="inlineStr">
+        <is>
+          <t>Не оценивается — агрегирующий уровень</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>Агрегирующий уровень</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr">
         <is>
-          <t>Сбор заявок в разных форматах и без общего срока — причина того, что реестр собирается в авральном режиме. Унификация формы даёт эффект сразу и не требует ничего, кроме распоряжения по филиалам.</t>
+          <t>Отдельных действий не требуется — очередь ведётся по подпроцессу 1.5</t>
         </is>
       </c>
       <c r="R13" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; First Pass Yield</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S13" s="12" t="inlineStr">
+        <is>
+          <t>Головной процесс бюджетирования. Оценку получает формирование ФЭМ и его этапы.</t>
+        </is>
+      </c>
+      <c r="T13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>2</t>
+        <v>28</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D14" s="27" t="inlineStr">
-        <is>
-          <t>Постпроектное сопровождение</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="n">
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Бюджетирование проекта</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Формирование и согласование бюджета (ФЭМ)</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H14" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="24" t="n">
+      <c r="M14" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="21" t="n">
-        <v>68</v>
-      </c>
-      <c r="M14" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N14" s="12" t="inlineStr">
-        <is>
-          <t>Паспорт процесса и границы</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить паспорт процесса сопровождения: границы, вход, выход и три показателя</t>
+      <c r="N14" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="O14" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr">
         <is>
-          <t>Фаза, в которой создаётся доход компании, описана хуже строительной: у блока 2 нет ни общих границ, ни показателей, ни регулярного учёта доходности объекта. Владелец — зам. по операционной деятельности — закреплён, но спрашивать с него не с чем: паспорта процесса нет, а по п. 176 Методики показатель без источника данных не учитывается. Вход процесса — принятый комплект объекта, его описывает чек-лист передачи (2.0). Оба документа входят в волну запуска и не держат очередь друг друга: место каждого задаёт балл.</t>
+          <t>Провести ревизию нормативов ФЭМ и согласовать с Финблоком срок рассмотрения модели</t>
         </is>
       </c>
       <c r="R14" s="12" t="inlineStr">
         <is>
-          <t>Паспорт процесса и карта SIPOC; Budget Variance; Назначение бизнес-владельца</t>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>Нормативы ФЭМ устарели (узкое место 11): бюджет проекта считается по ценам и нормам, не отражающим ни текущую стоимость поверки, ни фактическую частоту переносов. Ошибка здесь дороже любой другой — она тиражируется на весь срок проекта и возвращается перерасходом в блоке 2. Идёт в волне 2, потому что процессом целиком владеет Финблок, а данные для пересмотра норм даёт реестр переносов из волны 2.</t>
+        </is>
+      </c>
+      <c r="T14" s="12" t="inlineStr">
+        <is>
+          <t>Budget Variance; Стоимость объекта; SLA Compliance %</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Обработка запросов на перенос оборудования</t>
+          <t>Бюджетирование проекта</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G15" s="19" t="n">
+          <t>Формирование и согласование бюджета (ФЭМ)</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Формирование ФЭМ по шаблону</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H15" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" s="20" t="n">
+      <c r="K15" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="J15" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" s="21" t="n">
-        <v>66</v>
-      </c>
-      <c r="M15" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N15" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O15" s="12" t="inlineStr">
-        <is>
-          <t>Завести реестр переносов с сопоставлением «факт против ФЭМ»</t>
+      <c r="M15" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>83</v>
+      </c>
+      <c r="O15" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Пересмотр экономики</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr">
         <is>
-          <t>Переносы выполняются, но нигде не сопоставляются с количеством, заложенным в модель (узкое место 12), поэтому перерасход обнаруживается в конце года. Реестр заводится одной таблицей и решает вторую задачу: даёт фактические данные для ревизии нормативов ФЭМ в волне 2. Без него пересмотр норм снова будет экспертной оценкой.</t>
+          <t>Пересчитать нормы поверки, переносов и логистики по фактическим данным за два года</t>
         </is>
       </c>
       <c r="R15" s="12" t="inlineStr">
         <is>
-          <t>Budget Variance; COPQ; Пропускная способность</t>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>Единственный шаг процесса ФЭМ, который выполняет ДУП, и именно в нём применяются устаревшие нормы. Самая дешёвая правка с наибольшим денежным следом: меняются не шаги процесса, а числа в модели.</t>
+        </is>
+      </c>
+      <c r="T15" s="12" t="inlineStr">
+        <is>
+          <t>Budget Variance; Стоимость объекта</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>1</t>
+        <v>36</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D16" s="27" t="inlineStr">
-        <is>
-          <t>Реализация проекта</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Бюджетирование проекта</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" s="24" t="n">
+          <t>Формирование и согласование бюджета (ФЭМ)</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Проверка и согласование ФЭМ</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H16" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="24" t="n">
+      <c r="L16" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" s="21" t="n">
-        <v>64</v>
-      </c>
-      <c r="M16" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N16" s="12" t="inlineStr">
-        <is>
-          <t>Паспорт процесса и границы</t>
-        </is>
-      </c>
-      <c r="O16" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить паспорт процесса реализации: границы, вход, выход и три показателя</t>
+      <c r="N16" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="O16" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr">
         <is>
-          <t>Владелец закреплён — зам. по строительству и реализации, и это решение действует. Но девять подпроцессов блока не имеют общего описания: где фаза начинается, чем заканчивается и по каким показателям оценивается. Глава 8 и Приложение №2 Методики делают паспорт обязательным атрибутом процесса. Он пишется в волне запуска вместе с быстрыми победами и занимает место по баллу: чек-листы блока не ждут его утверждения. Общая граница с блоком 2 описана чек-листом передачи (2.0); оба документа делаются в одной волне.</t>
+          <t>Зафиксировать в SLA срок рассмотрения ФЭМ Финблоком и состав замечаний</t>
         </is>
       </c>
       <c r="R16" s="12" t="inlineStr">
         <is>
-          <t>Паспорт процесса и карта SIPOC; On-Time %; Назначение бизнес-владельца</t>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="S16" s="12" t="inlineStr">
+        <is>
+          <t>Шаг создаёт ожидание внутри цикла согласования бюджета, но целиком зависит от Финблока. Предметом работы является не порядок шагов, а норматив срока и требование давать замечания одним пакетом, а не итерациями.</t>
+        </is>
+      </c>
+      <c r="T16" s="12" t="inlineStr">
+        <is>
+          <t>Wait Time %; SLA Compliance %; Rework Rate</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Передача проекта «реализация → сопровождение»</t>
+          <t>Бюджетирование проекта</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" s="24" t="n">
+          <t>Формирование и согласование бюджета (ФЭМ)</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Утверждение бюджета, кредитование при необходимости</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="24" t="n">
+      <c r="J17" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" s="21" t="n">
-        <v>64</v>
-      </c>
-      <c r="M17" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N17" s="12" t="inlineStr">
-        <is>
-          <t>Проектирование TO-BE</t>
-        </is>
-      </c>
-      <c r="O17" s="12" t="inlineStr">
-        <is>
-          <t>Спроектировать чек-лист передачи и внести обязательную дату handover в карточку проекта</t>
+      <c r="K17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="O17" s="28" t="inlineStr">
+        <is>
+          <t>Вне очереди — наблюдение</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Наблюдение — вмешательство не планируется</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr">
         <is>
-          <t>Владелец точки передачи закреплён за передающей стороной — замом по строительству и реализации: принимающая сторона не может отвечать за полноту того, что ей не передали. Но самой процедуры не существует — момент, в который объект перестаёт быть стройкой и становится источником дохода, нигде не зафиксирован. Этот момент одновременно является выходом процесса блока 1 и входом процесса блока 2. Чек-лист описывает общую границу и делается в той же волне, что и оба паспорта; в очереди он стоит по своему баллу.</t>
+          <t>Отдельных действий не требуется — срок входит в SLA по объекту 1.5</t>
         </is>
       </c>
       <c r="R17" s="12" t="inlineStr">
         <is>
-          <t>Назначение бизнес-владельца; Паспорт процесса и карта SIPOC</t>
+          <t>1.5.2</t>
+        </is>
+      </c>
+      <c r="S17" s="12" t="inlineStr">
+        <is>
+          <t>Решение принимает Финблок, ДУП только получает утверждённый бюджет. Оптимизировать нечего: единственный управляемый параметр — срок, и он фиксируется в SLA по родительскому объекту.</t>
+        </is>
+      </c>
+      <c r="T17" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>ЗК</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -2629,77 +2828,99 @@
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>Методология и контроль качества (ПМО)</t>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Осуществление закупок</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" s="21" t="n">
-        <v>64</v>
-      </c>
-      <c r="M18" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N18" s="12" t="inlineStr">
-        <is>
-          <t>Паспорт процесса и границы</t>
-        </is>
-      </c>
-      <c r="O18" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить паспорт процесса методологии и положение о контроле качества проектных данных</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="H18" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O18" s="28" t="inlineStr">
+        <is>
+          <t>Не оценивается — агрегирующий уровень</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Агрегирующий уровень</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
-          <t>Роль главного менеджера проектов — несущая конструкция всей трансформации: именно она ведёт паспорта остальных процессов, аудит и портфельную отчётность. Владение и право остановить проект по результатам аудита закреплены, но собственного паспорта у процесса нет, а методолог без описанных границ своей работы не может требовать описания чужих. Объект никого не ждёт и идёт параллельно паспортам блоков 1 и 2.</t>
+          <t>Отдельных действий не требуется — очередь ведётся по подпроцессу 1.7</t>
         </is>
       </c>
       <c r="R18" s="12" t="inlineStr">
         <is>
-          <t>Паспорт процесса и карта SIPOC; Defect Rate; Назначение бизнес-владельца</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>Головной процесс закупок. Оценку получает инициация и контроль закупок и его этапы.</t>
+        </is>
+      </c>
+      <c r="T18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -2709,75 +2930,85 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Выявление нехватки бюджета и вынесение на ОСУ</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>ДУП и ОСУ</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="24" t="n">
+          <t>Осуществление закупок</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Инициация и контроль закупок</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="H19" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" s="21" t="n">
-        <v>59</v>
-      </c>
-      <c r="M19" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N19" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O19" s="12" t="inlineStr">
-        <is>
-          <t>Зафиксировать порог и срок вынесения вопроса о нехватке бюджета на ОСУ</t>
+      <c r="N19" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="O19" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>Объект исполняется, но порог и срок вынесения не формализованы, поэтому вопрос попадает на утверждающий орган тогда, когда деньги уже потрачены. Формализация критерия — одна строка регламента, а эффект — возможность принять решение, пока оно ещё что-то меняет.</t>
+          <t>Согласовать с Закупщиками нормативы сроков по шагам процедуры и правило эскалации</t>
         </is>
       </c>
       <c r="R19" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Budget Variance</t>
+          <t>1.7.1</t>
+        </is>
+      </c>
+      <c r="S19" s="12" t="inlineStr">
+        <is>
+          <t>Закупки — главный источник срыва сроков реализации (узкое место 13): нормативов по шагам процедуры нет, и задержка обнаруживается постфактум, когда сдвинуть уже нечего. Это единственный внешний процесс, где ДУП стоит и на входе, и на выходе, то есть рычаг есть с обеих сторон. В волне 2, потому что нормативы устанавливаются совместно с владельцем процедуры.</t>
+        </is>
+      </c>
+      <c r="T19" s="12" t="inlineStr">
+        <is>
+          <t>Cycle Time; SLA Compliance %; Wait Time %</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Б.5.1</t>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -2787,153 +3018,173 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Участие ДУП: потребность, данные по региону, приём площадки</t>
+          <t>Осуществление закупок</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="n">
+          <t>Инициация и контроль закупок</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Инициация заявки, сбор спецификаций и тех. карт (со СТ)</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="H20" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" s="20" t="n">
+      <c r="L20" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L20" s="21" t="n">
-        <v>59</v>
-      </c>
-      <c r="M20" s="22" t="inlineStr">
+      <c r="M20" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" s="21" t="n">
+        <v>82</v>
+      </c>
+      <c r="O20" s="22" t="inlineStr">
         <is>
           <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
-      <c r="N20" s="12" t="inlineStr">
+      <c r="P20" s="12" t="inlineStr">
         <is>
           <t>Регламент и чек-лист</t>
         </is>
       </c>
-      <c r="O20" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить критерий инициации открытия филиала и форму обоснования потребности</t>
-        </is>
-      </c>
-      <c r="P20" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>Вход в процесс: решение об открытии сегодня рождается по факту появления проекта в регионе без филиала, то есть поздно и авралом. Этап целиком в границах операционного контура ДУП, поэтому критерий и форма обоснования утверждаются внутренним документом, не дожидаясь сквозного маршрута.</t>
+          <t>Ввести форму заявки и правило: тех. карты СТ собираются до подачи заявки</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Cycle Time</t>
+          <t>1.1.2</t>
+        </is>
+      </c>
+      <c r="S20" s="12" t="inlineStr">
+        <is>
+          <t>Этот шаг целиком внутри ДУП: полнота заявки и наличие тех. карт определяют, сколько раз процедура вернётся на доработку. Его можно исправить, не дожидаясь договорённостей с Закупщиками, поэтому он остаётся в волне 1 отдельно от остальной части объекта 1.7.</t>
+        </is>
+      </c>
+      <c r="T20" s="12" t="inlineStr">
+        <is>
+          <t>First Pass Yield; Rework Rate; Defect Rate</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1.7.2</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Контроль качества и полноты проектных данных</t>
+          <t>Осуществление закупок</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="28" t="n">
+          <t>Инициация и контроль закупок</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Проведение процедуры закупки</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L21" s="21" t="n">
-        <v>57</v>
-      </c>
-      <c r="M21" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N21" s="12" t="inlineStr">
-        <is>
-          <t>Базовая линия и замер</t>
-        </is>
-      </c>
-      <c r="O21" s="12" t="inlineStr">
-        <is>
-          <t>Провести пилотный аудит одного филиала и развернуть его на весь портфель</t>
+      <c r="N21" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="O21" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
-          <t>Аудит остановлен после 2020 года, поэтому ни одно утверждение о состоянии процессов нельзя подтвердить цифрой. Пилот одного филиала не ждёт согласований: чек-листы готовы, филиал выбирает директор. Регулярный аудит на портфель имеет смысл, когда его результат влечёт последствия: право остановить проект зафиксировано за владельцем методологии вместе с паспортом процесса 4.</t>
+          <t>Внести шаги процедуры в общий трекер и установить точку эскалации при просрочке</t>
         </is>
       </c>
       <c r="R21" s="12" t="inlineStr">
         <is>
-          <t>Defect Rate; First Pass Yield; Паспорт процесса и карта SIPOC</t>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="S21" s="12" t="inlineStr">
+        <is>
+          <t>Самая длинная по времени часть цепочки реализации и при этом целиком вне периметра ДУП. По п. 140 Методики оптимизация соседних шагов не сократит общее время, пока не снято это ограничение, — поэтому объект берётся, хотя лёгкость реализации минимальная.</t>
+        </is>
+      </c>
+      <c r="T21" s="12" t="inlineStr">
+        <is>
+          <t>Cycle Time; Bottleneck Index; SLA Compliance %</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>1.7.3</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -2943,75 +3194,87 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Операционный статус руководству и госпартнёру</t>
+          <t>Осуществление закупок</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="n">
+          <t>Инициация и контроль закупок</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Контроль сроков поставки и приёмка</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" s="21" t="n">
-        <v>56</v>
-      </c>
-      <c r="M22" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N22" s="12" t="inlineStr">
-        <is>
-          <t>Устранение дублей и упрощение</t>
-        </is>
-      </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>Собирать операционный статус из протокола статус-встреч, без второго опроса</t>
+      <c r="N22" s="21" t="n">
+        <v>83</v>
+      </c>
+      <c r="O22" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>4.3.1</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
-          <t>Операционный отчёт госпартнёру и руководству повторял данные проектного статуса. После того как статус-встречи задают проектный уровень, этот этап только выбирает из них нужный срез.</t>
+          <t>Утвердить форму приёмки с фиксацией дефектов и маршрутом их передачи владельцу ТЗ</t>
         </is>
       </c>
       <c r="R22" s="12" t="inlineStr">
         <is>
-          <t>Трудоёмкость объекта; Rework Rate; CSAT external</t>
+          <t>1.7.2</t>
+        </is>
+      </c>
+      <c r="S22" s="12" t="inlineStr">
+        <is>
+          <t>Точка, где ДУП принимает результат и где обнаруживаются дефекты компонентов. Связана с объектом 2.7: без маршрута обратной связи дефект принимается молча и повторяется в следующей закупке — так возник кейс с хомутами.</t>
+        </is>
+      </c>
+      <c r="T22" s="12" t="inlineStr">
+        <is>
+          <t>Defect Rate; COPQ; On-Time %</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>ПЛ</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -3019,77 +3282,99 @@
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
-        <is>
-          <t>Управление филиальной сетью</t>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>Проведение платежей по проектам</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" s="21" t="n">
-        <v>55</v>
-      </c>
-      <c r="M23" s="22" t="inlineStr">
-        <is>
-          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
-        </is>
-      </c>
-      <c r="N23" s="12" t="inlineStr">
-        <is>
-          <t>Регламент и чек-лист</t>
-        </is>
-      </c>
-      <c r="O23" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить паспорт процесса филиальной сети: отношения вне проекта и стык с открытием филиала</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H23" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O23" s="28" t="inlineStr">
+        <is>
+          <t>Не оценивается — агрегирующий уровень</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>1, 2</t>
+          <t>Агрегирующий уровень</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr">
         <is>
-          <t>Владение закреплено за директором ДУП. Назначение куратора вынесено в одну матрицу (1.3), открытие филиала — в сквозной маршрут (Б.5). У самого процесса паспорта нет, поэтому регламент по филиальной сети исполняется на усмотрение исполнителя.</t>
+          <t>Отдельных действий не требуется — очередь ведётся по подпроцессу 1.9</t>
         </is>
       </c>
       <c r="R23" s="12" t="inlineStr">
         <is>
-          <t>Паспорт процесса и карта SIPOC; Cycle Time; On-Time %</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S23" s="12" t="inlineStr">
+        <is>
+          <t>Головной процесс платежей. Оценку получает реестр платежей и его этапы.</t>
+        </is>
+      </c>
+      <c r="T23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -3099,75 +3384,85 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Назначение куратора (проект и филиал)</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="n">
+          <t>Проведение платежей по проектам</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Формирование реестра платежей и приоритизация</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H24" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L24" s="21" t="n">
-        <v>54</v>
-      </c>
-      <c r="M24" s="22" t="inlineStr">
+      <c r="N24" s="21" t="n">
+        <v>83</v>
+      </c>
+      <c r="O24" s="22" t="inlineStr">
         <is>
           <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
-      <c r="N24" s="12" t="inlineStr">
+      <c r="P24" s="12" t="inlineStr">
         <is>
           <t>Регламент и чек-лист</t>
         </is>
       </c>
-      <c r="O24" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить одну матрицу «филиал → куратор» и срок назначения от даты регистрации проекта</t>
-        </is>
-      </c>
-      <c r="P24" s="12" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
       <c r="Q24" s="12" t="inlineStr">
         <is>
-          <t>Куратор проекта и куратор филиала — одна запись. Процесс исполняется, но срок назначения не нормирован, и проект какое-то время живёт без ответственного на местах (узкое место 8). Закрывается одной матрицей и одной строкой в регламенте.</t>
+          <t>Утвердить инструкцию по трём потокам платежей и единую форму реестра</t>
         </is>
       </c>
       <c r="R24" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; Назначение бизнес-владельца</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>Три потока платежей (ВУ / КИЗ / КОЗ) не формализованы, единой инструкции нет (узкие места 6 и 7). Задержка оплаты останавливает монтаж, то есть деньги и срок здесь связаны напрямую. Инструкция пишется внутри ДУП, от Финблока нужен только календарь приёма реестра — поэтому объект попадает в волну быстрых побед.</t>
+        </is>
+      </c>
+      <c r="T24" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Cycle Time; COPQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>4.3.3</t>
+          <t>1.9.1</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -3177,309 +3472,349 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Портфельная отчётность руководству и заказчикам</t>
+          <t>Проведение платежей по проектам</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="n">
+          <t>Формирование реестра платежей и приоритизация</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Агрегация заявок и данных филиалов</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H25" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" s="20" t="n">
+      <c r="M25" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L25" s="21" t="n">
-        <v>52</v>
-      </c>
-      <c r="M25" s="22" t="inlineStr">
+      <c r="N25" s="21" t="n">
+        <v>69</v>
+      </c>
+      <c r="O25" s="22" t="inlineStr">
         <is>
           <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
-      <c r="N25" s="12" t="inlineStr">
-        <is>
-          <t>Устранение дублей и упрощение</t>
-        </is>
-      </c>
-      <c r="O25" s="12" t="inlineStr">
-        <is>
-          <t>Собирать портфельный отчёт из проектного и операционного статуса</t>
-        </is>
-      </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr">
         <is>
-          <t>Портфель — третий адресат того же контура. Отдельного сбора данных не требует: он складывается из двух предыдущих этапов.</t>
+          <t>Ввести единую форму заявки филиала и срок её подачи до даты формирования реестра</t>
         </is>
       </c>
       <c r="R25" s="12" t="inlineStr">
         <is>
-          <t>Трудоёмкость объекта; Rework Rate</t>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="S25" s="12" t="inlineStr">
+        <is>
+          <t>Сбор заявок в разных форматах и без общего срока — причина того, что реестр собирается в авральном режиме. Унификация формы даёт эффект сразу и не требует ничего, кроме распоряжения по филиалам.</t>
+        </is>
+      </c>
+      <c r="T25" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; First Pass Yield</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.9.2</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Общие отношения с филиалом (вне привязки к проекту)</t>
+          <t>Проведение платежей по проектам</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G26" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" s="18" t="n">
+          <t>Формирование реестра платежей и приоритизация</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Приоритизация реестра (ВУ / КИЗ / КОЗ)</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H26" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="L26" s="21" t="n">
-        <v>41</v>
-      </c>
-      <c r="M26" s="22" t="inlineStr">
+      <c r="J26" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" s="21" t="n">
+        <v>86</v>
+      </c>
+      <c r="O26" s="22" t="inlineStr">
         <is>
           <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
-      <c r="N26" s="12" t="inlineStr">
+      <c r="P26" s="12" t="inlineStr">
         <is>
           <t>Регламент и чек-лист</t>
         </is>
       </c>
-      <c r="O26" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить порядок обращений филиала вне проектной рамки: кто принимает и в какой срок</t>
-        </is>
-      </c>
-      <c r="P26" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="Q26" s="12" t="inlineStr">
         <is>
-          <t>Владелец закреплён за замом по операционной деятельности — обращения филиалов касаются работающих объектов, а не строящихся. Собственной ценности объект почти не создаёт, но закрывается одной страницей регламента, поэтому идёт попутно с остальными объектами блока 3.</t>
+          <t>Описать правило очерёдности: какой платёж попадает в начало реестра и почему</t>
         </is>
       </c>
       <c r="R26" s="12" t="inlineStr">
         <is>
-          <t>On-Time %; CSAT internal</t>
+          <t>1.9.1</t>
+        </is>
+      </c>
+      <c r="S26" s="12" t="inlineStr">
+        <is>
+          <t>Ядро узких мест 6 и 7: правила, по которому платёж попадает в начало или в конец реестра, не существует, поэтому очередность определяется телефонным звонком. Формализация умещается на одну страницу, а эффект измеряется днями просрочки перед подрядчиками.</t>
+        </is>
+      </c>
+      <c r="T26" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Wait Time %; COPQ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.9.3</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Инициация и контроль закупок</t>
+          <t>Проведение платежей по проектам</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H27" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="I27" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" s="21" t="n">
-        <v>84</v>
-      </c>
-      <c r="M27" s="29" t="inlineStr">
+          <t>Формирование реестра платежей и приоритизация</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Решение об оплате и проведение платежа</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="O27" s="29" t="inlineStr">
         <is>
           <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
-      <c r="N27" s="12" t="inlineStr">
+      <c r="P27" s="12" t="inlineStr">
         <is>
           <t>SLA на стык с ЦО</t>
         </is>
       </c>
-      <c r="O27" s="12" t="inlineStr">
-        <is>
-          <t>Согласовать с Закупщиками нормативы сроков по шагам процедуры и правило эскалации</t>
-        </is>
-      </c>
-      <c r="P27" s="12" t="inlineStr">
-        <is>
-          <t>1.7.1</t>
-        </is>
-      </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
-          <t>Закупки — главный источник срыва сроков реализации (узкое место 13): нормативов по шагам процедуры нет, и задержка обнаруживается постфактум, когда сдвинуть уже нечего. Это единственный внешний процесс, где ДУП стоит и на входе, и на выходе, то есть рычаг есть с обеих сторон. В волне 2, потому что нормативы устанавливаются совместно с владельцем процедуры.</t>
+          <t>Согласовать с Финблоком норматив срока от передачи реестра до проведения платежа</t>
         </is>
       </c>
       <c r="R27" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; SLA Compliance %; Wait Time %</t>
+          <t>1.9.2</t>
+        </is>
+      </c>
+      <c r="S27" s="12" t="inlineStr">
+        <is>
+          <t>Шаг выполняет Финблок, ДУП получает информацию о проведении платежа. Предметом договорённости является норматив срока: без него приоритизация реестра в волне 1 не доводится до результата.</t>
+        </is>
+      </c>
+      <c r="T27" s="12" t="inlineStr">
+        <is>
+          <t>SLA Compliance %; On-Time %</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Подтверждение готовности продукта (пилот)</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>Постпроектное сопровождение</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H28" s="20" t="n">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I28" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I28" s="20" t="n">
+      <c r="J28" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="K28" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="21" t="n">
-        <v>83</v>
-      </c>
-      <c r="M28" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N28" s="12" t="inlineStr">
-        <is>
-          <t>Проектирование TO-BE</t>
-        </is>
-      </c>
-      <c r="O28" s="12" t="inlineStr">
-        <is>
-          <t>Разработать регламент gate: критерии пилота, подпись директора ДУП и право блокировать старт</t>
+      <c r="M28" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N28" s="21" t="n">
+        <v>68</v>
+      </c>
+      <c r="O28" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>Паспорт процесса и границы</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr">
         <is>
-          <t>Один из двух подлинных пробелов: процедуры не существует. Решение о готовности продукта принимает ДРБ, а последствия незрелого продукта несёт ДУП. Ядро регламента — право директора ДУП не пускать проект в реализацию без подписи: без блокировки gate остаётся уведомлением. Берётся в волне 2, потому что регламент проектируется с нуля и согласуется с внешним владельцем.</t>
+          <t>Утвердить паспорт процесса сопровождения: границы, вход, выход и три показателя</t>
         </is>
       </c>
       <c r="R28" s="12" t="inlineStr">
         <is>
-          <t>First Pass Yield; COPQ; Defect Rate</t>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="S28" s="12" t="inlineStr">
+        <is>
+          <t>Фаза, в которой создаётся доход компании, описана хуже строительной: у блока 2 нет ни общих границ, ни показателей, ни регулярного учёта доходности объекта. Владелец — зам. по операционной деятельности — закреплён, но спрашивать с него не с чем: паспорта процесса нет, а по п. 176 Методики показатель без источника данных не учитывается. Вход процесса — принятый комплект объекта, его описывает чек-лист передачи (2.0). Оба документа входят в волну запуска и не держат очередь друг друга: место каждого задаёт балл.</t>
+        </is>
+      </c>
+      <c r="T28" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса и карта SIPOC; Budget Variance; Назначение бизнес-владельца</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -3489,231 +3824,261 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Формирование и согласование бюджета (ФЭМ)</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H29" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" s="18" t="n">
-        <v>5</v>
+          <t>Постпроектное сопровождение</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Передача проекта «реализация → сопровождение»</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="J29" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K29" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="M29" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N29" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O29" s="12" t="inlineStr">
-        <is>
-          <t>Провести ревизию нормативов ФЭМ и согласовать с Финблоком срок рассмотрения модели</t>
+      <c r="M29" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" s="21" t="n">
+        <v>64</v>
+      </c>
+      <c r="O29" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>Проектирование TO-BE</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr">
         <is>
-          <t>Нормативы ФЭМ устарели (узкое место 11): бюджет проекта считается по ценам и нормам, не отражающим ни текущую стоимость поверки, ни фактическую частоту переносов. Ошибка здесь дороже любой другой — она тиражируется на весь срок проекта и возвращается перерасходом в блоке 2. Идёт в волне 2, потому что процессом целиком владеет Финблок, а данные для пересмотра норм даёт реестр переносов из волны 2.</t>
+          <t>Спроектировать чек-лист передачи и внести обязательную дату handover в карточку проекта</t>
         </is>
       </c>
       <c r="R29" s="12" t="inlineStr">
         <is>
-          <t>Budget Variance; Стоимость объекта; SLA Compliance %</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S29" s="12" t="inlineStr">
+        <is>
+          <t>Владелец точки передачи закреплён за передающей стороной — замом по строительству и реализации: принимающая сторона не может отвечать за полноту того, что ей не передали. Но самой процедуры не существует — момент, в который объект перестаёт быть стройкой и становится источником дохода, нигде не зафиксирован. Этот момент одновременно является выходом процесса блока 1 и входом процесса блока 2. Чек-лист описывает общую границу и делается в той же волне, что и оба паспорта; в очереди он стоит по своему баллу.</t>
+        </is>
+      </c>
+      <c r="T29" s="12" t="inlineStr">
+        <is>
+          <t>Назначение бизнес-владельца; Паспорт процесса и карта SIPOC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Формирование ФЭМ по шаблону</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="n">
+          <t>Постпроектное сопровождение</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Организация поверки оборудования</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="19" t="n">
+      <c r="L30" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" s="21" t="n">
-        <v>83</v>
-      </c>
-      <c r="M30" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N30" s="12" t="inlineStr">
+      <c r="M30" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="O30" s="27" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
+        </is>
+      </c>
+      <c r="P30" s="12" t="inlineStr">
         <is>
           <t>Пересмотр экономики</t>
         </is>
       </c>
-      <c r="O30" s="12" t="inlineStr">
-        <is>
-          <t>Пересчитать нормы поверки, переносов и логистики по фактическим данным за два года</t>
-        </is>
-      </c>
-      <c r="P30" s="12" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="Q30" s="12" t="inlineStr">
         <is>
-          <t>Единственный шаг процесса ФЭМ, который выполняет ДУП, и именно в нём применяются устаревшие нормы. Самая дешёвая правка с наибольшим денежным следом: меняются не шаги процесса, а числа в модели.</t>
+          <t>Рассчитать экономику собственной аккредитации против аутсорса поверки</t>
         </is>
       </c>
       <c r="R30" s="12" t="inlineStr">
         <is>
-          <t>Budget Variance; Стоимость объекта</t>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="S30" s="12" t="inlineStr">
+        <is>
+          <t>Самый крупный денежный объект реестра: около 6 000 комплексов на поверке, методика устарела (узкое место 10), стоимость услуги растёт. Оптимизируется не порядок шагов, а модель оказания услуги, поэтому нужен расчёт и бюджетное решение. Берётся после того, как появится достоверная стоимость процесса по методу ABC — иначе сравнивать не с чем.</t>
+        </is>
+      </c>
+      <c r="T30" s="12" t="inlineStr">
+        <is>
+          <t>Стоимость объекта; CPT; ROI автоматизации</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Проверка завершения пилота / тестовой эксплуатации</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="F31" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H31" s="19" t="n">
+          <t>Постпроектное сопровождение</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Сопровождение канала связи</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="I31" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K31" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" s="21" t="n">
-        <v>69</v>
-      </c>
-      <c r="M31" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N31" s="12" t="inlineStr">
-        <is>
-          <t>Проектирование TO-BE</t>
-        </is>
-      </c>
-      <c r="O31" s="12" t="inlineStr">
-        <is>
-          <t>Определить измеримые критерии завершения пилота и форму подтверждения от ДРБ</t>
+      <c r="N31" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="O31" s="27" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>Автоматизация</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr">
         <is>
-          <t>Без измеримых критериев готовности подпись под gate превращается в формальность. Это содержательная часть нового регламента: сначала критерии, затем процедура подписания.</t>
+          <t>Закрепить мониторинг канала связи в Zabbix и правило реакции на отказ</t>
         </is>
       </c>
       <c r="R31" s="12" t="inlineStr">
         <is>
-          <t>First Pass Yield; CSAT internal</t>
+          <t>1.1.3</t>
+        </is>
+      </c>
+      <c r="S31" s="12" t="inlineStr">
+        <is>
+          <t>Объект исполняется, узких мест по нему не зафиксировано. Берётся в последней волне как часть ИТ-контура: дежурный мониторинг дешевле ручных проверок, но самостоятельной управленческой проблемы здесь нет.</t>
+        </is>
+      </c>
+      <c r="T31" s="12" t="inlineStr">
+        <is>
+          <t>Уровень автоматизации; Средний LOA; On-Time %</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
@@ -3723,387 +4088,451 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Инициация продления / модернизации контракта</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G32" s="20" t="n">
+          <t>Постпроектное сопровождение</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Обработка запросов на перенос оборудования</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H32" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="20" t="n">
+      <c r="L32" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="J32" s="20" t="n">
+      <c r="M32" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K32" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L32" s="21" t="n">
-        <v>69</v>
-      </c>
-      <c r="M32" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N32" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O32" s="12" t="inlineStr">
-        <is>
-          <t>Установить срок инициации продления до окончания договора и точку передачи в ДРБ</t>
+      <c r="N32" s="21" t="n">
+        <v>66</v>
+      </c>
+      <c r="O32" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="Q32" s="12" t="inlineStr">
+        <is>
+          <t>Завести реестр переносов с сопоставлением «факт против ФЭМ»</t>
+        </is>
+      </c>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q32" s="12" t="inlineStr">
-        <is>
-          <t>Объект напрямую связан с доходом: пропущенный срок инициации означает паузу или потерю контракта, который уже работает. Сегодня срок отслеживается вручную, а коммерческое предложение готовится совместно с ДРБ — поэтому предметом работы является точка передачи между двумя департаментами, а не внутренняя процедура.</t>
-        </is>
-      </c>
-      <c r="R32" s="12" t="inlineStr">
-        <is>
-          <t>On-Time %; SLA Compliance %; Budget Variance</t>
+      <c r="S32" s="12" t="inlineStr">
+        <is>
+          <t>Переносы выполняются, но нигде не сопоставляются с количеством, заложенным в модель (узкое место 12), поэтому перерасход обнаруживается в конце года. Реестр заводится одной таблицей и решает вторую задачу: даёт фактические данные для ревизии нормативов ФЭМ в волне 2. Без него пересмотр норм снова будет экспертной оценкой.</t>
+        </is>
+      </c>
+      <c r="T32" s="12" t="inlineStr">
+        <is>
+          <t>Budget Variance; COPQ; Пропускная способность</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>1.7.2</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Проведение процедуры закупки</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="F33" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="n">
+          <t>Постпроектное сопровождение</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I33" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H33" s="18" t="n">
+      <c r="J33" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="I33" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K33" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="21" t="n">
-        <v>67</v>
-      </c>
-      <c r="M33" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N33" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O33" s="12" t="inlineStr">
-        <is>
-          <t>Внести шаги процедуры в общий трекер и установить точку эскалации при просрочке</t>
+      <c r="M33" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="O33" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr">
         <is>
-          <t>Самая длинная по времени часть цепочки реализации и при этом целиком вне периметра ДУП. По п. 140 Методики оптимизация соседних шагов не сократит общее время, пока не снято это ограничение, — поэтому объект берётся, хотя лёгкость реализации минимальная.</t>
+          <t>Утвердить форму фиксации дефекта и маршрут «эксплуатация → владелец ТЗ → закупки»</t>
         </is>
       </c>
       <c r="R33" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; Bottleneck Index; SLA Compliance %</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S33" s="12" t="inlineStr">
+        <is>
+          <t>Ущерб уже реализовался: кейс с хомутами показал, что сведения о дефекте компонента из эксплуатации не доходят до владельца технического задания и повторяются в следующей закупке (узкое место 9). Владелец закреплён за замом по операционной деятельности — тем, кто дефект обнаруживает и несёт потери от его повторения. Осталось описать маршрут: фиксация дефекта делается внутри ДУП, встречный срок реакции СТ фиксируется в волне 2 через объект Б.7.</t>
+        </is>
+      </c>
+      <c r="T33" s="12" t="inlineStr">
+        <is>
+          <t>COPQ; Defect Rate; Rework Rate</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="n">
-        <v>33</v>
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>1.7.3</t>
+          <t>ПР</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Контроль сроков поставки и приёмка</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>Прогноз и контроль бюджета</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="F34" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H34" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J34" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K34" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" s="21" t="n">
-        <v>83</v>
-      </c>
-      <c r="M34" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N34" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O34" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить форму приёмки с фиксацией дефектов и маршрутом их передачи владельцу ТЗ</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H34" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O34" s="28" t="inlineStr">
+        <is>
+          <t>Не оценивается — агрегирующий уровень</t>
         </is>
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>1.7.2</t>
+          <t>Агрегирующий уровень</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr">
         <is>
-          <t>Точка, где ДУП принимает результат и где обнаруживаются дефекты компонентов. Связана с объектом 2.7: без маршрута обратной связи дефект принимается молча и повторяется в следующей закупке — так возник кейс с хомутами.</t>
+          <t>Отдельных действий не требуется — очередь ведётся по подпроцессам 2.3 и 2.6</t>
         </is>
       </c>
       <c r="R34" s="12" t="inlineStr">
         <is>
-          <t>Defect Rate; COPQ; On-Time %</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S34" s="12" t="inlineStr">
+        <is>
+          <t>Головной процесс прогноза и контроля бюджета. Оценку получают прогноз поступлений и вынесение нехватки бюджета на ОСУ.</t>
+        </is>
+      </c>
+      <c r="T34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="26" t="inlineStr">
-        <is>
-          <t>Б.7</t>
+        <v>6</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D35" s="27" t="inlineStr">
-        <is>
-          <t>Производство, монтаж и калибровка оборудования</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>СТ</t>
-        </is>
-      </c>
-      <c r="F35" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G35" s="19" t="n">
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Прогноз и контроль бюджета</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Прогноз поступлений / расходов и контроль бюджета</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H35" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="19" t="n">
+      <c r="K35" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M35" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="I35" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" s="21" t="n">
-        <v>57</v>
-      </c>
-      <c r="M35" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N35" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O35" s="12" t="inlineStr">
-        <is>
-          <t>Зафиксировать со СТ срок выдачи тех. карт — до подачи заявки на закупку</t>
+      <c r="N35" s="21" t="n">
+        <v>73</v>
+      </c>
+      <c r="O35" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr">
         <is>
-          <t>Тех. карты нужны до закупки, но этот порядок нигде не закреплён, и спецификация иногда собирается параллельно с заявкой. Объект связан сразу с двумя другими: он питает инициацию закупки (1.7.1) и принимает обратную связь по дефектам (2.7).</t>
+          <t>Завести единый реестр прогноза и календарь его обновления</t>
         </is>
       </c>
       <c r="R35" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Defect Rate</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S35" s="12" t="inlineStr">
+        <is>
+          <t>Прогноз ведётся в чатах и ad-hoc (узкие места 6 и 7), из-за чего компания узнаёт о разрыве поступлений позже, чем могла бы. Реестр и календарь — инструменты внутри ДУП: от Финблока нужна только форма выгрузки. Это делает объект исполнимым в волне 1. Встречный срок Финблока фиксируется отдельно, на этапе 2.3.2.</t>
+        </is>
+      </c>
+      <c r="T35" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Budget Variance; Cycle Time</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="26" t="inlineStr">
-        <is>
-          <t>Б.5</t>
+        <v>7</v>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D36" s="27" t="inlineStr">
-        <is>
-          <t>Открытие нового филиала</t>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Прогноз и контроль бюджета</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G36" s="19" t="n">
+          <t>Прогноз поступлений / расходов и контроль бюджета</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Сбор данных и подтверждений по проектам</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H36" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I36" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H36" s="19" t="n">
+      <c r="K36" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="20" t="n">
+      <c r="L36" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="K36" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" s="21" t="n">
-        <v>56</v>
-      </c>
-      <c r="M36" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N36" s="12" t="inlineStr">
-        <is>
-          <t>Проектирование TO-BE</t>
-        </is>
-      </c>
-      <c r="O36" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить на Операционном комитете сквозной маршрут Юр → HR → Финблок → ДУП и сроки по этапам</t>
+      <c r="M36" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N36" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="O36" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>Б.5.1</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr">
         <is>
-          <t>Единственная строка открытия филиала. Участок ДУП — этап Б.5.1, он описывается раньше. Владельцем по Таблице 4 Методики закреплён директор ДУП как курирующий руководитель кросс-функционального процесса: Юр блок отвечает только за регистрацию, HR — только за штат, за работающий филиал целиком не отвечает никто другой. Назначение владельца чужого сквозного процесса ДУП не утверждает в одностороннем порядке, поэтому объект идёт в волне 2: предметом работы является решение Операционного комитета, а не внутренний документ.</t>
+          <t>Утвердить форму и срок подачи данных филиалами в реестр прогноза</t>
         </is>
       </c>
       <c r="R36" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; On-Time %; Паспорт процесса и карта SIPOC</t>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="S36" s="12" t="inlineStr">
+        <is>
+          <t>Шаг, который ДУП выполняет сам и который определяет достоверность всего прогноза. Отсутствие формы и срока — причина того, что данные приходят разрозненно и требуют ручной сверки.</t>
+        </is>
+      </c>
+      <c r="T36" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; First Pass Yield; Defect Rate</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>2.3.2</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -4113,309 +4542,363 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Проверка и согласование ФЭМ</t>
+          <t>Прогноз и контроль бюджета</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
+          <t>Прогноз поступлений / расходов и контроль бюджета</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Планирование и решение по прогнозу</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G37" s="19" t="n">
+      <c r="H37" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="19" t="n">
+      <c r="J37" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="I37" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K37" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" s="21" t="n">
-        <v>53</v>
-      </c>
-      <c r="M37" s="29" t="inlineStr">
+      <c r="M37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="O37" s="29" t="inlineStr">
         <is>
           <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
-      <c r="N37" s="12" t="inlineStr">
+      <c r="P37" s="12" t="inlineStr">
         <is>
           <t>SLA на стык с ЦО</t>
         </is>
       </c>
-      <c r="O37" s="12" t="inlineStr">
-        <is>
-          <t>Зафиксировать в SLA срок рассмотрения ФЭМ Финблоком и состав замечаний</t>
-        </is>
-      </c>
-      <c r="P37" s="12" t="inlineStr">
-        <is>
-          <t>1.5.1</t>
-        </is>
-      </c>
       <c r="Q37" s="12" t="inlineStr">
         <is>
-          <t>Шаг создаёт ожидание внутри цикла согласования бюджета, но целиком зависит от Финблока. Предметом работы является не порядок шагов, а норматив срока и требование давать замечания одним пакетом, а не итерациями.</t>
+          <t>Согласовать с Финблоком срок возврата утверждённого прогноза в ДУП</t>
         </is>
       </c>
       <c r="R37" s="12" t="inlineStr">
         <is>
-          <t>Wait Time %; SLA Compliance %; Rework Rate</t>
+          <t>2.3.1</t>
+        </is>
+      </c>
+      <c r="S37" s="12" t="inlineStr">
+        <is>
+          <t>Планирование и решение принимает Финблок. ДУП управляет здесь одним параметром — сроком получения утверждённого прогноза, без которого планирование работ на объектах ведётся вслепую.</t>
+        </is>
+      </c>
+      <c r="T37" s="12" t="inlineStr">
+        <is>
+          <t>SLA Compliance %; Wait Time %</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="26" t="inlineStr">
-        <is>
-          <t>Б.10</t>
+        <v>18</v>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>2.6</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Прогноз и контроль бюджета</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Выявление нехватки бюджета и вынесение на ОСУ</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>ДУП и ОСУ</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N38" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="O38" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
+        </is>
+      </c>
+      <c r="P38" s="12" t="inlineStr">
+        <is>
+          <t>Регламент и чек-лист</t>
+        </is>
+      </c>
+      <c r="Q38" s="12" t="inlineStr">
+        <is>
+          <t>Зафиксировать порог и срок вынесения вопроса о нехватке бюджета на ОСУ</t>
+        </is>
+      </c>
+      <c r="R38" s="12" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="S38" s="12" t="inlineStr">
+        <is>
+          <t>Объект исполняется, но порог и срок вынесения не формализованы, поэтому вопрос попадает на утверждающий орган тогда, когда деньги уже потрачены. Формализация критерия — одна строка регламента, а эффект — возможность принять решение, пока оно ещё что-то меняет.</t>
+        </is>
+      </c>
+      <c r="T38" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Budget Variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>КН</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D38" s="27" t="inlineStr">
-        <is>
-          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>Зерек</t>
-        </is>
-      </c>
-      <c r="F38" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G38" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H38" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I38" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K38" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L38" s="21" t="n">
-        <v>53</v>
-      </c>
-      <c r="M38" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N38" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O38" s="12" t="inlineStr">
-        <is>
-          <t>Включить интерфейс с Зерек в карту процессов и согласовать срок монтажа ИТ-инфраструктуры</t>
-        </is>
-      </c>
-      <c r="P38" s="12" t="inlineStr">
-        <is>
-          <t>1.7.1</t>
-        </is>
-      </c>
-      <c r="Q38" s="12" t="inlineStr">
-        <is>
-          <t>Стык существует, а договорённостей по нему нет: интерфейс не был отражён в дереве процессов до версии 3. Монтаж ИТ-инфраструктуры расположен на критическом пути ввода объекта в эксплуатацию, поэтому норматив срока нужен наравне с закупками. Входом служит та же техническая спецификация, что и для объекта Б.7, поэтому срок согласуется после того, как её состав зафиксирован (1.7.1).</t>
-        </is>
-      </c>
-      <c r="R38" s="12" t="inlineStr">
-        <is>
-          <t>SLA Compliance %; On-Time %; Cycle Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="26" t="inlineStr">
-        <is>
-          <t>Б.8</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D39" s="27" t="inlineStr">
-        <is>
-          <t>Юридическое сопровождение договоров с контрагентами</t>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>Продление и модернизация контракта</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="F39" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L39" s="21" t="n">
-        <v>53</v>
-      </c>
-      <c r="M39" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N39" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O39" s="12" t="inlineStr">
-        <is>
-          <t>Согласовать с Юр блоком срок рассмотрения договора и типовые условия по проектам</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="H39" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N39" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O39" s="28" t="inlineStr">
+        <is>
+          <t>Не оценивается — агрегирующий уровень</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>Агрегирующий уровень</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr">
         <is>
-          <t>Объект исполняется, острых узких мест нет, но согласование договоров расположено на критическом пути запуска проекта. Типовые условия снимают повторное обсуждение одних и тех же пунктов по каждому проекту.</t>
+          <t>Отдельных действий не требуется — очередь ведётся по подпроцессу 2.4</t>
         </is>
       </c>
       <c r="R39" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; Cycle Time; Rework Rate</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S39" s="12" t="inlineStr">
+        <is>
+          <t>Головной процесс продления контракта. Оценку получает инициация продления.</t>
+        </is>
+      </c>
+      <c r="T39" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Б.5.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Регистрация и запуск филиала</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="F40" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G40" s="19" t="n">
+          <t>Продление и модернизация контракта</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Инициация продления / модернизации контракта</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="H40" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I40" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L40" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M40" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K40" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L40" s="21" t="n">
-        <v>52</v>
-      </c>
-      <c r="M40" s="29" t="inlineStr">
+      <c r="N40" s="21" t="n">
+        <v>69</v>
+      </c>
+      <c r="O40" s="29" t="inlineStr">
         <is>
           <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
-      <c r="N40" s="12" t="inlineStr">
+      <c r="P40" s="12" t="inlineStr">
         <is>
           <t>SLA на стык с ЦО</t>
         </is>
       </c>
-      <c r="O40" s="12" t="inlineStr">
-        <is>
-          <t>Согласовать с Юр блоком срок регистрации филиала и чек-лист приёма его в работу</t>
-        </is>
-      </c>
-      <c r="P40" s="12" t="inlineStr">
-        <is>
-          <t>Б.5</t>
-        </is>
-      </c>
       <c r="Q40" s="12" t="inlineStr">
         <is>
-          <t>Регистрация целиком выполняется Юр блоком, ДУП здесь клиент: он передаёт данные и принимает зарегистрированный филиал. Предметом работы является не порядок шагов, а норматив срока и момент, с которого филиал считается принятым в управление, — зеркало объекта 2.0 на границе двух подразделений.</t>
+          <t>Установить срок инициации продления до окончания договора и точку передачи в ДРБ</t>
         </is>
       </c>
       <c r="R40" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %; Defect Rate</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S40" s="12" t="inlineStr">
+        <is>
+          <t>Объект напрямую связан с доходом: пропущенный срок инициации означает паузу или потерю контракта, который уже работает. Сегодня срок отслеживается вручную, а коммерческое предложение готовится совместно с ДРБ — поэтому предметом работы является точка передачи между двумя департаментами, а не внутренняя процедура.</t>
+        </is>
+      </c>
+      <c r="T40" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; SLA Compliance %; Budget Variance</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="26" t="inlineStr">
-        <is>
-          <t>Б.9</t>
+        <v>22</v>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -4423,233 +4906,263 @@
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D41" s="27" t="inlineStr">
-        <is>
-          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>Управление филиальной сетью</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F41" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G41" s="19" t="n">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="19" t="n">
+      <c r="J41" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L41" s="21" t="n">
-        <v>52</v>
-      </c>
-      <c r="M41" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N41" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O41" s="12" t="inlineStr">
-        <is>
-          <t>Согласовать с HR срок оформления штата и кадровых приказов по филиалу</t>
+      <c r="M41" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N41" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="O41" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr">
         <is>
-          <t>Оформление штата и кадровых приказов — процесс HR, владелец подтверждён. ДУП здесь клиент: формирует потребность и принимает результат, поэтому предметом договорённости является не порядок шагов, а срок (узкое место 8). Норматив согласуется в общем пакете SLA со смежными подразделениями — вместе с Юр блоком, Финблоком и Закупщиками, одним заходом на Операционный комитет.</t>
+          <t>Утвердить паспорт процесса филиальной сети: отношения вне проекта и стык с открытием филиала</t>
         </is>
       </c>
       <c r="R41" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %</t>
+          <t>1, 2</t>
+        </is>
+      </c>
+      <c r="S41" s="12" t="inlineStr">
+        <is>
+          <t>Владение закреплено за директором ДУП. Назначение куратора вынесено в одну матрицу (1.3), открытие филиала — в сквозной маршрут (Б.5). У самого процесса паспорта нет, поэтому регламент по филиальной сети исполняется на усмотрение исполнителя.</t>
+        </is>
+      </c>
+      <c r="T41" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса и карта SIPOC; Cycle Time; On-Time %</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Управление филиальной сетью</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Общие отношения с филиалом (вне привязки к проекту)</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I42" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N42" s="21" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>1.9.3</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>Решение об оплате и проведение платежа</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F42" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G42" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I42" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K42" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="21" t="n">
-        <v>46</v>
-      </c>
-      <c r="M42" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N42" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O42" s="12" t="inlineStr">
-        <is>
-          <t>Согласовать с Финблоком норматив срока от передачи реестра до проведения платежа</t>
+      <c r="O42" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>1.9.2</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr">
         <is>
-          <t>Шаг выполняет Финблок, ДУП получает информацию о проведении платежа. Предметом договорённости является норматив срока: без него приоритизация реестра в волне 1 не доводится до результата.</t>
+          <t>Утвердить порядок обращений филиала вне проектной рамки: кто принимает и в какой срок</t>
         </is>
       </c>
       <c r="R42" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S42" s="12" t="inlineStr">
+        <is>
+          <t>Владелец закреплён за замом по операционной деятельности — обращения филиалов касаются работающих объектов, а не строящихся. Собственной ценности объект почти не создаёт, но закрывается одной страницей регламента, поэтому идёт попутно с остальными объектами блока 3.</t>
+        </is>
+      </c>
+      <c r="T42" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; CSAT internal</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>Б.5</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>Планирование и решение по прогнозу</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>Открытие нового филиала</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F43" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G43" s="19" t="n">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="24" t="n">
+      <c r="J43" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I43" s="24" t="n">
+      <c r="L43" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M43" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" s="21" t="n">
-        <v>46</v>
-      </c>
-      <c r="M43" s="29" t="inlineStr">
+      <c r="N43" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="O43" s="29" t="inlineStr">
         <is>
           <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
-      <c r="N43" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>Согласовать с Финблоком срок возврата утверждённого прогноза в ДУП</t>
-        </is>
-      </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>Проектирование TO-BE</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr">
         <is>
-          <t>Планирование и решение принимает Финблок. ДУП управляет здесь одним параметром — сроком получения утверждённого прогноза, без которого планирование работ на объектах ведётся вслепую.</t>
+          <t>Утвердить на Операционном комитете сквозной маршрут Юр → HR → Финблок → ДУП и сроки по этапам</t>
         </is>
       </c>
       <c r="R43" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; Wait Time %</t>
+          <t>Б.5.1</t>
+        </is>
+      </c>
+      <c r="S43" s="12" t="inlineStr">
+        <is>
+          <t>Единственная строка открытия филиала. Участок ДУП — этап Б.5.1, он описывается раньше. Владельцем по Таблице 4 Методики закреплён директор ДУП как курирующий руководитель кросс-функционального процесса: Юр блок отвечает только за регистрацию, HR — только за штат, за работающий филиал целиком не отвечает никто другой. Назначение владельца чужого сквозного процесса ДУП не утверждает в одностороннем порядке, поэтому объект идёт в волне 2: предметом работы является решение Операционного комитета, а не внутренний документ.</t>
+        </is>
+      </c>
+      <c r="T43" s="12" t="inlineStr">
+        <is>
+          <t>Cycle Time; On-Time %; Паспорт процесса и карта SIPOC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Б.5.2</t>
+          <t>Б.5.1</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -4659,543 +5172,613 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Подготовка пакета документов и доверенностей</t>
+          <t>Открытие нового филиала</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="n">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>Участие ДУП: потребность, данные по региону, приём площадки</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K44" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L44" s="21" t="n">
-        <v>36</v>
-      </c>
-      <c r="M44" s="29" t="inlineStr">
-        <is>
-          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
-        </is>
-      </c>
-      <c r="N44" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O44" s="12" t="inlineStr">
-        <is>
-          <t>Согласовать с Юр блоком срок подготовки пакета документов и доверенностей</t>
+      <c r="L44" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N44" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="O44" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>Б.5.1</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr">
         <is>
-          <t>Шаг исполняется Юр блоком и проблем не вызывает. Включается в общий регламент открытия филиала только для того, чтобы у сквозного маршрута не осталось участка без норматива срока.</t>
+          <t>Утвердить критерий инициации открытия филиала и форму обоснования потребности</t>
         </is>
       </c>
       <c r="R44" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S44" s="12" t="inlineStr">
+        <is>
+          <t>Вход в процесс: решение об открытии сегодня рождается по факту появления проекта в регионе без филиала, то есть поздно и авралом. Этап целиком в границах операционного контура ДУП, поэтому критерий и форма обоснования утверждаются внутренним документом, не дожидаясь сквозного маршрута.</t>
+        </is>
+      </c>
+      <c r="T44" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Cycle Time</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>Б.5.2</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Организация поверки оборудования</t>
+          <t>Открытие нового филиала</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G45" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" s="24" t="n">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Подготовка пакета документов и доверенностей</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="H45" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I45" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I45" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J45" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K45" s="24" t="n">
+      <c r="J45" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L45" s="21" t="n">
-        <v>61</v>
-      </c>
-      <c r="M45" s="30" t="inlineStr">
-        <is>
-          <t>Волна 3. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="N45" s="12" t="inlineStr">
-        <is>
-          <t>Пересмотр экономики</t>
-        </is>
-      </c>
-      <c r="O45" s="12" t="inlineStr">
-        <is>
-          <t>Рассчитать экономику собственной аккредитации против аутсорса поверки</t>
+      <c r="K45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="O45" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr">
         <is>
-          <t>Самый крупный денежный объект реестра: около 6 000 комплексов на поверке, методика устарела (узкое место 10), стоимость услуги растёт. Оптимизируется не порядок шагов, а модель оказания услуги, поэтому нужен расчёт и бюджетное решение. Берётся после того, как появится достоверная стоимость процесса по методу ABC — иначе сравнивать не с чем.</t>
+          <t>Согласовать с Юр блоком срок подготовки пакета документов и доверенностей</t>
         </is>
       </c>
       <c r="R45" s="12" t="inlineStr">
         <is>
-          <t>Стоимость объекта; CPT; ROI автоматизации</t>
+          <t>Б.5.1</t>
+        </is>
+      </c>
+      <c r="S45" s="12" t="inlineStr">
+        <is>
+          <t>Шаг исполняется Юр блоком и проблем не вызывает. Включается в общий регламент открытия филиала только для того, чтобы у сквозного маршрута не осталось участка без норматива срока.</t>
+        </is>
+      </c>
+      <c r="T45" s="12" t="inlineStr">
+        <is>
+          <t>SLA Compliance %; On-Time %</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>Б.5.3</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Разработка проектной документации (устав, план, приказ)</t>
+          <t>Открытие нового филиала</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G46" s="19" t="n">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Регистрация и запуск филиала</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="H46" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H46" s="24" t="n">
+      <c r="J46" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="24" t="n">
+      <c r="K46" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J46" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L46" s="21" t="n">
+      <c r="L46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N46" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="M46" s="30" t="inlineStr">
-        <is>
-          <t>Волна 3. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="N46" s="12" t="inlineStr">
-        <is>
-          <t>Шаблонизация</t>
-        </is>
-      </c>
-      <c r="O46" s="12" t="inlineStr">
-        <is>
-          <t>Утвердить типовой комплект: устав, план проекта, приказ</t>
+      <c r="O46" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
         </is>
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr">
         <is>
-          <t>Объект исполняется, узких мест по нему не зафиксировано, поэтому в первых волнах он вытеснил бы более острые задачи. Берётся ради масштабируемости: типовой комплект сокращает подготовку документации и делает проекты сравнимыми между собой — без этого портфельная отчётность собирается вручную.</t>
+          <t>Согласовать с Юр блоком срок регистрации филиала и чек-лист приёма его в работу</t>
         </is>
       </c>
       <c r="R46" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; Трудоёмкость объекта</t>
+          <t>Б.5</t>
+        </is>
+      </c>
+      <c r="S46" s="12" t="inlineStr">
+        <is>
+          <t>Регистрация целиком выполняется Юр блоком, ДУП здесь клиент: он передаёт данные и принимает зарегистрированный филиал. Предметом работы является не порядок шагов, а норматив срока и момент, с которого филиал считается принятым в управление, — зеркало объекта 2.0 на границе двух подразделений.</t>
+        </is>
+      </c>
+      <c r="T46" s="12" t="inlineStr">
+        <is>
+          <t>SLA Compliance %; On-Time %; Defect Rate</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>Разработка и поддержка методологии, шаблонов, реестров</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>Методология и контроль качества (ПМО)</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="H47" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G47" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H47" s="24" t="n">
+      <c r="I47" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I47" s="24" t="n">
+      <c r="K47" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J47" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K47" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L47" s="21" t="n">
-        <v>52</v>
-      </c>
-      <c r="M47" s="30" t="inlineStr">
-        <is>
-          <t>Волна 3. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="N47" s="12" t="inlineStr">
-        <is>
-          <t>Устранение дублей и упрощение</t>
-        </is>
-      </c>
-      <c r="O47" s="12" t="inlineStr">
-        <is>
-          <t>Актуализировать методологию: роли вместо фамилий, глоссарий, архивация устаревшего</t>
+      <c r="L47" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M47" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N47" s="21" t="n">
+        <v>64</v>
+      </c>
+      <c r="O47" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Паспорт процесса и границы</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr">
         <is>
-          <t>В реестре методологии 434 документа, около 28% архива устарело, последняя правка — 2021 год. Задача не в переписывании, а в актуализации, и делать её имеет смысл тогда, когда новые регламенты волн 1 и 2 уже написаны — иначе методологию придётся актуализировать дважды.</t>
+          <t>Утвердить паспорт процесса методологии и положение о контроле качества проектных данных</t>
         </is>
       </c>
       <c r="R47" s="12" t="inlineStr">
         <is>
-          <t>Паспорт процесса и карта SIPOC; CSAT internal</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S47" s="12" t="inlineStr">
+        <is>
+          <t>Роль главного менеджера проектов — несущая конструкция всей трансформации: именно она ведёт паспорта остальных процессов, аудит и портфельную отчётность. Владение и право остановить проект по результатам аудита закреплены, но собственного паспорта у процесса нет, а методолог без описанных границ своей работы не может требовать описания чужих. Объект никого не ждёт и идёт параллельно паспортам блоков 1 и 2.</t>
+        </is>
+      </c>
+      <c r="T47" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса и карта SIPOC; Defect Rate; Назначение бизнес-владельца</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>1.1.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Регистрация проекта в портфеле / системе</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
+          <t>Методология и контроль качества (ПМО)</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Разработка и поддержка методологии, шаблонов, реестров</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G48" s="19" t="n">
+      <c r="I48" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="24" t="n">
+      <c r="J48" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I48" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="24" t="n">
+      <c r="K48" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="K48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L48" s="21" t="n">
-        <v>48</v>
-      </c>
-      <c r="M48" s="30" t="inlineStr">
+      <c r="L48" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N48" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="O48" s="27" t="inlineStr">
         <is>
           <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
-      <c r="N48" s="12" t="inlineStr">
-        <is>
-          <t>Автоматизация</t>
-        </is>
-      </c>
-      <c r="O48" s="12" t="inlineStr">
-        <is>
-          <t>Определить обязательные поля карточки проекта в SimBASE и запретить регистрацию без них</t>
-        </is>
-      </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>Устранение дублей и упрощение</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr">
         <is>
-          <t>Ручная регистрация сама по себе потерь почти не создаёт, поэтому балл низкий. Но именно она задаёт единый идентификатор проекта, без которого метрики по портфелю нельзя собрать автоматически. Объект берётся не ради экономии, а как обязательный элемент единой карточки проекта.</t>
+          <t>Актуализировать методологию: роли вместо фамилий, глоссарий, архивация устаревшего</t>
         </is>
       </c>
       <c r="R48" s="12" t="inlineStr">
         <is>
-          <t>Уровень автоматизации; Cycle Time</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S48" s="12" t="inlineStr">
+        <is>
+          <t>В реестре методологии 434 документа, около 28% архива устарело, последняя правка — 2021 год. Задача не в переписывании, а в актуализации, и делать её имеет смысл тогда, когда новые регламенты волн 1 и 2 уже написаны — иначе методологию придётся актуализировать дважды.</t>
+        </is>
+      </c>
+      <c r="T48" s="12" t="inlineStr">
+        <is>
+          <t>Паспорт процесса и карта SIPOC; CSAT internal</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Подпроцесс</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Оформление приказа на реализацию</t>
-        </is>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
+          <t>Методология и контроль качества (ПМО)</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>Контроль качества и полноты проектных данных</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
+      <c r="H49" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G49" s="24" t="n">
+      <c r="I49" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" s="18" t="n">
+      <c r="L49" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M49" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="L49" s="21" t="n">
-        <v>42</v>
-      </c>
-      <c r="M49" s="30" t="inlineStr">
-        <is>
-          <t>Волна 3. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="N49" s="12" t="inlineStr">
-        <is>
-          <t>Шаблонизация</t>
-        </is>
-      </c>
-      <c r="O49" s="12" t="inlineStr">
-        <is>
-          <t>Свести устав и план в единую форму приказа на реализацию</t>
+      <c r="N49" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="O49" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>Базовая линия и замер</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr">
         <is>
-          <t>Последний шаг комплекта 1.4, а не отдельный процесс. Исполняется, узких мест нет. Эффект — экономия времени на оформлении, поэтому шаг идёт вместе с типовым комплектом, а не раньше объектов с деньгами и сроками.</t>
+          <t>Провести пилотный аудит одного филиала и развернуть его на весь портфель</t>
         </is>
       </c>
       <c r="R49" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S49" s="12" t="inlineStr">
+        <is>
+          <t>Аудит остановлен после 2020 года, поэтому ни одно утверждение о состоянии процессов нельзя подтвердить цифрой. Пилот одного филиала не ждёт согласований: чек-листы готовы, филиал выбирает директор. Регулярный аудит на портфель имеет смысл, когда его результат влечёт последствия: право остановить проект зафиксировано за владельцем методологии вместе с паспортом процесса 4.</t>
+        </is>
+      </c>
+      <c r="T49" s="12" t="inlineStr">
+        <is>
+          <t>Defect Rate; First Pass Yield; Паспорт процесса и карта SIPOC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="26" t="inlineStr">
-        <is>
-          <t>Б.2</t>
+        <v>9</v>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="D50" s="27" t="inlineStr">
-        <is>
-          <t>Финансовое закрытие проекта</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="n">
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>Методология и контроль качества (ПМО)</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Отчётность по проектам</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I50" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H50" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I50" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K50" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L50" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="M50" s="30" t="inlineStr">
-        <is>
-          <t>Волна 3. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="N50" s="12" t="inlineStr">
-        <is>
-          <t>SLA на стык с ЦО</t>
-        </is>
-      </c>
-      <c r="O50" s="12" t="inlineStr">
-        <is>
-          <t>Согласовать с Финблоком состав и срок пакета документов на закрытие проекта</t>
+      <c r="L50" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M50" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N50" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="O50" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr">
         <is>
-          <t>Закрытие проекта выполняет Финблок, у ДУП здесь роль поставщика данных. Объект не создаёт ни срочности, ни денежного эффекта, поэтому берётся в конце: к этому моменту уже будет работать точка передачи 2.0, задающая, какие документы вообще накапливаются по проекту.</t>
+          <t>Утвердить один регламент отчётности: проект, операция, портфель</t>
         </is>
       </c>
       <c r="R50" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %; On-Time %</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S50" s="12" t="inlineStr">
+        <is>
+          <t>Три отчёта собирались отдельно и описывали одни и те же данные. Один регламент внутри ДУП задаёт частоту, адресата и запрет повторного сбора. Самое дешёвое восстановление управляемости портфеля: внешних согласований нет.</t>
+        </is>
+      </c>
+      <c r="T50" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Time-to-Complete; Трудоёмкость объекта</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Б.2.1</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -5205,474 +5788,960 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Служебная записка о необходимости закрытия</t>
+          <t>Методология и контроль качества (ПМО)</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t>Участник</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="n">
+          <t>Отчётность по проектам</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>Статус-встречи по проекту</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I51" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H51" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K51" s="20" t="n">
+      <c r="L51" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L51" s="21" t="n">
-        <v>46</v>
-      </c>
-      <c r="M51" s="30" t="inlineStr">
-        <is>
-          <t>Волна 3. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>Шаблонизация</t>
-        </is>
-      </c>
-      <c r="O51" s="12" t="inlineStr">
-        <is>
-          <t>Ввести типовую форму служебной записки о закрытии проекта</t>
+      <c r="M51" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N51" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="O51" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>Б.2</t>
+          <t>Регламент и чек-лист</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr">
         <is>
-          <t>Шаг выполняет ДУП, и он дёшев в исправлении, но повторяется несколько раз в год и ни на что не влияет до наступления самого закрытия. Типовая форма снимает переписку об уточнениях.</t>
+          <t>Ввести статус-встречи: частота, повестка, протокол, адресат решений</t>
         </is>
       </c>
       <c r="R51" s="12" t="inlineStr">
         <is>
-          <t>Cycle Time; First Pass Yield</t>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="S51" s="12" t="inlineStr">
+        <is>
+          <t>Проектный уровень контура. Регламента нет, обязанности менеджера центрального аппарата исполняются примерно на одну шестую (узкое место 8). Идёт сразу за общим регламентом отчётности.</t>
+        </is>
+      </c>
+      <c r="T51" s="12" t="inlineStr">
+        <is>
+          <t>On-Time %; Time-to-Complete; CSAT internal</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Подпроцесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Сопровождение канала связи</t>
+          <t>Методология и контроль качества (ПМО)</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
+          <t>Отчётность по проектам</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Операционный статус руководству и госпартнёру</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="G52" s="24" t="n">
+      <c r="I52" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H52" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="24" t="n">
+      <c r="L52" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K52" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L52" s="21" t="n">
-        <v>39</v>
-      </c>
-      <c r="M52" s="30" t="inlineStr">
-        <is>
-          <t>Волна 3. Масштаб, экономика и автоматизация</t>
-        </is>
-      </c>
-      <c r="N52" s="12" t="inlineStr">
-        <is>
-          <t>Автоматизация</t>
-        </is>
-      </c>
-      <c r="O52" s="12" t="inlineStr">
-        <is>
-          <t>Закрепить мониторинг канала связи в Zabbix и правило реакции на отказ</t>
+      <c r="M52" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N52" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="O52" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>1.1.3</t>
+          <t>Устранение дублей и упрощение</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr">
         <is>
-          <t>Объект исполняется, узких мест по нему не зафиксировано. Берётся в последней волне как часть ИТ-контура: дежурный мониторинг дешевле ручных проверок, но самостоятельной управленческой проблемы здесь нет.</t>
+          <t>Собирать операционный статус из протокола статус-встреч, без второго опроса</t>
         </is>
       </c>
       <c r="R52" s="12" t="inlineStr">
         <is>
-          <t>Уровень автоматизации; Средний LOA; On-Time %</t>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="S52" s="12" t="inlineStr">
+        <is>
+          <t>Операционный отчёт госпартнёру и руководству повторял данные проектного статуса. После того как статус-встречи задают проектный уровень, этот этап только выбирает из них нужный срез.</t>
+        </is>
+      </c>
+      <c r="T52" s="12" t="inlineStr">
+        <is>
+          <t>Трудоёмкость объекта; Rework Rate; CSAT external</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>4.3.3</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>Методология и контроль качества (ПМО)</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>Отчётность по проектам</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Портфельная отчётность руководству и заказчикам</t>
+        </is>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L53" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N53" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>1.5.3</t>
-        </is>
-      </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>Утверждение бюджета, кредитование при необходимости</t>
-        </is>
-      </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="F53" s="25" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="G53" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K53" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="21" t="n">
-        <v>33</v>
-      </c>
-      <c r="M53" s="31" t="inlineStr">
-        <is>
-          <t>Вне очереди — наблюдение</t>
-        </is>
-      </c>
-      <c r="N53" s="12" t="inlineStr">
-        <is>
-          <t>Наблюдение — вмешательство не планируется</t>
-        </is>
-      </c>
-      <c r="O53" s="12" t="inlineStr">
-        <is>
-          <t>Отдельных действий не требуется — срок входит в SLA по объекту 1.5</t>
+      <c r="O53" s="22" t="inlineStr">
+        <is>
+          <t>Волна 1. Запуск: паспорта и быстрые победы</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>Устранение дублей и упрощение</t>
         </is>
       </c>
       <c r="Q53" s="12" t="inlineStr">
         <is>
-          <t>Решение принимает Финблок, ДУП только получает утверждённый бюджет. Оптимизировать нечего: единственный управляемый параметр — срок, и он фиксируется в SLA по родительскому объекту.</t>
+          <t>Собирать портфельный отчёт из проектного и операционного статуса</t>
         </is>
       </c>
       <c r="R53" s="12" t="inlineStr">
         <is>
-          <t>On-Time %</t>
+          <t>4.3.2</t>
+        </is>
+      </c>
+      <c r="S53" s="12" t="inlineStr">
+        <is>
+          <t>Портфель — третий адресат того же контура. Отдельного сбора данных не требует: он складывается из двух предыдущих этапов.</t>
+        </is>
+      </c>
+      <c r="T53" s="12" t="inlineStr">
+        <is>
+          <t>Трудоёмкость объекта; Rework Rate</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>Б.2.2</t>
+          <t>Б.2</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>Сбор актов сверок, уведомления о расторжении договоров</t>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>Финансовое закрытие проекта</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
+      <c r="H54" s="30" t="inlineStr">
         <is>
           <t>Участник</t>
         </is>
       </c>
-      <c r="G54" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="M54" s="31" t="inlineStr">
-        <is>
-          <t>Вне очереди — наблюдение</t>
-        </is>
-      </c>
-      <c r="N54" s="12" t="inlineStr">
-        <is>
-          <t>Наблюдение — вмешательство не планируется</t>
-        </is>
-      </c>
-      <c r="O54" s="12" t="inlineStr">
-        <is>
-          <t>Отдельных действий не требуется — данные предоставляются по запросу</t>
+      <c r="I54" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K54" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L54" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="O54" s="27" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>Б.2.1</t>
+          <t>SLA на стык с ЦО</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr">
         <is>
-          <t>Сбор актов сверок и уведомлений о расторжении ведут Финблок и Юр блок. ДУП предоставляет данные по запросу и ни срока, ни качества шага не определяет. Объект остаётся в реестре для полноты картины.</t>
+          <t>Согласовать с Финблоком состав и срок пакета документов на закрытие проекта</t>
         </is>
       </c>
       <c r="R54" s="12" t="inlineStr">
         <is>
-          <t>SLA Compliance %</t>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="S54" s="12" t="inlineStr">
+        <is>
+          <t>Закрытие проекта выполняет Финблок, у ДУП здесь роль поставщика данных. Объект не создаёт ни срочности, ни денежного эффекта, поэтому берётся в конце: к этому моменту уже будет работать точка передачи 2.0, задающая, какие документы вообще накапливаются по проекту.</t>
+        </is>
+      </c>
+      <c r="T54" s="12" t="inlineStr">
+        <is>
+          <t>SLA Compliance %; On-Time %</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Б.2.1</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Финансовое закрытие проекта</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>Служебная записка о необходимости закрытия</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H55" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N55" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="O55" s="27" t="inlineStr">
+        <is>
+          <t>Волна 3. Масштаб, экономика и автоматизация</t>
+        </is>
+      </c>
+      <c r="P55" s="12" t="inlineStr">
+        <is>
+          <t>Шаблонизация</t>
+        </is>
+      </c>
+      <c r="Q55" s="12" t="inlineStr">
+        <is>
+          <t>Ввести типовую форму служебной записки о закрытии проекта</t>
+        </is>
+      </c>
+      <c r="R55" s="12" t="inlineStr">
+        <is>
+          <t>Б.2</t>
+        </is>
+      </c>
+      <c r="S55" s="12" t="inlineStr">
+        <is>
+          <t>Шаг выполняет ДУП, и он дёшев в исправлении, но повторяется несколько раз в год и ни на что не влияет до наступления самого закрытия. Типовая форма снимает переписку об уточнениях.</t>
+        </is>
+      </c>
+      <c r="T55" s="12" t="inlineStr">
+        <is>
+          <t>Cycle Time; First Pass Yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>Б.2.2</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Финансовое закрытие проекта</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Сбор актов сверок, уведомления о расторжении договоров</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="H56" s="30" t="inlineStr">
+        <is>
+          <t>Участник</t>
+        </is>
+      </c>
+      <c r="I56" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="O56" s="28" t="inlineStr">
+        <is>
+          <t>Вне очереди — наблюдение</t>
+        </is>
+      </c>
+      <c r="P56" s="12" t="inlineStr">
+        <is>
+          <t>Наблюдение — вмешательство не планируется</t>
+        </is>
+      </c>
+      <c r="Q56" s="12" t="inlineStr">
+        <is>
+          <t>Отдельных действий не требуется — данные предоставляются по запросу</t>
+        </is>
+      </c>
+      <c r="R56" s="12" t="inlineStr">
+        <is>
+          <t>Б.2.1</t>
+        </is>
+      </c>
+      <c r="S56" s="12" t="inlineStr">
+        <is>
+          <t>Сбор актов сверок и уведомлений о расторжении ведут Финблок и Юр блок. ДУП предоставляет данные по запросу и ни срока, ни качества шага не определяет. Объект остаётся в реестре для полноты картины.</t>
+        </is>
+      </c>
+      <c r="T56" s="12" t="inlineStr">
+        <is>
+          <t>SLA Compliance %</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>Б.2.3</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>Финансовое закрытие проекта</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>Формирование бюджета на логистику / демонтаж, закрытие</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t>Финблок</t>
         </is>
       </c>
-      <c r="F55" s="25" t="inlineStr">
+      <c r="H57" s="25" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="G55" s="28" t="n">
+      <c r="I57" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="28" t="n">
+      <c r="J57" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="I55" s="24" t="n">
+      <c r="K57" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J55" s="28" t="n">
+      <c r="L57" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="K55" s="28" t="n">
+      <c r="M57" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="L55" s="21" t="n">
+      <c r="N57" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="M55" s="31" t="inlineStr">
+      <c r="O57" s="28" t="inlineStr">
         <is>
           <t>Вне очереди — наблюдение</t>
         </is>
       </c>
-      <c r="N55" s="12" t="inlineStr">
+      <c r="P57" s="12" t="inlineStr">
         <is>
           <t>Наблюдение — вмешательство не планируется</t>
         </is>
       </c>
-      <c r="O55" s="12" t="inlineStr">
+      <c r="Q57" s="12" t="inlineStr">
         <is>
           <t>Отдельных действий не требуется — подтверждение закрытия приходит из Финблока</t>
         </is>
       </c>
-      <c r="P55" s="12" t="inlineStr">
+      <c r="R57" s="12" t="inlineStr">
         <is>
           <t>Б.2.2</t>
         </is>
       </c>
-      <c r="Q55" s="12" t="inlineStr">
+      <c r="S57" s="12" t="inlineStr">
         <is>
           <t>Завершающий шаг целиком в периметре Финблока. Единственный интерес ДУП — получить подтверждение закрытия, чтобы снять проект с сопровождения; это обеспечивается точкой передачи, а не отдельной оптимизацией.</t>
         </is>
       </c>
-      <c r="R55" s="12" t="inlineStr">
+      <c r="T57" s="12" t="inlineStr">
         <is>
           <t>SLA Compliance %</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B56" s="26" t="inlineStr">
-        <is>
-          <t>ДУП.0</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Б.7</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>Процесс</t>
         </is>
       </c>
-      <c r="D56" s="27" t="inlineStr">
-        <is>
-          <t>Управление проектами (ГЧП / ГЗ)</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="F56" s="13" t="inlineStr">
-        <is>
-          <t>Владелец</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J56" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K56" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L56" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M56" s="31" t="inlineStr">
-        <is>
-          <t>Не оценивается — агрегирующий уровень</t>
-        </is>
-      </c>
-      <c r="N56" s="12" t="inlineStr">
-        <is>
-          <t>Агрегирующий уровень</t>
-        </is>
-      </c>
-      <c r="O56" s="12" t="inlineStr">
-        <is>
-          <t>Отдельных действий не требуется</t>
-        </is>
-      </c>
-      <c r="P56" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q56" s="12" t="inlineStr">
-        <is>
-          <t>Корень дерева процессов: его результат складывается из блоков 1–4. Оптимизируется не сам по себе, а через входящие в него объекты, поэтому собственного места в очереди не занимает.</t>
-        </is>
-      </c>
-      <c r="R56" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>Производство, монтаж и калибровка оборудования</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>СТ</t>
+        </is>
+      </c>
+      <c r="H58" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I58" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L58" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M58" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="O58" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
+        </is>
+      </c>
+      <c r="P58" s="12" t="inlineStr">
+        <is>
+          <t>SLA на стык с ЦО</t>
+        </is>
+      </c>
+      <c r="Q58" s="12" t="inlineStr">
+        <is>
+          <t>Зафиксировать со СТ срок выдачи тех. карт — до подачи заявки на закупку</t>
+        </is>
+      </c>
+      <c r="R58" s="12" t="inlineStr">
+        <is>
+          <t>1.7.1</t>
+        </is>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>Тех. карты нужны до закупки, но этот порядок нигде не закреплён, и спецификация иногда собирается параллельно с заявкой. Объект связан сразу с двумя другими: он питает инициацию закупки (1.7.1) и принимает обратную связь по дефектам (2.7).</t>
+        </is>
+      </c>
+      <c r="T58" s="12" t="inlineStr">
+        <is>
+          <t>SLA Compliance %; On-Time %; Defect Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Б.8</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>Юридическое сопровождение договоров с контрагентами</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="H59" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I59" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K59" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N59" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="O59" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
+        </is>
+      </c>
+      <c r="P59" s="12" t="inlineStr">
+        <is>
+          <t>SLA на стык с ЦО</t>
+        </is>
+      </c>
+      <c r="Q59" s="12" t="inlineStr">
+        <is>
+          <t>Согласовать с Юр блоком срок рассмотрения договора и типовые условия по проектам</t>
+        </is>
+      </c>
+      <c r="R59" s="12" t="inlineStr">
+        <is>
+          <t>1.1.2</t>
+        </is>
+      </c>
+      <c r="S59" s="12" t="inlineStr">
+        <is>
+          <t>Объект исполняется, острых узких мест нет, но согласование договоров расположено на критическом пути запуска проекта. Типовые условия снимают повторное обсуждение одних и тех же пунктов по каждому проекту.</t>
+        </is>
+      </c>
+      <c r="T59" s="12" t="inlineStr">
+        <is>
+          <t>SLA Compliance %; Cycle Time; Rework Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Б.9</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H60" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I60" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K60" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M60" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N60" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="O60" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
+        </is>
+      </c>
+      <c r="P60" s="12" t="inlineStr">
+        <is>
+          <t>SLA на стык с ЦО</t>
+        </is>
+      </c>
+      <c r="Q60" s="12" t="inlineStr">
+        <is>
+          <t>Согласовать с HR срок оформления штата и кадровых приказов по филиалу</t>
+        </is>
+      </c>
+      <c r="R60" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S60" s="12" t="inlineStr">
+        <is>
+          <t>Оформление штата и кадровых приказов — процесс HR, владелец подтверждён. ДУП здесь клиент: формирует потребность и принимает результат, поэтому предметом договорённости является не порядок шагов, а срок (узкое место 8). Норматив согласуется в общем пакете SLA со смежными подразделениями — вместе с Юр блоком, Финблоком и Закупщиками, одним заходом на Операционный комитет.</t>
+        </is>
+      </c>
+      <c r="T60" s="12" t="inlineStr">
+        <is>
+          <t>SLA Compliance %; On-Time %</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>Б.10</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>Зерек</t>
+        </is>
+      </c>
+      <c r="H61" s="25" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="I61" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J61" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K61" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L61" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M61" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N61" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="O61" s="29" t="inlineStr">
+        <is>
+          <t>Волна 2. Стыки с ЦО и закрытие пробелов</t>
+        </is>
+      </c>
+      <c r="P61" s="12" t="inlineStr">
+        <is>
+          <t>SLA на стык с ЦО</t>
+        </is>
+      </c>
+      <c r="Q61" s="12" t="inlineStr">
+        <is>
+          <t>Включить интерфейс с Зерек в карту процессов и согласовать срок монтажа ИТ-инфраструктуры</t>
+        </is>
+      </c>
+      <c r="R61" s="12" t="inlineStr">
+        <is>
+          <t>1.7.1</t>
+        </is>
+      </c>
+      <c r="S61" s="12" t="inlineStr">
+        <is>
+          <t>Стык существует, а договорённостей по нему нет: интерфейс не был отражён в дереве процессов до версии 3. Монтаж ИТ-инфраструктуры расположен на критическом пути ввода объекта в эксплуатацию, поэтому норматив срока нужен наравне с закупками. Входом служит та же техническая спецификация, что и для объекта Б.7, поэтому срок согласуется после того, как её состав зафиксирован (1.7.1).</t>
+        </is>
+      </c>
+      <c r="T61" s="12" t="inlineStr">
+        <is>
+          <t>SLA Compliance %; On-Time %; Cycle Time</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R56"/>
+  <autoFilter ref="A1:T61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="2"/>
 </worksheet>
@@ -5698,7 +6767,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>Порядок работ по волнам</t>
         </is>
@@ -6101,7 +7170,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>Первые 11 шагов: программа старта реинжиниринга</t>
         </is>
@@ -6152,7 +7221,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="n">
+      <c r="A5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -6187,7 +7256,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="n">
+      <c r="A6" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -6222,7 +7291,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="n">
+      <c r="A7" s="32" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -6257,7 +7326,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="n">
+      <c r="A8" s="32" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -6292,7 +7361,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="n">
+      <c r="A9" s="32" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -6327,7 +7396,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="n">
+      <c r="A10" s="32" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -6362,7 +7431,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n">
+      <c r="A11" s="32" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -6397,7 +7466,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="n">
+      <c r="A12" s="32" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -6432,7 +7501,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="n">
+      <c r="A13" s="32" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -6467,7 +7536,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="n">
+      <c r="A14" s="32" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -6502,7 +7571,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="n">
+      <c r="A15" s="32" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -6564,7 +7633,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>Матрица «ценность — лёгкость реализации»</t>
         </is>
@@ -6624,7 +7693,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n"/>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>Заполнители — 12
 2.6, Б.5.1, 4.2, 4.3.2, 3, 1.3, 4.3.3, 3.3, 1.4, 1.1.3, 1.4.1, Б.2.1</t>
@@ -6632,7 +7701,7 @@
       </c>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="12" t="n"/>
-      <c r="F7" s="31" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>Отложить — 15
 Б.5, 1.5.2, Б.10, Б.8, Б.5.3, Б.9, 1.9.3, 2.3.2, Б.5.2, 4.1, Б.2, 2.2, 1.5.3, Б.2.2, Б.2.3</t>
@@ -6711,7 +7780,7 @@
       <c r="G12" s="12" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
@@ -6732,7 +7801,7 @@
       <c r="G13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
@@ -7469,7 +8538,7 @@
           <t>Крупные проекты</t>
         </is>
       </c>
-      <c r="F39" s="30" t="inlineStr">
+      <c r="F39" s="27" t="inlineStr">
         <is>
           <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
@@ -7650,7 +8719,7 @@
       <c r="D45" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="31" t="inlineStr">
+      <c r="E45" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
@@ -7681,7 +8750,7 @@
       <c r="D46" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E46" s="34" t="inlineStr">
+      <c r="E46" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
@@ -7712,7 +8781,7 @@
       <c r="D47" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E47" s="34" t="inlineStr">
+      <c r="E47" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
@@ -7743,7 +8812,7 @@
       <c r="D48" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="31" t="inlineStr">
+      <c r="E48" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
@@ -7774,7 +8843,7 @@
       <c r="D49" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="31" t="inlineStr">
+      <c r="E49" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
@@ -7805,7 +8874,7 @@
       <c r="D50" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E50" s="34" t="inlineStr">
+      <c r="E50" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
@@ -7836,7 +8905,7 @@
       <c r="D51" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E51" s="31" t="inlineStr">
+      <c r="E51" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
@@ -7867,7 +8936,7 @@
       <c r="D52" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E52" s="34" t="inlineStr">
+      <c r="E52" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
@@ -7898,7 +8967,7 @@
       <c r="D53" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E53" s="31" t="inlineStr">
+      <c r="E53" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
@@ -7929,7 +8998,7 @@
       <c r="D54" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E54" s="31" t="inlineStr">
+      <c r="E54" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
@@ -7960,12 +9029,12 @@
       <c r="D55" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E55" s="31" t="inlineStr">
+      <c r="E55" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F55" s="30" t="inlineStr">
+      <c r="F55" s="27" t="inlineStr">
         <is>
           <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
@@ -7991,7 +9060,7 @@
       <c r="D56" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="31" t="inlineStr">
+      <c r="E56" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
@@ -8022,7 +9091,7 @@
       <c r="D57" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="31" t="inlineStr">
+      <c r="E57" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
@@ -8053,7 +9122,7 @@
       <c r="D58" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E58" s="34" t="inlineStr">
+      <c r="E58" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
@@ -8084,7 +9153,7 @@
       <c r="D59" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E59" s="34" t="inlineStr">
+      <c r="E59" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
@@ -8115,12 +9184,12 @@
       <c r="D60" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E60" s="34" t="inlineStr">
+      <c r="E60" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F60" s="30" t="inlineStr">
+      <c r="F60" s="27" t="inlineStr">
         <is>
           <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
@@ -8146,7 +9215,7 @@
       <c r="D61" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E61" s="34" t="inlineStr">
+      <c r="E61" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
@@ -8177,12 +9246,12 @@
       <c r="D62" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E62" s="34" t="inlineStr">
+      <c r="E62" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F62" s="30" t="inlineStr">
+      <c r="F62" s="27" t="inlineStr">
         <is>
           <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
@@ -8208,12 +9277,12 @@
       <c r="D63" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E63" s="34" t="inlineStr">
+      <c r="E63" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F63" s="30" t="inlineStr">
+      <c r="F63" s="27" t="inlineStr">
         <is>
           <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
@@ -8239,12 +9308,12 @@
       <c r="D64" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E64" s="31" t="inlineStr">
+      <c r="E64" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F64" s="30" t="inlineStr">
+      <c r="F64" s="27" t="inlineStr">
         <is>
           <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
@@ -8270,12 +9339,12 @@
       <c r="D65" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E65" s="31" t="inlineStr">
+      <c r="E65" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F65" s="30" t="inlineStr">
+      <c r="F65" s="27" t="inlineStr">
         <is>
           <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
@@ -8301,7 +9370,7 @@
       <c r="D66" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E66" s="31" t="inlineStr">
+      <c r="E66" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
@@ -8332,12 +9401,12 @@
       <c r="D67" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="31" t="inlineStr">
+      <c r="E67" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F67" s="31" t="inlineStr">
+      <c r="F67" s="28" t="inlineStr">
         <is>
           <t>Вне очереди — наблюдение</t>
         </is>
@@ -8363,12 +9432,12 @@
       <c r="D68" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E68" s="34" t="inlineStr">
+      <c r="E68" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F68" s="27" t="inlineStr">
         <is>
           <t>Волна 3. Масштаб, экономика и автоматизация</t>
         </is>
@@ -8394,7 +9463,7 @@
       <c r="D69" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E69" s="34" t="inlineStr">
+      <c r="E69" s="33" t="inlineStr">
         <is>
           <t>Заполнители</t>
         </is>
@@ -8425,12 +9494,12 @@
       <c r="D70" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E70" s="31" t="inlineStr">
+      <c r="E70" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F70" s="31" t="inlineStr">
+      <c r="F70" s="28" t="inlineStr">
         <is>
           <t>Вне очереди — наблюдение</t>
         </is>
@@ -8456,12 +9525,12 @@
       <c r="D71" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E71" s="31" t="inlineStr">
+      <c r="E71" s="28" t="inlineStr">
         <is>
           <t>Отложить</t>
         </is>
       </c>
-      <c r="F71" s="31" t="inlineStr">
+      <c r="F71" s="28" t="inlineStr">
         <is>
           <t>Вне очереди — наблюдение</t>
         </is>
